--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -53,19 +53,19 @@
     <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554025173187</t>
+    <t xml:space="preserve">1.25554037094116</t>
   </si>
   <si>
     <t xml:space="preserve">1.24861621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515804767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246049880981</t>
+    <t xml:space="preserve">1.27515816688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
     <t xml:space="preserve">1.19437873363495</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15975916385651</t>
+    <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
     <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25784802436829</t>
+    <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
     <t xml:space="preserve">1.25438630580902</t>
@@ -89,55 +89,55 @@
     <t xml:space="preserve">1.24746227264404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26361811161041</t>
+    <t xml:space="preserve">1.27285015583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746617794037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
     <t xml:space="preserve">1.20591866970062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053469181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207084178925</t>
+    <t xml:space="preserve">1.21168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2105348110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207072257996</t>
   </si>
   <si>
     <t xml:space="preserve">1.2082267999649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23130643367767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899854183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476839065552</t>
+    <t xml:space="preserve">1.23130655288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899842262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476850986481</t>
   </si>
   <si>
     <t xml:space="preserve">1.23707640171051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29015982151031</t>
+    <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
     <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28900575637817</t>
+    <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28439009189606</t>
+    <t xml:space="preserve">1.28438985347748</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169609069824</t>
@@ -146,58 +146,58 @@
     <t xml:space="preserve">1.28323602676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054569244385</t>
+    <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862355232239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093168258667</t>
+    <t xml:space="preserve">1.31093180179596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247149944305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208550930023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30746984481812</t>
+    <t xml:space="preserve">1.32247173786163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30746960639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516183376312</t>
+    <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
     <t xml:space="preserve">1.32016372680664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3236255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708764076233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323957443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824170589447</t>
+    <t xml:space="preserve">1.32362568378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323969364166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
   </si>
   <si>
     <t xml:space="preserve">1.35132133960724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34439742565155</t>
+    <t xml:space="preserve">1.34439754486084</t>
   </si>
   <si>
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016739368439</t>
+    <t xml:space="preserve">1.3501672744751</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478329658508</t>
@@ -209,70 +209,70 @@
     <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34324359893799</t>
+    <t xml:space="preserve">1.3432434797287</t>
   </si>
   <si>
     <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36516916751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017117977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786304950714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747717857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286127567291</t>
+    <t xml:space="preserve">1.36516928672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786316871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3674772977829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251494407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42702007293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332279682159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
+    <t xml:space="preserve">1.39251518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621186256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701983451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332315444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
   </si>
   <si>
     <t xml:space="preserve">1.44427239894867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44550454616547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043396949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536303520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110054969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863530158997</t>
+    <t xml:space="preserve">1.44550466537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275699138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863565921783</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342345237732</t>
@@ -281,136 +281,136 @@
     <t xml:space="preserve">1.51821112632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54162514209747</t>
+    <t xml:space="preserve">1.54162526130676</t>
   </si>
   <si>
     <t xml:space="preserve">1.50465571880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51574671268463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5403927564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433172225952</t>
+    <t xml:space="preserve">1.51574647426605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849426746368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817015171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433148384094</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707939624786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52437281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077631473541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5465544462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257462501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59584712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362416744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006911754608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883649349213</t>
+    <t xml:space="preserve">1.52437269687653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641305446625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6007764339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190792560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5946147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883673191071</t>
   </si>
   <si>
     <t xml:space="preserve">1.65992736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66115963459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661412715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400772571564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7252402305603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756277561188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429074764252</t>
+    <t xml:space="preserve">1.66115987300873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661353111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7215428352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400796413422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523987293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429062843323</t>
   </si>
   <si>
     <t xml:space="preserve">1.70059394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851261615753</t>
+    <t xml:space="preserve">1.70675551891327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784627437592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851249694824</t>
   </si>
   <si>
     <t xml:space="preserve">1.79301738739014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439104557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206790447235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7486537694931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7461895942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453255653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7622092962265</t>
+    <t xml:space="preserve">1.75604796409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439092636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206766605377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988639354706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837086677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7745326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220965385437</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699744701385</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">1.76344180107117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6574627161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855347156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443213939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186707019806</t>
+    <t xml:space="preserve">1.65746259689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855359077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249231815338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186695098877</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158404827118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
+    <t xml:space="preserve">1.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035202026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679601669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6426750421524</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376591682434</t>
@@ -458,58 +458,58 @@
     <t xml:space="preserve">1.63281655311584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309945583344</t>
+    <t xml:space="preserve">1.61309921741486</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556398868561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61802840232849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021027088165</t>
+    <t xml:space="preserve">1.61802875995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65130114555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6562305688858</t>
+    <t xml:space="preserve">1.65130126476288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623033046722</t>
   </si>
   <si>
     <t xml:space="preserve">1.61926078796387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64513945579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144265651703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091770648956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546369075775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972653388977</t>
+    <t xml:space="preserve">1.64513969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546392917633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356508255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479734897614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972641468048</t>
   </si>
   <si>
     <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55887758731842</t>
+    <t xml:space="preserve">1.55887722969055</t>
   </si>
   <si>
     <t xml:space="preserve">1.58845317363739</t>
@@ -524,46 +524,46 @@
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
+    <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598828315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105909824371</t>
+    <t xml:space="preserve">1.57120037078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59338223934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722114562988</t>
+    <t xml:space="preserve">1.59338235855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5872209072113</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66485667228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499794483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841172218323</t>
+    <t xml:space="preserve">1.6648565530777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594742774963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225027084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841196060181</t>
   </si>
   <si>
     <t xml:space="preserve">1.69073510169983</t>
@@ -575,64 +575,64 @@
     <t xml:space="preserve">1.67717957496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68703830242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457353115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727987289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016917705536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330005168915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946186065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742150306702</t>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552313327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457341194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125981330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330029010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946174144745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7474217414856</t>
   </si>
   <si>
     <t xml:space="preserve">1.78069412708282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150186061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297581672668</t>
+    <t xml:space="preserve">1.79178488254547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590609550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8176634311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695599555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
     <t xml:space="preserve">1.89899623394012</t>
@@ -641,31 +641,31 @@
     <t xml:space="preserve">1.90762233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90392506122589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92980408668518</t>
+    <t xml:space="preserve">1.90392541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459187984467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9298038482666</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279368877411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00867199897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687428474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729846000671</t>
+    <t xml:space="preserve">2.00867247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838969230652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687404632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729822158813</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796456336975</t>
@@ -674,19 +674,19 @@
     <t xml:space="preserve">2.05303549766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905603408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10725736618042</t>
+    <t xml:space="preserve">2.06905555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10725784301758</t>
   </si>
   <si>
     <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0998637676239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13806509971619</t>
+    <t xml:space="preserve">2.09986329078674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13806533813477</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669156074524</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18119645118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010521888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531754493713</t>
+    <t xml:space="preserve">2.18119597434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380213737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531778335571</t>
   </si>
   <si>
     <t xml:space="preserve">2.16640853881836</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2181658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323609352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2317214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27978110313416</t>
+    <t xml:space="preserve">2.17996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172116279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27978134155273</t>
   </si>
   <si>
     <t xml:space="preserve">2.28717517852783</t>
@@ -749,61 +749,61 @@
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877203941345</t>
+    <t xml:space="preserve">2.35877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289408683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477975845337</t>
+    <t xml:space="preserve">2.33289384841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477952003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137853622437</t>
+    <t xml:space="preserve">2.25137877464294</t>
   </si>
   <si>
     <t xml:space="preserve">2.29019546508789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25267267227173</t>
+    <t xml:space="preserve">2.25267291069031</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313444137573</t>
+    <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866121292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3367760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100889205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806967735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34453940391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3613600730896</t>
+    <t xml:space="preserve">2.33677554130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100865364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782908439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34453964233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">2.32901239395142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34842133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40535235404968</t>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971451759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324526786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642459869385</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">2.31219148635864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537129402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666471481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396656990051</t>
+    <t xml:space="preserve">2.29537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396633148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.24490928649902</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26172995567322</t>
+    <t xml:space="preserve">2.26172971725464</t>
   </si>
   <si>
     <t xml:space="preserve">2.26690530776978</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">2.20609211921692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903109550476</t>
+    <t xml:space="preserve">2.19703507423401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197031021118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24102735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771849632263</t>
+    <t xml:space="preserve">2.24102759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771897315979</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348586082458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407715797424</t>
+    <t xml:space="preserve">2.29407739639282</t>
   </si>
   <si>
     <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855086326599</t>
+    <t xml:space="preserve">2.27855038642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24879050254822</t>
+    <t xml:space="preserve">2.24879121780396</t>
   </si>
   <si>
     <t xml:space="preserve">2.29278349876404</t>
@@ -920,49 +920,49 @@
     <t xml:space="preserve">2.35747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28502011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
+    <t xml:space="preserve">2.28501987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2863142490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337503433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33160018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572247505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664649009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745920181274</t>
+    <t xml:space="preserve">2.33160042762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418822288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30572199821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359597206116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745944023132</t>
   </si>
   <si>
     <t xml:space="preserve">2.44675707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44546318054199</t>
+    <t xml:space="preserve">2.44546294212341</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651648521423</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34195137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524176597595</t>
+    <t xml:space="preserve">2.34195184707642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40793991088867</t>
@@ -986,52 +986,52 @@
     <t xml:space="preserve">2.39370727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37688660621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464999198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31607341766357</t>
+    <t xml:space="preserve">2.37688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36265397071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38464975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.316073179245</t>
   </si>
   <si>
     <t xml:space="preserve">2.36459469795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3807680606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37429881095886</t>
+    <t xml:space="preserve">2.38076829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37429857254028</t>
   </si>
   <si>
     <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3193085193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13492798805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346773147583</t>
+    <t xml:space="preserve">2.31930828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13492822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346796989441</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0896418094635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07993745803833</t>
+    <t xml:space="preserve">2.08964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07993769645691</t>
   </si>
   <si>
     <t xml:space="preserve">2.11551952362061</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.12198925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699872016907</t>
+    <t xml:space="preserve">2.06699848175049</t>
   </si>
   <si>
     <t xml:space="preserve">2.05082488059998</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">2.01847743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966051101685</t>
+    <t xml:space="preserve">1.97966063022614</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494716644287</t>
+    <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04759001731873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08640670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0411205291748</t>
+    <t xml:space="preserve">2.08640694618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04112076759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.07023334503174</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">2.09934592247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905051231384</t>
+    <t xml:space="preserve">2.10905027389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
@@ -1103,31 +1103,31 @@
     <t xml:space="preserve">2.12845873832703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110206604004</t>
+    <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962286949158</t>
+    <t xml:space="preserve">2.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755261421204</t>
+    <t xml:space="preserve">2.26755237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.28460168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958495140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18230628967285</t>
+    <t xml:space="preserve">2.2505030632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958471298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18230581283569</t>
   </si>
   <si>
     <t xml:space="preserve">2.223224401474</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">2.16866683959961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751866340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10046982765198</t>
+    <t xml:space="preserve">2.13456797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342051506042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04932188987732</t>
+    <t xml:space="preserve">2.04932165145874</t>
   </si>
   <si>
     <t xml:space="preserve">1.96066558361053</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614161491394</t>
+    <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.04591178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227281570435</t>
+    <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02886271476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909230232239</t>
+    <t xml:space="preserve">2.02886247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
@@ -1199,55 +1199,55 @@
     <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01522302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817395210266</t>
+    <t xml:space="preserve">2.01522326469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817407131195</t>
   </si>
   <si>
     <t xml:space="preserve">1.98794424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97089517116547</t>
+    <t xml:space="preserve">1.97089540958405</t>
   </si>
   <si>
     <t xml:space="preserve">1.96748530864716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95384573936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725584030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9777147769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043587684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436160326004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820742607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.185715675354</t>
+    <t xml:space="preserve">1.95384550094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725548267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771489620209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504359960556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361615180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18571591377258</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417574882507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801131248474</t>
+    <t xml:space="preserve">2.2880117893219</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004388809204</t>
+    <t xml:space="preserve">2.23004364967346</t>
   </si>
   <si>
     <t xml:space="preserve">2.21640467643738</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">2.11410880088806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06296110153198</t>
+    <t xml:space="preserve">2.06296133995056</t>
   </si>
   <si>
     <t xml:space="preserve">2.1277482509613</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209282875061</t>
+    <t xml:space="preserve">2.10387969017029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
     <t xml:space="preserve">2.13115811347961</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">2.15502738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15161752700806</t>
+    <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
     <t xml:space="preserve">2.16184687614441</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05955123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315697669983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453438282013</t>
+    <t xml:space="preserve">2.05955147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315721511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9811247587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.984534740448</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">2.0936496257782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319092750549</t>
+    <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
     <t xml:space="preserve">2.05273151397705</t>
@@ -1328,25 +1328,25 @@
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594550132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207646369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253540039062</t>
+    <t xml:space="preserve">2.24027371406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686361312866</t>
+    <t xml:space="preserve">2.23686385154724</t>
   </si>
   <si>
     <t xml:space="preserve">2.25391292572021</t>
@@ -1361,28 +1361,28 @@
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483127593994</t>
+    <t xml:space="preserve">2.29483103752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.31528997421265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30165100097656</t>
+    <t xml:space="preserve">2.30165076255798</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961866378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233952522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643838882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892966270447</t>
+    <t xml:space="preserve">2.35961842536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892990112305</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32552003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35279893875122</t>
+    <t xml:space="preserve">2.32551956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
     <t xml:space="preserve">2.3732578754425</t>
@@ -1406,13 +1406,13 @@
     <t xml:space="preserve">2.3971266746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666773796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099571228027</t>
+    <t xml:space="preserve">2.38689732551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099595069885</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804502487183</t>
@@ -1427,28 +1427,28 @@
     <t xml:space="preserve">2.44827437400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46191382408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942255020142</t>
+    <t xml:space="preserve">2.4619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942207336426</t>
   </si>
   <si>
     <t xml:space="preserve">2.51306176185608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670121192932</t>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5267014503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60171794891357</t>
+    <t xml:space="preserve">2.601717710495</t>
   </si>
   <si>
     <t xml:space="preserve">2.59830808639526</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">2.62558698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6153576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855242729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61541223526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61167049407959</t>
+    <t xml:space="preserve">2.61535739898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61541247367859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61167097091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.56677103042603</t>
@@ -1475,61 +1475,61 @@
     <t xml:space="preserve">2.58547902107239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928802490234</t>
+    <t xml:space="preserve">2.55928778648376</t>
   </si>
   <si>
     <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269559860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67153692245483</t>
+    <t xml:space="preserve">2.71269536018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908719062805</t>
+    <t xml:space="preserve">2.65657067298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908695220947</t>
   </si>
   <si>
     <t xml:space="preserve">2.64160370826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66405391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031193733215</t>
+    <t xml:space="preserve">2.66405367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643710136414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772887229919</t>
+    <t xml:space="preserve">2.72766160964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521211624146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7201783657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73140358924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262881278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7912700176239</t>
+    <t xml:space="preserve">2.72017860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73140335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79126977920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137195110321</t>
+    <t xml:space="preserve">2.81372022628784</t>
   </si>
   <si>
     <t xml:space="preserve">2.80623650550842</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984467506409</t>
+    <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338558197021</t>
@@ -1562,19 +1562,19 @@
     <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93719410896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331879615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">2.93719387054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331903457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576924324036</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060192108154</t>
+    <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">3.15046834945679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18040156364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16169309616089</t>
+    <t xml:space="preserve">3.18040084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16169333457947</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801814079285</t>
@@ -1616,40 +1616,40 @@
     <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583579063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9746105670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91100287437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07189345359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06815195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00454378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351939201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835206985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467759132385</t>
+    <t xml:space="preserve">2.98583555221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97461032867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91100263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0718936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0681517124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951050758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0045440196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835230827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209404945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467711448669</t>
   </si>
   <si>
     <t xml:space="preserve">2.94841909408569</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80249500274658</t>
+    <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
     <t xml:space="preserve">2.83991146087646</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84365272521973</t>
+    <t xml:space="preserve">2.84365248680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.86236143112183</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848587989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89603590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596912384033</t>
+    <t xml:space="preserve">2.91848611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89603567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726113319397</t>
@@ -1700,25 +1700,25 @@
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.798752784729</t>
+    <t xml:space="preserve">2.79875326156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76881957054138</t>
+    <t xml:space="preserve">2.76882004737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76133680343628</t>
+    <t xml:space="preserve">2.76133704185486</t>
   </si>
   <si>
     <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00828528404236</t>
+    <t xml:space="preserve">3.00828576087952</t>
   </si>
   <si>
     <t xml:space="preserve">3.0307354927063</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88481116294861</t>
+    <t xml:space="preserve">2.88481092453003</t>
   </si>
   <si>
     <t xml:space="preserve">2.87358593940735</t>
@@ -1739,43 +1739,43 @@
     <t xml:space="preserve">2.78378653526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81746125221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989577293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36374187469482</t>
+    <t xml:space="preserve">2.8174614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487771034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98957705497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761766433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986680030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3637421131134</t>
   </si>
   <si>
     <t xml:space="preserve">3.42360830307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44980001449585</t>
+    <t xml:space="preserve">3.44979977607727</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2664589881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24026775360107</t>
+    <t xml:space="preserve">3.26645922660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2402675151825</t>
   </si>
   <si>
     <t xml:space="preserve">3.22530126571655</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">3.2814257144928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32258439064026</t>
+    <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
     <t xml:space="preserve">3.2963924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924336433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305165290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06441020965576</t>
+    <t xml:space="preserve">3.13924312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440997123718</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679315567017</t>
+    <t xml:space="preserve">3.11679339408875</t>
   </si>
   <si>
     <t xml:space="preserve">3.08685994148254</t>
@@ -1814,25 +1814,25 @@
     <t xml:space="preserve">2.57425427436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621438026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853006362915</t>
+    <t xml:space="preserve">2.03545689582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2562141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39091372489929</t>
+    <t xml:space="preserve">2.39091348648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581318855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942135810852</t>
+    <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
@@ -1841,37 +1841,37 @@
     <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4657461643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4283299446106</t>
+    <t xml:space="preserve">2.46574664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42832970619202</t>
   </si>
   <si>
     <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51812958717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38343024253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35723853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4133632183075</t>
+    <t xml:space="preserve">2.51812934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38343000411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465498924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35723876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839673042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710495948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41336345672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">2.40962195396423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4545214176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46948838233948</t>
+    <t xml:space="preserve">2.45452165603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
     <t xml:space="preserve">2.5218710899353</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">2.49193787574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935481071472</t>
+    <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
@@ -1901,25 +1901,25 @@
     <t xml:space="preserve">2.50690460205078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670424461365</t>
+    <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265093803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17801690101624</t>
+    <t xml:space="preserve">3.15795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265069961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17801713943481</t>
   </si>
   <si>
     <t xml:space="preserve">3.1072199344635</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99709033966064</t>
+    <t xml:space="preserve">2.99709057807922</t>
   </si>
   <si>
     <t xml:space="preserve">3.06788778305054</t>
@@ -1955,34 +1955,34 @@
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202542304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595909118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842651367188</t>
+    <t xml:space="preserve">2.94202566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989228248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595885276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
     <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8082971572876</t>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79649758338928</t>
+    <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469800949097</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73750019073486</t>
+    <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
     <t xml:space="preserve">2.66276907920837</t>
@@ -2003,7 +2003,7 @@
     <t xml:space="preserve">2.78863143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74536609649658</t>
+    <t xml:space="preserve">2.74536657333374</t>
   </si>
   <si>
     <t xml:space="preserve">2.76109910011292</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770440101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6981680393219</t>
+    <t xml:space="preserve">2.60770463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69816827774048</t>
   </si>
   <si>
     <t xml:space="preserve">2.74143290519714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963356971741</t>
+    <t xml:space="preserve">2.72963333129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2042,13 +2042,13 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63916993141174</t>
+    <t xml:space="preserve">2.63917016983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6549026966095</t>
+    <t xml:space="preserve">2.65490293502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.65883636474609</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6470365524292</t>
+    <t xml:space="preserve">2.64703631401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59590530395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59983825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65096950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75323271751404</t>
+    <t xml:space="preserve">2.5959050655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59983801841736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65096974372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75323247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.52510762214661</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084014892578</t>
+    <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970866203308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51330828666687</t>
+    <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
     <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50544166564941</t>
+    <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397613525391</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117419242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4936420917511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610999107361</t>
+    <t xml:space="preserve">2.52117443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49364185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610975265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38351273536682</t>
+    <t xml:space="preserve">2.38351249694824</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39924550056458</t>
+    <t xml:space="preserve">2.399245262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">2.39137935638428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35598039627075</t>
+    <t xml:space="preserve">2.35598063468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.39531230926514</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
+    <t xml:space="preserve">2.340247631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384677886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557102203369</t>
+    <t xml:space="preserve">2.57230615615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557126045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.73356652259827</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503205299377</t>
+    <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
     <t xml:space="preserve">2.71783375740051</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6903018951416</t>
+    <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
     <t xml:space="preserve">2.70603442192078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210075378418</t>
+    <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87909436225891</t>
+    <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449356079102</t>
+    <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0206892490387</t>
+    <t xml:space="preserve">3.02068948745728</t>
   </si>
   <si>
     <t xml:space="preserve">2.9616916179657</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976268768311</t>
+    <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84762907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82009720802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302826881409</t>
+    <t xml:space="preserve">2.8476288318634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302779197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
@@ -2246,43 +2246,43 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91055989265442</t>
+    <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876079559326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95775818824768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9538254737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87516140937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796311378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495648384094</t>
+    <t xml:space="preserve">2.95775842666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95382523536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87516164779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796335220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729502677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
     <t xml:space="preserve">3.01675653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02462291717529</t>
+    <t xml:space="preserve">3.02462244033813</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00889015197754</t>
+    <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349119186401</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">3.05215501785278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02855587005615</t>
+    <t xml:space="preserve">3.02855610847473</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002163887024</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04428839683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148693084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12688541412354</t>
+    <t xml:space="preserve">3.04428863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148716926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
     <t xml:space="preserve">3.10328650474548</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">3.19374966621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15441799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981671333313</t>
+    <t xml:space="preserve">3.15441823005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
@@ -68802,7 +68802,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6493171296</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>117285</v>
@@ -68823,6 +68823,32 @@
         <v>1257</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495949074</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>36375</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>3.10500001907349</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>3.07500004768372</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>3.08500003814697</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>3.07500004768372</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27861988544464</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
+    <t xml:space="preserve">1.27977383136749</t>
   </si>
   <si>
     <t xml:space="preserve">1.26823401451111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26938807964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25554037094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861621856689</t>
+    <t xml:space="preserve">1.26938831806183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25554025173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977028369904</t>
+    <t xml:space="preserve">1.24977004528046</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25784826278687</t>
+    <t xml:space="preserve">1.18283879756927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25784814357758</t>
   </si>
   <si>
     <t xml:space="preserve">1.25438630580902</t>
@@ -92,37 +92,37 @@
     <t xml:space="preserve">1.27285015583038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27746617794037</t>
+    <t xml:space="preserve">1.27746605873108</t>
   </si>
   <si>
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591866970062</t>
+    <t xml:space="preserve">1.20591855049133</t>
   </si>
   <si>
     <t xml:space="preserve">1.21168863773346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2105348110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899842262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476850986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707640171051</t>
+    <t xml:space="preserve">1.21053469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130643367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28208196163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28438985347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323602676392</t>
+    <t xml:space="preserve">1.28208184242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28439009189606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169620990753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
     <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862355232239</t>
+    <t xml:space="preserve">1.30862379074097</t>
   </si>
   <si>
     <t xml:space="preserve">1.31093180179596</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247173786163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208562850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30746960639954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362568378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708740234375</t>
+    <t xml:space="preserve">1.32247149944305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208574771881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30746972560883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016360759735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31323969364166</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3501672744751</t>
+    <t xml:space="preserve">1.35016715526581</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478329658508</t>
@@ -209,49 +209,49 @@
     <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3432434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516928672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324690818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017094135284</t>
+    <t xml:space="preserve">1.34324324131012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555125236511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017106056213</t>
   </si>
   <si>
     <t xml:space="preserve">1.37786316871643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3674772977829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286115646362</t>
+    <t xml:space="preserve">1.36747717857361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286103725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621186256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687856197357</t>
+    <t xml:space="preserve">1.39251530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621198177338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687844276428</t>
   </si>
   <si>
     <t xml:space="preserve">1.44427239894867</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">1.44550466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043385028839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536327362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46275699138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110019207001</t>
+    <t xml:space="preserve">1.45043396949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536291599274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">1.48863565921783</t>
@@ -278,67 +278,67 @@
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51821112632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162526130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465571880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574647426605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849426746368</t>
+    <t xml:space="preserve">1.5182112455368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4984940290451</t>
   </si>
   <si>
     <t xml:space="preserve">1.54039287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60817015171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433148384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707939624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52437269687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958490371704</t>
+    <t xml:space="preserve">1.60817003250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707915782928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5243729352951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
     <t xml:space="preserve">1.55641305446625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6007764339447</t>
+    <t xml:space="preserve">1.60077619552612</t>
   </si>
   <si>
     <t xml:space="preserve">1.54655432701111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190792560577</t>
+    <t xml:space="preserve">1.52190828323364</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257450580597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59584701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883673191071</t>
+    <t xml:space="preserve">1.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6636244058609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461438655853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883637428284</t>
   </si>
   <si>
     <t xml:space="preserve">1.65992736816406</t>
@@ -347,61 +347,61 @@
     <t xml:space="preserve">1.66115987300873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71661353111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7215428352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400796413422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523987293243</t>
+    <t xml:space="preserve">1.71661376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827044963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523999214172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059394836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675551891327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784627437592</t>
+    <t xml:space="preserve">1.70429074764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675528049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784603595734</t>
   </si>
   <si>
     <t xml:space="preserve">1.75851249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604796409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439092636108</t>
+    <t xml:space="preserve">1.79301702976227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604784488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439116477966</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206766605377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988639354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865388870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618923664093</t>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865424633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618947505951</t>
   </si>
   <si>
     <t xml:space="preserve">1.76837086677551</t>
@@ -410,25 +410,25 @@
     <t xml:space="preserve">1.7745326757431</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76220965385437</t>
+    <t xml:space="preserve">1.76220953464508</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699744701385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76344180107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855359077454</t>
+    <t xml:space="preserve">1.76344168186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855347156525</t>
   </si>
   <si>
     <t xml:space="preserve">1.74249231815338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443225860596</t>
+    <t xml:space="preserve">1.69443202018738</t>
   </si>
   <si>
     <t xml:space="preserve">1.61186695098877</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">1.63158404827118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035202026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679601669312</t>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679625511169</t>
   </si>
   <si>
     <t xml:space="preserve">1.6426750421524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376591682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309921741486</t>
+    <t xml:space="preserve">1.65376555919647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049317359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309945583344</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556398868561</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">1.61802875995636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021039009094</t>
+    <t xml:space="preserve">1.64021015167236</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760422706604</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">1.65130126476288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65623033046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404846191406</t>
+    <t xml:space="preserve">1.65623009204865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513957500458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144265651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404870033264</t>
   </si>
   <si>
     <t xml:space="preserve">1.59091758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53546392917633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356508255005</t>
+    <t xml:space="preserve">1.53546345233917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356484413147</t>
   </si>
   <si>
     <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49972641468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247396945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887722969055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503915786743</t>
+    <t xml:space="preserve">1.49972653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247385025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887758731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503891944885</t>
   </si>
   <si>
     <t xml:space="preserve">1.53423130512238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49726176261902</t>
+    <t xml:space="preserve">1.49726188182831</t>
   </si>
   <si>
     <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532206058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120037078857</t>
+    <t xml:space="preserve">1.54532194137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120072841644</t>
   </si>
   <si>
     <t xml:space="preserve">1.58598852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.581059217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200846195221</t>
+    <t xml:space="preserve">1.58105909824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200834274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.59338235855103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5872209072113</t>
+    <t xml:space="preserve">1.58722066879272</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
@@ -557,10 +557,10 @@
     <t xml:space="preserve">1.65499806404114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225027084351</t>
+    <t xml:space="preserve">1.67594730854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225050926208</t>
   </si>
   <si>
     <t xml:space="preserve">1.67841196060181</t>
@@ -572,115 +572,115 @@
     <t xml:space="preserve">1.66978573799133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717957496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703806400299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552313327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538126468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7129168510437</t>
+    <t xml:space="preserve">1.67717969417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703818321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552289485931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538138389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291661262512</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457341194153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467418670654</t>
+    <t xml:space="preserve">1.76467394828796</t>
   </si>
   <si>
     <t xml:space="preserve">1.75728011131287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74125981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946174144745</t>
+    <t xml:space="preserve">1.74126029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016929626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330040931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946162223816</t>
   </si>
   <si>
     <t xml:space="preserve">1.7474217414856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069412708282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178488254547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590609550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8176634311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150197982788</t>
+    <t xml:space="preserve">1.78069424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766331195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695599555969</t>
+    <t xml:space="preserve">1.86695623397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89899623394012</t>
+    <t xml:space="preserve">1.8989964723587</t>
   </si>
   <si>
     <t xml:space="preserve">1.90762233734131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90392541885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459187984467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9298038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279368877411</t>
+    <t xml:space="preserve">1.90392553806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279416561127</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867247581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838969230652</t>
+    <t xml:space="preserve">2.02838945388794</t>
   </si>
   <si>
     <t xml:space="preserve">2.04687404632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01483368873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729822158813</t>
+    <t xml:space="preserve">2.01483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796456336975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303549766541</t>
+    <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10725784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09493446350098</t>
+    <t xml:space="preserve">2.10725736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0949342250824</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986329078674</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">2.14669156074524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024708747864</t>
+    <t xml:space="preserve">2.16024661064148</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887331008911</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">2.17257022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15654993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119597434998</t>
+    <t xml:space="preserve">2.15655016899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.17380213737488</t>
@@ -713,10 +713,10 @@
     <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640853881836</t>
+    <t xml:space="preserve">2.15531754493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640830039978</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
+    <t xml:space="preserve">2.17996406555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
@@ -734,64 +734,64 @@
     <t xml:space="preserve">2.20953965187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21323657035828</t>
+    <t xml:space="preserve">2.2132363319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717517852783</t>
+    <t xml:space="preserve">2.27978157997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717541694641</t>
   </si>
   <si>
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877227783203</t>
+    <t xml:space="preserve">2.35877180099487</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583330154419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289384841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
+    <t xml:space="preserve">2.33289432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477975845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526070594788</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137877464294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267291069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313467979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866121292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33677554130554</t>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973345756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866145133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3367760181427</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35489058494568</t>
+    <t xml:space="preserve">2.36782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.30054664611816</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">2.33806991577148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34453964233398</t>
+    <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
     <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653542518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34065747261047</t>
+    <t xml:space="preserve">2.36653566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065771102905</t>
   </si>
   <si>
     <t xml:space="preserve">2.32901239395142</t>
@@ -818,31 +818,31 @@
     <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971451759338</t>
+    <t xml:space="preserve">2.34971523284912</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4053521156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31219148635864</t>
+    <t xml:space="preserve">2.40535235404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642436027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24490928649902</t>
+    <t xml:space="preserve">2.29666471481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396656990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490904808044</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
@@ -851,43 +851,43 @@
     <t xml:space="preserve">2.26043581962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26172971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20609211921692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703507423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197031021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102759361267</t>
+    <t xml:space="preserve">2.25784850120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26172995567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361538887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2060923576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903109550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319700717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.32254266738892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31736755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771897315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348586082458</t>
+    <t xml:space="preserve">2.31736731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771849632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
     <t xml:space="preserve">2.29407739639282</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855038642883</t>
+    <t xml:space="preserve">2.27855062484741</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
@@ -905,22 +905,22 @@
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24879121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.24879050254822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33548188209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28501987457275</t>
+    <t xml:space="preserve">2.33548212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28502035140991</t>
   </si>
   <si>
     <t xml:space="preserve">2.2863142490387</t>
@@ -929,22 +929,22 @@
     <t xml:space="preserve">2.27337503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26819944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160042762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960416793823</t>
+    <t xml:space="preserve">2.26819920539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30572199821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359597206116</t>
+    <t xml:space="preserve">2.3057222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
     <t xml:space="preserve">2.37171101570129</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">2.40664625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745944023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
+    <t xml:space="preserve">2.41699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546294212341</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38723802566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241337776184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34195184707642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524152755737</t>
+    <t xml:space="preserve">2.38723754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241313934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34195160865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524176597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.40793991088867</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.37688684463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36265397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37429857254028</t>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38464999198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607365608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076853752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37429881095886</t>
   </si>
   <si>
     <t xml:space="preserve">2.37753343582153</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435563087463</t>
+    <t xml:space="preserve">2.13492798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.10258054733276</t>
@@ -1031,94 +1031,94 @@
     <t xml:space="preserve">2.08964157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993769645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06699848175049</t>
+    <t xml:space="preserve">2.07993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551976203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198877334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06699872016907</t>
   </si>
   <si>
     <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966063022614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494692802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04759001731873</t>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847767829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0152428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494740486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640694618225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04112076759338</t>
+    <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
     <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07670283317566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10581541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06052899360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934592247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905027389526</t>
+    <t xml:space="preserve">2.07670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10581564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06052923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934544563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905051231384</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875414848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845873832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110182762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433645248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.199622631073</t>
+    <t xml:space="preserve">2.11875462532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433621406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19962310791016</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460168838501</t>
+    <t xml:space="preserve">2.26755261421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460144996643</t>
   </si>
   <si>
     <t xml:space="preserve">2.2505030632019</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230581283569</t>
+    <t xml:space="preserve">2.18230628967285</t>
   </si>
   <si>
     <t xml:space="preserve">2.223224401474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16866683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13456797599792</t>
+    <t xml:space="preserve">2.16866660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1345682144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.12433838844299</t>
@@ -1145,49 +1145,49 @@
     <t xml:space="preserve">2.11751890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11069893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10046935081482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08342051506042</t>
+    <t xml:space="preserve">2.11069917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1004695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066558361053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0118134021759</t>
+    <t xml:space="preserve">1.96066534519196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01181364059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227257728577</t>
+    <t xml:space="preserve">2.04591202735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227210044861</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001041412354</t>
+    <t xml:space="preserve">2.08001017570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02886247634888</t>
+    <t xml:space="preserve">2.02886271476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04250192642212</t>
+    <t xml:space="preserve">2.0425021648407</t>
   </si>
   <si>
     <t xml:space="preserve">1.99135434627533</t>
@@ -1196,61 +1196,61 @@
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0697808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522326469421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817407131195</t>
+    <t xml:space="preserve">2.06978106498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817395210266</t>
   </si>
   <si>
     <t xml:space="preserve">1.98794424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97089540958405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748530864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384550094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725548267365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771489620209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504359960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361615180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18571591377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417574882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2880117893219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663426399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004364967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21640467643738</t>
+    <t xml:space="preserve">1.97089517116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748507022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384573936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771501541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820742607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.185715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801131248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2300443649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2164044380188</t>
   </si>
   <si>
     <t xml:space="preserve">2.17889618873596</t>
@@ -1259,28 +1259,28 @@
     <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410880088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1277482509613</t>
+    <t xml:space="preserve">2.11410856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296110153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12774848937988</t>
   </si>
   <si>
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387969017029</t>
+    <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584370136261</t>
+    <t xml:space="preserve">2.13115835189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15843725204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.15502738952637</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00499367713928</t>
+    <t xml:space="preserve">2.00499391555786</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863312721252</t>
@@ -1304,13 +1304,13 @@
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9811247587204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.984534740448</t>
+    <t xml:space="preserve">1.92315697669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453438282013</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
@@ -1319,70 +1319,70 @@
     <t xml:space="preserve">2.0936496257782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273151397705</t>
+    <t xml:space="preserve">2.07319092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273175239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027371406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1925356388092</t>
+    <t xml:space="preserve">2.24027323722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19253540039062</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686385154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391292572021</t>
+    <t xml:space="preserve">2.23686361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391340255737</t>
   </si>
   <si>
     <t xml:space="preserve">2.25732278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.30506062507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483103752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31528997421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
+    <t xml:space="preserve">2.29483127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961842536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233976364136</t>
+    <t xml:space="preserve">2.35961818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
     <t xml:space="preserve">2.3664379119873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32892990112305</t>
+    <t xml:space="preserve">2.32892942428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32551956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256911277771</t>
+    <t xml:space="preserve">2.32552027702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256935119629</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
@@ -1406,22 +1406,22 @@
     <t xml:space="preserve">2.3971266746521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099595069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43122553825378</t>
+    <t xml:space="preserve">2.38689708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666773796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804526329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463492393494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827437400818</t>
@@ -1430,31 +1430,31 @@
     <t xml:space="preserve">2.4619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51306176185608</t>
+    <t xml:space="preserve">2.49942231178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5130615234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.48919272422791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47896337509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5267014503479</t>
+    <t xml:space="preserve">2.47896313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670121192932</t>
   </si>
   <si>
     <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.601717710495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830808639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558698654175</t>
+    <t xml:space="preserve">2.60171794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830832481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
     <t xml:space="preserve">2.61535739898682</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">2.88855266571045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61541247367859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61167097091675</t>
+    <t xml:space="preserve">2.61541223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.56677103042603</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269536018372</t>
+    <t xml:space="preserve">2.71269512176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
@@ -1490,25 +1490,25 @@
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657067298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908695220947</t>
+    <t xml:space="preserve">2.65657043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908742904663</t>
   </si>
   <si>
     <t xml:space="preserve">2.64160370826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66405367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031217575073</t>
+    <t xml:space="preserve">2.66405344009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031193733215</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643710136414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766160964966</t>
+    <t xml:space="preserve">2.72766208648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772863388062</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">2.70521211624146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72017860412598</t>
+    <t xml:space="preserve">2.7201783657074</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262809753418</t>
+    <t xml:space="preserve">2.74262833595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79126977920532</t>
+    <t xml:space="preserve">2.7912700176239</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81372022628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868623733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82494497299194</t>
+    <t xml:space="preserve">2.81371998786926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868647575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82494521141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338558197021</t>
+    <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971086502075</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93719387054443</t>
+    <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
     <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576924324036</t>
+    <t xml:space="preserve">3.01576852798462</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821849822998</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556864738464</t>
+    <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053513526917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18040084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16169333457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801814079285</t>
+    <t xml:space="preserve">3.15046787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18040156364441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801837921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10931038856506</t>
+    <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
     <t xml:space="preserve">3.09434366226196</t>
@@ -1613,31 +1613,31 @@
     <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706053733826</t>
+    <t xml:space="preserve">2.99706077575684</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97461032867432</t>
+    <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
+    <t xml:space="preserve">2.91474437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951050758362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0045440196991</t>
+    <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351963043213</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">2.98209404945374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94467711448669</t>
+    <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
     <t xml:space="preserve">2.94841909408569</t>
@@ -1661,46 +1661,46 @@
     <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84739446640015</t>
+    <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.802494764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84365248680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86236143112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86610293388367</t>
+    <t xml:space="preserve">2.80249500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113644599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84365296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86236119270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86610269546509</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89603567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726113319397</t>
+    <t xml:space="preserve">2.89603590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
+    <t xml:space="preserve">2.79875302314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">2.76882004737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80997824668884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76133704185486</t>
+    <t xml:space="preserve">2.80997800827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7613365650177</t>
   </si>
   <si>
     <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00828576087952</t>
+    <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481092453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358593940735</t>
+    <t xml:space="preserve">2.95590209960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481116294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1742,28 +1742,28 @@
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487771034241</t>
+    <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30761766433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32632565498352</t>
+    <t xml:space="preserve">3.30761742591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632613182068</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986680030823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3637421131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360830307007</t>
+    <t xml:space="preserve">3.36374187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.44979977607727</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">3.26645922660828</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2814257144928</t>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530102729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28142595291138</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2963924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924312591553</t>
+    <t xml:space="preserve">3.29639220237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924336433411</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305141448975</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679339408875</t>
+    <t xml:space="preserve">3.11679315567017</t>
   </si>
   <si>
     <t xml:space="preserve">3.08685994148254</t>
@@ -1814,31 +1814,31 @@
     <t xml:space="preserve">2.57425427436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545689582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2562141418457</t>
+    <t xml:space="preserve">2.03545713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621438026428</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968873977661</t>
+    <t xml:space="preserve">2.37968850135803</t>
   </si>
   <si>
     <t xml:space="preserve">2.39091348648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43581318855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48445463180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51438784599304</t>
+    <t xml:space="preserve">2.43581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4994215965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48445439338684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51438760757446</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574664115906</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35723876953125</t>
+    <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
     <t xml:space="preserve">2.39839673042297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458820343018</t>
+    <t xml:space="preserve">2.41710472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458844184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.41336345672607</t>
@@ -1877,31 +1877,31 @@
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962195396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452165603638</t>
+    <t xml:space="preserve">2.40962171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4545214176178</t>
   </si>
   <si>
     <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5218710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193787574768</t>
+    <t xml:space="preserve">2.52187132835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193811416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50316286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50690460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670400619507</t>
+    <t xml:space="preserve">2.50316262245178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50690412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670424461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
@@ -1910,19 +1910,19 @@
     <t xml:space="preserve">3.15795111656189</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768445014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714412689209</t>
+    <t xml:space="preserve">3.29265117645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768468856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801713943481</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1072199344635</t>
+    <t xml:space="preserve">3.10721945762634</t>
   </si>
   <si>
     <t xml:space="preserve">3.00102353096008</t>
@@ -1931,7 +1931,7 @@
     <t xml:space="preserve">2.99709057807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788778305054</t>
+    <t xml:space="preserve">3.06788802146912</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">3.07182097434998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96955823898315</t>
+    <t xml:space="preserve">2.96955847740173</t>
   </si>
   <si>
     <t xml:space="preserve">2.92235970497131</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989228248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742414474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595885276794</t>
+    <t xml:space="preserve">2.9498918056488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9026939868927</t>
+    <t xml:space="preserve">2.90269374847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.86336207389832</t>
@@ -1979,13 +1979,13 @@
     <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78076505661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79649782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469800949097</t>
+    <t xml:space="preserve">2.78076529502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79649758338928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.76896548271179</t>
@@ -1994,46 +1994,46 @@
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536657333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109910011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
+    <t xml:space="preserve">2.73749971389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63523650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737083435059</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69816827774048</t>
+    <t xml:space="preserve">2.60770440101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
     <t xml:space="preserve">2.74143290519714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963333129883</t>
+    <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">2.65490293502808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65883636474609</t>
+    <t xml:space="preserve">2.65883612632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
@@ -2060,43 +2060,43 @@
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130378723145</t>
+    <t xml:space="preserve">2.63130354881287</t>
   </si>
   <si>
     <t xml:space="preserve">2.64703631401062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62343716621399</t>
+    <t xml:space="preserve">2.62343740463257</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983801841736</t>
+    <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096974372864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323247909546</t>
+    <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
     <t xml:space="preserve">2.52510762214661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52904081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970866203308</t>
+    <t xml:space="preserve">2.52904057502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54084014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150871276855</t>
+    <t xml:space="preserve">2.50150847434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50937485694885</t>
+    <t xml:space="preserve">2.50937509536743</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364185333252</t>
+    <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
     <t xml:space="preserve">2.46610975265503</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38351249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45431017875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.399245262146</t>
+    <t xml:space="preserve">2.38351273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39137935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598063468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531230926514</t>
+    <t xml:space="preserve">2.3913791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531254768372</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
@@ -2156,25 +2156,25 @@
     <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36384677886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57230615615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557126045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.33631467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36384701728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57230567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503229141235</t>
+    <t xml:space="preserve">2.76503205299377</t>
   </si>
   <si>
     <t xml:space="preserve">2.71783375740051</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89482736587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87909460067749</t>
+    <t xml:space="preserve">2.89482760429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87909483909607</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">2.88696122169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87122845649719</t>
+    <t xml:space="preserve">2.87122821807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.91449332237244</t>
@@ -2216,25 +2216,25 @@
     <t xml:space="preserve">3.02068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9616916179657</t>
+    <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976292610168</t>
+    <t xml:space="preserve">2.83976268768311</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8476288318634</t>
+    <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.82009673118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8515625</t>
+    <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88302779197693</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775842666626</t>
+    <t xml:space="preserve">2.91056036949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775866508484</t>
   </si>
   <si>
     <t xml:space="preserve">2.95382523536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516164779663</t>
+    <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
     <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.93022608757019</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462244033813</t>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2285,34 +2285,34 @@
     <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98922371864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98529100418091</t>
+    <t xml:space="preserve">2.97349143028259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98922395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855610847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002163887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04428863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148716926575</t>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002140045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09541988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04428839683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688565254211</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382676124573</t>
+    <t xml:space="preserve">3.10382652282715</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2354,25 +2354,25 @@
     <t xml:space="preserve">3.08744764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06697368621826</t>
+    <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012084960938</t>
+    <t xml:space="preserve">3.07106828689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01783680915833</t>
+    <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
@@ -2390,19 +2390,19 @@
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335280418396</t>
+    <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
     <t xml:space="preserve">3.0751633644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98507857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99326825141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96460461616516</t>
+    <t xml:space="preserve">2.98507881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99326801300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
@@ -2411,31 +2411,31 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908862113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.9031834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137290000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585666656494</t>
+    <t xml:space="preserve">2.84585690498352</t>
   </si>
   <si>
     <t xml:space="preserve">2.87042546272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91956257820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003629684448</t>
+    <t xml:space="preserve">2.91956281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9400360584259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86223578453064</t>
@@ -2453,31 +2453,31 @@
     <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86633062362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499402046204</t>
+    <t xml:space="preserve">2.86633086204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499425888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87861514091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452030181885</t>
+    <t xml:space="preserve">2.87861490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452006340027</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775225639343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736285209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98917365074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">2.99736309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869969367981</t>
+    <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
+    <t xml:space="preserve">2.9318470954895</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
@@ -2510,43 +2510,43 @@
     <t xml:space="preserve">2.81719374656677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85814142227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051001548767</t>
+    <t xml:space="preserve">2.82128834724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85814118385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84995150566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">2.91546750068665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357286453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.83357262611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84176206588745</t>
+    <t xml:space="preserve">2.77215123176575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80900430679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83766746520996</t>
+    <t xml:space="preserve">2.80900406837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83766722679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.80081462860107</t>
@@ -2564,16 +2564,16 @@
     <t xml:space="preserve">2.69435095787048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521384239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387723922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
+    <t xml:space="preserve">2.64521360397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387700080872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805663108826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348759651184</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95615863800049</t>
+    <t xml:space="preserve">2.7271089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939299583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95615839958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303664207458</t>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84873986244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725620269775</t>
+    <t xml:space="preserve">2.84873962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725596427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
+    <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90459775924683</t>
+    <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
     <t xml:space="preserve">2.90889406204224</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54796767234802</t>
+    <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.53507781028748</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.44914269447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43195581436157</t>
+    <t xml:space="preserve">2.43195605278015</t>
   </si>
   <si>
     <t xml:space="preserve">2.48781371116638</t>
@@ -2705,22 +2705,22 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602093696594</t>
+    <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
     <t xml:space="preserve">2.26867985725403</t>
@@ -2732,31 +2732,31 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3975818157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35031771659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38469195365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625283241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.39758205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38469171524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883405685425</t>
+    <t xml:space="preserve">2.3546142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898825645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883381843567</t>
   </si>
   <si>
     <t xml:space="preserve">2.33742761611938</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10540342330933</t>
+    <t xml:space="preserve">2.10540366172791</t>
   </si>
   <si>
     <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06243634223938</t>
+    <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985487937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14407420158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399722099304</t>
+    <t xml:space="preserve">2.16985464096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14407396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2822,25 +2822,25 @@
     <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83041203022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78744447231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.83041214942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6774480342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416839599609</t>
+    <t xml:space="preserve">1.67744791507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416851520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
+    <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650110721588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">1.96790778636932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
+    <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524946212769</t>
+    <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
@@ -2909,34 +2909,34 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2128221988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1956353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.21282196044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19563508033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681034088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10970020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133830070496</t>
+    <t xml:space="preserve">2.06673264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681010246277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10969996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453727722168</t>
+    <t xml:space="preserve">2.32453751564026</t>
   </si>
   <si>
     <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40617537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609815597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.40617561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609839439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.427659034729</t>
+    <t xml:space="preserve">2.36750483512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42765927314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149250030518</t>
@@ -2999,19 +2999,19 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
+    <t xml:space="preserve">2.27297616004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39328503608704</t>
+    <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062659263611</t>
+    <t xml:space="preserve">2.47062635421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -68828,7 +68828,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495949074</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>36375</v>
@@ -68849,6 +68849,32 @@
         <v>1245</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.649525463</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>83530</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>3.06500005722046</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>3.09500002861023</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">1.27977395057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26823401451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26938819885254</t>
+    <t xml:space="preserve">1.2682341337204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.25554025173187</t>
@@ -62,175 +62,175 @@
     <t xml:space="preserve">1.27515804767609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977040290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246037960052</t>
+    <t xml:space="preserve">1.24977016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246026039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.19437885284424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1978405714035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975916385651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283891677856</t>
+    <t xml:space="preserve">1.19784069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283879756927</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438618659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746215343475</t>
+    <t xml:space="preserve">1.25438630580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746239185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.27285003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2774658203125</t>
+    <t xml:space="preserve">1.27746605873108</t>
   </si>
   <si>
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591855049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168863773346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053469181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207060337067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899866104126</t>
+    <t xml:space="preserve">1.20591843128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207072257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822656154633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130631446838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899842262268</t>
   </si>
   <si>
     <t xml:space="preserve">1.23476850986481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23707664012909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2901599407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669798374176</t>
+    <t xml:space="preserve">1.23707628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29016005992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669786453247</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28208184242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28438985347748</t>
+    <t xml:space="preserve">1.28208196163177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28439009189606</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862379074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093180179596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477962970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247173786163</t>
+    <t xml:space="preserve">1.28323578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054581165314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862367153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093192100525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477939128876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30746948719025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516183376312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016360759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362544536591</t>
+    <t xml:space="preserve">1.30746972560883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516171455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016348838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362568378448</t>
   </si>
   <si>
     <t xml:space="preserve">1.32708764076233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31323957443237</t>
+    <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824170589447</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439730644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670531749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016739368439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478341579437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208941459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3432434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516904830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017106056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786328792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747717857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286115646362</t>
+    <t xml:space="preserve">1.35132110118866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439742565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3501672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478329658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170732975006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208953380585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34324336051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3455513715744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516916751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324726581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786304950714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747705936432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286103725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">1.39251530170441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39621186256409</t>
+    <t xml:space="preserve">1.39621210098267</t>
   </si>
   <si>
     <t xml:space="preserve">1.41099989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42701995372772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687856197357</t>
+    <t xml:space="preserve">1.42701971530914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332315444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687844276428</t>
   </si>
   <si>
     <t xml:space="preserve">1.44427239894867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44550442695618</t>
+    <t xml:space="preserve">1.44550454616547</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043396949768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110054969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863542079926</t>
+    <t xml:space="preserve">1.45536303520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275699138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110043048859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863554000854</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342345237732</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">1.5182112455368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54162526130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465571880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574635505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849438667297</t>
+    <t xml:space="preserve">1.54162502288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
     <t xml:space="preserve">1.5403927564621</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">1.59707927703857</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52437269687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641281604767</t>
+    <t xml:space="preserve">1.52437281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641293525696</t>
   </si>
   <si>
     <t xml:space="preserve">1.60077619552612</t>
@@ -320,58 +320,58 @@
     <t xml:space="preserve">1.5465544462204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257450580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59584701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006911754608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115975379944</t>
+    <t xml:space="preserve">1.52190804481506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257462501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6636244058609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006864070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461462497711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883649349213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992748737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115963459015</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154319286346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400748729706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950271606445</t>
+    <t xml:space="preserve">1.72154307365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950295448303</t>
   </si>
   <si>
     <t xml:space="preserve">1.68827044963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72523987293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756337165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059382915497</t>
+    <t xml:space="preserve">1.72523975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429050922394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059359073639</t>
   </si>
   <si>
     <t xml:space="preserve">1.7067551612854</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">1.71784615516663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75851249694824</t>
+    <t xml:space="preserve">1.75851261615753</t>
   </si>
   <si>
     <t xml:space="preserve">1.79301750659943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75604772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439128398895</t>
+    <t xml:space="preserve">1.75604784488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439092636108</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206778526306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865400791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618935585022</t>
+    <t xml:space="preserve">1.74988627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7486537694931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618923664093</t>
   </si>
   <si>
     <t xml:space="preserve">1.7683709859848</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">1.77453279495239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7622092962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344156265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746307373047</t>
+    <t xml:space="preserve">1.76220941543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7769969701767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344215869904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746295452118</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855359077454</t>
@@ -428,91 +428,91 @@
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158404827118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035202026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376555919647</t>
+    <t xml:space="preserve">1.69443213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186718940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6315838098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6426750421524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376591682434</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309945583344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6155641078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760422706604</t>
+    <t xml:space="preserve">1.63281643390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309921741486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556398868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802875995636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021027088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760434627533</t>
   </si>
   <si>
     <t xml:space="preserve">1.65130114555359</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65623033046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144253730774</t>
+    <t xml:space="preserve">1.65623009204865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513945579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144277572632</t>
   </si>
   <si>
     <t xml:space="preserve">1.63404858112335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59091758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479711055756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972653388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247408866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845329284668</t>
+    <t xml:space="preserve">1.59091782569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546345233917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356472492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4997261762619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247420787811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845317363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503903865814</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532217979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120072841644</t>
+    <t xml:space="preserve">1.54532194137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120060920715</t>
   </si>
   <si>
     <t xml:space="preserve">1.58598828315735</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">1.58105933666229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60200870037079</t>
+    <t xml:space="preserve">1.60200834274292</t>
   </si>
   <si>
     <t xml:space="preserve">1.59338247776031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58722078800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651323318481</t>
+    <t xml:space="preserve">1.58722066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651347160339</t>
   </si>
   <si>
     <t xml:space="preserve">1.6648565530777</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">1.65499794483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6722503900528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841196060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073498249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978561878204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870379447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552289485931</t>
+    <t xml:space="preserve">1.67594730854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841219902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073522090912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978585720062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717945575714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552277565002</t>
   </si>
   <si>
     <t xml:space="preserve">1.71538150310516</t>
@@ -587,58 +587,58 @@
     <t xml:space="preserve">1.7129168510437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6845737695694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467430591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728046894073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946174144745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742197990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069412708282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178488254547</t>
+    <t xml:space="preserve">1.68457365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728023052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125993251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016929626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330005168915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7806943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178512096405</t>
   </si>
   <si>
     <t xml:space="preserve">1.76590645313263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614814281464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297605514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9076224565506</t>
+    <t xml:space="preserve">1.81766355037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150221824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614861965179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8669558763504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297629356384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899659156799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762269496918</t>
   </si>
   <si>
     <t xml:space="preserve">1.90392553806305</t>
@@ -647,40 +647,40 @@
     <t xml:space="preserve">1.94459199905396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980408668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279345035553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00867199897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0468738079071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483368873596</t>
+    <t xml:space="preserve">1.92980420589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9827938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687404632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483345031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05796480178833</t>
+    <t xml:space="preserve">2.05796504020691</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905579566956</t>
+    <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0949342250824</t>
+    <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986352920532</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">2.13806533813477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14669156074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1725697517395</t>
+    <t xml:space="preserve">2.14669132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024661064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17256999015808</t>
   </si>
   <si>
     <t xml:space="preserve">2.15655016899109</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380213737488</t>
+    <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010545730591</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.21446871757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366074562073</t>
+    <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.17996382713318</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">2.21816539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2132363319397</t>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717517852783</t>
+    <t xml:space="preserve">2.27978157997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717565536499</t>
   </si>
   <si>
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877203941345</t>
+    <t xml:space="preserve">2.35877156257629</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583282470703</t>
@@ -764,28 +764,28 @@
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137877464294</t>
+    <t xml:space="preserve">2.25137901306152</t>
   </si>
   <si>
     <t xml:space="preserve">2.29019546508789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25267291069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866097450256</t>
+    <t xml:space="preserve">2.25267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973345756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313420295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.3367760181427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35100889205933</t>
+    <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
     <t xml:space="preserve">2.36782932281494</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806991577148</t>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806967735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453916549683</t>
@@ -809,49 +809,49 @@
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065747261047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901215553284</t>
+    <t xml:space="preserve">2.34065771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901239395142</t>
   </si>
   <si>
     <t xml:space="preserve">2.34842133522034</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324526786804</t>
+    <t xml:space="preserve">2.34971499443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
     <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32642436027527</t>
+    <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219148635864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537105560303</t>
+    <t xml:space="preserve">2.29537153244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.29666495323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25396656990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24490904808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26043581962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784826278687</t>
+    <t xml:space="preserve">2.25396633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949286460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26043605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784802436829</t>
   </si>
   <si>
     <t xml:space="preserve">2.26172995567322</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">2.26690554618835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24361515045166</t>
+    <t xml:space="preserve">2.24361538887024</t>
   </si>
   <si>
     <t xml:space="preserve">2.2060923576355</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23197031021118</t>
+    <t xml:space="preserve">2.23197054862976</t>
   </si>
   <si>
     <t xml:space="preserve">2.24102759361267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32254314422607</t>
+    <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
     <t xml:space="preserve">2.31736731529236</t>
@@ -890,46 +890,46 @@
     <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407715797424</t>
+    <t xml:space="preserve">2.29407739639282</t>
   </si>
   <si>
     <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855062484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26431822776794</t>
+    <t xml:space="preserve">2.27855038642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2487907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278326034546</t>
+    <t xml:space="preserve">2.24879097938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278349876404</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33548212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28501987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631377220154</t>
+    <t xml:space="preserve">2.33548188209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747790336609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28502011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">2.27337503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26819920539856</t>
+    <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160042762756</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418822288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572247505188</t>
+    <t xml:space="preserve">2.33418798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3057222366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171101570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699743270874</t>
+    <t xml:space="preserve">2.37171077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699767112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.46745920181274</t>
@@ -965,40 +965,40 @@
     <t xml:space="preserve">2.44546294212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38723802566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241361618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34195137023926</t>
+    <t xml:space="preserve">2.47651648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3872377872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241337776184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34195160865784</t>
   </si>
   <si>
     <t xml:space="preserve">2.36524128913879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40793991088867</t>
+    <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.39370727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37688660621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38465023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31607341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
+    <t xml:space="preserve">2.37688636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36265397071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38464999198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
@@ -1007,64 +1007,64 @@
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3193085193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13492774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258102416992</t>
+    <t xml:space="preserve">2.37753319740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13492798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258078575134</t>
   </si>
   <si>
     <t xml:space="preserve">2.07346773147583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03788590431213</t>
+    <t xml:space="preserve">2.03788614273071</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993721961975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06699848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0508246421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818179130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966051101685</t>
+    <t xml:space="preserve">2.07993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551928520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198901176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06699824333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05082488059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818155288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966063022614</t>
   </si>
   <si>
     <t xml:space="preserve">2.0152428150177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494692802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04758977890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640670776367</t>
+    <t xml:space="preserve">2.02494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04759001731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640694618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
@@ -1073,28 +1073,28 @@
     <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07670283317566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522387504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10581541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06052923202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934592247009</t>
+    <t xml:space="preserve">2.07670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10581564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06052875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934616088867</t>
   </si>
   <si>
     <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14139747619629</t>
+    <t xml:space="preserve">2.14139723777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.11875438690186</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15433645248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19962310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28372597694397</t>
+    <t xml:space="preserve">2.15433621406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19962334632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460144996643</t>
+    <t xml:space="preserve">2.28460168838501</t>
   </si>
   <si>
     <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20958495140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18230628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.223224401474</t>
+    <t xml:space="preserve">2.20958471298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18230605125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322416305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.16866660118103</t>
@@ -1139,145 +1139,145 @@
     <t xml:space="preserve">2.1345682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12433838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10046982765198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08342051506042</t>
+    <t xml:space="preserve">2.12433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069941520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1004695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066534519196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01181364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05614161491394</t>
+    <t xml:space="preserve">1.96066570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0118134021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05614185333252</t>
   </si>
   <si>
     <t xml:space="preserve">2.04591178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227257728577</t>
+    <t xml:space="preserve">2.03227281570435</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08682990074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909206390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04250168800354</t>
+    <t xml:space="preserve">2.08001017570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909230232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0425021648407</t>
   </si>
   <si>
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09024000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
+    <t xml:space="preserve">2.09024024009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817395210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794400691986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089529037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748530864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384573936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725560188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771501541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043587684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361650943756</t>
+    <t xml:space="preserve">1.99817430973053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794436454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089540958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748518943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9538459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725572109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771489620209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504359960556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
   </si>
   <si>
     <t xml:space="preserve">2.14138770103455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14820742607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.185715675354</t>
+    <t xml:space="preserve">2.14820766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18571543693542</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801155090332</t>
+    <t xml:space="preserve">2.28801131248474</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2164044380188</t>
+    <t xml:space="preserve">2.23004364967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
     <t xml:space="preserve">2.17889595031738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13797807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410880088806</t>
+    <t xml:space="preserve">2.13797783851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410903930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296110153198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12774848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387969017029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209282875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13115859031677</t>
+    <t xml:space="preserve">2.1277482509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705996513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092852592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13115811347961</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.15502738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1516170501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16184711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637096405029</t>
+    <t xml:space="preserve">2.15161728858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16184687614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637072563171</t>
   </si>
   <si>
     <t xml:space="preserve">2.00499391555786</t>
@@ -1304,34 +1304,34 @@
     <t xml:space="preserve">2.05955123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315697669983</t>
+    <t xml:space="preserve">1.92315709590912</t>
   </si>
   <si>
     <t xml:space="preserve">1.98112463951111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98453438282013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0766007900238</t>
+    <t xml:space="preserve">1.98453485965729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07660055160522</t>
   </si>
   <si>
     <t xml:space="preserve">2.0936496257782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273175239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299433708191</t>
+    <t xml:space="preserve">2.07319045066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299481391907</t>
   </si>
   <si>
     <t xml:space="preserve">2.24027371406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19594550132751</t>
+    <t xml:space="preserve">2.19594526290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.17207622528076</t>
@@ -1340,67 +1340,67 @@
     <t xml:space="preserve">2.18912553787231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1925356388092</t>
+    <t xml:space="preserve">2.19253540039062</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686385154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391316413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29824090003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29483151435852</t>
+    <t xml:space="preserve">2.23686361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732254981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29824113845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
     <t xml:space="preserve">2.31529021263123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30165123939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30847024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961818695068</t>
+    <t xml:space="preserve">2.30165076255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30847072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961866378784</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892990112305</t>
+    <t xml:space="preserve">2.36643815040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892942428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32211017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32552003860474</t>
+    <t xml:space="preserve">2.32210993766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35279870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732578754425</t>
+    <t xml:space="preserve">2.35279893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37325811386108</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099595069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
+    <t xml:space="preserve">2.37666797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804478645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44827485084534</t>
+    <t xml:space="preserve">2.44827437400818</t>
   </si>
   <si>
     <t xml:space="preserve">2.46191382408142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942207336426</t>
+    <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
     <t xml:space="preserve">2.51306176185608</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">2.47896337509155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52670097351074</t>
+    <t xml:space="preserve">2.5267014503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60171794891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830808639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558674812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61535739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855242729187</t>
+    <t xml:space="preserve">2.60171818733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830832481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558722496033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6153576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855290412903</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541223526001</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56677103042603</t>
+    <t xml:space="preserve">2.56677079200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.58547925949097</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67153716087341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6939868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65657067298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908719062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160370826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405391693115</t>
+    <t xml:space="preserve">2.71269536018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67153692245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69398665428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65657043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908742904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160418510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
     <t xml:space="preserve">2.66031217575073</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">2.71643710136414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766208648682</t>
+    <t xml:space="preserve">2.72766184806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70521211624146</t>
+    <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
     <t xml:space="preserve">2.72017860412598</t>
@@ -1523,34 +1523,34 @@
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79126977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120299339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616971969604</t>
+    <t xml:space="preserve">2.74262857437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7912700176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.806236743927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868623733521</t>
+    <t xml:space="preserve">2.80623650550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984443664551</t>
+    <t xml:space="preserve">2.86984467506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338558197021</t>
@@ -1559,43 +1559,43 @@
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977765083313</t>
+    <t xml:space="preserve">2.89977741241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99331879615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01576900482178</t>
+    <t xml:space="preserve">2.99331903457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060192108154</t>
+    <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12053513526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
+    <t xml:space="preserve">3.10556817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12053489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046811103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169285774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801837921143</t>
+    <t xml:space="preserve">3.16169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801790237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
@@ -1607,16 +1607,16 @@
     <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0943431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0457022190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99706053733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583579063416</t>
+    <t xml:space="preserve">3.09434366226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04570198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
@@ -1625,40 +1625,40 @@
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
+    <t xml:space="preserve">2.91474413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
   </si>
   <si>
     <t xml:space="preserve">3.06815195083618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951050758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00454378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351939201355</t>
+    <t xml:space="preserve">3.01951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0045440196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351915359497</t>
   </si>
   <si>
     <t xml:space="preserve">2.97835230827332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98209404945374</t>
+    <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467759132385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841885566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086882591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964407920837</t>
+    <t xml:space="preserve">2.94841933250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964384078979</t>
   </si>
   <si>
     <t xml:space="preserve">2.84739446640015</t>
@@ -1667,13 +1667,13 @@
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.802494764328</t>
+    <t xml:space="preserve">2.80249500274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85113596916199</t>
+    <t xml:space="preserve">2.85113644599915</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365272521973</t>
@@ -1685,40 +1685,40 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89603590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596960067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726089477539</t>
+    <t xml:space="preserve">2.91848587989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89603567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596936225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004503250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76881980895996</t>
+    <t xml:space="preserve">2.79875326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76882004737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7613365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106942176819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00828552246094</t>
+    <t xml:space="preserve">2.76133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106966018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00828576087952</t>
   </si>
   <si>
     <t xml:space="preserve">3.0307354927063</t>
@@ -1727,10 +1727,10 @@
     <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96712732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481140136719</t>
+    <t xml:space="preserve">2.96712708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481116294861</t>
   </si>
   <si>
     <t xml:space="preserve">2.87358617782593</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487794876099</t>
+    <t xml:space="preserve">2.85487818717957</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
@@ -1751,13 +1751,13 @@
     <t xml:space="preserve">3.30761742591858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38619232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986680030823</t>
+    <t xml:space="preserve">3.38619208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986727714539</t>
   </si>
   <si>
     <t xml:space="preserve">3.36374187469482</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">3.42360830307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44980001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26645922660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24026775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530102729797</t>
+    <t xml:space="preserve">3.44980025291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664589881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2402675151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530126571655</t>
   </si>
   <si>
     <t xml:space="preserve">3.28142595291138</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924360275269</t>
+    <t xml:space="preserve">3.13924336433411</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0644097328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093561172485</t>
+    <t xml:space="preserve">3.06441020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093608856201</t>
   </si>
   <si>
     <t xml:space="preserve">3.11679315567017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08686017990112</t>
+    <t xml:space="preserve">3.08685994148254</t>
   </si>
   <si>
     <t xml:space="preserve">3.04944348335266</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">2.25621438026428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33853054046631</t>
+    <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968850135803</t>
@@ -1829,10 +1829,10 @@
     <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43581318855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942111968994</t>
+    <t xml:space="preserve">2.43581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
@@ -1841,37 +1841,37 @@
     <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46574664115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42832970619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812982559204</t>
+    <t xml:space="preserve">2.46574640274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4283299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213823318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465522766113</t>
+    <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839673042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41336345672607</t>
+    <t xml:space="preserve">2.39839649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4133632183075</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">2.40962171554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452165603638</t>
+    <t xml:space="preserve">2.4545214176178</t>
   </si>
   <si>
     <t xml:space="preserve">2.4694881439209</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">2.49193787574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935457229614</t>
+    <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">2.5069043636322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670400619507</t>
+    <t xml:space="preserve">2.59670424461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">3.27768445014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714436531067</t>
+    <t xml:space="preserve">3.34714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">3.10721969604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709010124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788802146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935307502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04822182655334</t>
+    <t xml:space="preserve">3.00102376937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788754463196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04822158813477</t>
   </si>
   <si>
     <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1229522228241</t>
+    <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182097434998</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">2.96955823898315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92235994338989</t>
+    <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.94202566146851</t>
@@ -1964,19 +1964,19 @@
     <t xml:space="preserve">2.97742462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94595885276794</t>
+    <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90269374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336207389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
+    <t xml:space="preserve">2.9026939868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
@@ -1985,31 +1985,31 @@
     <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469800949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896548271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863120079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109933853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456889152527</t>
+    <t xml:space="preserve">2.78469824790955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73750019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863167762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456912994385</t>
   </si>
   <si>
     <t xml:space="preserve">2.6352367401123</t>
@@ -2018,61 +2018,61 @@
     <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62737035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803868293762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60770463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6981680393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74143290519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72963333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68636846542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63917016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65490317344666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883612632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58410573005676</t>
+    <t xml:space="preserve">2.62737059593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58803844451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60770440101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69816780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74143314361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72963356971741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68636798858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63916993141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670250892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6549026966095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017230033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
     <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64703679084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343740463257</t>
+    <t xml:space="preserve">2.6470365524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983849525452</t>
+    <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096950531006</t>
@@ -2081,19 +2081,19 @@
     <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510762214661</t>
+    <t xml:space="preserve">2.52510738372803</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084038734436</t>
+    <t xml:space="preserve">2.54084014892578</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51330780982971</t>
+    <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
     <t xml:space="preserve">2.50150847434998</t>
@@ -2102,19 +2102,19 @@
     <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397637367249</t>
+    <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
     <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50937485694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52117443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49364233016968</t>
+    <t xml:space="preserve">2.50937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117419242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
     <t xml:space="preserve">2.46610999107361</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38351273536682</t>
+    <t xml:space="preserve">2.38351249694824</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39924550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564635276794</t>
+    <t xml:space="preserve">2.399245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564659118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35598015785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.35598063468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340247631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631443977356</t>
+    <t xml:space="preserve">2.34024786949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631467819214</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230591773987</t>
+    <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
     <t xml:space="preserve">2.61557102203369</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7571656703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503229141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71783399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390056610107</t>
+    <t xml:space="preserve">2.75716590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503205299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71783375740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
     <t xml:space="preserve">2.69030165672302</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.70603466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210123062134</t>
+    <t xml:space="preserve">2.70210099220276</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449332237244</t>
+    <t xml:space="preserve">2.91449356079102</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562480926514</t>
+    <t xml:space="preserve">2.96562504768372</t>
   </si>
   <si>
     <t xml:space="preserve">2.83976268768311</t>
@@ -2231,25 +2231,25 @@
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009673118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156226158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302755355835</t>
+    <t xml:space="preserve">2.82009696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156273841858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90662717819214</t>
+    <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89876055717468</t>
+    <t xml:space="preserve">2.89876079559326</t>
   </si>
   <si>
     <t xml:space="preserve">2.95775842666626</t>
@@ -2267,22 +2267,22 @@
     <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93022608757019</t>
+    <t xml:space="preserve">2.93022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462267875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035544395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888991355896</t>
+    <t xml:space="preserve">3.01675653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00889015197754</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349119186401</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855587005615</t>
+    <t xml:space="preserve">3.07575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0521547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855610847473</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002140045166</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04428863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148669242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12688565254211</t>
+    <t xml:space="preserve">3.04428839683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148716926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12688541412354</t>
   </si>
   <si>
     <t xml:space="preserve">3.10328650474548</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441799163818</t>
+    <t xml:space="preserve">3.19374966621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441823005676</t>
   </si>
   <si>
     <t xml:space="preserve">3.18981647491455</t>
@@ -2342,13 +2342,13 @@
     <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06287908554077</t>
+    <t xml:space="preserve">3.06287932395935</t>
   </si>
   <si>
     <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12839484214783</t>
+    <t xml:space="preserve">3.12839531898499</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01374197006226</t>
+    <t xml:space="preserve">3.01374220848083</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00555276870728</t>
+    <t xml:space="preserve">3.03421592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0178370475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
     <t xml:space="preserve">3.03831076622009</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">3.02602624893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05468940734863</t>
+    <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335280418396</t>
+    <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
     <t xml:space="preserve">3.07516360282898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98507857322693</t>
+    <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460461616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93594145774841</t>
+    <t xml:space="preserve">2.96460485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93594169616699</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9031834602356</t>
+    <t xml:space="preserve">2.90318369865417</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137313842773</t>
+    <t xml:space="preserve">2.91137290000916</t>
   </si>
   <si>
     <t xml:space="preserve">2.90727806091309</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585690498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8704252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91956257820129</t>
+    <t xml:space="preserve">2.84585666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87042570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91956281661987</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223578453064</t>
+    <t xml:space="preserve">2.86223554611206</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">2.77624607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78853011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80490946769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633062362671</t>
+    <t xml:space="preserve">2.78853034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80490922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.89499402046204</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">2.87452030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92775201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989173412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193140983582</t>
+    <t xml:space="preserve">2.92775225639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99736285209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98917365074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193164825439</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2489,25 +2489,25 @@
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869969367981</t>
+    <t xml:space="preserve">2.96869993209839</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184685707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680481910706</t>
+    <t xml:space="preserve">2.93184661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680458068848</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8130989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719374656677</t>
+    <t xml:space="preserve">2.81309866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.82128834724426</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995198249817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051025390625</t>
+    <t xml:space="preserve">2.84995174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357238769531</t>
+    <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176230430603</t>
+    <t xml:space="preserve">2.84176206588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8008143901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034090995789</t>
+    <t xml:space="preserve">2.80081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978240013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034067153931</t>
   </si>
   <si>
     <t xml:space="preserve">2.75986671447754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69435095787048</t>
+    <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.64521360397339</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7271089553833</t>
+    <t xml:space="preserve">2.76396155357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72710871696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897128105164</t>
+    <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83155298233032</t>
+    <t xml:space="preserve">2.83155274391174</t>
   </si>
   <si>
     <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84873986244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725620269775</t>
+    <t xml:space="preserve">2.84873962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725596427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717898368835</t>
+    <t xml:space="preserve">2.79717874526978</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86163020133972</t>
+    <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.90459752082825</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968322753906</t>
+    <t xml:space="preserve">2.65968346595764</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405698776245</t>
+    <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5350775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57804489135742</t>
+    <t xml:space="preserve">2.53507781028748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.578045129776</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47922015190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929713249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359415054321</t>
+    <t xml:space="preserve">2.47921991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929737091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359391212463</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.44914293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43195557594299</t>
+    <t xml:space="preserve">2.43195581436157</t>
   </si>
   <si>
     <t xml:space="preserve">2.4878134727478</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735015869141</t>
+    <t xml:space="preserve">2.30735039710999</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">2.33742737770081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28156995773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711874008179</t>
+    <t xml:space="preserve">2.28156971931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711850166321</t>
   </si>
   <si>
     <t xml:space="preserve">2.10540342330933</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">2.13118386268616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0624361038208</t>
+    <t xml:space="preserve">2.06243634223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829352378845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10110664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1225905418396</t>
+    <t xml:space="preserve">2.10110688209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12259030342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14407420158386</t>
+    <t xml:space="preserve">2.14407396316528</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399698257446</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197302818298</t>
+    <t xml:space="preserve">1.88197290897369</t>
   </si>
   <si>
     <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89056646823883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85619246959686</t>
+    <t xml:space="preserve">1.89056658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
     <t xml:space="preserve">1.81322503089905</t>
@@ -2834,28 +2834,28 @@
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6774480342865</t>
+    <t xml:space="preserve">1.67744791507721</t>
   </si>
   <si>
     <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6241682767868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65854227542877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.62416839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65854239463806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92494022846222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84330236911774</t>
+    <t xml:space="preserve">1.9249404668808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
     <t xml:space="preserve">1.96790778636932</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9593141078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0796229839325</t>
+    <t xml:space="preserve">1.95931434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07962322235107</t>
   </si>
   <si>
     <t xml:space="preserve">2.08821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524922370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102942466736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17844820022583</t>
+    <t xml:space="preserve">2.04524946212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17844796180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2128221988678</t>
+    <t xml:space="preserve">2.21282196044922</t>
   </si>
   <si>
     <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837098121643</t>
+    <t xml:space="preserve">2.19993162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673264503479</t>
+    <t xml:space="preserve">2.06673288345337</t>
   </si>
   <si>
     <t xml:space="preserve">2.09681010246277</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">2.23000884056091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28586673736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32024073600769</t>
+    <t xml:space="preserve">2.28586649894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32024049758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149273872375</t>
+    <t xml:space="preserve">2.25149250030518</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2428994178772</t>
+    <t xml:space="preserve">2.27297639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41047239303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070381164551</t>
+    <t xml:space="preserve">2.41047215461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062659263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070405006409</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -68906,7 +68906,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6493634259</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>79309</v>
@@ -68927,6 +68927,32 @@
         <v>1244</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6493402778</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>74831</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>3.13499999046326</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>3.13499999046326</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977395057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2682341337204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26938807964325</t>
+    <t xml:space="preserve">1.27977406978607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26823425292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26938819885254</t>
   </si>
   <si>
     <t xml:space="preserve">1.25554025173187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24861621856689</t>
+    <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515804767609</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">1.24977016448975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23246026039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437885284424</t>
+    <t xml:space="preserve">1.23246049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.19784069061279</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283879756927</t>
+    <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
@@ -86,115 +86,115 @@
     <t xml:space="preserve">1.25438630580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
+    <t xml:space="preserve">1.24746227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285015583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746617794037</t>
   </si>
   <si>
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591843128204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822656154633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130631446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899842262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476850986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29016005992889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669786453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900587558746</t>
+    <t xml:space="preserve">1.20591878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053493022919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2082267999649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130667209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2347686290741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2370765209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669798374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900575637817</t>
   </si>
   <si>
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28439009189606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323578834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054581165314</t>
+    <t xml:space="preserve">1.28438997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169597148895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054569244385</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862367153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093192100525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208562850952</t>
+    <t xml:space="preserve">1.31093180179596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477974891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247173786163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208550930023</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593369483948</t>
+    <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
     <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32016348838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362568378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708764076233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824170589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132110118866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439742565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670519828796</t>
+    <t xml:space="preserve">1.32016384601593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323981285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824146747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501672744751</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">1.35478329658508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36170732975006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208953380585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34324336051941</t>
+    <t xml:space="preserve">1.36170709133148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3432434797287</t>
   </si>
   <si>
     <t xml:space="preserve">1.3455513715744</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37324726581573</t>
+    <t xml:space="preserve">1.37324714660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.38017094135284</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36747705936432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286103725433</t>
+    <t xml:space="preserve">1.36747717857361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286127567291</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251530170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701971530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427239894867</t>
+    <t xml:space="preserve">1.39251518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621198177338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099965572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701983451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332303524017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427251815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550454616547</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">1.45043396949768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536303520203</t>
+    <t xml:space="preserve">1.45536315441132</t>
   </si>
   <si>
     <t xml:space="preserve">1.46275699138641</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5182112455368</t>
+    <t xml:space="preserve">1.51821100711823</t>
   </si>
   <si>
     <t xml:space="preserve">1.54162502288818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574659347534</t>
+    <t xml:space="preserve">1.50465571880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574647426605</t>
   </si>
   <si>
     <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5403927564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433148384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707927703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52437281608582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5465544462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190804481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257462501526</t>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60816991329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707939624786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52437269687653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641281604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077607631683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190816402435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
   </si>
   <si>
     <t xml:space="preserve">1.5958468914032</t>
@@ -335,10 +335,10 @@
     <t xml:space="preserve">1.65006864070892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59461462497711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883649349213</t>
+    <t xml:space="preserve">1.5946147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883661270142</t>
   </si>
   <si>
     <t xml:space="preserve">1.65992748737335</t>
@@ -347,49 +347,49 @@
     <t xml:space="preserve">1.66115963459015</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71661376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523975372314</t>
+    <t xml:space="preserve">1.71661400794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400784492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950307369232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827068805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72524011135101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429050922394</t>
+    <t xml:space="preserve">1.70429074764252</t>
   </si>
   <si>
     <t xml:space="preserve">1.70059359073639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851261615753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301750659943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439092636108</t>
+    <t xml:space="preserve">1.70675528049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784639358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851237773895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439104557037</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206778526306</t>
@@ -398,91 +398,91 @@
     <t xml:space="preserve">1.74988627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7486537694931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618923664093</t>
+    <t xml:space="preserve">1.74865412712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618947505951</t>
   </si>
   <si>
     <t xml:space="preserve">1.7683709859848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220941543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7769969701767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344215869904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746295452118</t>
+    <t xml:space="preserve">1.7745326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220953464508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344192028046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855359077454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74249243736267</t>
+    <t xml:space="preserve">1.74249231815338</t>
   </si>
   <si>
     <t xml:space="preserve">1.69443213939667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61186718940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6315838098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
+    <t xml:space="preserve">1.61186695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158404827118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447323322296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679625511169</t>
   </si>
   <si>
     <t xml:space="preserve">1.6426750421524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376591682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281643390656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309921741486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556398868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802875995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021027088165</t>
+    <t xml:space="preserve">1.65376567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049329280853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281655311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309933662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556386947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65130114555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623009204865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513945579529</t>
+    <t xml:space="preserve">1.65130126476288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623033046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513969421387</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144277572632</t>
@@ -491,166 +491,166 @@
     <t xml:space="preserve">1.63404858112335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59091782569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546345233917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356472492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4997261762619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247420787811</t>
+    <t xml:space="preserve">1.59091770648956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546369075775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479711055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972641468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247373104095</t>
   </si>
   <si>
     <t xml:space="preserve">1.55887746810913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58845317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423130512238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4972620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51451420783997</t>
+    <t xml:space="preserve">1.5884530544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5342310667038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726176261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51451408863068</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532194137573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120060920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598828315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105933666229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338247776031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651347160339</t>
+    <t xml:space="preserve">1.57120048999786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598816394806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105897903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338223934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722078800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
     <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499794483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594730854034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225062847137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841219902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073522090912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978585720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717945575714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703806400299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552277565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538150310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457365036011</t>
+    <t xml:space="preserve">1.65499806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225050926208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6784120798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717957496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703830242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552265644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538138389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291661262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457353115082</t>
   </si>
   <si>
     <t xml:space="preserve">1.76467418670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75728023052216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125993251801</t>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126005172729</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016929626465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77330005168915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946186065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742162227631</t>
+    <t xml:space="preserve">1.77330029010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946197986603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74742186069489</t>
   </si>
   <si>
     <t xml:space="preserve">1.7806943655014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178512096405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590645313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766355037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150221824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614861965179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8669558763504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297629356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89899659156799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762269496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392553806305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459199905396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92980420589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9827938079834</t>
+    <t xml:space="preserve">1.79178500175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590621471405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695635318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8989964723587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762233734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392565727234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459176063538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279345035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.02838945388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04687404632568</t>
+    <t xml:space="preserve">2.0468738079071</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483345031738</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05796504020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303573608398</t>
+    <t xml:space="preserve">2.05796456336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303549766541</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905555725098</t>
@@ -686,49 +686,49 @@
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806533813477</t>
+    <t xml:space="preserve">2.13806557655334</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024661064148</t>
+    <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17256999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15655016899109</t>
+    <t xml:space="preserve">2.17257022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531754493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
+    <t xml:space="preserve">2.17380213737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010569572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640830039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
     <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816539764404</t>
+    <t xml:space="preserve">2.17996406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
     <t xml:space="preserve">2.20953965187073</t>
@@ -740,49 +740,49 @@
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978157997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717565536499</t>
+    <t xml:space="preserve">2.27978134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
   </si>
   <si>
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877156257629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583282470703</t>
+    <t xml:space="preserve">2.35877227783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583258628845</t>
   </si>
   <si>
     <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477975845337</t>
+    <t xml:space="preserve">2.31477928161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019546508789</t>
+    <t xml:space="preserve">2.25137877464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019522666931</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973345756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313420295715</t>
+    <t xml:space="preserve">2.23973369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3367760181427</t>
+    <t xml:space="preserve">2.33677554130554</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806967735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34453916549683</t>
+    <t xml:space="preserve">2.30054640769958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
     <t xml:space="preserve">2.3613600730896</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971499443054</t>
+    <t xml:space="preserve">2.34065747261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901263237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4053521156311</t>
+    <t xml:space="preserve">2.40535235404968</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31219148635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29537153244019</t>
+    <t xml:space="preserve">2.3121919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">2.29666495323181</t>
@@ -851,43 +851,43 @@
     <t xml:space="preserve">2.26043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784802436829</t>
+    <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690554618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361538887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2060923576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703507423401</t>
+    <t xml:space="preserve">2.26690530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20609211921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703483581543</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23197054862976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102759361267</t>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31736731529236</t>
+    <t xml:space="preserve">2.31736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31348562240601</t>
+    <t xml:space="preserve">2.31348586082458</t>
   </si>
   <si>
     <t xml:space="preserve">2.29407739639282</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855038642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26431775093079</t>
+    <t xml:space="preserve">2.27855062484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26431751251221</t>
   </si>
   <si>
     <t xml:space="preserve">2.28890180587769</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">2.24879097938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33548188209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747790336609</t>
+    <t xml:space="preserve">2.33548164367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747814178467</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
@@ -926,40 +926,40 @@
     <t xml:space="preserve">2.28631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27337503433228</t>
+    <t xml:space="preserve">2.2733747959137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33160042762756</t>
+    <t xml:space="preserve">2.33160018920898</t>
   </si>
   <si>
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3057222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359644889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171077728271</t>
+    <t xml:space="preserve">2.33418822288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30572199821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
+    <t xml:space="preserve">2.41699719429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745944023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546294212341</t>
@@ -968,34 +968,34 @@
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3872377872467</t>
+    <t xml:space="preserve">2.38723754882812</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34195160865784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524128913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40794014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.34195113182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524176597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40793991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39370703697205</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688636779785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36265397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464999198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
+    <t xml:space="preserve">2.36265349388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38465023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607365608215</t>
   </si>
   <si>
     <t xml:space="preserve">2.36459445953369</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753319740295</t>
+    <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
@@ -1019,73 +1019,73 @@
     <t xml:space="preserve">2.04435563087463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788614273071</t>
+    <t xml:space="preserve">2.10258102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346796989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551928520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198901176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06699824333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05082488059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966063022614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0152428150177</t>
+    <t xml:space="preserve">2.07993721961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06699848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966039180756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524233818054</t>
   </si>
   <si>
     <t xml:space="preserve">2.02494716644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04759001731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0411205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07023334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670259475708</t>
+    <t xml:space="preserve">2.0475902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04112076759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07023310661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670307159424</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10581564903259</t>
+    <t xml:space="preserve">2.10581517219543</t>
   </si>
   <si>
     <t xml:space="preserve">2.06052875518799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06376361846924</t>
+    <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934616088867</t>
@@ -1094,25 +1094,25 @@
     <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14139723777771</t>
+    <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
     <t xml:space="preserve">2.11875438690186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12845826148987</t>
+    <t xml:space="preserve">2.12845873832703</t>
   </si>
   <si>
     <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15433621406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19962334632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28372621536255</t>
+    <t xml:space="preserve">2.15433645248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19962286949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
     <t xml:space="preserve">2.26755261421204</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20958471298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18230605125427</t>
+    <t xml:space="preserve">2.20958495140076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18230581283569</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322416305542</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">2.16866660118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433862686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751866340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069941520691</t>
+    <t xml:space="preserve">2.13456797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069893836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.1004695892334</t>
@@ -1157,58 +1157,58 @@
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066570281982</t>
+    <t xml:space="preserve">1.96066558361053</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227281570435</t>
+    <t xml:space="preserve">2.05614161491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591202735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001017570496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08683013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886271476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909230232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0425021648407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99135434627533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09024024009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0697808265686</t>
+    <t xml:space="preserve">2.08001041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08682990074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04250168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99135410785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09023976325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06978106498718</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817430973053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794436454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089540958405</t>
+    <t xml:space="preserve">1.99817419052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794400691986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089517116547</t>
   </si>
   <si>
     <t xml:space="preserve">1.96748518943787</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">1.95725572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97771489620209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504359960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361627101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
+    <t xml:space="preserve">1.97771465778351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043611526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361650943756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18571543693542</t>
+    <t xml:space="preserve">2.18571591377258</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801131248474</t>
+    <t xml:space="preserve">2.28801155090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17889595031738</t>
+    <t xml:space="preserve">2.17889642715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797783851624</t>
@@ -1262,13 +1262,13 @@
     <t xml:space="preserve">2.11410903930664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06296110153198</t>
+    <t xml:space="preserve">2.06296133995056</t>
   </si>
   <si>
     <t xml:space="preserve">2.1277482509613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09705996513367</t>
+    <t xml:space="preserve">2.09705924987793</t>
   </si>
   <si>
     <t xml:space="preserve">2.10387945175171</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115811347961</t>
+    <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
@@ -1289,10 +1289,10 @@
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637072563171</t>
+    <t xml:space="preserve">2.16184735298157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637120246887</t>
   </si>
   <si>
     <t xml:space="preserve">2.00499391555786</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05955123901367</t>
+    <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
     <t xml:space="preserve">1.92315709590912</t>
@@ -1310,37 +1310,37 @@
     <t xml:space="preserve">1.98112463951111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98453485965729</t>
+    <t xml:space="preserve">1.984534740448</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0936496257782</t>
+    <t xml:space="preserve">2.09364986419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319045066833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299481391907</t>
+    <t xml:space="preserve">2.05273199081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.24027371406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253540039062</t>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345375061035</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732254981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506110191345</t>
+    <t xml:space="preserve">2.25391268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732278823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824113845825</t>
@@ -1370,58 +1370,58 @@
     <t xml:space="preserve">2.30165076255798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30847072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961866378784</t>
+    <t xml:space="preserve">2.3084704875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961842536926</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
+    <t xml:space="preserve">2.36643838882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892966270447</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32210993766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551980018616</t>
+    <t xml:space="preserve">2.32211017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32551956176758</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35279893875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37325811386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39712691307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38689732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804478645325</t>
+    <t xml:space="preserve">2.35279870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3732578754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39712715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38689708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099595069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804502487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122529983521</t>
+    <t xml:space="preserve">2.43122553825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827437400818</t>
@@ -1439,34 +1439,34 @@
     <t xml:space="preserve">2.48919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47896337509155</t>
+    <t xml:space="preserve">2.47896361351013</t>
   </si>
   <si>
     <t xml:space="preserve">2.5267014503479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54034066200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171818733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830832481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558722496033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6153576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855290412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61541223526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61167073249817</t>
+    <t xml:space="preserve">2.54034090042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830808639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558674812317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61535716056824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61541247367859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61167097091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.56677079200745</t>
@@ -1475,34 +1475,34 @@
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928778648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63037896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71269536018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67153692245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69398665428162</t>
+    <t xml:space="preserve">2.55928754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63037919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67153716087341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
     <t xml:space="preserve">2.65657043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64908742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160418510437</t>
+    <t xml:space="preserve">2.64908695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160394668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031217575073</t>
+    <t xml:space="preserve">2.66031241416931</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643710136414</t>
@@ -1511,31 +1511,31 @@
     <t xml:space="preserve">2.72766184806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69772863388062</t>
+    <t xml:space="preserve">2.69772839546204</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72017860412598</t>
+    <t xml:space="preserve">2.72017884254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262857437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7912700176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616948127747</t>
+    <t xml:space="preserve">2.74262833595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861921310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79126977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
@@ -1544,49 +1544,49 @@
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868647575378</t>
+    <t xml:space="preserve">2.82868599891663</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984467506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96338558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92971086502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89977741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719410896301</t>
+    <t xml:space="preserve">2.86984443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96338534355164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92971110343933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89977765083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719387054443</t>
   </si>
   <si>
     <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">3.01576900482178</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060168266296</t>
+    <t xml:space="preserve">3.09060215950012</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556817054749</t>
+    <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046811103821</t>
+    <t xml:space="preserve">3.15046834945679</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
@@ -1595,31 +1595,31 @@
     <t xml:space="preserve">3.16169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12801790237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06066870689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07937669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10931015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434366226196</t>
+    <t xml:space="preserve">3.12801837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06066846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07937693595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10930991172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434342384338</t>
   </si>
   <si>
     <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583555221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9746105670929</t>
+    <t xml:space="preserve">2.99706053733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583579063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97461032867432</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">3.07189345359802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06815195083618</t>
+    <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0045440196991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351915359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835230827332</t>
+    <t xml:space="preserve">3.00454378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835254669189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98209381103516</t>
@@ -1652,28 +1652,28 @@
     <t xml:space="preserve">2.94467759132385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841933250427</t>
+    <t xml:space="preserve">2.94841885566711</t>
   </si>
   <si>
     <t xml:space="preserve">2.97086906433105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95964384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739446640015</t>
+    <t xml:space="preserve">2.95964431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80249500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113644599915</t>
+    <t xml:space="preserve">2.80249428749084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991169929504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365272521973</t>
@@ -1685,19 +1685,19 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848587989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89603567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229440689087</t>
+    <t xml:space="preserve">2.91848611831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89603590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229464530945</t>
   </si>
   <si>
     <t xml:space="preserve">2.79875326156616</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106966018677</t>
+    <t xml:space="preserve">2.7613365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828576087952</t>
@@ -1724,25 +1724,25 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590233802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481116294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78378653526306</t>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78378677368164</t>
   </si>
   <si>
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487818717957</t>
+    <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">3.30761742591858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38619208335876</t>
+    <t xml:space="preserve">3.38619184494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.32632565498352</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">3.41986727714539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36374187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980025291443</t>
+    <t xml:space="preserve">3.3637421131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980001449585</t>
   </si>
   <si>
     <t xml:space="preserve">3.35625886917114</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">3.2402675151825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28142595291138</t>
+    <t xml:space="preserve">3.22530102729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2814257144928</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29639267921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924336433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06441020965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093608856201</t>
+    <t xml:space="preserve">3.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924360275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06441044807434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.11679315567017</t>
@@ -1814,40 +1814,40 @@
     <t xml:space="preserve">2.57425451278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545665740967</t>
+    <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
     <t xml:space="preserve">2.25621438026428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33853030204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37968850135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091324806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942135810852</t>
+    <t xml:space="preserve">2.33853054046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37968873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581318855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438784599304</t>
+    <t xml:space="preserve">2.51438760757446</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574640274048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4283299446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213823318481</t>
+    <t xml:space="preserve">2.42833018302917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213871002197</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812958717346</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">2.39839649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41710472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458820343018</t>
+    <t xml:space="preserve">2.41710495948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458844184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133632183075</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962171554565</t>
+    <t xml:space="preserve">2.40962147712708</t>
   </si>
   <si>
     <t xml:space="preserve">2.4545214176178</t>
@@ -1889,61 +1889,61 @@
     <t xml:space="preserve">2.5218710899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49193787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935481071472</t>
+    <t xml:space="preserve">2.49193811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935433387756</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5069043636322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670424461365</t>
+    <t xml:space="preserve">2.50690460205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670448303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265093803406</t>
+    <t xml:space="preserve">3.15795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265069961548</t>
   </si>
   <si>
     <t xml:space="preserve">3.27768445014954</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714412689209</t>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102376937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709057807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788754463196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04822158813477</t>
+    <t xml:space="preserve">3.1072199344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00102353096008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709010124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788778305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935307502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04822182655334</t>
   </si>
   <si>
     <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12295246124268</t>
+    <t xml:space="preserve">3.12295269966125</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182097434998</t>
@@ -1952,40 +1952,40 @@
     <t xml:space="preserve">2.96955823898315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92235970497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94202566146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989228248596</t>
+    <t xml:space="preserve">2.92235994338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94202542304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94595909118652</t>
+    <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8082971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78076505661011</t>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80829739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78076481819153</t>
   </si>
   <si>
     <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469824790955</t>
+    <t xml:space="preserve">2.78469777107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.76896524429321</t>
@@ -1994,40 +1994,40 @@
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73750019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863167762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
+    <t xml:space="preserve">2.73749995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276884078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109910011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63523697853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770440101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69816780090332</t>
+    <t xml:space="preserve">2.60770463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
     <t xml:space="preserve">2.74143314361572</t>
@@ -2036,22 +2036,22 @@
     <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68636798858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68243503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63916993141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670250892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6549026966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883636474609</t>
+    <t xml:space="preserve">2.686368227005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68243527412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6391704082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65490293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883612632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">2.6470365524292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62343716621399</t>
+    <t xml:space="preserve">2.62343740463257</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
@@ -2075,19 +2075,19 @@
     <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65096950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75323271751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510738372803</t>
+    <t xml:space="preserve">2.65096974372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75323247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510762214661</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084014892578</t>
+    <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970890045166</t>
@@ -2111,49 +2111,49 @@
     <t xml:space="preserve">2.50937461853027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117419242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4936420917511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610999107361</t>
+    <t xml:space="preserve">2.52117443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49364233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610951423645</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40317893028259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38351249694824</t>
+    <t xml:space="preserve">2.40317869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564659118652</t>
+    <t xml:space="preserve">2.39924550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35598063468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31271553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024786949158</t>
+    <t xml:space="preserve">2.35598039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531254768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698252677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631467819214</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.73356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503205299377</t>
+    <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
     <t xml:space="preserve">2.71783375740051</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70603466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210099220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482736587524</t>
+    <t xml:space="preserve">2.70603442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210123062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482760429382</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85942888259888</t>
+    <t xml:space="preserve">2.8594286441803</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2207,37 +2207,37 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92629289627075</t>
+    <t xml:space="preserve">2.91449332237244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92629313468933</t>
   </si>
   <si>
     <t xml:space="preserve">3.02068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562504768372</t>
+    <t xml:space="preserve">2.9616916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.83976268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189630508423</t>
+    <t xml:space="preserve">2.83189654350281</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302803039551</t>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
+    <t xml:space="preserve">2.91056036949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89876055717468</t>
   </si>
   <si>
     <t xml:space="preserve">2.95775842666626</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">2.9538254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516140937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796311378479</t>
+    <t xml:space="preserve">2.87516117095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
     <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93022632598877</t>
+    <t xml:space="preserve">2.93022608757019</t>
   </si>
   <si>
     <t xml:space="preserve">3.00495672225952</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">3.02462291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04035568237305</t>
+    <t xml:space="preserve">3.04035520553589</t>
   </si>
   <si>
     <t xml:space="preserve">3.00889015197754</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922371864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98529076576233</t>
+    <t xml:space="preserve">2.98922395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98529100418091</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575440406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0521547794342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855610847473</t>
+    <t xml:space="preserve">3.05215501785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09542012214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04428839683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148716926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12688541412354</t>
+    <t xml:space="preserve">3.09541988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04428863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148693084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
     <t xml:space="preserve">3.10328650474548</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374966621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441823005676</t>
+    <t xml:space="preserve">3.19374990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
     <t xml:space="preserve">3.18981647491455</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382676124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06287932395935</t>
+    <t xml:space="preserve">3.10382652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06287884712219</t>
   </si>
   <si>
     <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12839531898499</t>
+    <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2369,28 +2369,28 @@
     <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0178370475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0055525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468964576721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04649996757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08335304260254</t>
+    <t xml:space="preserve">3.03421568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602601051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04650020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">3.07516360282898</t>
@@ -2399,46 +2399,46 @@
     <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99326825141907</t>
+    <t xml:space="preserve">2.99326801300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93594169616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94822573661804</t>
+    <t xml:space="preserve">2.93594145774841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94822597503662</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318369865417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89908862113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137290000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.89908838272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585666656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87042570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91956281661987</t>
+    <t xml:space="preserve">2.84585690498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87042546272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223554611206</t>
+    <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">2.77624607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78853034973145</t>
+    <t xml:space="preserve">2.78853011131287</t>
   </si>
   <si>
     <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86633086204529</t>
+    <t xml:space="preserve">2.86633062362671</t>
   </si>
   <si>
     <t xml:space="preserve">2.89499402046204</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87861514091492</t>
+    <t xml:space="preserve">2.87861490249634</t>
   </si>
   <si>
     <t xml:space="preserve">2.87452030181885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92775225639343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99736285209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98917365074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">2.92775201797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99736309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869993209839</t>
+    <t xml:space="preserve">2.96869969367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680458068848</t>
+    <t xml:space="preserve">2.93184685707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680481910706</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309866905212</t>
+    <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357286453247</t>
+    <t xml:space="preserve">2.83357238769531</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215123176575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84176206588745</t>
+    <t xml:space="preserve">2.77215099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766746520996</t>
+    <t xml:space="preserve">2.83766722679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.80081462860107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66978240013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034067153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986671447754</t>
+    <t xml:space="preserve">2.66978216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034090995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.64521360397339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67387723922729</t>
+    <t xml:space="preserve">2.67387700080872</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396155357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72710871696472</t>
+    <t xml:space="preserve">2.76396179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7271089553833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897151947021</t>
+    <t xml:space="preserve">2.93897128105164</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83155274391174</t>
+    <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
     <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84873962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725596427917</t>
+    <t xml:space="preserve">2.84873986244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725620269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717874526978</t>
+    <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86162996292114</t>
+    <t xml:space="preserve">2.86163020133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.90459752082825</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405722618103</t>
+    <t xml:space="preserve">2.69405698776245</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53507781028748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.578045129776</t>
+    <t xml:space="preserve">2.5350775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929737091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359391212463</t>
+    <t xml:space="preserve">2.47922015190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929713249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.44914293289185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43195581436157</t>
+    <t xml:space="preserve">2.43195557594299</t>
   </si>
   <si>
     <t xml:space="preserve">2.4878134727478</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">2.33742737770081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28156971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711850166321</t>
+    <t xml:space="preserve">2.28156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10540342330933</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">2.13118386268616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06243634223938</t>
+    <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829352378845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10110688209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.10110664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14407396316528</t>
+    <t xml:space="preserve">2.14407420158386</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399698257446</t>
@@ -2807,16 +2807,16 @@
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197290897369</t>
+    <t xml:space="preserve">1.88197302818298</t>
   </si>
   <si>
     <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89056658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85619258880615</t>
+    <t xml:space="preserve">1.89056646823883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85619246959686</t>
   </si>
   <si>
     <t xml:space="preserve">1.81322503089905</t>
@@ -2834,28 +2834,28 @@
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67744791507721</t>
+    <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
     <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62416839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65854239463806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.6241682767868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65854227542877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84330224990845</t>
+    <t xml:space="preserve">1.92494022846222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84330236911774</t>
   </si>
   <si>
     <t xml:space="preserve">1.96790778636932</t>
@@ -2876,22 +2876,22 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95931434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07962322235107</t>
+    <t xml:space="preserve">1.9593141078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0796229839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.08821678161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524946212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17844796180725</t>
+    <t xml:space="preserve">2.04524922370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102942466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
@@ -2909,25 +2909,25 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21282196044922</t>
+    <t xml:space="preserve">2.2128221988678</t>
   </si>
   <si>
     <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
+    <t xml:space="preserve">2.06673264503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.09681010246277</t>
@@ -2945,10 +2945,10 @@
     <t xml:space="preserve">2.23000884056091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28586649894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.28586673736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149250030518</t>
+    <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24289917945862</t>
+    <t xml:space="preserve">2.27297616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2428994178772</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41047215461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062659263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070405006409</t>
+    <t xml:space="preserve">2.41047239303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -68932,7 +68932,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493402778</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>74831</v>
@@ -68953,6 +68953,32 @@
         <v>1242</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6493518519</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>67806</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>3.10500001907349</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26823425292969</t>
+    <t xml:space="preserve">1.27977395057678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2682341337204</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938819885254</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">1.27515804767609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246049880981</t>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
     <t xml:space="preserve">1.19437873363495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975904464722</t>
+    <t xml:space="preserve">1.19784080982208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975892543793</t>
   </si>
   <si>
     <t xml:space="preserve">1.18283891677856</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438630580902</t>
+    <t xml:space="preserve">1.25438618659973</t>
   </si>
   <si>
     <t xml:space="preserve">1.24746227264404</t>
@@ -92,76 +92,76 @@
     <t xml:space="preserve">1.27285015583038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27746617794037</t>
+    <t xml:space="preserve">1.27746605873108</t>
   </si>
   <si>
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168863773346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053493022919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130667209625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2347686290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2370765209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2901599407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669798374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208196163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28438997268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169597148895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054569244385</t>
+    <t xml:space="preserve">1.20591866970062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168875694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207072257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130643367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899842262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707640171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29016005992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669774532318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900587558746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208184242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28439009189606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169620990753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862367153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093180179596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477974891663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247173786163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208550930023</t>
+    <t xml:space="preserve">1.31093192100525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247149944305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208574771881</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746972560883</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016384601593</t>
+    <t xml:space="preserve">1.30516183376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016372680664</t>
   </si>
   <si>
     <t xml:space="preserve">1.3236255645752</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">1.32708752155304</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31323981285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439730644226</t>
+    <t xml:space="preserve">1.31323945522308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132133960724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439754486084</t>
   </si>
   <si>
     <t xml:space="preserve">1.34670543670654</t>
@@ -200,55 +200,55 @@
     <t xml:space="preserve">1.3501672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478329658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170709133148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208941459656</t>
+    <t xml:space="preserve">1.35478353500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208917617798</t>
   </si>
   <si>
     <t xml:space="preserve">1.3432434797287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3455513715744</t>
+    <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
     <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37324714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017094135284</t>
+    <t xml:space="preserve">1.37324726581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017106056213</t>
   </si>
   <si>
     <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36747717857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286127567291</t>
+    <t xml:space="preserve">1.36747694015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621198177338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099965572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332303524017</t>
+    <t xml:space="preserve">1.39251530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621222019196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
   </si>
   <si>
     <t xml:space="preserve">1.43687856197357</t>
@@ -260,43 +260,43 @@
     <t xml:space="preserve">1.44550454616547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043396949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46275699138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110043048859</t>
+    <t xml:space="preserve">1.45043408870697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">1.48863554000854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50342345237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821100711823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162502288818</t>
+    <t xml:space="preserve">1.50342321395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821112632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162526130676</t>
   </si>
   <si>
     <t xml:space="preserve">1.50465571880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51574647426605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60816991329193</t>
+    <t xml:space="preserve">1.51574683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849390983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5403927564621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.61433172225952</t>
@@ -308,34 +308,34 @@
     <t xml:space="preserve">1.52437269687653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641281604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077607631683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655432701111</t>
+    <t xml:space="preserve">1.50958490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077631473541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655456542969</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190816402435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56257450580597</t>
+    <t xml:space="preserve">1.56257438659668</t>
   </si>
   <si>
     <t xml:space="preserve">1.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6636244058609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006864070892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
+    <t xml:space="preserve">1.66362416744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500688791275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461462497711</t>
   </si>
   <si>
     <t xml:space="preserve">1.64883661270142</t>
@@ -344,121 +344,121 @@
     <t xml:space="preserve">1.65992748737335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66115963459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661400794983</t>
+    <t xml:space="preserve">1.66115975379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661388874054</t>
   </si>
   <si>
     <t xml:space="preserve">1.72154295444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72400784492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950307369232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827068805695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72524011135101</t>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950295448303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523999214172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429074764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059359073639</t>
+    <t xml:space="preserve">1.70429050922394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059394836426</t>
   </si>
   <si>
     <t xml:space="preserve">1.70675528049469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71784639358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851237773895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604772567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439104557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206778526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865412712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618947505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7683709859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7745326757431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220953464508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344192028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6574627161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855359077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249231815338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443213939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158404827118</t>
+    <t xml:space="preserve">1.71784591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301714897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604808330536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206790447235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865400791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837074756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453255653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220917701721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344168186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855335235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249243736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186707019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158428668976</t>
   </si>
   <si>
     <t xml:space="preserve">1.60447323322296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63035154342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679625511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6426750421524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049329280853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309933662415</t>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679637432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267480373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376591682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049353122711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309945583344</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556386947632</t>
@@ -470,73 +470,73 @@
     <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64760434627533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130126476288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623033046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091770648956</t>
+    <t xml:space="preserve">1.64760422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130114555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6562305688858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513981342316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144265651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091782569885</t>
   </si>
   <si>
     <t xml:space="preserve">1.53546369075775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49356496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479711055756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972641468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247373104095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887746810913</t>
+    <t xml:space="preserve">1.49356472492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479746818542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247396945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887758731842</t>
   </si>
   <si>
     <t xml:space="preserve">1.5884530544281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56503915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5342310667038</t>
+    <t xml:space="preserve">1.56503903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423118591309</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532194137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120048999786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598816394806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105897903442</t>
+    <t xml:space="preserve">1.51451432704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532206058502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120084762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
@@ -545,106 +545,106 @@
     <t xml:space="preserve">1.59338223934174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58722078800201</t>
+    <t xml:space="preserve">1.5872209072113</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6648565530777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499806404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6784120798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073510169983</t>
+    <t xml:space="preserve">1.66485619544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594742774963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225074768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841184139252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073522090912</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978573799133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717957496643</t>
+    <t xml:space="preserve">1.67717969417572</t>
   </si>
   <si>
     <t xml:space="preserve">1.68703830242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70552265644073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291661262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457353115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467418670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
+    <t xml:space="preserve">1.70552289485931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6845737695694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75727999210358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016941547394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330005168915</t>
   </si>
   <si>
     <t xml:space="preserve">1.77946197986603</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74742186069489</t>
+    <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
     <t xml:space="preserve">1.7806943655014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150197982788</t>
+    <t xml:space="preserve">1.79178512096405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590645313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
   </si>
   <si>
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695635318756</t>
+    <t xml:space="preserve">1.86695623397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762233734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392565727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459176063538</t>
+    <t xml:space="preserve">1.89899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392553806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459164142609</t>
   </si>
   <si>
     <t xml:space="preserve">1.92980408668518</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0468738079071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729846000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796456336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303549766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905555725098</t>
+    <t xml:space="preserve">2.02838921546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687428474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0690553188324</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806557655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669132232666</t>
+    <t xml:space="preserve">2.13806509971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669156074524</t>
   </si>
   <si>
     <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16887307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17257022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15654993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380213737488</t>
+    <t xml:space="preserve">2.16887283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17256999015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15655016899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119645118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380285263062</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010569572449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531778335571</t>
+    <t xml:space="preserve">2.15531754493713</t>
   </si>
   <si>
     <t xml:space="preserve">2.16640830039978</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996406555176</t>
+    <t xml:space="preserve">2.17996382713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953965187073</t>
+    <t xml:space="preserve">2.20953917503357</t>
   </si>
   <si>
     <t xml:space="preserve">2.21323657035828</t>
@@ -743,37 +743,37 @@
     <t xml:space="preserve">2.27978134155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28717517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3303062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877227783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583258628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289408683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137877464294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019522666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973369598389</t>
+    <t xml:space="preserve">2.28717541694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33030652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583306312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477975845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526070594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019594192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973345756531</t>
   </si>
   <si>
     <t xml:space="preserve">2.30313467979431</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33677554130554</t>
+    <t xml:space="preserve">2.3367760181427</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054640769958</t>
+    <t xml:space="preserve">2.36782956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054688453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.33806991577148</t>
@@ -803,52 +803,52 @@
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3613600730896</t>
+    <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065747261047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901263237</t>
+    <t xml:space="preserve">2.34065723419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901239395142</t>
   </si>
   <si>
     <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971475601196</t>
+    <t xml:space="preserve">2.34971499443054</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3121919631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29537105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666495323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24490928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949286460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26043605804443</t>
+    <t xml:space="preserve">2.40535187721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642483711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31219172477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29537129402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396656990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490904808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26043581962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784826278687</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24361515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20609211921692</t>
+    <t xml:space="preserve">2.24361562728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
     <t xml:space="preserve">2.19703483581543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21903133392334</t>
+    <t xml:space="preserve">2.21903157234192</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197031021118</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31736755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771873474121</t>
+    <t xml:space="preserve">2.31736731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771825790405</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348586082458</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">2.29407739639282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725648880005</t>
+    <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">2.26431751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890180587769</t>
+    <t xml:space="preserve">2.28890156745911</t>
   </si>
   <si>
     <t xml:space="preserve">2.24879097938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29278326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548164367676</t>
+    <t xml:space="preserve">2.29278302192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041687965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548212051392</t>
   </si>
   <si>
     <t xml:space="preserve">2.35747814178467</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819944381714</t>
+    <t xml:space="preserve">2.28631377220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337503433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819920539856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160018920898</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418822288513</t>
+    <t xml:space="preserve">2.33418798446655</t>
   </si>
   <si>
     <t xml:space="preserve">2.30572199821472</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">2.37171101570129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40664625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699719429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745944023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
+    <t xml:space="preserve">2.40664649009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546318054199</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651648521423</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34195113182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524176597595</t>
+    <t xml:space="preserve">2.34195137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40793991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370703697205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37688636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36265349388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38465023040771</t>
+    <t xml:space="preserve">2.39370727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37688660621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
     <t xml:space="preserve">2.31607365608215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36459445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076829910278</t>
+    <t xml:space="preserve">2.36459469795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3807680606842</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
+    <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">2.04435563087463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258102416992</t>
+    <t xml:space="preserve">2.10258054733276</t>
   </si>
   <si>
     <t xml:space="preserve">2.07346796989441</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07993721961975</t>
+    <t xml:space="preserve">2.0896418094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07993745803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12198925018311</t>
+    <t xml:space="preserve">2.12198877334595</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699848175049</t>
@@ -1046,61 +1046,61 @@
     <t xml:space="preserve">2.05082511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02818179130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966039180756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524233818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494716644287</t>
+    <t xml:space="preserve">2.02818155288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0152428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494740486145</t>
   </si>
   <si>
     <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08640670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04112076759338</t>
+    <t xml:space="preserve">2.08640694618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
     <t xml:space="preserve">2.07023310661316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07670307159424</t>
+    <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522411346436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10581517219543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06052875518799</t>
+    <t xml:space="preserve">2.10581541061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06052899360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09934616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875438690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845873832703</t>
+    <t xml:space="preserve">2.09934592247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10904979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139771461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875462532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
     <t xml:space="preserve">2.15110182762146</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">2.19962286949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28372597694397</t>
+    <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2505030632019</t>
+    <t xml:space="preserve">2.28460144996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050330162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230581283569</t>
+    <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322416305542</t>
@@ -1136,16 +1136,16 @@
     <t xml:space="preserve">2.16866660118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13456797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069893836975</t>
+    <t xml:space="preserve">2.13456845283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069917678833</t>
   </si>
   <si>
     <t xml:space="preserve">2.1004695892334</t>
@@ -1160,16 +1160,16 @@
     <t xml:space="preserve">1.96066558361053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0118134021759</t>
+    <t xml:space="preserve">2.01181364059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.05614161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591202735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227257728577</t>
+    <t xml:space="preserve">2.04591178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227281570435</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04250168800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99135410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09023976325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
+    <t xml:space="preserve">2.0425021648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99135434627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09024000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794400691986</t>
+    <t xml:space="preserve">1.99817395210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794448375702</t>
   </si>
   <si>
     <t xml:space="preserve">1.97089517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96748518943787</t>
+    <t xml:space="preserve">1.96748542785645</t>
   </si>
   <si>
     <t xml:space="preserve">1.9538459777832</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">1.95725572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97771465778351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043611526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361650943756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820766448975</t>
+    <t xml:space="preserve">1.97771489620209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138746261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820790290833</t>
   </si>
   <si>
     <t xml:space="preserve">2.18571591377258</t>
@@ -1244,64 +1244,64 @@
     <t xml:space="preserve">2.28801155090332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22663426399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004364967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21640467643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13797783851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1277482509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705924987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12092852592468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13115835189819</t>
+    <t xml:space="preserve">2.22663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2300443649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2164044380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889618873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13797807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12774872779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705972671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387969017029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1209282875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502738952637</t>
+    <t xml:space="preserve">2.15502715110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184735298157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637120246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499391555786</t>
+    <t xml:space="preserve">2.16184711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499367713928</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05955147743225</t>
+    <t xml:space="preserve">2.05955123901367</t>
   </si>
   <si>
     <t xml:space="preserve">1.92315709590912</t>
@@ -1310,10 +1310,10 @@
     <t xml:space="preserve">1.98112463951111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.984534740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660055160522</t>
+    <t xml:space="preserve">1.98453450202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0766007900238</t>
   </si>
   <si>
     <t xml:space="preserve">2.09364986419678</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">2.07319045066833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273199081421</t>
+    <t xml:space="preserve">2.05273175239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
@@ -1337,49 +1337,49 @@
     <t xml:space="preserve">2.17207646369934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18912577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1925356388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23345375061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23686361312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
+    <t xml:space="preserve">2.18912553787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19253540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23345398902893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23686337471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29824113845825</t>
+    <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
     <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961842536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233952522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643838882446</t>
+    <t xml:space="preserve">2.35961818695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36643815040588</t>
   </si>
   <si>
     <t xml:space="preserve">2.32892966270447</t>
@@ -1388,34 +1388,34 @@
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32211017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256911277771</t>
+    <t xml:space="preserve">2.32210993766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32552003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256887435913</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3732578754425</t>
+    <t xml:space="preserve">2.37325763702393</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689708709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099595069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
+    <t xml:space="preserve">2.38689732551575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666773796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099571228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804478645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">2.43122553825378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44827437400818</t>
+    <t xml:space="preserve">2.44827485084534</t>
   </si>
   <si>
     <t xml:space="preserve">2.46191382408142</t>
@@ -1433,22 +1433,22 @@
     <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306176185608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896361351013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5267014503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034090042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171794891357</t>
+    <t xml:space="preserve">2.51306200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171818733215</t>
   </si>
   <si>
     <t xml:space="preserve">2.59830808639526</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61535716056824</t>
+    <t xml:space="preserve">2.6153576374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855266571045</t>
@@ -1466,85 +1466,85 @@
     <t xml:space="preserve">2.61541247367859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61167097091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56677079200745</t>
+    <t xml:space="preserve">2.61167073249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63037919998169</t>
+    <t xml:space="preserve">2.55928778648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63037872314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.71269512176514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67153716087341</t>
+    <t xml:space="preserve">2.67153692245483</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160394668579</t>
+    <t xml:space="preserve">2.65657019615173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908742904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160418510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031241416931</t>
+    <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643710136414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766184806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772839546204</t>
+    <t xml:space="preserve">2.72766208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772887229919</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72017884254456</t>
+    <t xml:space="preserve">2.7201783657074</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262833595276</t>
+    <t xml:space="preserve">2.74262857437134</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861921310425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79126977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120299339294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616971969604</t>
+    <t xml:space="preserve">2.7912700176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120323181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868599891663</t>
+    <t xml:space="preserve">2.80623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
@@ -1553,85 +1553,85 @@
     <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338534355164</t>
+    <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971110343933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977765083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719387054443</t>
+    <t xml:space="preserve">2.89977741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
     <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576900482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03821873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09060215950012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10182666778564</t>
+    <t xml:space="preserve">3.0157687664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03821849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09060192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10182690620422</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12053489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
+    <t xml:space="preserve">3.12053513526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046787261963</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06066846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07937693595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10930991172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434342384338</t>
+    <t xml:space="preserve">3.16169285774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801814079285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06066870689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07937669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10931015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434366226196</t>
   </si>
   <si>
     <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706053733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583579063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97461032867432</t>
+    <t xml:space="preserve">2.99706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583555221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474413871765</t>
+    <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.07189345359802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0681517124176</t>
+    <t xml:space="preserve">3.06815195083618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951026916504</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">2.90351963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835254669189</t>
+    <t xml:space="preserve">2.97835230827332</t>
   </si>
   <si>
     <t xml:space="preserve">2.98209381103516</t>
@@ -1652,37 +1652,37 @@
     <t xml:space="preserve">2.94467759132385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841885566711</t>
+    <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
     <t xml:space="preserve">2.97086906433105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95964431762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739470481873</t>
+    <t xml:space="preserve">2.95964384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8473949432373</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80249428749084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991169929504</t>
+    <t xml:space="preserve">2.802494764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84365272521973</t>
+    <t xml:space="preserve">2.84365296363831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86236119270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86610293388367</t>
+    <t xml:space="preserve">2.86610269546509</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848611831665</t>
@@ -1694,22 +1694,22 @@
     <t xml:space="preserve">2.92596912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229464530945</t>
+    <t xml:space="preserve">2.90726113319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
     <t xml:space="preserve">2.79875326156616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78004479408264</t>
+    <t xml:space="preserve">2.78004503250122</t>
   </si>
   <si>
     <t xml:space="preserve">2.76882004737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80997824668884</t>
+    <t xml:space="preserve">2.80997800827026</t>
   </si>
   <si>
     <t xml:space="preserve">2.7613365650177</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00828576087952</t>
+    <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590257644653</t>
+    <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.96712732315063</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">2.88481092453003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87358593940735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78378677368164</t>
+    <t xml:space="preserve">2.87358617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78378653526306</t>
   </si>
   <si>
     <t xml:space="preserve">2.8174614906311</t>
@@ -1745,109 +1745,109 @@
     <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98957705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32632565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986727714539</t>
+    <t xml:space="preserve">2.98957681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986703872681</t>
   </si>
   <si>
     <t xml:space="preserve">3.3637421131134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42360854148865</t>
+    <t xml:space="preserve">3.42360830307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.44980001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402675151825</t>
+    <t xml:space="preserve">3.24026799201965</t>
   </si>
   <si>
     <t xml:space="preserve">3.22530102729797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2814257144928</t>
+    <t xml:space="preserve">3.28142619132996</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2963924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924360275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305165290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06441044807434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679315567017</t>
+    <t xml:space="preserve">3.29639267921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440997123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679339408875</t>
   </si>
   <si>
     <t xml:space="preserve">3.08685994148254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944348335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425451278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03545689582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621438026428</t>
+    <t xml:space="preserve">3.04944324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425427436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03545665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2562141418457</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581318855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942111968994</t>
+    <t xml:space="preserve">2.37968850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091324806213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581342697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438760757446</t>
+    <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574640274048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42833018302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213871002197</t>
+    <t xml:space="preserve">2.42832970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213823318481</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812958717346</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465498924255</t>
+    <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
+    <t xml:space="preserve">2.39839696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133632183075</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962147712708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4545214176178</t>
+    <t xml:space="preserve">2.40962171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452117919922</t>
   </si>
   <si>
     <t xml:space="preserve">2.4694881439209</t>
@@ -1898,52 +1898,52 @@
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670448303223</t>
+    <t xml:space="preserve">2.50690412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670424461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795111656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768445014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714436531067</t>
+    <t xml:space="preserve">3.15795135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265117645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1072199344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709010124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788778305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935307502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04822182655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968735694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12295269966125</t>
+    <t xml:space="preserve">3.10721945762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0010232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788802146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04822206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968759536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182097434998</t>
@@ -1952,25 +1952,25 @@
     <t xml:space="preserve">2.96955823898315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92235994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94202542304993</t>
+    <t xml:space="preserve">2.92235970497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94202589988708</t>
   </si>
   <si>
     <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595885276794</t>
+    <t xml:space="preserve">2.97742438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90269374847412</t>
+    <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.86336207389832</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78076481819153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79649782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469777107239</t>
+    <t xml:space="preserve">2.78076505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79649758338928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77289867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276884078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863143920898</t>
+    <t xml:space="preserve">2.77289843559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73749971389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276907920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863120079041</t>
   </si>
   <si>
     <t xml:space="preserve">2.74536633491516</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">2.76109910011292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67456889152527</t>
+    <t xml:space="preserve">2.67456865310669</t>
   </si>
   <si>
     <t xml:space="preserve">2.63523697853088</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58803844451904</t>
+    <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
@@ -2039,16 +2039,16 @@
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6391704082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65490293502808</t>
+    <t xml:space="preserve">2.68243551254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63917016983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670250892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6549026966095</t>
   </si>
   <si>
     <t xml:space="preserve">2.65883612632751</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130378723145</t>
+    <t xml:space="preserve">2.63130354881287</t>
   </si>
   <si>
     <t xml:space="preserve">2.6470365524292</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">2.52510762214661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52904081344604</t>
+    <t xml:space="preserve">2.52904057502747</t>
   </si>
   <si>
     <t xml:space="preserve">2.54084038734436</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150847434998</t>
+    <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4857759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50937461853027</t>
+    <t xml:space="preserve">2.48577570915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117443084717</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">2.49364233016968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46610951423645</t>
+    <t xml:space="preserve">2.46610975265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
@@ -2135,25 +2135,25 @@
     <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37564635276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3913791179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598039627075</t>
+    <t xml:space="preserve">2.37564659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39137935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598063468933</t>
   </si>
   <si>
     <t xml:space="preserve">2.39531254768372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29698252677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.340247631073</t>
+    <t xml:space="preserve">2.29698276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31271576881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34024786949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631467819214</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356676101685</t>
+    <t xml:space="preserve">2.57230591773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69030165672302</t>
+    <t xml:space="preserve">2.69030141830444</t>
   </si>
   <si>
     <t xml:space="preserve">2.70603442192078</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89482760429382</t>
+    <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
@@ -2210,37 +2210,37 @@
     <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92629313468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02068948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9616916179657</t>
+    <t xml:space="preserve">2.92629289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0206892490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83189654350281</t>
+    <t xml:space="preserve">2.83976292610168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83189606666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009673118591</t>
+    <t xml:space="preserve">2.82009696960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809247016907</t>
+    <t xml:space="preserve">2.88302803039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809223175049</t>
   </si>
   <si>
     <t xml:space="preserve">2.90662693977356</t>
@@ -2249,25 +2249,25 @@
     <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89876055717468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775842666626</t>
+    <t xml:space="preserve">2.8987603187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775818824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516117095947</t>
+    <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
     <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022608757019</t>
+    <t xml:space="preserve">2.86729502677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022584915161</t>
   </si>
   <si>
     <t xml:space="preserve">3.00495672225952</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">3.02462291717529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04035520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00889015197754</t>
+    <t xml:space="preserve">3.04035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349119186401</t>
@@ -2294,19 +2294,19 @@
     <t xml:space="preserve">2.98529100418091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575440406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855587005615</t>
+    <t xml:space="preserve">3.07575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855563163757</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09541988372803</t>
+    <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">3.10328650474548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
@@ -2330,22 +2330,22 @@
     <t xml:space="preserve">3.19374990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15441799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981647491455</t>
+    <t xml:space="preserve">3.15441823005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981623649597</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382652282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06287884712219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925820350647</t>
+    <t xml:space="preserve">3.10382676124573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06287908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
+    <t xml:space="preserve">3.07106852531433</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374220848083</t>
@@ -2375,52 +2375,52 @@
     <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00555276870728</t>
+    <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
     <t xml:space="preserve">3.03831052780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02602601051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468940734863</t>
+    <t xml:space="preserve">3.02602624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07516360282898</t>
+    <t xml:space="preserve">3.08335304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0751633644104</t>
   </si>
   <si>
     <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99326801300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96460485458374</t>
+    <t xml:space="preserve">2.99326825141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96460461616516</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94822597503662</t>
+    <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318369865417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89908838272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.89908885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137290000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2435,28 +2435,28 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94003629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223578453064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85404634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77624607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80490922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633062362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499402046204</t>
+    <t xml:space="preserve">2.9400360584259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223602294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8540461063385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77624583244324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80490946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633086204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499425888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">2.87861490249634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87452030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989173412323</t>
+    <t xml:space="preserve">2.87452006340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775225639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99736285209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
     <t xml:space="preserve">3.02193140983582</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">2.97279453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95232057571411</t>
+    <t xml:space="preserve">2.95232081413269</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
@@ -2498,25 +2498,25 @@
     <t xml:space="preserve">2.93184685707092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88680481910706</t>
+    <t xml:space="preserve">2.88680458068848</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8130989074707</t>
+    <t xml:space="preserve">2.81309866905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128834724426</t>
+    <t xml:space="preserve">2.82128858566284</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
+    <t xml:space="preserve">2.84995150566101</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051001548767</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357238769531</t>
+    <t xml:space="preserve">2.83357262611389</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
+    <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
     <t xml:space="preserve">2.84176230430603</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034090995789</t>
+    <t xml:space="preserve">2.83766746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081486701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978240013123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034067153931</t>
   </si>
   <si>
     <t xml:space="preserve">2.75986695289612</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521360397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387700080872</t>
+    <t xml:space="preserve">2.64521384239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.743488073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396179199219</t>
+    <t xml:space="preserve">2.76396203041077</t>
   </si>
   <si>
     <t xml:space="preserve">2.7271089553833</t>
@@ -2597,19 +2597,19 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897128105164</t>
+    <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85303664207458</t>
+    <t xml:space="preserve">2.85303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600372314453</t>
+    <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881684303284</t>
+    <t xml:space="preserve">2.87881708145142</t>
   </si>
   <si>
     <t xml:space="preserve">2.86163020133972</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405698776245</t>
+    <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
+    <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
     <t xml:space="preserve">2.5479679107666</t>
@@ -2672,43 +2672,43 @@
     <t xml:space="preserve">2.5350775718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57804489135742</t>
+    <t xml:space="preserve">2.578045129776</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47922015190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929713249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359415054321</t>
+    <t xml:space="preserve">2.47921991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929737091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359391212463</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195557594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4878134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49211025238037</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48781371116638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49211049079895</t>
   </si>
   <si>
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
@@ -2720,7 +2720,7 @@
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602117538452</t>
+    <t xml:space="preserve">2.34602093696594</t>
   </si>
   <si>
     <t xml:space="preserve">2.26867961883545</t>
@@ -2729,22 +2729,22 @@
     <t xml:space="preserve">2.25578951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36320805549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35031771659851</t>
+    <t xml:space="preserve">2.36320781707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3975818157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469171524048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43625259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.43625283241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33742737770081</t>
+    <t xml:space="preserve">2.33742761611938</t>
   </si>
   <si>
     <t xml:space="preserve">2.28156995773315</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">2.13118386268616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0624361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829352378845</t>
+    <t xml:space="preserve">2.06243634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829376220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10110664367676</t>
@@ -2798,34 +2798,34 @@
     <t xml:space="preserve">2.14407420158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08392000198364</t>
+    <t xml:space="preserve">2.11399722099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197302818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212746620178</t>
+    <t xml:space="preserve">1.88197290897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212734699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85619246959686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81322503089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041203022003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78744459152222</t>
+    <t xml:space="preserve">1.85619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81322491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041214942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78744447231293</t>
   </si>
   <si>
     <t xml:space="preserve">1.71869671344757</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6241682767868</t>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
@@ -2855,34 +2855,34 @@
     <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84330236911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96790778636932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353378772736</t>
+    <t xml:space="preserve">1.84330224990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96790766716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353366851807</t>
   </si>
   <si>
     <t xml:space="preserve">1.97650134563446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04954600334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593141078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0796229839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08821678161621</t>
+    <t xml:space="preserve">2.0495457649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95931422710419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07962322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.04524922370911</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.07102942466736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17844820022583</t>
+    <t xml:space="preserve">2.17844843864441</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2906,13 +2906,13 @@
     <t xml:space="preserve">2.13548064231873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18704175949097</t>
+    <t xml:space="preserve">2.18704152107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.2128221988678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19563508033752</t>
+    <t xml:space="preserve">2.1956353187561</t>
   </si>
   <si>
     <t xml:space="preserve">2.19993185997009</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07532620429993</t>
+    <t xml:space="preserve">2.07532644271851</t>
   </si>
   <si>
     <t xml:space="preserve">2.06673264503479</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
+    <t xml:space="preserve">2.23000907897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.28586673736572</t>
@@ -2954,13 +2954,13 @@
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438283920288</t>
+    <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609815597534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33313059806824</t>
+    <t xml:space="preserve">2.37609839439392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.427659034729</t>
+    <t xml:space="preserve">2.42765927314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149273872375</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2428994178772</t>
+    <t xml:space="preserve">2.27297639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24289894104004</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">2.41047239303589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070381164551</t>
+    <t xml:space="preserve">2.47062659263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070357322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -68958,7 +68958,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493518519</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>67806</v>
@@ -68979,6 +68979,32 @@
         <v>1240</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6495717593</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>201507</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>3.20499992370605</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1273">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">1.27515804767609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977028369904</t>
+    <t xml:space="preserve">1.24977016448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975892543793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283891677856</t>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784092903137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283867835999</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.25438618659973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746227264404</t>
+    <t xml:space="preserve">1.24746239185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.27285015583038</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591866970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168875694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053469181061</t>
+    <t xml:space="preserve">1.20591855049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053445339203</t>
   </si>
   <si>
     <t xml:space="preserve">1.19207072257996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20822668075562</t>
+    <t xml:space="preserve">1.20822656154633</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130643367767</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">1.23707640171051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29016005992889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669774532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900587558746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208184242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439009189606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169620990753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323602676392</t>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669810295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900599479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208196163177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438985347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
     <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862367153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093192100525</t>
+    <t xml:space="preserve">1.30862355232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093168258667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247149944305</t>
+    <t xml:space="preserve">1.32247173786163</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208574771881</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">1.30516183376312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32016372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3236255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708752155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323945522308</t>
+    <t xml:space="preserve">1.32016348838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362544536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708764076233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824158668518</t>
@@ -191,91 +191,91 @@
     <t xml:space="preserve">1.35132133960724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34439754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670543670654</t>
+    <t xml:space="preserve">1.34439718723297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670531749725</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478353500366</t>
+    <t xml:space="preserve">1.35478329658508</t>
   </si>
   <si>
     <t xml:space="preserve">1.36170721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34208917617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3432434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516916751862</t>
+    <t xml:space="preserve">1.34208941459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34324324131012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3455513715744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516880989075</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324726581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38017106056213</t>
+    <t xml:space="preserve">1.38017094135284</t>
   </si>
   <si>
     <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36747694015503</t>
+    <t xml:space="preserve">1.36747705936432</t>
   </si>
   <si>
     <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39497971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251530170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621222019196</t>
+    <t xml:space="preserve">1.394979596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621198177338</t>
   </si>
   <si>
     <t xml:space="preserve">1.41099989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42701995372772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687856197357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550454616547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043408870697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536327362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863554000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342321395874</t>
+    <t xml:space="preserve">1.42701983451843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332303524017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687832355499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427239894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550442695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536303520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275699138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863542079926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342357158661</t>
   </si>
   <si>
     <t xml:space="preserve">1.51821112632751</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">1.50465571880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51574683189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849390983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5403927564621</t>
+    <t xml:space="preserve">1.51574671268463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849438667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039299488068</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
@@ -302,124 +302,124 @@
     <t xml:space="preserve">1.61433172225952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59707939624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52437269687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077631473541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655456542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
+    <t xml:space="preserve">1.59707951545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52437281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958514213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077619552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190840244293</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362416744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500688791275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461462497711</t>
+    <t xml:space="preserve">1.59584701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006852149963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5946147441864</t>
   </si>
   <si>
     <t xml:space="preserve">1.64883661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65992748737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115975379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661388874054</t>
+    <t xml:space="preserve">1.65992712974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115939617157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
     <t xml:space="preserve">1.72154295444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72400772571564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523999214172</t>
+    <t xml:space="preserve">1.72400760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950307369232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827068805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72524011135101</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429050922394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059394836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675528049469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851273536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301714897156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604808330536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439116477966</t>
+    <t xml:space="preserve">1.70429074764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7067551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784603595734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301750659943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604784488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439080715179</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206790447235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865400791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618935585022</t>
+    <t xml:space="preserve">1.74988627433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865424633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7461895942688</t>
   </si>
   <si>
     <t xml:space="preserve">1.76837074756622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77453255653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220917701721</t>
+    <t xml:space="preserve">1.7745326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220965385437</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699720859528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76344168186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746283531189</t>
+    <t xml:space="preserve">1.76344180107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855335235596</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443202018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158428668976</t>
+    <t xml:space="preserve">1.69443225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158404827118</t>
   </si>
   <si>
     <t xml:space="preserve">1.60447323322296</t>
@@ -446,43 +446,43 @@
     <t xml:space="preserve">1.61679637432098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64267480373383</t>
+    <t xml:space="preserve">1.64267468452454</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376591682434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62049353122711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309945583344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556386947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802864074707</t>
+    <t xml:space="preserve">1.62049317359924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281655311584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309933662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556398868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802852153778</t>
   </si>
   <si>
     <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64760422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130114555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6562305688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926114559174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513981342316</t>
+    <t xml:space="preserve">1.64760398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130126476288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623044967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513969421387</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144265651703</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">1.63404870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59091782569885</t>
+    <t xml:space="preserve">1.59091770648956</t>
   </si>
   <si>
     <t xml:space="preserve">1.53546369075775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49356472492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479746818542</t>
+    <t xml:space="preserve">1.49356496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972653388977</t>
@@ -509,94 +509,94 @@
     <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884530544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49726176261902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51451432704926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532206058502</t>
+    <t xml:space="preserve">1.558877825737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845317363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423142433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726188182831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51451408863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532194137573</t>
   </si>
   <si>
     <t xml:space="preserve">1.57120084762573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58598840236664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.581059217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200846195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338223934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5872209072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6365133523941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66485619544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
+    <t xml:space="preserve">1.58598852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105933666229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6020085811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338212013245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722054958344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651311397552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66485643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
   </si>
   <si>
     <t xml:space="preserve">1.67225074768066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67841184139252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073522090912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978573799133</t>
+    <t xml:space="preserve">1.67841196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978585720062</t>
   </si>
   <si>
     <t xml:space="preserve">1.67717969417572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68703830242157</t>
+    <t xml:space="preserve">1.68703842163086</t>
   </si>
   <si>
     <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538126468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6845737695694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126017093658</t>
+    <t xml:space="preserve">1.71538162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291697025299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467430591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125993251801</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016941547394</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">1.77330005168915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77946197986603</t>
+    <t xml:space="preserve">1.77946186065674</t>
   </si>
   <si>
     <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806943655014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178512096405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590645313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766319274902</t>
+    <t xml:space="preserve">1.78069460391998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8176634311676</t>
   </si>
   <si>
     <t xml:space="preserve">1.81150209903717</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297617435455</t>
+    <t xml:space="preserve">1.86695635318756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297629356384</t>
   </si>
   <si>
     <t xml:space="preserve">1.89899635314941</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94459164142609</t>
+    <t xml:space="preserve">1.94459187984467</t>
   </si>
   <si>
     <t xml:space="preserve">1.92980408668518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98279345035553</t>
+    <t xml:space="preserve">1.9827938079834</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">2.02838921546936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04687428474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483368873596</t>
+    <t xml:space="preserve">2.04687404632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483392715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.01729822158813</t>
@@ -671,43 +671,43 @@
     <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0690553188324</t>
+    <t xml:space="preserve">2.05303549766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09493446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09986352920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13806509971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669156074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887283325195</t>
+    <t xml:space="preserve">2.0949342250824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0998637676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13806533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024708747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887307167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.17256999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15655016899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119645118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380285263062</t>
+    <t xml:space="preserve">2.15654993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010569572449</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.15531754493713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16640830039978</t>
+    <t xml:space="preserve">2.16640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
@@ -725,58 +725,58 @@
     <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816563606262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23172116279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27978134155273</t>
+    <t xml:space="preserve">2.1799635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816539764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2317214012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27978157997131</t>
   </si>
   <si>
     <t xml:space="preserve">2.28717541694641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33030652999878</t>
+    <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.35877180099487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34583306312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289432525635</t>
+    <t xml:space="preserve">2.34583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
     <t xml:space="preserve">2.31477975845337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25526070594788</t>
+    <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019594192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267243385315</t>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267267227173</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973345756531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313467979431</t>
+    <t xml:space="preserve">2.30313444137573</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866145133972</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782956123352</t>
+    <t xml:space="preserve">2.36782932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.35489058494568</t>
@@ -803,19 +803,19 @@
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36135983467102</t>
+    <t xml:space="preserve">2.3613600730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842109680176</t>
+    <t xml:space="preserve">2.34065771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901215553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842085838318</t>
   </si>
   <si>
     <t xml:space="preserve">2.34971499443054</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535187721252</t>
+    <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642483711243</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537129402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666543006897</t>
+    <t xml:space="preserve">2.29537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666495323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.25396656990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24490904808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949310302734</t>
+    <t xml:space="preserve">2.24490928649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949286460876</t>
   </si>
   <si>
     <t xml:space="preserve">2.26043581962585</t>
@@ -854,46 +854,46 @@
     <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26172995567322</t>
+    <t xml:space="preserve">2.2617301940918</t>
   </si>
   <si>
     <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24361562728882</t>
+    <t xml:space="preserve">2.24361515045166</t>
   </si>
   <si>
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903157234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197031021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102735519409</t>
+    <t xml:space="preserve">2.19703531265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319700717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102783203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31736731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771825790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348586082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725672721863</t>
+    <t xml:space="preserve">2.31736755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348562240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">2.24879097938538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29278302192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041687965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747814178467</t>
+    <t xml:space="preserve">2.29278349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548188209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747861862183</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">2.28631377220154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27337503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819920539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960392951965</t>
+    <t xml:space="preserve">2.2733747959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160042762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960416793823</t>
   </si>
   <si>
     <t xml:space="preserve">2.33418798446655</t>
@@ -944,31 +944,31 @@
     <t xml:space="preserve">2.30572199821472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35359668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171101570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664649009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546318054199</t>
+    <t xml:space="preserve">2.35359644889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171125411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745896339417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546294212341</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38723754882812</t>
+    <t xml:space="preserve">2.3872377872467</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241337776184</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40793991088867</t>
+    <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.39370727539062</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">2.37688660621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3626537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464999198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31607365608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
+    <t xml:space="preserve">2.36265349388123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38465023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.3807680606842</t>
@@ -1013,37 +1013,37 @@
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492798805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788590431213</t>
+    <t xml:space="preserve">2.13492822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258078575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788614273071</t>
   </si>
   <si>
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198877334595</t>
+    <t xml:space="preserve">2.07993769645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551976203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05082511901855</t>
+    <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
     <t xml:space="preserve">2.02818155288696</t>
@@ -1055,10 +1055,10 @@
     <t xml:space="preserve">1.97966051101685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0152428150177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494740486145</t>
+    <t xml:space="preserve">2.01524257659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494716644287</t>
   </si>
   <si>
     <t xml:space="preserve">2.0475902557373</t>
@@ -1070,10 +1070,10 @@
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670283317566</t>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670307159424</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522411346436</t>
@@ -1082,34 +1082,34 @@
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052899360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
+    <t xml:space="preserve">2.06052923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0637640953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934592247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10904979705811</t>
+    <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139771461487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875462532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845849990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110182762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433645248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19962286949158</t>
+    <t xml:space="preserve">2.11875414848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845873832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958495140076</t>
+    <t xml:space="preserve">2.28460168838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2505030632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322416305542</t>
+    <t xml:space="preserve">2.22322392463684</t>
   </si>
   <si>
     <t xml:space="preserve">2.16866660118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13456845283508</t>
+    <t xml:space="preserve">2.1345682144165</t>
   </si>
   <si>
     <t xml:space="preserve">2.12433862686157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11751866340637</t>
+    <t xml:space="preserve">2.11751890182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.11069917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1004695892334</t>
+    <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342027664185</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066558361053</t>
+    <t xml:space="preserve">1.96066546440125</t>
   </si>
   <si>
     <t xml:space="preserve">2.01181364059448</t>
@@ -1166,55 +1166,55 @@
     <t xml:space="preserve">2.05614161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227281570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840353965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08001041412354</t>
+    <t xml:space="preserve">2.04591155052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840330123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08001017570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.08682990074158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02886247634888</t>
+    <t xml:space="preserve">2.0288622379303</t>
   </si>
   <si>
     <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0425021648407</t>
+    <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09024000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0697808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817395210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794448375702</t>
+    <t xml:space="preserve">2.09024024009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06978130340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522326469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817383289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794436454773</t>
   </si>
   <si>
     <t xml:space="preserve">1.97089517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96748542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9538459777832</t>
+    <t xml:space="preserve">1.96748518943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384621620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.95725572109222</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">1.97771489620209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95043587684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361627101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138746261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820790290833</t>
+    <t xml:space="preserve">1.9504359960556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361650943756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820742607117</t>
   </si>
   <si>
     <t xml:space="preserve">2.18571591377258</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2300443649292</t>
+    <t xml:space="preserve">2.28801131248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663426399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004388809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.2164044380188</t>
@@ -1256,40 +1256,40 @@
     <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13797807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410927772522</t>
+    <t xml:space="preserve">2.13797783851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410880088806</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296157836914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12774872779846</t>
+    <t xml:space="preserve">2.12774848937988</t>
   </si>
   <si>
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387969017029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209282875061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13115787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584370136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15502715110779</t>
+    <t xml:space="preserve">2.10387945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092852592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13115835189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15843725204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15502691268921</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184711456299</t>
+    <t xml:space="preserve">2.16184687614441</t>
   </si>
   <si>
     <t xml:space="preserve">2.06637096405029</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05955123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112463951111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453450202942</t>
+    <t xml:space="preserve">2.05955147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315721511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453462123871</t>
   </si>
   <si>
     <t xml:space="preserve">2.0766007900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09364986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319045066833</t>
+    <t xml:space="preserve">2.0936496257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
     <t xml:space="preserve">2.05273175239563</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">2.17207646369934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18912553787231</t>
+    <t xml:space="preserve">2.18912577629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253540039062</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">2.23345398902893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686337471008</t>
+    <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25391292572021</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483127593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165100097656</t>
+    <t xml:space="preserve">2.29483103752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31529021263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165076255798</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">2.35961818695068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892966270447</t>
+    <t xml:space="preserve">2.33233952522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892942428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32552003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256887435913</t>
+    <t xml:space="preserve">2.32551980018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256935119629</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">2.37325763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39712715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38689732551575</t>
+    <t xml:space="preserve">2.39712691307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38689684867859</t>
   </si>
   <si>
     <t xml:space="preserve">2.37666773796082</t>
@@ -1415,52 +1415,52 @@
     <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43804478645325</t>
+    <t xml:space="preserve">2.43804502487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122553825378</t>
+    <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827485084534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46191382408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942231178284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51306200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919272422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896337509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034042358398</t>
+    <t xml:space="preserve">2.46191430091858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942207336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5130615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670121192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171818733215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830808639526</t>
+    <t xml:space="preserve">2.59830832481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6153576374054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855266571045</t>
+    <t xml:space="preserve">2.61535739898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855290412903</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541247367859</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928778648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63037872314453</t>
+    <t xml:space="preserve">2.55928754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63037919998169</t>
   </si>
   <si>
     <t xml:space="preserve">2.71269512176514</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657019615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160418510437</t>
+    <t xml:space="preserve">2.65657043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160370826721</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643710136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772887229919</t>
+    <t xml:space="preserve">2.71643686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766184806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
@@ -1526,46 +1526,46 @@
     <t xml:space="preserve">2.74262857437134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85861921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7912700176239</t>
+    <t xml:space="preserve">2.85861945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79126977920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120323181152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83616948127747</t>
+    <t xml:space="preserve">2.83616924285889</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623626708984</t>
+    <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
     <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82494497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86984443664551</t>
+    <t xml:space="preserve">2.82494473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86984419822693</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92971110343933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89977741241455</t>
+    <t xml:space="preserve">2.92971086502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99331903457642</t>
+    <t xml:space="preserve">2.99331879615784</t>
   </si>
   <si>
     <t xml:space="preserve">3.0157687664032</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">3.09060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10182690620422</t>
+    <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556840896606</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">3.12053513526917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046787261963</t>
+    <t xml:space="preserve">3.15046811103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169285774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801814079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06066870689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07937669754028</t>
+    <t xml:space="preserve">3.16169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801790237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06066846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0793764591217</t>
   </si>
   <si>
     <t xml:space="preserve">3.10931015014648</t>
@@ -1610,10 +1610,10 @@
     <t xml:space="preserve">3.09434366226196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04570198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99706077575684</t>
+    <t xml:space="preserve">3.0457022190094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583555221558</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100263595581</t>
+    <t xml:space="preserve">2.91100287437439</t>
   </si>
   <si>
     <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07189345359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06815195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00454378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835230827332</t>
+    <t xml:space="preserve">3.0718936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0681517124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951050758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0045440196991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351939201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835254669189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94467759132385</t>
+    <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
     <t xml:space="preserve">2.94841909408569</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">2.95964384078979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8473949432373</t>
+    <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991122245789</t>
+    <t xml:space="preserve">2.83991146087646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85113620758057</t>
@@ -1691,7 +1691,7 @@
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596912384033</t>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726113319397</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">2.79875326156616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78004503250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76882004737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997800827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7613365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106942176819</t>
+    <t xml:space="preserve">2.78004479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76882028579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997824668884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76133680343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106918334961</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88481092453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358617782593</t>
+    <t xml:space="preserve">2.88481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358593940735</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619232177734</t>
+    <t xml:space="preserve">2.85487818717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98957705497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761766433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
     <t xml:space="preserve">3.3263258934021</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">3.44980001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.35625863075256</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24026799201965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530102729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28142619132996</t>
+    <t xml:space="preserve">3.2402675151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28142595291138</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29639267921448</t>
+    <t xml:space="preserve">3.2963924407959</t>
   </si>
   <si>
     <t xml:space="preserve">3.13924312591553</t>
@@ -1796,25 +1796,25 @@
     <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06440997123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093608856201</t>
+    <t xml:space="preserve">3.06441020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.11679339408875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08685994148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944324493408</t>
+    <t xml:space="preserve">3.08686017990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425427436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545665740967</t>
+    <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
     <t xml:space="preserve">2.2562141418457</t>
@@ -1823,28 +1823,28 @@
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968850135803</t>
+    <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
     <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942135810852</t>
+    <t xml:space="preserve">2.43581318855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4994215965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438784599304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46574640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42832970619202</t>
+    <t xml:space="preserve">2.51438760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46574664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4283299446106</t>
   </si>
   <si>
     <t xml:space="preserve">2.40213823318481</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38343000411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465522766113</t>
+    <t xml:space="preserve">2.38343024253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710472106934</t>
+    <t xml:space="preserve">2.39839673042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710495948792</t>
   </si>
   <si>
     <t xml:space="preserve">2.42458820343018</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">2.40962171554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452117919922</t>
+    <t xml:space="preserve">2.4545214176178</t>
   </si>
   <si>
     <t xml:space="preserve">2.4694881439209</t>
@@ -1892,55 +1892,55 @@
     <t xml:space="preserve">2.49193811416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935433387756</t>
+    <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670424461365</t>
+    <t xml:space="preserve">2.5069043636322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265117645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714412689209</t>
+    <t xml:space="preserve">3.15795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265069961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721945762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0010232925415</t>
+    <t xml:space="preserve">3.10721969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00102376937866</t>
   </si>
   <si>
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788802146912</t>
+    <t xml:space="preserve">3.06788778305054</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04822206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968759536743</t>
+    <t xml:space="preserve">3.04822182655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
@@ -1955,52 +1955,52 @@
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595909118652</t>
+    <t xml:space="preserve">2.94202566146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989228248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336207389832</t>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336183547974</t>
   </si>
   <si>
     <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78076505661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79649758338928</t>
+    <t xml:space="preserve">2.78076529502869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469824790955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73749971389771</t>
+    <t xml:space="preserve">2.76896548271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
     <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78863120079041</t>
+    <t xml:space="preserve">2.78863167762756</t>
   </si>
   <si>
     <t xml:space="preserve">2.74536633491516</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">2.76109910011292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67456865310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63523697853088</t>
+    <t xml:space="preserve">2.67456889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6352367401123</t>
   </si>
   <si>
     <t xml:space="preserve">2.61950421333313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62737035751343</t>
+    <t xml:space="preserve">2.62737059593201</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770463943481</t>
+    <t xml:space="preserve">2.60770440101624</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243551254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63917016983032</t>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63916993141174</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">2.6549026966095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65883612632751</t>
+    <t xml:space="preserve">2.65883636474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">2.63130354881287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6470365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343740463257</t>
+    <t xml:space="preserve">2.64703631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65096974372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75323247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904057502747</t>
+    <t xml:space="preserve">2.65096950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75323271751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
     <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970890045166</t>
+    <t xml:space="preserve">2.48970913887024</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544142723083</t>
+    <t xml:space="preserve">2.50150847434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544166564941</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397613525391</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49364233016968</t>
+    <t xml:space="preserve">2.52117419242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
     <t xml:space="preserve">2.46610975265503</t>
@@ -2138,64 +2138,64 @@
     <t xml:space="preserve">2.37564659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39137935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598063468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.3913791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271576881409</t>
+    <t xml:space="preserve">2.31271529197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.34024786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631467819214</t>
+    <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230591773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557126045227</t>
+    <t xml:space="preserve">2.57230567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716590881348</t>
+    <t xml:space="preserve">2.75716614723206</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783375740051</t>
+    <t xml:space="preserve">2.71783399581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69030141830444</t>
+    <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
     <t xml:space="preserve">2.70603442192078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210123062134</t>
+    <t xml:space="preserve">2.70210099220276</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87909460067749</t>
+    <t xml:space="preserve">2.87909483909607</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">2.88696122169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87122845649719</t>
+    <t xml:space="preserve">2.87122869491577</t>
   </si>
   <si>
     <t xml:space="preserve">2.91449332237244</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189606666565</t>
+    <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
@@ -2234,13 +2234,13 @@
     <t xml:space="preserve">2.82009696960449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85156226158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809223175049</t>
+    <t xml:space="preserve">2.8515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809247016907</t>
   </si>
   <si>
     <t xml:space="preserve">2.90662693977356</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8987603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775842666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
@@ -2264,76 +2264,76 @@
     <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022584915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495672225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035544395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00888991355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97349119186401</t>
+    <t xml:space="preserve">2.86729526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022632598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495648384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00889015197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97349095344543</t>
   </si>
   <si>
     <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98529100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215525627136</t>
+    <t xml:space="preserve">2.98529076576233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215501785278</t>
   </si>
   <si>
     <t xml:space="preserve">3.02855563163757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06002140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.06002163887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148693084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12688565254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948266983032</t>
+    <t xml:space="preserve">3.09148716926575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12688541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1032862663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441823005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981623649597</t>
+    <t xml:space="preserve">3.19374942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">3.08744764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06697392463684</t>
+    <t xml:space="preserve">3.06697368621826</t>
   </si>
   <si>
     <t xml:space="preserve">3.05059480667114</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">3.07106852531433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01374220848083</t>
+    <t xml:space="preserve">3.01374197006226</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012108802795</t>
@@ -2372,37 +2372,37 @@
     <t xml:space="preserve">3.03421568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01783657073975</t>
+    <t xml:space="preserve">3.01783680915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602624893188</t>
+    <t xml:space="preserve">3.03831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602601051331</t>
   </si>
   <si>
     <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04650020599365</t>
+    <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
     <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0751633644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507881164551</t>
+    <t xml:space="preserve">3.07516360282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507857322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460461616516</t>
+    <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
@@ -2411,16 +2411,16 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
+    <t xml:space="preserve">2.9031834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908885955811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137290000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.91137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2435,37 +2435,37 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9400360584259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8540461063385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77624583244324</t>
+    <t xml:space="preserve">2.94003629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223578453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85404634475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77624607086182</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490946769714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633086204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499425888062</t>
+    <t xml:space="preserve">2.80490922927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633062362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499402046204</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87861490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452006340027</t>
+    <t xml:space="preserve">2.8786153793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452030181885</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775225639343</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02193140983582</t>
+    <t xml:space="preserve">3.02193164825439</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95232081413269</t>
+    <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869969367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94413113594055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93184685707092</t>
+    <t xml:space="preserve">2.96869945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94413137435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93184661865234</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
@@ -2504,19 +2504,19 @@
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309866905212</t>
+    <t xml:space="preserve">2.81309914588928</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128858566284</t>
+    <t xml:space="preserve">2.82128834724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995150566101</t>
+    <t xml:space="preserve">2.84995174407959</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051001548767</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357262611389</t>
+    <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215123176575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84176230430603</t>
+    <t xml:space="preserve">2.77215099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84176206588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081486701965</t>
+    <t xml:space="preserve">2.83766722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081462860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034067153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986695289612</t>
+    <t xml:space="preserve">2.78034090995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986671447754</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
@@ -2567,22 +2567,22 @@
     <t xml:space="preserve">2.64521384239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67387723922729</t>
+    <t xml:space="preserve">2.67387700080872</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.743488073349</t>
+    <t xml:space="preserve">2.74348783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396203041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7271089553833</t>
+    <t xml:space="preserve">2.76396179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72710871696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
@@ -2600,43 +2600,43 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303640365601</t>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82725620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80577254295349</t>
+    <t xml:space="preserve">2.82725596427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80577230453491</t>
   </si>
   <si>
     <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82295942306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81436610221863</t>
+    <t xml:space="preserve">2.82295966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81436586380005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86163020133972</t>
+    <t xml:space="preserve">2.87881684303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.90459752082825</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6983540058136</t>
+    <t xml:space="preserve">2.69835376739502</t>
   </si>
   <si>
     <t xml:space="preserve">2.65968322753906</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64679288864136</t>
+    <t xml:space="preserve">2.64679312705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.59952878952026</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5350775718689</t>
+    <t xml:space="preserve">2.53507781028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.578045129776</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">2.47921991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50929737091064</t>
+    <t xml:space="preserve">2.50929713249207</t>
   </si>
   <si>
     <t xml:space="preserve">2.51359391212463</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
+    <t xml:space="preserve">2.44914293289185</t>
   </si>
   <si>
     <t xml:space="preserve">2.43195581436157</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41906571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35891103744507</t>
+    <t xml:space="preserve">2.49211025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41906595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35891127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.34172415733337</t>
@@ -2717,37 +2717,37 @@
     <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27727317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.27727341651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34602117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3975818157196</t>
+    <t xml:space="preserve">2.36320805549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469171524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625283241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180161476135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40187883377075</t>
+    <t xml:space="preserve">2.38469195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40187859535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.35461449623108</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
+    <t xml:space="preserve">2.13118410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2795,22 +2795,22 @@
     <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14407420158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399722099304</t>
+    <t xml:space="preserve">2.14407396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041214942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78744447231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.81322503089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041203022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307391643524</t>
+    <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
     <t xml:space="preserve">1.62416839599609</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650134563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087498664856</t>
+    <t xml:space="preserve">1.96790754795074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087522506714</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
+    <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07102942466736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17844843864441</t>
+    <t xml:space="preserve">2.07102966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
@@ -2903,16 +2903,16 @@
     <t xml:space="preserve">2.12688708305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13548064231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18704152107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2128221988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1956353187561</t>
+    <t xml:space="preserve">2.13548040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18704175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21282196044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
     <t xml:space="preserve">2.19993185997009</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07532644271851</t>
+    <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
     <t xml:space="preserve">2.06673264503479</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20422863960266</t>
+    <t xml:space="preserve">2.20422840118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.31594395637512</t>
@@ -2969,16 +2969,16 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438307762146</t>
+    <t xml:space="preserve">2.26438283920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609839439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.37609815597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2996,25 +2996,25 @@
     <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22141551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27297639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24289894104004</t>
+    <t xml:space="preserve">2.22141575813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27297616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41047239303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062659263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070357322693</t>
+    <t xml:space="preserve">2.41047215461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3828,6 +3828,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.01500010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24499988555908</t>
   </si>
 </sst>
 </file>
@@ -68984,7 +68987,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6495717593</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>201507</v>
@@ -69005,6 +69008,32 @@
         <v>1265</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6495949074</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>283363</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>3.18499994277954</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>3.18499994277954</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>3.24499988555908</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>1272</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1273" uniqueCount="1273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="1274">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27862012386322</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977395057678</t>
+    <t xml:space="preserve">1.27977406978607</t>
   </si>
   <si>
     <t xml:space="preserve">1.2682341337204</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515804767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246037960052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784092903137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283867835999</t>
+    <t xml:space="preserve">1.27515828609467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2324606180191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975916385651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">1.27285015583038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27746605873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2636182308197</t>
+    <t xml:space="preserve">1.27746593952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26361811161041</t>
   </si>
   <si>
     <t xml:space="preserve">1.20591855049133</t>
@@ -104,31 +104,31 @@
     <t xml:space="preserve">1.21168851852417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21053445339203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822656154633</t>
+    <t xml:space="preserve">1.2105348110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130643367767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899842262268</t>
+    <t xml:space="preserve">1.22899854183197</t>
   </si>
   <si>
     <t xml:space="preserve">1.23476839065552</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23707640171051</t>
+    <t xml:space="preserve">1.23707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669810295105</t>
+    <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900599479675</t>
@@ -143,58 +143,58 @@
     <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054581165314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862355232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093168258667</t>
+    <t xml:space="preserve">1.28323602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054545402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862367153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093192100525</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247173786163</t>
+    <t xml:space="preserve">1.32247149944305</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208574771881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30746972560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516183376312</t>
+    <t xml:space="preserve">1.3074699640274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593381404877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
     <t xml:space="preserve">1.32016348838806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362544536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708764076233</t>
+    <t xml:space="preserve">1.32362568378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708775997162</t>
   </si>
   <si>
     <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824158668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670531749725</t>
+    <t xml:space="preserve">1.32824146747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439742565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501672744751</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">1.36170721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34208941459656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34324324131012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3455513715744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516880989075</t>
+    <t xml:space="preserve">1.34208929538727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3432434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324726581573</t>
@@ -224,103 +224,103 @@
     <t xml:space="preserve">1.38017094135284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37786304950714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747705936432</t>
+    <t xml:space="preserve">1.37786316871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747717857361</t>
   </si>
   <si>
     <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.394979596138</t>
+    <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
     <t xml:space="preserve">1.39251518249512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39621198177338</t>
+    <t xml:space="preserve">1.39621222019196</t>
   </si>
   <si>
     <t xml:space="preserve">1.41099989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332303524017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687832355499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427239894867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550442695618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043385028839</t>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687844276428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427251815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550454616547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043396949768</t>
   </si>
   <si>
     <t xml:space="preserve">1.45536303520203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46275699138641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110019207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863542079926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342357158661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821112632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162526130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465571880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574671268463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849438667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039299488068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707951545715</t>
+    <t xml:space="preserve">1.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110043048859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863565921783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342333316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821088790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162538051605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574647426605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4984940290451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60816979408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433160305023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707915782928</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437281608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958514213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655432701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190840244293</t>
+    <t xml:space="preserve">1.50958490371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6007764339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5465544462204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190804481506</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257438659668</t>
@@ -329,88 +329,88 @@
     <t xml:space="preserve">1.59584701061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006852149963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115939617157</t>
+    <t xml:space="preserve">1.66362416744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006864070892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461462497711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883649349213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992748737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115963459015</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154295444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950307369232</t>
+    <t xml:space="preserve">1.72154331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950283527374</t>
   </si>
   <si>
     <t xml:space="preserve">1.68827068805695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72524011135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756301403046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429074764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059382915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784603595734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301750659943</t>
+    <t xml:space="preserve">1.72523987293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756325244904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429062843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059370994568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675539970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784615516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851261615753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
   </si>
   <si>
     <t xml:space="preserve">1.75604784488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78439080715179</t>
+    <t xml:space="preserve">1.78439116477966</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206790447235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988627433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865424633026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7461895942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837074756622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7745326757431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220965385437</t>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865412712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618971347809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837086677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453279495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7622092962265</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699720859528</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">1.76344180107117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6574627161026</t>
+    <t xml:space="preserve">1.65746283531189</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855335235596</t>
@@ -428,49 +428,49 @@
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158404827118</t>
+    <t xml:space="preserve">1.69443190097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186707019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
     <t xml:space="preserve">1.60447323322296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267468452454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376591682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049317359924</t>
+    <t xml:space="preserve">1.63035190105438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679661273956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376555919647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049329280853</t>
   </si>
   <si>
     <t xml:space="preserve">1.63281655311584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309933662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556398868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802852153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021039009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760398864746</t>
+    <t xml:space="preserve">1.61309945583344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6155641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760410785675</t>
   </si>
   <si>
     <t xml:space="preserve">1.65130126476288</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">1.65623044967651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513969421387</t>
+    <t xml:space="preserve">1.61926078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513981342316</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144265651703</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">1.63404870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59091770648956</t>
+    <t xml:space="preserve">1.59091782569885</t>
   </si>
   <si>
     <t xml:space="preserve">1.53546369075775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49356496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479722976685</t>
+    <t xml:space="preserve">1.49356472492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972653388977</t>
@@ -509,70 +509,70 @@
     <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.558877825737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423142433167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49726188182831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51451408863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532194137573</t>
+    <t xml:space="preserve">1.55887758731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845329284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423130512238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726176261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51451432704926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
     <t xml:space="preserve">1.57120084762573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58598852157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105933666229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6020085811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338212013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722054958344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651311397552</t>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105909824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338223934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5872209072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651347160339</t>
   </si>
   <si>
     <t xml:space="preserve">1.66485643386841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499806404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594754695892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225074768066</t>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6759477853775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6722503900528</t>
   </si>
   <si>
     <t xml:space="preserve">1.67841196060181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073510169983</t>
+    <t xml:space="preserve">1.69073522090912</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978585720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717969417572</t>
+    <t xml:space="preserve">1.67717981338501</t>
   </si>
   <si>
     <t xml:space="preserve">1.68703842163086</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538162231445</t>
+    <t xml:space="preserve">1.71538126468658</t>
   </si>
   <si>
     <t xml:space="preserve">1.71291697025299</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">1.76467430591583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75728011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125993251801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330005168915</t>
+    <t xml:space="preserve">1.75727987289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126005172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016953468323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330017089844</t>
   </si>
   <si>
     <t xml:space="preserve">1.77946186065674</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069460391998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178476333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8176634311676</t>
+    <t xml:space="preserve">1.78069400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590645313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766366958618</t>
   </si>
   <si>
     <t xml:space="preserve">1.81150209903717</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695635318756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297629356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89899635314941</t>
+    <t xml:space="preserve">1.86695623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297641277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8989964723587</t>
   </si>
   <si>
     <t xml:space="preserve">1.9076224565506</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94459187984467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92980408668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9827938079834</t>
+    <t xml:space="preserve">1.94459211826324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9298038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279345035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687404632568</t>
+    <t xml:space="preserve">2.02838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687428474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483392715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01729822158813</t>
+    <t xml:space="preserve">2.01729869842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303549766541</t>
+    <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905555725098</t>
@@ -686,67 +686,67 @@
     <t xml:space="preserve">2.0998637676239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024708747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17256999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15654993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119621276855</t>
+    <t xml:space="preserve">2.13806509971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669156074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1725697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15655016899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119645118713</t>
   </si>
   <si>
     <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17010569572449</t>
+    <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.15531754493713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16640853881836</t>
+    <t xml:space="preserve">2.16640830039978</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1799635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816539764404</t>
+    <t xml:space="preserve">2.18366074562073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
     <t xml:space="preserve">2.20953941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21323680877686</t>
+    <t xml:space="preserve">2.2132363319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.2317214012146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978157997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717541694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3303062915802</t>
+    <t xml:space="preserve">2.27978134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33030652999878</t>
   </si>
   <si>
     <t xml:space="preserve">2.35877180099487</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">2.34583282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289408683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477975845337</t>
+    <t xml:space="preserve">2.33289384841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477952003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.2552604675293</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">2.25137853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019570350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973345756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313444137573</t>
+    <t xml:space="preserve">2.29019546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973369598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866145133972</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782932281494</t>
+    <t xml:space="preserve">2.36782956123352</t>
   </si>
   <si>
     <t xml:space="preserve">2.35489058494568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806991577148</t>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806967735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453940391541</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">2.32901215553284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34842085838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971499443054</t>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4053521156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642483711243</t>
+    <t xml:space="preserve">2.40535235404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219172477722</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666495323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396656990051</t>
+    <t xml:space="preserve">2.29666543006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396680831909</t>
   </si>
   <si>
     <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26949286460876</t>
+    <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
     <t xml:space="preserve">2.26043581962585</t>
@@ -854,61 +854,61 @@
     <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2617301940918</t>
+    <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
     <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24361515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2060923576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703531265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2319700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3225429058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407715797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725648880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855062484741</t>
+    <t xml:space="preserve">2.24361538887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20609259605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903157234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23197054862976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102735519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254266738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771825790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348586082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855086326599</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890156745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879097938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.28890180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">2.33548188209534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747861862183</t>
+    <t xml:space="preserve">2.35747790336609</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">2.28631377220154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819944381714</t>
+    <t xml:space="preserve">2.27337503433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819896697998</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160042762756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30960416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572199821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359644889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171125411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745896339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651648521423</t>
+    <t xml:space="preserve">2.30960392951965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418774604797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3057222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664649009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">2.3872377872467</t>
@@ -977,52 +977,52 @@
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524152755737</t>
+    <t xml:space="preserve">2.36524128913879</t>
   </si>
   <si>
     <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.39370703697205</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688660621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36265349388123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38465023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3807680606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37429904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37753343582153</t>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38464999198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459469795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37429928779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492822647095</t>
+    <t xml:space="preserve">2.13492774963379</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346820831299</t>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346796989441</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788614273071</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993769645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551976203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198925018311</t>
+    <t xml:space="preserve">2.07993698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198877334595</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699848175049</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494716644287</t>
+    <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0475902557373</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522411346436</t>
+    <t xml:space="preserve">2.07023310661316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670283317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052923202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0637640953064</t>
+    <t xml:space="preserve">2.06052875518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934592247009</t>
@@ -1097,19 +1097,19 @@
     <t xml:space="preserve">2.14139771461487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875414848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845873832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110158920288</t>
+    <t xml:space="preserve">2.11875438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1511013507843</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.199622631073</t>
+    <t xml:space="preserve">2.19962286949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2505030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958471298218</t>
+    <t xml:space="preserve">2.28460144996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322392463684</t>
+    <t xml:space="preserve">2.22322416305542</t>
   </si>
   <si>
     <t xml:space="preserve">2.16866660118103</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.1345682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12433862686157</t>
+    <t xml:space="preserve">2.12433838844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.11751890182495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11069917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10046935081482</t>
+    <t xml:space="preserve">2.11069893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342027664185</t>
@@ -1157,34 +1157,34 @@
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066546440125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01181364059448</t>
+    <t xml:space="preserve">1.96066534519196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
     <t xml:space="preserve">2.05614161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591155052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840330123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08001017570496</t>
+    <t xml:space="preserve">2.04591178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227257728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840353965759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08001041412354</t>
   </si>
   <si>
     <t xml:space="preserve">2.08682990074158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0288622379303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909206390381</t>
+    <t xml:space="preserve">2.02886247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909230232239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
@@ -1193,28 +1193,28 @@
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09024024009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978130340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522326469421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817383289337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794436454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089517116547</t>
+    <t xml:space="preserve">2.09024000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06978058815002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817419052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089493274689</t>
   </si>
   <si>
     <t xml:space="preserve">1.96748518943787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95384621620178</t>
+    <t xml:space="preserve">1.9538459777832</t>
   </si>
   <si>
     <t xml:space="preserve">1.95725572109222</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">1.97771489620209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9504359960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361650943756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820742607117</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801131248474</t>
+    <t xml:space="preserve">2.28801155090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004388809204</t>
+    <t xml:space="preserve">2.23004412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2164044380188</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13797783851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410880088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296157836914</t>
+    <t xml:space="preserve">2.13797760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296133995056</t>
   </si>
   <si>
     <t xml:space="preserve">2.12774848937988</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115835189819</t>
+    <t xml:space="preserve">2.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">2.15843725204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502691268921</t>
+    <t xml:space="preserve">2.15502715110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
@@ -1295,22 +1295,22 @@
     <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00499367713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315721511841</t>
+    <t xml:space="preserve">2.00499391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0186333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9231573343277</t>
   </si>
   <si>
     <t xml:space="preserve">1.98112487792969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98453462123871</t>
+    <t xml:space="preserve">1.98453426361084</t>
   </si>
   <si>
     <t xml:space="preserve">2.0766007900238</t>
@@ -1322,22 +1322,22 @@
     <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273175239563</t>
+    <t xml:space="preserve">2.05273127555847</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027371406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594550132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207646369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912577629089</t>
+    <t xml:space="preserve">2.24027347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253540039062</t>
@@ -1349,43 +1349,43 @@
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732254981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506110191345</t>
+    <t xml:space="preserve">2.25391268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483103752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3084704875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961818695068</t>
+    <t xml:space="preserve">2.29483127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165123939514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30847024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961842536926</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3391592502594</t>
+    <t xml:space="preserve">2.36643815040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33915901184082</t>
   </si>
   <si>
     <t xml:space="preserve">2.32210993766785</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34256935119629</t>
+    <t xml:space="preserve">2.34256887435913</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
@@ -1403,10 +1403,10 @@
     <t xml:space="preserve">2.37325763702393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39712691307068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38689684867859</t>
+    <t xml:space="preserve">2.39712715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
     <t xml:space="preserve">2.37666773796082</t>
@@ -1418,37 +1418,37 @@
     <t xml:space="preserve">2.43804502487183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43463516235352</t>
+    <t xml:space="preserve">2.43463492393494</t>
   </si>
   <si>
     <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44827485084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46191430091858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5130615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670121192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034066200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171818733215</t>
+    <t xml:space="preserve">2.44827437400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942231178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51306200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034018516541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
     <t xml:space="preserve">2.59830832481384</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61535739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855290412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61541247367859</t>
+    <t xml:space="preserve">2.6153576374054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
     <t xml:space="preserve">2.61167073249817</t>
@@ -1475,16 +1475,16 @@
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928754806519</t>
+    <t xml:space="preserve">2.55928778648376</t>
   </si>
   <si>
     <t xml:space="preserve">2.63037919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269512176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67153692245483</t>
+    <t xml:space="preserve">2.71269536018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
@@ -1493,22 +1493,22 @@
     <t xml:space="preserve">2.65657043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64908719062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160370826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031217575073</t>
+    <t xml:space="preserve">2.64908695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031193733215</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766184806824</t>
+    <t xml:space="preserve">2.72766208648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772863388062</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7201783657074</t>
+    <t xml:space="preserve">2.72017860412598</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79126977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616924285889</t>
+    <t xml:space="preserve">2.79127025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82494473457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86984419822693</t>
+    <t xml:space="preserve">2.80623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82494497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977765083313</t>
+    <t xml:space="preserve">2.89977741241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99331879615784</t>
+    <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
     <t xml:space="preserve">3.0157687664032</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12053513526917</t>
+    <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
     <t xml:space="preserve">3.15046811103821</t>
@@ -1592,31 +1592,31 @@
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169309616089</t>
+    <t xml:space="preserve">3.16169285774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06066846847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0793764591217</t>
+    <t xml:space="preserve">3.06066870689392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
     <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09434366226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0457022190094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99706053733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583555221558</t>
+    <t xml:space="preserve">3.09434342384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04570198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583579063416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
@@ -1628,34 +1628,34 @@
     <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951050758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0045440196991</t>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00454354286194</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835254669189</t>
+    <t xml:space="preserve">2.97835230827332</t>
   </si>
   <si>
     <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94467735290527</t>
+    <t xml:space="preserve">2.94467759132385</t>
   </si>
   <si>
     <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97086906433105</t>
+    <t xml:space="preserve">2.97086930274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964384078979</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113620758057</t>
+    <t xml:space="preserve">2.83991122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113596916199</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365296363831</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">2.86236119270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86610269546509</t>
+    <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
     <t xml:space="preserve">2.91848611831665</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">2.90726113319397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89229440689087</t>
+    <t xml:space="preserve">2.89229416847229</t>
   </si>
   <si>
     <t xml:space="preserve">2.79875326156616</t>
@@ -1706,16 +1706,16 @@
     <t xml:space="preserve">2.78004479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76882028579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997824668884</t>
+    <t xml:space="preserve">2.76882004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997800827026</t>
   </si>
   <si>
     <t xml:space="preserve">2.76133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88106918334961</t>
+    <t xml:space="preserve">2.88106966018677</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96712732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358593940735</t>
+    <t xml:space="preserve">2.96712708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481116294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1742,58 +1742,58 @@
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487818717957</t>
+    <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30761766433716</t>
+    <t xml:space="preserve">3.3076171875</t>
   </si>
   <si>
     <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3263258934021</t>
+    <t xml:space="preserve">3.32632613182068</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986703872681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3637421131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360830307007</t>
+    <t xml:space="preserve">3.36374187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.44980001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530078887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28142595291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2963924407959</t>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2814257144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32258439064026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
     <t xml:space="preserve">3.13924312591553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11305141448975</t>
+    <t xml:space="preserve">3.11305165290833</t>
   </si>
   <si>
     <t xml:space="preserve">3.06441020965576</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">3.08686017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944348335266</t>
+    <t xml:space="preserve">3.04944324493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425427436829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545689582825</t>
+    <t xml:space="preserve">2.03545665740967</t>
   </si>
   <si>
     <t xml:space="preserve">2.2562141418457</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968873977661</t>
+    <t xml:space="preserve">2.37968850135803</t>
   </si>
   <si>
     <t xml:space="preserve">2.39091324806213</t>
@@ -1832,13 +1832,13 @@
     <t xml:space="preserve">2.43581318855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4994215965271</t>
+    <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438760757446</t>
+    <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574664115906</t>
@@ -1847,16 +1847,16 @@
     <t xml:space="preserve">2.4283299446106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40213823318481</t>
+    <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38343024253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465498924255</t>
+    <t xml:space="preserve">2.38343000411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723853111267</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">2.39839673042297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41710495948792</t>
+    <t xml:space="preserve">2.41710472106934</t>
   </si>
   <si>
     <t xml:space="preserve">2.42458820343018</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">2.4545214176178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4694881439209</t>
+    <t xml:space="preserve">2.46948838233948</t>
   </si>
   <si>
     <t xml:space="preserve">2.5218710899353</t>
@@ -1892,46 +1892,46 @@
     <t xml:space="preserve">2.49193811416626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935481071472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50316286087036</t>
+    <t xml:space="preserve">2.52935457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50316309928894</t>
   </si>
   <si>
     <t xml:space="preserve">2.5069043636322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670400619507</t>
+    <t xml:space="preserve">2.59670424461365</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795111656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768445014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714436531067</t>
+    <t xml:space="preserve">3.15795135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265093803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102376937866</t>
+    <t xml:space="preserve">3.1072199344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0010232925415</t>
   </si>
   <si>
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788778305054</t>
+    <t xml:space="preserve">3.06788802146912</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
@@ -1946,7 +1946,7 @@
     <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182097434998</t>
+    <t xml:space="preserve">3.0718207359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.96955823898315</t>
@@ -1958,37 +1958,37 @@
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989228248596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595885276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842675209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90269374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78076529502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79649782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469824790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896548271179</t>
+    <t xml:space="preserve">2.94989204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9026939868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78076505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7964973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78863167762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536633491516</t>
+    <t xml:space="preserve">2.78863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536609649658</t>
   </si>
   <si>
     <t xml:space="preserve">2.76109910011292</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
+    <t xml:space="preserve">2.63523697853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770440101624</t>
+    <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.686368227005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68243503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63916993141174</t>
+    <t xml:space="preserve">2.68636846542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68243527412415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63917016983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130354881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64703631401062</t>
+    <t xml:space="preserve">2.63130378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6470365524292</t>
   </si>
   <si>
     <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5959050655365</t>
+    <t xml:space="preserve">2.59590530395508</t>
   </si>
   <si>
     <t xml:space="preserve">2.59983825683594</t>
@@ -2078,31 +2078,31 @@
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323271751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510738372803</t>
+    <t xml:space="preserve">2.75323247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510762214661</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970913887024</t>
+    <t xml:space="preserve">2.54084014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970866203308</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150847434998</t>
+    <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544166564941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397613525391</t>
+    <t xml:space="preserve">2.47397637367249</t>
   </si>
   <si>
     <t xml:space="preserve">2.48577570915222</t>
@@ -2117,13 +2117,13 @@
     <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46610975265503</t>
+    <t xml:space="preserve">2.46610999107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40317869186401</t>
+    <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
     <t xml:space="preserve">2.38351273536682</t>
@@ -2135,43 +2135,43 @@
     <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37564659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3913791179657</t>
+    <t xml:space="preserve">2.37564635276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39137935638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31271529197693</t>
+    <t xml:space="preserve">2.39531254768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698300361633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.34024786949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33631443977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36384701728821</t>
+    <t xml:space="preserve">2.33631467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36384677886963</t>
   </si>
   <si>
     <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61557102203369</t>
+    <t xml:space="preserve">2.61557126045227</t>
   </si>
   <si>
     <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716614723206</t>
+    <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503229141235</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87909483909607</t>
+    <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2204,19 +2204,19 @@
     <t xml:space="preserve">2.88696122169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87122869491577</t>
+    <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
     <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92629289627075</t>
+    <t xml:space="preserve">2.92629313468933</t>
   </si>
   <si>
     <t xml:space="preserve">3.0206892490387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96169185638428</t>
+    <t xml:space="preserve">2.9616916179657</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
@@ -2225,34 +2225,34 @@
     <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189630508423</t>
+    <t xml:space="preserve">2.83189606666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009696960449</t>
+    <t xml:space="preserve">2.82009720802307</t>
   </si>
   <si>
     <t xml:space="preserve">2.8515625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809247016907</t>
+    <t xml:space="preserve">2.88302826881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809223175049</t>
   </si>
   <si>
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91056036949158</t>
+    <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876055717468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95775842666626</t>
+    <t xml:space="preserve">2.95775818824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
@@ -2261,79 +2261,79 @@
     <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82796335220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01675629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462267875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00889015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97349095344543</t>
+    <t xml:space="preserve">2.82796311378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729502677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495672225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01675653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035520553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888991355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98529076576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575440406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855563163757</t>
+    <t xml:space="preserve">2.98529100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002163887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09541988372803</t>
+    <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148716926575</t>
+    <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1032862663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.10328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374942779541</t>
+    <t xml:space="preserve">3.19374990463257</t>
   </si>
   <si>
     <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18981647491455</t>
+    <t xml:space="preserve">3.18981671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
@@ -2354,19 +2354,19 @@
     <t xml:space="preserve">3.08744764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06697368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05059480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07106852531433</t>
+    <t xml:space="preserve">3.06697392463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05059504508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374197006226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012108802795</t>
+    <t xml:space="preserve">3.03012084960938</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
@@ -2378,31 +2378,31 @@
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602601051331</t>
+    <t xml:space="preserve">3.03831052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602624893188</t>
   </si>
   <si>
     <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04649996757507</t>
+    <t xml:space="preserve">3.04650020599365</t>
   </si>
   <si>
     <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07516360282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507857322693</t>
+    <t xml:space="preserve">3.0751633644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460485458374</t>
+    <t xml:space="preserve">2.96460461616516</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9031834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908885955811</t>
+    <t xml:space="preserve">2.90318369865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
     <t xml:space="preserve">2.91137313842773</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585690498352</t>
+    <t xml:space="preserve">2.84585666656494</t>
   </si>
   <si>
     <t xml:space="preserve">2.87042546272278</t>
@@ -2435,25 +2435,25 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94003629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223578453064</t>
+    <t xml:space="preserve">2.9400360584259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223602294922</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624607086182</t>
+    <t xml:space="preserve">2.77624583244324</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633062362671</t>
+    <t xml:space="preserve">2.80490946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.89499402046204</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8786153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452030181885</t>
+    <t xml:space="preserve">2.87861490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452006340027</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775225639343</t>
@@ -2483,31 +2483,31 @@
     <t xml:space="preserve">2.97279453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95232057571411</t>
+    <t xml:space="preserve">2.95232081413269</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94413137435913</t>
+    <t xml:space="preserve">2.96869969367981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
     <t xml:space="preserve">2.93184661865234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88680458068848</t>
+    <t xml:space="preserve">2.88680481910706</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309914588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719350814819</t>
+    <t xml:space="preserve">2.81309866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719374656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.82128834724426</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91546773910522</t>
+    <t xml:space="preserve">2.91546750068665</t>
   </si>
   <si>
     <t xml:space="preserve">2.83357286453247</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
+    <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
     <t xml:space="preserve">2.84176206588745</t>
@@ -2546,19 +2546,19 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081462860107</t>
+    <t xml:space="preserve">2.83766746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081486701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034090995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986671447754</t>
+    <t xml:space="preserve">2.78034067153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">2.64521384239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67387700080872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805663108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.67387723922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.743488073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95615839958191</t>
+    <t xml:space="preserve">2.95615863800049</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170742034912</t>
+    <t xml:space="preserve">2.89170718193054</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303664207458</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600372314453</t>
+    <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82725596427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80577230453491</t>
+    <t xml:space="preserve">2.82725620269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82295966148376</t>
+    <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
     <t xml:space="preserve">2.81436586380005</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881684303284</t>
+    <t xml:space="preserve">2.87881708145142</t>
   </si>
   <si>
     <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90459752082825</t>
+    <t xml:space="preserve">2.90459775924683</t>
   </si>
   <si>
     <t xml:space="preserve">2.90889406204224</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69835376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65968322753906</t>
+    <t xml:space="preserve">2.6983540058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65968346595764</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64679312705994</t>
+    <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5479679107666</t>
+    <t xml:space="preserve">2.54796767234802</t>
   </si>
   <si>
     <t xml:space="preserve">2.53507781028748</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">2.47921991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50929713249207</t>
+    <t xml:space="preserve">2.50929737091064</t>
   </si>
   <si>
     <t xml:space="preserve">2.51359391212463</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
+    <t xml:space="preserve">2.44914269447327</t>
   </si>
   <si>
     <t xml:space="preserve">2.43195581436157</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">2.49211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41906595230103</t>
+    <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
     <t xml:space="preserve">2.35891127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34172415733337</t>
+    <t xml:space="preserve">2.34172439575195</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735015869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27727341651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34602117538452</t>
+    <t xml:space="preserve">2.30735039710999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27727317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34602093696594</t>
   </si>
   <si>
     <t xml:space="preserve">2.26867985725403</t>
@@ -2732,22 +2732,22 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35031795501709</t>
+    <t xml:space="preserve">2.3975818157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469195365906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43625259399414</t>
+    <t xml:space="preserve">2.43625283241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40187859535217</t>
+    <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
     <t xml:space="preserve">2.35461449623108</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0624361038208</t>
+    <t xml:space="preserve">2.06243634223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1225905418396</t>
+    <t xml:space="preserve">2.12259030342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985464096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14407396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399698257446</t>
+    <t xml:space="preserve">2.16985487937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14407420158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399722099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197302818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212746620178</t>
+    <t xml:space="preserve">2.02376532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197290897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212734699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322503089905</t>
+    <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869683265686</t>
+    <t xml:space="preserve">1.78744447231293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869671344757</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2846,25 +2846,25 @@
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92494022846222</t>
+    <t xml:space="preserve">1.9249404668808</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790754795074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353378772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650122642517</t>
+    <t xml:space="preserve">1.96790766716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353366851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650110721588</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04954600334167</t>
+    <t xml:space="preserve">2.0495457649231</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524922370911</t>
+    <t xml:space="preserve">2.04524946212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
@@ -2903,34 +2903,34 @@
     <t xml:space="preserve">2.12688708305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13548040390015</t>
+    <t xml:space="preserve">2.13548064231873</t>
   </si>
   <si>
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21282196044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19563508033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837098121643</t>
+    <t xml:space="preserve">2.2128221988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1956353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681010246277</t>
+    <t xml:space="preserve">2.06673288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681034088135</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024073600769</t>
+    <t xml:space="preserve">2.32024049758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860239982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20422840118408</t>
+    <t xml:space="preserve">2.23860263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
     <t xml:space="preserve">2.31594395637512</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438283920288</t>
+    <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313059806824</t>
+    <t xml:space="preserve">2.33313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750483512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42765927314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149273872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22141575813293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27297616004944</t>
+    <t xml:space="preserve">2.36750507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.427659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22141551971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27297639846802</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39328527450562</t>
+    <t xml:space="preserve">2.39328503608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062635421753</t>
+    <t xml:space="preserve">2.47062659263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874121665955</t>
+    <t xml:space="preserve">2.42874097824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.356778383255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280637741089</t>
+    <t xml:space="preserve">2.35677814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280613899231</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237401008606</t>
+    <t xml:space="preserve">2.23084378242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237377166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787624359131</t>
+    <t xml:space="preserve">2.19486260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787648200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337847709656</t>
+    <t xml:space="preserve">2.16337871551514</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189506530762</t>
+    <t xml:space="preserve">2.13189482688904</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06892776489258</t>
+    <t xml:space="preserve">2.068927526474</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591364860535</t>
+    <t xml:space="preserve">2.08691835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591341018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495552062988</t>
+    <t xml:space="preserve">2.01495575904846</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.933997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701138973236</t>
+    <t xml:space="preserve">1.93399751186371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701150894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600704193115</t>
+    <t xml:space="preserve">1.91600692272186</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9115092754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500221729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749057292938</t>
+    <t xml:space="preserve">1.93849527835846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91150915622711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500233650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749045372009</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648574829102</t>
+    <t xml:space="preserve">1.95648598670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050445079803</t>
+    <t xml:space="preserve">1.92050457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902080059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287589550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848340034485</t>
+    <t xml:space="preserve">1.78287577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848328113556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388060092926</t>
+    <t xml:space="preserve">1.77388048171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055126667023</t>
+    <t xml:space="preserve">1.83055114746094</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303938388824</t>
+    <t xml:space="preserve">1.85303950309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347175121307</t>
+    <t xml:space="preserve">1.98347187042236</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246716499329</t>
+    <t xml:space="preserve">1.99246728420258</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844882011414</t>
+    <t xml:space="preserve">2.02844858169556</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194140434265</t>
+    <t xml:space="preserve">2.04194164276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.221848487854</t>
+    <t xml:space="preserve">2.10490894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089059829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22184824943542</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -3831,6 +3831,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.24499988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25999999046326</t>
   </si>
 </sst>
 </file>
@@ -69013,7 +69016,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495949074</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>283363</v>
@@ -69034,6 +69037,32 @@
         <v>1272</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6495833333</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>81288</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>3.27500009536743</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>3.22499990463257</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>3.24499988555908</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="1274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="1275">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862012386322</t>
+    <t xml:space="preserve">1.27862000465393</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2682341337204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26938819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25554025173187</t>
+    <t xml:space="preserve">1.27977383136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26823401451111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26938807964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25554037094116</t>
   </si>
   <si>
     <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515828609467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977028369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2324606180191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784069061279</t>
+    <t xml:space="preserve">1.27515804767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977040290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246037960052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975916385651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283891677856</t>
+    <t xml:space="preserve">1.18283903598785</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438618659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285015583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746593952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26361811161041</t>
+    <t xml:space="preserve">1.25438630580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746203422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285039424896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746605873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26361835002899</t>
   </si>
   <si>
     <t xml:space="preserve">1.20591855049133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2105348110199</t>
+    <t xml:space="preserve">1.21168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053469181061</t>
   </si>
   <si>
     <t xml:space="preserve">1.19207084178925</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">1.20822668075562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23130643367767</t>
+    <t xml:space="preserve">1.23130655288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.22899854183197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23476839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707628250122</t>
+    <t xml:space="preserve">1.23476850986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707640171051</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
@@ -131,82 +131,82 @@
     <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28900599479675</t>
+    <t xml:space="preserve">1.28900575637817</t>
   </si>
   <si>
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28438985347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169609069824</t>
+    <t xml:space="preserve">1.28438997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169597148895</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323602676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054545402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862367153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093192100525</t>
+    <t xml:space="preserve">1.30054569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862379074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093168258667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247149944305</t>
+    <t xml:space="preserve">1.32247173786163</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208574771881</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3074699640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593381404877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016348838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362568378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708775997162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439742565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670543670654</t>
+    <t xml:space="preserve">1.30746960639954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516183376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016360759735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132133960724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439706802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670555591583</t>
   </si>
   <si>
     <t xml:space="preserve">1.3501672744751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478329658508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208929538727</t>
+    <t xml:space="preserve">1.35478341579437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170709133148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208953380585</t>
   </si>
   <si>
     <t xml:space="preserve">1.3432434797287</t>
@@ -215,79 +215,79 @@
     <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36516916751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324726581573</t>
+    <t xml:space="preserve">1.36516928672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324714660645</t>
   </si>
   <si>
     <t xml:space="preserve">1.38017094135284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37786316871643</t>
+    <t xml:space="preserve">1.37786340713501</t>
   </si>
   <si>
     <t xml:space="preserve">1.36747717857361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36286115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621222019196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099989414215</t>
+    <t xml:space="preserve">1.36286103725433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.394979596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251506328583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621198177338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099977493286</t>
   </si>
   <si>
     <t xml:space="preserve">1.42701995372772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550454616547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043396949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536303520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110043048859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863565921783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342333316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821088790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162538051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574647426605</t>
+    <t xml:space="preserve">1.42332303524017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427239894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550442695618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536315441132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275699138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110066890717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863554000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821112632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162514209747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465571880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574659347534</t>
   </si>
   <si>
     <t xml:space="preserve">1.4984940290451</t>
@@ -296,16 +296,16 @@
     <t xml:space="preserve">1.54039287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60816979408264</t>
+    <t xml:space="preserve">1.6081702709198</t>
   </si>
   <si>
     <t xml:space="preserve">1.61433160305023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59707915782928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52437281608582</t>
+    <t xml:space="preserve">1.59707939624786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52437257766724</t>
   </si>
   <si>
     <t xml:space="preserve">1.50958490371704</t>
@@ -314,67 +314,67 @@
     <t xml:space="preserve">1.55641317367554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6007764339447</t>
+    <t xml:space="preserve">1.60077631473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.5465544462204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190804481506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257438659668</t>
+    <t xml:space="preserve">1.52190828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
   </si>
   <si>
     <t xml:space="preserve">1.59584701061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362416744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006864070892</t>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006852149963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59461462497711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64883649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992748737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115963459015</t>
+    <t xml:space="preserve">1.64883661270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992736816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115951538086</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400772571564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950283527374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827068805695</t>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400784492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950307369232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827044963837</t>
   </si>
   <si>
     <t xml:space="preserve">1.72523987293243</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73756325244904</t>
+    <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
     <t xml:space="preserve">1.70429062843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059370994568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675539970398</t>
+    <t xml:space="preserve">1.7005934715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675551891327</t>
   </si>
   <si>
     <t xml:space="preserve">1.71784615516663</t>
@@ -383,136 +383,136 @@
     <t xml:space="preserve">1.75851261615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439116477966</t>
+    <t xml:space="preserve">1.79301714897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604796409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439092636108</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206790447235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865412712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618971347809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837086677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7622092962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699720859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344180107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249243736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443190097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186707019806</t>
+    <t xml:space="preserve">1.7498859167099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837074756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453255653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220941543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699732780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344168186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855370998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249255657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447323322296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035190105438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679661273956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376555919647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049329280853</t>
+    <t xml:space="preserve">1.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679625511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267480373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049317359924</t>
   </si>
   <si>
     <t xml:space="preserve">1.63281655311584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309945583344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6155641078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130126476288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623044967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513981342316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144265651703</t>
+    <t xml:space="preserve">1.61309933662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556398868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802887916565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021027088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760434627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130114555359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623033046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144241809845</t>
   </si>
   <si>
     <t xml:space="preserve">1.63404870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59091782569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546369075775</t>
+    <t xml:space="preserve">1.59091770648956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546392917633</t>
   </si>
   <si>
     <t xml:space="preserve">1.49356472492218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49479734897614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972653388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247396945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845329284668</t>
+    <t xml:space="preserve">1.49479711055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972641468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247408866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.558877825737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845341205597</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503903865814</t>
@@ -524,40 +524,40 @@
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451432704926</t>
+    <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120084762573</t>
+    <t xml:space="preserve">1.57120060920715</t>
   </si>
   <si>
     <t xml:space="preserve">1.58598840236664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58105909824371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200846195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338223934174</t>
+    <t xml:space="preserve">1.581059217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6020085811615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338247776031</t>
   </si>
   <si>
     <t xml:space="preserve">1.5872209072113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63651347160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66485643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6759477853775</t>
+    <t xml:space="preserve">1.63651323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66485667228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499842166901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
   </si>
   <si>
     <t xml:space="preserve">1.6722503900528</t>
@@ -566,91 +566,91 @@
     <t xml:space="preserve">1.67841196060181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073522090912</t>
+    <t xml:space="preserve">1.69073510169983</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978585720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538126468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291697025299</t>
+    <t xml:space="preserve">1.6771799325943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703818321228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552277565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538114547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291720867157</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467430591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727987289429</t>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728046894073</t>
   </si>
   <si>
     <t xml:space="preserve">1.74126005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946186065674</t>
+    <t xml:space="preserve">1.73016905784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330029010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946197986603</t>
   </si>
   <si>
     <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069400787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178524017334</t>
+    <t xml:space="preserve">1.78069412708282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.76590645313263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614838123322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297641277313</t>
+    <t xml:space="preserve">1.81766331195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614814281464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695611476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297629356384</t>
   </si>
   <si>
     <t xml:space="preserve">1.8989964723587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9076224565506</t>
+    <t xml:space="preserve">1.90762269496918</t>
   </si>
   <si>
     <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94459211826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9298038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279345035553</t>
+    <t xml:space="preserve">1.94459164142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9827938079834</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">2.02838945388794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04687428474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729869842529</t>
+    <t xml:space="preserve">2.04687404632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905555725098</t>
+    <t xml:space="preserve">2.05303549766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0949342250824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0998637676239</t>
+    <t xml:space="preserve">2.09493446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.13806509971619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14669156074524</t>
+    <t xml:space="preserve">2.14669132232666</t>
   </si>
   <si>
     <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16887331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1725697517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15655016899109</t>
+    <t xml:space="preserve">2.16887283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17256999015808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18119645118713</t>
@@ -719,28 +719,28 @@
     <t xml:space="preserve">2.16640830039978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21446895599365</t>
+    <t xml:space="preserve">2.21446871757507</t>
   </si>
   <si>
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
+    <t xml:space="preserve">2.17996406555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2132363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2317214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27978134155273</t>
+    <t xml:space="preserve">2.20953917503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323657035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172116279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27978181838989</t>
   </si>
   <si>
     <t xml:space="preserve">2.28717517852783</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">2.33030652999878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289384841919</t>
+    <t xml:space="preserve">2.35877203941345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583306312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289432525635</t>
   </si>
   <si>
     <t xml:space="preserve">2.31477952003479</t>
@@ -764,10 +764,10 @@
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019546508789</t>
+    <t xml:space="preserve">2.25137901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019594192505</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267243385315</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313467979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866145133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3367760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100865364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782956123352</t>
+    <t xml:space="preserve">2.30313444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866121292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33677577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100913047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.35489058494568</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3613600730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36653542518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34065771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901215553284</t>
+    <t xml:space="preserve">2.36135983467102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36653566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065747261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901287078857</t>
   </si>
   <si>
     <t xml:space="preserve">2.34842109680176</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34324550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40535235404968</t>
+    <t xml:space="preserve">2.34324526786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40535259246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31219172477722</t>
+    <t xml:space="preserve">2.31219220161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396680831909</t>
+    <t xml:space="preserve">2.29666519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396656990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.24490928649902</t>
@@ -851,67 +851,67 @@
     <t xml:space="preserve">2.26043581962585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784826278687</t>
+    <t xml:space="preserve">2.25784802436829</t>
   </si>
   <si>
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690530776978</t>
+    <t xml:space="preserve">2.26690578460693</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361538887024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20609259605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903157234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197054862976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771825790405</t>
+    <t xml:space="preserve">2.2060923576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703531265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903109550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3225429058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348586082458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855086326599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26431751251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28890180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879121780396</t>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725648880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855038642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26431775093079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28890204429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2487907409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37041711807251</t>
+    <t xml:space="preserve">2.37041735649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.33548188209534</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">2.35747790336609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28502011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631377220154</t>
+    <t xml:space="preserve">2.28501987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">2.27337503433228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26819896697998</t>
+    <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160042762756</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418774604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3057222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171077728271</t>
+    <t xml:space="preserve">2.33418798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30572247505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359644889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664649009705</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">2.41699743270874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46745920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546318054199</t>
+    <t xml:space="preserve">2.46745944023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546341896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651672363281</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">2.3872377872467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39241337776184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34195137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524128913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40794014930725</t>
+    <t xml:space="preserve">2.39241313934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34195113182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524152755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40793991088867</t>
   </si>
   <si>
     <t xml:space="preserve">2.39370703697205</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">2.37688660621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3626537322998</t>
+    <t xml:space="preserve">2.36265349388123</t>
   </si>
   <si>
     <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31607341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37429928779602</t>
+    <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
     <t xml:space="preserve">2.37753367424011</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492774963379</t>
+    <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">2.10258054733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07346796989441</t>
+    <t xml:space="preserve">2.07346773147583</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788614273071</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993698120117</t>
+    <t xml:space="preserve">2.07993769645691</t>
   </si>
   <si>
     <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12198877334595</t>
+    <t xml:space="preserve">2.12198925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699848175049</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">2.01847743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966051101685</t>
+    <t xml:space="preserve">1.97966063022614</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494692802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0475902557373</t>
+    <t xml:space="preserve">2.02494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04759049415588</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640694618225</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
+    <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12522387504578</t>
+    <t xml:space="preserve">2.12522411346436</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14139771461487</t>
+    <t xml:space="preserve">2.14139723777771</t>
   </si>
   <si>
     <t xml:space="preserve">2.11875438690186</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1511013507843</t>
+    <t xml:space="preserve">2.15110158920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433669090271</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">2.19962286949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28372621536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26755261421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050330162048</t>
+    <t xml:space="preserve">2.28372597694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26755213737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050282478333</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958495140076</t>
@@ -1130,115 +1130,115 @@
     <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069893836975</t>
+    <t xml:space="preserve">2.223224401474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866636276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456845283508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069941520691</t>
   </si>
   <si>
     <t xml:space="preserve">2.1004695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08342027664185</t>
+    <t xml:space="preserve">2.08342051506042</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066534519196</t>
+    <t xml:space="preserve">1.96066558361053</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614161491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591178894043</t>
+    <t xml:space="preserve">2.05614137649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591155052185</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00840353965759</t>
+    <t xml:space="preserve">2.00840330123901</t>
   </si>
   <si>
     <t xml:space="preserve">2.08001041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08682990074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909230232239</t>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909182548523</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99135434627533</t>
+    <t xml:space="preserve">1.99135410785675</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06978058815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794448375702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089493274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9538459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725572109222</t>
+    <t xml:space="preserve">2.0697808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522326469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817407131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794436454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089540958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748542785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384585857391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725560188293</t>
   </si>
   <si>
     <t xml:space="preserve">1.97771489620209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95043587684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361627101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820742607117</t>
+    <t xml:space="preserve">1.95043563842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361615180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
     <t xml:space="preserve">2.18571591377258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41417598724365</t>
+    <t xml:space="preserve">2.41417622566223</t>
   </si>
   <si>
     <t xml:space="preserve">2.28801155090332</t>
@@ -1247,46 +1247,46 @@
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2164044380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889618873596</t>
+    <t xml:space="preserve">2.23004388809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21640467643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889595031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410903930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12774848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387945175171</t>
+    <t xml:space="preserve">2.11410880088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0629608631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1277482509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705948829651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387921333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115787506104</t>
+    <t xml:space="preserve">2.13115811347961</t>
   </si>
   <si>
     <t xml:space="preserve">2.15843725204468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502715110779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15161728858948</t>
+    <t xml:space="preserve">2.15502738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15161752700806</t>
   </si>
   <si>
     <t xml:space="preserve">2.16184687614441</t>
@@ -1295,67 +1295,67 @@
     <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00499391555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0186333656311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955171585083</t>
+    <t xml:space="preserve">2.00499367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863312721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
     <t xml:space="preserve">1.9231573343277</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453426361084</t>
+    <t xml:space="preserve">1.98112440109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453462123871</t>
   </si>
   <si>
     <t xml:space="preserve">2.0766007900238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0936496257782</t>
+    <t xml:space="preserve">2.09364986419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273127555847</t>
+    <t xml:space="preserve">2.05273175239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594526290894</t>
+    <t xml:space="preserve">2.24027395248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594550132751</t>
   </si>
   <si>
     <t xml:space="preserve">2.17207622528076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18912553787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23345398902893</t>
+    <t xml:space="preserve">2.18912577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1925356388092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732231140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.25391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732254981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
@@ -1367,43 +1367,43 @@
     <t xml:space="preserve">2.3152904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30165123939514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30847024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961842536926</t>
+    <t xml:space="preserve">2.30165100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3084704875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961818695068</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892990112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33915901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32210993766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551980018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256887435913</t>
+    <t xml:space="preserve">2.3664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33915948867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32211017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32551956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37325763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39712715148926</t>
+    <t xml:space="preserve">2.3732578754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39712691307068</t>
   </si>
   <si>
     <t xml:space="preserve">2.38689732551575</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43804502487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463492393494</t>
+    <t xml:space="preserve">2.43804526329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
     <t xml:space="preserve">2.43122529983521</t>
@@ -1427,37 +1427,37 @@
     <t xml:space="preserve">2.44827437400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4619140625</t>
+    <t xml:space="preserve">2.46191382408142</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919272422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896337509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034018516541</t>
+    <t xml:space="preserve">2.51306176185608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896313667297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670121192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830832481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558674812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6153576374054</t>
+    <t xml:space="preserve">2.59830784797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558698654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61535739898682</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855266571045</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928778648376</t>
+    <t xml:space="preserve">2.55928754806519</t>
   </si>
   <si>
     <t xml:space="preserve">2.63037919998169</t>
@@ -1487,31 +1487,31 @@
     <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6939868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65657043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160394668579</t>
+    <t xml:space="preserve">2.69398713111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65657067298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160418510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405391693115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031193733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772863388062</t>
+    <t xml:space="preserve">2.66031241416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643710136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766184806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772839546204</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
@@ -1520,88 +1520,88 @@
     <t xml:space="preserve">2.72017860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73140358924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262857437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79127025604248</t>
+    <t xml:space="preserve">2.7314031124115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7912700176239</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83616971969604</t>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623626708984</t>
+    <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
     <t xml:space="preserve">2.82868623733521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82494497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86984443664551</t>
+    <t xml:space="preserve">2.82494473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86984467506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92971086502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89977741241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719410896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331903457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03821849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09060192108154</t>
+    <t xml:space="preserve">2.92971110343933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89977788925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719387054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331879615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03821873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556840896606</t>
+    <t xml:space="preserve">3.10556864738464</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046811103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18040132522583</t>
+    <t xml:space="preserve">3.15046834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18040108680725</t>
   </si>
   <si>
     <t xml:space="preserve">3.16169285774231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12801790237427</t>
+    <t xml:space="preserve">3.12801837921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07937669754028</t>
+    <t xml:space="preserve">3.0793764591217</t>
   </si>
   <si>
     <t xml:space="preserve">3.10931015014648</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">2.99706077575684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583579063416</t>
+    <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">2.91100287437439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474437713623</t>
+    <t xml:space="preserve">2.91474413871765</t>
   </si>
   <si>
     <t xml:space="preserve">3.07189345359802</t>
@@ -1637,25 +1637,25 @@
     <t xml:space="preserve">3.01951026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00454354286194</t>
+    <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835230827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467759132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086930274963</t>
+    <t xml:space="preserve">2.97835206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209404945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841885566711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086906433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964384078979</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75011157989502</t>
+    <t xml:space="preserve">2.7501118183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.802494764328</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85113596916199</t>
+    <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365296363831</t>
@@ -1685,37 +1685,37 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848611831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89603590965271</t>
+    <t xml:space="preserve">2.91848587989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89603614807129</t>
   </si>
   <si>
     <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726113319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229416847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79875326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004479408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76882004737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997800827026</t>
+    <t xml:space="preserve">2.90726065635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79875302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004503250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76881980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88106966018677</t>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590233802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481116294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358617782593</t>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358593940735</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">2.8174614906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957705497742</t>
+    <t xml:space="preserve">2.85487771034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989577293396</t>
   </si>
   <si>
     <t xml:space="preserve">3.3076171875</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632613182068</t>
+    <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986703872681</t>
@@ -1769,46 +1769,46 @@
     <t xml:space="preserve">3.44980001449585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.3562593460083</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24026775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2814257144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258439064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639267921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924312591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305165290833</t>
+    <t xml:space="preserve">3.2402675151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530102729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28142595291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32258415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639291763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924360275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
     <t xml:space="preserve">3.06441020965576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94093585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679339408875</t>
+    <t xml:space="preserve">2.94093561172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679315567017</t>
   </si>
   <si>
     <t xml:space="preserve">3.08686017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944324493408</t>
+    <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425427436829</t>
@@ -1817,19 +1817,19 @@
     <t xml:space="preserve">2.03545665740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2562141418457</t>
+    <t xml:space="preserve">2.25621438026428</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968850135803</t>
+    <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
     <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43581318855286</t>
+    <t xml:space="preserve">2.43581342697144</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942111968994</t>
@@ -1838,22 +1838,22 @@
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438784599304</t>
+    <t xml:space="preserve">2.51438760757446</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574664115906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4283299446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812958717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38343000411987</t>
+    <t xml:space="preserve">2.42832970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812982559204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38342976570129</t>
   </si>
   <si>
     <t xml:space="preserve">2.39465522766113</t>
@@ -1868,88 +1868,88 @@
     <t xml:space="preserve">2.41710472106934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42458820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4133632183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43207168579102</t>
+    <t xml:space="preserve">2.42458844184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41336345672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43207192420959</t>
   </si>
   <si>
     <t xml:space="preserve">2.40962171554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4545214176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46948838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5218710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193811416626</t>
+    <t xml:space="preserve">2.45452165603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46948790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4919376373291</t>
   </si>
   <si>
     <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50316309928894</t>
+    <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
     <t xml:space="preserve">2.5069043636322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670424461365</t>
+    <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795135498047</t>
+    <t xml:space="preserve">3.15795159339905</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17801690101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1072199344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0010232925415</t>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17801713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10721969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788802146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04822182655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968735694885</t>
+    <t xml:space="preserve">3.06788778305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935307502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04822206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968759536743</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0718207359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96955823898315</t>
+    <t xml:space="preserve">3.07182121276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96955800056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.92235970497131</t>
@@ -1967,31 +1967,31 @@
     <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91842651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9026939868927</t>
+    <t xml:space="preserve">2.91842675209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90269374847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8082971572876</t>
+    <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7964973449707</t>
+    <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289867401123</t>
+    <t xml:space="preserve">2.76896548271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289843559265</t>
   </si>
   <si>
     <t xml:space="preserve">2.73749995231628</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109910011292</t>
+    <t xml:space="preserve">2.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523697853088</t>
+    <t xml:space="preserve">2.6352367401123</t>
   </si>
   <si>
     <t xml:space="preserve">2.61950397491455</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74143314361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72963356971741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68636846542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68243527412415</t>
+    <t xml:space="preserve">2.74143290519714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72963333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.686368227005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68243503570557</t>
   </si>
   <si>
     <t xml:space="preserve">2.63917016983032</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6549026966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017230033875</t>
+    <t xml:space="preserve">2.65490293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883612632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017253875732</t>
   </si>
   <si>
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6470365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343716621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59590530395508</t>
+    <t xml:space="preserve">2.63130354881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64703679084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343764305115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
     <t xml:space="preserve">2.59983825683594</t>
@@ -2078,40 +2078,40 @@
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54084014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970866203308</t>
+    <t xml:space="preserve">2.75323271751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904057502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397637367249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48577570915222</t>
+    <t xml:space="preserve">2.50150847434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544142723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117419242859</t>
+    <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
     <t xml:space="preserve">2.4936420917511</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">2.47790932655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40317893028259</t>
+    <t xml:space="preserve">2.40317869186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.38351273536682</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39137935638428</t>
+    <t xml:space="preserve">2.3913791179657</t>
   </si>
   <si>
     <t xml:space="preserve">2.35598039627075</t>
@@ -2147,28 +2147,28 @@
     <t xml:space="preserve">2.39531254768372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29698300361633</t>
+    <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36384677886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557126045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.340247631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36384701728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57230591773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783399581909</t>
+    <t xml:space="preserve">2.71783375740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.70603442192078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210099220276</t>
+    <t xml:space="preserve">2.70210146903992</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2198,25 +2198,25 @@
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594286441803</t>
+    <t xml:space="preserve">2.85942888259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87122845649719</t>
+    <t xml:space="preserve">2.87122821807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92629313468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0206892490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9616916179657</t>
+    <t xml:space="preserve">2.92629289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02068948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83189606666565</t>
+    <t xml:space="preserve">2.83189654350281</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009720802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302826881409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809223175049</t>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809270858765</t>
   </si>
   <si>
     <t xml:space="preserve">2.90662693977356</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">2.89876055717468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.95775842666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">2.82796311378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.93022608757019</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035520553589</t>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888991355896</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98529100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575416564941</t>
+    <t xml:space="preserve">2.98529076576233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575440406799</t>
   </si>
   <si>
     <t xml:space="preserve">3.05215525627136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02855587005615</t>
+    <t xml:space="preserve">3.02855563163757</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002163887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12688541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948266983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2055492401123</t>
+    <t xml:space="preserve">3.12688565254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948243141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20554947853088</t>
   </si>
   <si>
     <t xml:space="preserve">3.19374990463257</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18981671333313</t>
+    <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06287908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.06287884712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05059504508972</t>
+    <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
     <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01374197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03421568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783680915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0055525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831052780151</t>
+    <t xml:space="preserve">3.01374220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012108802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03421545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831076622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02602624893188</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">3.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335304260254</t>
+    <t xml:space="preserve">3.08335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">3.0751633644104</t>
@@ -2399,19 +2399,19 @@
     <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99326825141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96460461616516</t>
+    <t xml:space="preserve">2.99326801300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94822573661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90318369865417</t>
+    <t xml:space="preserve">2.94822597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9031834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.90727853775024</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585666656494</t>
+    <t xml:space="preserve">2.84585690498352</t>
   </si>
   <si>
     <t xml:space="preserve">2.87042546272278</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9400360584259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223602294922</t>
+    <t xml:space="preserve">2.94003629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490946769714</t>
+    <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633086204529</t>
@@ -2459,16 +2459,16 @@
     <t xml:space="preserve">2.89499402046204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88270974159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87861490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452006340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775225639343</t>
+    <t xml:space="preserve">2.88270998001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861514091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.99736285209656</t>
@@ -2477,37 +2477,37 @@
     <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02193164825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97279453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95232081413269</t>
+    <t xml:space="preserve">3.02193140983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97279477119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869969367981</t>
+    <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680481910706</t>
+    <t xml:space="preserve">2.93184685707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680458068848</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309866905212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719374656677</t>
+    <t xml:space="preserve">2.8130989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.82128834724426</t>
@@ -2522,13 +2522,13 @@
     <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91546750068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357286453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.91546773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357262611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2537,25 +2537,25 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176206588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262518882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80900406837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978240013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034067153931</t>
+    <t xml:space="preserve">2.84176230430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80900382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83766722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034090995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.75986695289612</t>
@@ -2564,19 +2564,19 @@
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521384239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387723922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70254039764404</t>
+    <t xml:space="preserve">2.64521360397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387700080872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805639266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348759651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70254015922546</t>
   </si>
   <si>
     <t xml:space="preserve">2.76396179199219</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95615863800049</t>
+    <t xml:space="preserve">2.95615839958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
+    <t xml:space="preserve">2.89170742034912</t>
   </si>
   <si>
     <t xml:space="preserve">2.85303664207458</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82725620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80577254295349</t>
+    <t xml:space="preserve">2.82725596427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80577230453491</t>
   </si>
   <si>
     <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82295942306519</t>
+    <t xml:space="preserve">2.82295966148376</t>
   </si>
   <si>
     <t xml:space="preserve">2.81436586380005</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
+    <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
     <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90459775924683</t>
+    <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
     <t xml:space="preserve">2.90889406204224</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6983540058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.69835376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64679288864136</t>
+    <t xml:space="preserve">2.64679312705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54796767234802</t>
+    <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.53507781028748</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">2.47921991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50929737091064</t>
+    <t xml:space="preserve">2.50929713249207</t>
   </si>
   <si>
     <t xml:space="preserve">2.51359391212463</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
+    <t xml:space="preserve">2.44914293289185</t>
   </si>
   <si>
     <t xml:space="preserve">2.43195581436157</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">2.49211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41906571388245</t>
+    <t xml:space="preserve">2.41906595230103</t>
   </si>
   <si>
     <t xml:space="preserve">2.35891127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27727317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34602093696594</t>
+    <t xml:space="preserve">2.30735015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27727341651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
     <t xml:space="preserve">2.26867985725403</t>
@@ -2732,22 +2732,22 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3975818157196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35031771659851</t>
+    <t xml:space="preserve">2.39758205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469195365906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43625283241272</t>
+    <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40187883377075</t>
+    <t xml:space="preserve">2.40187859535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.35461449623108</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06243634223938</t>
+    <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985487937927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14407420158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399722099304</t>
+    <t xml:space="preserve">2.16985464096069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14407396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322491168976</t>
+    <t xml:space="preserve">1.81322503089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744447231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.78744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2846,25 +2846,25 @@
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
+    <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650110721588</t>
+    <t xml:space="preserve">1.96790754795074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650122642517</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
+    <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524946212769</t>
+    <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
@@ -2903,34 +2903,34 @@
     <t xml:space="preserve">2.12688708305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13548064231873</t>
+    <t xml:space="preserve">2.13548040390015</t>
   </si>
   <si>
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2128221988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1956353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.21282196044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19563508033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681034088135</t>
+    <t xml:space="preserve">2.06673264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20422863960266</t>
+    <t xml:space="preserve">2.23860239982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20422840118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.31594395637512</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438307762146</t>
+    <t xml:space="preserve">2.26438283920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.427659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149250030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22141551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27297639846802</t>
+    <t xml:space="preserve">2.36750483512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42765927314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149273872375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22141575813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27297616004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39328503608704</t>
+    <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062659263611</t>
+    <t xml:space="preserve">2.47062635421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -3834,6 +3834,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.25999999046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23000001907349</t>
   </si>
 </sst>
 </file>
@@ -69042,7 +69045,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6495833333</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>81288</v>
@@ -69063,6 +69066,32 @@
         <v>1273</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6495138889</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>91441</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27861988544464</t>
+    <t xml:space="preserve">1.27862012386322</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977395057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2682341337204</t>
+    <t xml:space="preserve">1.27977406978607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26823425292969</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">1.25554013252258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24861633777618</t>
+    <t xml:space="preserve">1.24861621856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
+    <t xml:space="preserve">1.24977004528046</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437861442566</t>
+    <t xml:space="preserve">1.19437873363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15975916385651</t>
+    <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
     <t xml:space="preserve">1.18283879756927</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">1.25784838199615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438642501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285015583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
+    <t xml:space="preserve">1.25438630580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746593952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.26361811161041</t>
@@ -101,34 +101,34 @@
     <t xml:space="preserve">1.20591866970062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168851852417</t>
+    <t xml:space="preserve">1.21168863773346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21053469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19207096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822668075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130667209625</t>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2082267999649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130655288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.22899854183197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2347686290741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707628250122</t>
+    <t xml:space="preserve">1.23476850986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707664012909</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669786453247</t>
+    <t xml:space="preserve">1.28669774532318</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28439009189606</t>
+    <t xml:space="preserve">1.28438997268677</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323602676392</t>
+    <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
     <t xml:space="preserve">1.30054569244385</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">1.30862379074097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093168258667</t>
+    <t xml:space="preserve">1.31093180179596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477962970734</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">1.32247161865234</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31208574771881</t>
+    <t xml:space="preserve">1.31208550930023</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593369483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016348838806</t>
+    <t xml:space="preserve">1.32593357563019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.32362544536591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32708764076233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439730644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670555591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016751289368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478329658508</t>
+    <t xml:space="preserve">1.32708740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323981285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132133960724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439754486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670543670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35016703605652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478341579437</t>
   </si>
   <si>
     <t xml:space="preserve">1.36170721054077</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">1.34324336051941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516904830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324726581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017094135284</t>
+    <t xml:space="preserve">1.3455513715744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516928672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017106056213</t>
   </si>
   <si>
     <t xml:space="preserve">1.37786304950714</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">1.3674772977829</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36286115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.394979596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251506328583</t>
+    <t xml:space="preserve">1.3628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497983455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251530170441</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621198177338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41100001335144</t>
+    <t xml:space="preserve">1.41099965572357</t>
   </si>
   <si>
     <t xml:space="preserve">1.42701983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687856197357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427251815796</t>
+    <t xml:space="preserve">1.42332303524017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687844276428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427227973938</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550466537476</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">1.45043408870697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46275722980499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110054969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863554000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342345237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162514209747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
+    <t xml:space="preserve">1.4553633928299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863577842712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5034236907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821112632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162538051605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465548038483</t>
   </si>
   <si>
     <t xml:space="preserve">1.51574659347534</t>
@@ -293,73 +293,73 @@
     <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54039287567139</t>
+    <t xml:space="preserve">1.54039299488068</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61433172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707927703857</t>
+    <t xml:space="preserve">1.61433160305023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707951545715</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437281608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958490371704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641281604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6007764339447</t>
+    <t xml:space="preserve">1.50958502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077619552612</t>
   </si>
   <si>
     <t xml:space="preserve">1.54655432701111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958468914032</t>
+    <t xml:space="preserve">1.52190816402435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584712982178</t>
   </si>
   <si>
     <t xml:space="preserve">1.66362416744232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65006911754608</t>
+    <t xml:space="preserve">1.65006852149963</t>
   </si>
   <si>
     <t xml:space="preserve">1.59461462497711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64883649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992724895477</t>
+    <t xml:space="preserve">1.64883661270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992736816406</t>
   </si>
   <si>
     <t xml:space="preserve">1.66115975379944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71661376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154295444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950283527374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
+    <t xml:space="preserve">1.71661400794983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154307365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827068805695</t>
   </si>
   <si>
     <t xml:space="preserve">1.72523999214172</t>
@@ -371,31 +371,31 @@
     <t xml:space="preserve">1.70429050922394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059359073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675528049469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
+    <t xml:space="preserve">1.70059382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675539970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784627437592</t>
   </si>
   <si>
     <t xml:space="preserve">1.75851261615753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79301726818085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604808330536</t>
+    <t xml:space="preserve">1.79301714897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604784488678</t>
   </si>
   <si>
     <t xml:space="preserve">1.78439080715179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77206802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988615512848</t>
+    <t xml:space="preserve">1.77206790447235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988603591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.74865412712097</t>
@@ -404,79 +404,79 @@
     <t xml:space="preserve">1.74618935585022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7683709859848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7745326757431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7622092962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699720859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344168186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746283531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855382919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249243736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158428668976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035142421722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267480373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376603603363</t>
+    <t xml:space="preserve">1.76837074756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453255653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220953464508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699732780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344180107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746247768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855359077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249231815338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186683177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158392906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035190105438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679637432098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376567840576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309933662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556386947632</t>
+    <t xml:space="preserve">1.63281643390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556398868561</t>
   </si>
   <si>
     <t xml:space="preserve">1.61802864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130114555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623033046722</t>
+    <t xml:space="preserve">1.64021027088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760410785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130138397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623044967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.61926090717316</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">1.64513957500458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64144265651703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091782569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546369075775</t>
+    <t xml:space="preserve">1.64144277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091770648956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546345233917</t>
   </si>
   <si>
     <t xml:space="preserve">1.49356508255005</t>
@@ -512,34 +512,34 @@
     <t xml:space="preserve">1.55887758731842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5884530544281</t>
+    <t xml:space="preserve">1.58845317363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503915786743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53423130512238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49726188182831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51451420783997</t>
+    <t xml:space="preserve">1.53423142433167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726176261902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51451408863068</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532194137573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598828315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.581059217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6020085811615</t>
+    <t xml:space="preserve">1.57120072841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105909824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
   </si>
   <si>
     <t xml:space="preserve">1.59338235855103</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
+    <t xml:space="preserve">1.65499830245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
   </si>
   <si>
     <t xml:space="preserve">1.67225050926208</t>
@@ -566,91 +566,91 @@
     <t xml:space="preserve">1.6784120798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073522090912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978585720062</t>
+    <t xml:space="preserve">1.69073510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978597640991</t>
   </si>
   <si>
     <t xml:space="preserve">1.67717945575714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68703830242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7055230140686</t>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
     <t xml:space="preserve">1.71538150310516</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7129168510437</t>
+    <t xml:space="preserve">1.71291661262512</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467418670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946197986603</t>
+    <t xml:space="preserve">1.76467406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016905784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330040931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946209907532</t>
   </si>
   <si>
     <t xml:space="preserve">1.74742162227631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806943655014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150186061859</t>
+    <t xml:space="preserve">1.78069424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178488254547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590657234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8176634311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150221824646</t>
   </si>
   <si>
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695611476898</t>
+    <t xml:space="preserve">1.86695623397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89899611473083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9076224565506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392529964447</t>
+    <t xml:space="preserve">1.8989964723587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762233734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392565727234</t>
   </si>
   <si>
     <t xml:space="preserve">1.94459176063538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980408668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279368877411</t>
+    <t xml:space="preserve">1.92980420589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279356956482</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
@@ -662,28 +662,28 @@
     <t xml:space="preserve">2.04687404632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01483368873596</t>
+    <t xml:space="preserve">2.01483392715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05796504020691</t>
+    <t xml:space="preserve">2.05796432495117</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905579566956</t>
+    <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0949342250824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09986329078674</t>
+    <t xml:space="preserve">2.09493446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.13806533813477</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380213737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531754493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1664080619812</t>
+    <t xml:space="preserve">2.17380237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010521888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640830039978</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446871757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366098403931</t>
+    <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
     <t xml:space="preserve">2.17996382713318</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">2.2317214012146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978134155273</t>
+    <t xml:space="preserve">2.27978157997131</t>
   </si>
   <si>
     <t xml:space="preserve">2.28717541694641</t>
@@ -755,31 +755,31 @@
     <t xml:space="preserve">2.34583306312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289384841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477999687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25526022911072</t>
+    <t xml:space="preserve">2.33289408683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137877464294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267291069031</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973345756531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866145133972</t>
+    <t xml:space="preserve">2.30313444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866121292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.33677577972412</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782932281494</t>
+    <t xml:space="preserve">2.36782908439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054664611816</t>
+    <t xml:space="preserve">2.30054688453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.33806967735291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34453916549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36135983467102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36653566360474</t>
+    <t xml:space="preserve">2.34453940391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36136031150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
     <t xml:space="preserve">2.34065747261047</t>
@@ -815,100 +815,100 @@
     <t xml:space="preserve">2.32901263237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34842133522034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971499443054</t>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31219148635864</t>
+    <t xml:space="preserve">2.40535187721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642436027527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537129402161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666495323181</t>
+    <t xml:space="preserve">2.29666519165039</t>
   </si>
   <si>
     <t xml:space="preserve">2.25396633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24490928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949286460876</t>
+    <t xml:space="preserve">2.2449095249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
     <t xml:space="preserve">2.26043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26172971725464</t>
+    <t xml:space="preserve">2.25784802436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
     <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24361515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20609259605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703483581543</t>
+    <t xml:space="preserve">2.24361538887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2060923576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903109550476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3225429058075</t>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254266738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.31736755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32771849632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407715797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725648880005</t>
+    <t xml:space="preserve">2.32771873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348586082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407739639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26431798934937</t>
+    <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
     <t xml:space="preserve">2.28890156745911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2487907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.24879121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">2.35747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28502035140991</t>
+    <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
     <t xml:space="preserve">2.28631377220154</t>
@@ -938,28 +938,28 @@
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418822288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3057222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359644889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171125411987</t>
+    <t xml:space="preserve">2.33418798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30572247505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699719429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
+    <t xml:space="preserve">2.41699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745944023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546294212341</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">2.38723754882812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39241337776184</t>
+    <t xml:space="preserve">2.39241361618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34195137023926</t>
@@ -980,133 +980,133 @@
     <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40794014930725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.40793991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3937075138092</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688684463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36265397071838</t>
+    <t xml:space="preserve">2.36265349388123</t>
   </si>
   <si>
     <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.316073179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076829910278</t>
+    <t xml:space="preserve">2.31607365608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459493637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076853752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429881095886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
+    <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492774963379</t>
+    <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346820831299</t>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346796989441</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08964157104492</t>
+    <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
     <t xml:space="preserve">2.07993769645691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11551952362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198925018311</t>
+    <t xml:space="preserve">2.11551976203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198877334595</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699872016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05082440376282</t>
+    <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
     <t xml:space="preserve">2.02818155288696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01847720146179</t>
+    <t xml:space="preserve">2.01847767829895</t>
   </si>
   <si>
     <t xml:space="preserve">1.97966051101685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01524305343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494716644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04759001731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640694618225</t>
+    <t xml:space="preserve">2.0152428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494692802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0475902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640670776367</t>
   </si>
   <si>
     <t xml:space="preserve">2.04112076759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
+    <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12522411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10581564903259</t>
+    <t xml:space="preserve">2.12522435188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
     <t xml:space="preserve">2.06052923202515</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06376361846924</t>
+    <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934616088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875462532043</t>
+    <t xml:space="preserve">2.10905051231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875438690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433621406555</t>
+    <t xml:space="preserve">2.15110158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
     <t xml:space="preserve">2.19962286949158</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755261421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2505030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958471298218</t>
+    <t xml:space="preserve">2.26755237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460168838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433886528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751866340637</t>
+    <t xml:space="preserve">2.223224401474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433838844299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751890182495</t>
   </si>
   <si>
     <t xml:space="preserve">2.11069917678833</t>
@@ -1151,28 +1151,28 @@
     <t xml:space="preserve">2.1004695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08342051506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0493221282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066582202911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01181364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05614161491394</t>
+    <t xml:space="preserve">2.08342027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96066558361053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0118134021759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.04591202735901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227257728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840377807617</t>
+    <t xml:space="preserve">2.03227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
     <t xml:space="preserve">2.08001017570496</t>
@@ -1181,82 +1181,82 @@
     <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02886271476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909206390381</t>
+    <t xml:space="preserve">2.02886247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909230232239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99135410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09024024009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817419052124</t>
+    <t xml:space="preserve">1.99135398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09024000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522326469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817395210266</t>
   </si>
   <si>
     <t xml:space="preserve">1.98794424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97089517116547</t>
+    <t xml:space="preserve">1.97089529037476</t>
   </si>
   <si>
     <t xml:space="preserve">1.96748530864716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9538459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725584030151</t>
+    <t xml:space="preserve">1.95384609699249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725560188293</t>
   </si>
   <si>
     <t xml:space="preserve">1.9777147769928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95043563842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361650943756</t>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361639022827</t>
   </si>
   <si>
     <t xml:space="preserve">2.14138793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14820718765259</t>
+    <t xml:space="preserve">2.14820742607117</t>
   </si>
   <si>
     <t xml:space="preserve">2.185715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41417574882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801131248474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663426399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004412651062</t>
+    <t xml:space="preserve">2.41417598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004388809204</t>
   </si>
   <si>
     <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17889642715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13797807693481</t>
+    <t xml:space="preserve">2.17889618873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
     <t xml:space="preserve">2.11410880088806</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1209282875061</t>
+    <t xml:space="preserve">2.12092876434326</t>
   </si>
   <si>
     <t xml:space="preserve">2.13115835189819</t>
@@ -1286,31 +1286,31 @@
     <t xml:space="preserve">2.15502738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15161752700806</t>
+    <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
     <t xml:space="preserve">2.16184687614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06637072563171</t>
+    <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
     <t xml:space="preserve">2.00499367713928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955123901367</t>
+    <t xml:space="preserve">2.01863288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
     <t xml:space="preserve">1.92315721511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453462123871</t>
+    <t xml:space="preserve">1.9811247587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453450202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594550132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207646369934</t>
+    <t xml:space="preserve">2.24027371406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207622528076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18912577629089</t>
@@ -1343,55 +1343,55 @@
     <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23345398902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23686337471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391316413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506110191345</t>
+    <t xml:space="preserve">2.23345375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23686361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483127593994</t>
+    <t xml:space="preserve">2.29483103752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.31529021263123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30165100097656</t>
+    <t xml:space="preserve">2.30165076255798</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961866378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233952522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
+    <t xml:space="preserve">2.35961842536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36643838882446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892966270447</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32211017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32552003860474</t>
+    <t xml:space="preserve">2.32210993766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
@@ -1400,37 +1400,37 @@
     <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3732578754425</t>
+    <t xml:space="preserve">2.37325811386108</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666773796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099547386169</t>
+    <t xml:space="preserve">2.38689708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804502487183</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43463492393494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43122553825378</t>
+    <t xml:space="preserve">2.43463516235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46191382408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942255020142</t>
+    <t xml:space="preserve">2.4619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
     <t xml:space="preserve">2.51306176185608</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">2.47896313667297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52670097351074</t>
+    <t xml:space="preserve">2.52670121192932</t>
   </si>
   <si>
     <t xml:space="preserve">2.54034066200256</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830808639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558674812317</t>
+    <t xml:space="preserve">2.59830784797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558698654175</t>
   </si>
   <si>
     <t xml:space="preserve">2.61535739898682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88855242729187</t>
+    <t xml:space="preserve">2.88855266571045</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61167073249817</t>
+    <t xml:space="preserve">2.61167097091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.56677103042603</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908695220947</t>
+    <t xml:space="preserve">2.65657067298889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
     <t xml:space="preserve">2.64160370826721</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643710136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772887229919</t>
+    <t xml:space="preserve">2.71643686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766184806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7201783657074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73140358924866</t>
+    <t xml:space="preserve">2.72017860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73140335083008</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262833595276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85861921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79126977920532</t>
+    <t xml:space="preserve">2.85861968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7912700176239</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137195110321</t>
+    <t xml:space="preserve">2.81371998786926</t>
   </si>
   <si>
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868623733521</t>
+    <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984467506409</t>
+    <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
@@ -1571,10 +1571,10 @@
     <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03821873664856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09060168266296</t>
+    <t xml:space="preserve">3.03821849822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09060215950012</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
@@ -1583,19 +1583,19 @@
     <t xml:space="preserve">3.10556817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12053489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046811103821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18040156364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801837921143</t>
+    <t xml:space="preserve">3.12053513526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046834945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18040132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16169333457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801790237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
@@ -1604,22 +1604,22 @@
     <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10931038856506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434342384338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04570174217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99706029891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583555221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9746105670929</t>
+    <t xml:space="preserve">3.10931015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434366226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0457022190094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99706053733826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583579063416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97461032867432</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
@@ -1628,40 +1628,40 @@
     <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07189345359802</t>
+    <t xml:space="preserve">3.0718936920166</t>
   </si>
   <si>
     <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951050758362</t>
+    <t xml:space="preserve">3.01951026916504</t>
   </si>
   <si>
     <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90351915359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835230827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467759132385</t>
+    <t xml:space="preserve">2.90351939201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209404945374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
     <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97086930274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964407920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739446640015</t>
+    <t xml:space="preserve">2.97086906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964431762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113620758057</t>
+    <t xml:space="preserve">2.83991146087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113644599915</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365272521973</t>
@@ -1682,34 +1682,34 @@
     <t xml:space="preserve">2.86236119270325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86610293388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848587989807</t>
+    <t xml:space="preserve">2.86610269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229416847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.798752784729</t>
+    <t xml:space="preserve">2.92596912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79875326156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004503250122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76881980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997800827026</t>
+    <t xml:space="preserve">2.76882028579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76133680343628</t>
@@ -1718,19 +1718,19 @@
     <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00828528404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0307354927063</t>
+    <t xml:space="preserve">3.00828552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03073573112488</t>
   </si>
   <si>
     <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96712732315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481140136719</t>
+    <t xml:space="preserve">2.96712708473206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481092453003</t>
   </si>
   <si>
     <t xml:space="preserve">2.87358617782593</t>
@@ -1742,37 +1742,37 @@
     <t xml:space="preserve">2.81746125221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487818717957</t>
+    <t xml:space="preserve">2.85487771034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986727714539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36374163627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2664589881897</t>
+    <t xml:space="preserve">3.30761766433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986703872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36374187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44979977607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625863075256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26645922660828</t>
   </si>
   <si>
     <t xml:space="preserve">3.24026775360107</t>
@@ -1781,103 +1781,103 @@
     <t xml:space="preserve">3.22530126571655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2814257144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258439064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639267921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924360275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06441020965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679315567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944348335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425451278687</t>
+    <t xml:space="preserve">3.28142595291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32258415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924336433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440997123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08685994148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425403594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25621438026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853030204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37968850135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581318855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942135810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48445439338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51438784599304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46574640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42832970619202</t>
+    <t xml:space="preserve">2.2562141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853054046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37968873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091324806213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581295013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48445463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51438760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46574664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4283299446106</t>
   </si>
   <si>
     <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51812982559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38343024253845</t>
+    <t xml:space="preserve">2.51812958717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
     <t xml:space="preserve">2.39465498924255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35723853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839673042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41336369514465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43207144737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40962195396423</t>
+    <t xml:space="preserve">2.35723876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710519790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41336297988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43207168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40962171554565</t>
   </si>
   <si>
     <t xml:space="preserve">2.4545214176178</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187132835388</t>
+    <t xml:space="preserve">2.5218710899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.49193787574768</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50316309928894</t>
+    <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
     <t xml:space="preserve">2.50690460205078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670424461365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78752827644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15795159339905</t>
+    <t xml:space="preserve">2.59670400619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7875280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15795111656189</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
@@ -1916,22 +1916,22 @@
     <t xml:space="preserve">3.27768421173096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714412689209</t>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102376937866</t>
+    <t xml:space="preserve">3.10721945762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788778305054</t>
+    <t xml:space="preserve">3.06788802146912</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
@@ -1940,40 +1940,40 @@
     <t xml:space="preserve">3.04822182655334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07968735694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12295269966125</t>
+    <t xml:space="preserve">3.07968711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182097434998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96955823898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92235994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94202542304993</t>
+    <t xml:space="preserve">2.96955847740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92235970497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595885276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842675209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
+    <t xml:space="preserve">2.97742438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595909118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
     <t xml:space="preserve">2.8082971572876</t>
@@ -1985,22 +1985,22 @@
     <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78469777107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896500587463</t>
+    <t xml:space="preserve">2.78469800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896548271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863143920898</t>
+    <t xml:space="preserve">2.73749971389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863120079041</t>
   </si>
   <si>
     <t xml:space="preserve">2.74536633491516</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
+    <t xml:space="preserve">2.63523650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.62737059593201</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770463943481</t>
+    <t xml:space="preserve">2.60770440101624</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">2.74143314361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963356971741</t>
+    <t xml:space="preserve">2.72963333129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63917016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670227050781</t>
+    <t xml:space="preserve">2.6391704082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
     <t xml:space="preserve">2.65490293502808</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">2.58017230033875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58410573005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63130402565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64703679084778</t>
+    <t xml:space="preserve">2.58410549163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63130354881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64703631401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.62343740463257</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983849525452</t>
+    <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096974372864</t>
@@ -2081,25 +2081,25 @@
     <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510762214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904105186462</t>
+    <t xml:space="preserve">2.52510786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904057502747</t>
   </si>
   <si>
     <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150847434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544166564941</t>
+    <t xml:space="preserve">2.48970866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330780982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397613525391</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46610975265503</t>
+    <t xml:space="preserve">2.46610999107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45431017875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.399245262146</t>
+    <t xml:space="preserve">2.45430994033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
@@ -2141,73 +2141,73 @@
     <t xml:space="preserve">2.3913791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35598063468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698252677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31271553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36384701728821</t>
+    <t xml:space="preserve">2.35598039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531254768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34024739265442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36384677886963</t>
   </si>
   <si>
     <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356676101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716614723206</t>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356652259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783375740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69030165672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70603466033936</t>
+    <t xml:space="preserve">2.71783399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6903018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7060341835022</t>
   </si>
   <si>
     <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89482736587524</t>
+    <t xml:space="preserve">2.89482760429382</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594286441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88696098327637</t>
+    <t xml:space="preserve">2.85942840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88696122169495</t>
   </si>
   <si>
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449356079102</t>
+    <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">3.02068948745728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9616916179657</t>
+    <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8476288318634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8515625</t>
+    <t xml:space="preserve">2.84762907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88302779197693</t>
@@ -2246,19 +2246,19 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.91056036949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775842666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.95382523536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516140937805</t>
+    <t xml:space="preserve">2.87516164779663</t>
   </si>
   <si>
     <t xml:space="preserve">2.82796335220337</t>
@@ -2270,34 +2270,34 @@
     <t xml:space="preserve">2.93022608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00495648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035520553589</t>
+    <t xml:space="preserve">3.00495672225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98922371864319</t>
+    <t xml:space="preserve">2.97349143028259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575440406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0521547794342</t>
+    <t xml:space="preserve">3.07575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215525627136</t>
   </si>
   <si>
     <t xml:space="preserve">3.02855587005615</t>
@@ -2306,49 +2306,49 @@
     <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428839683533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148693084717</t>
+    <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1032862663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.10328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1544177532196</t>
+    <t xml:space="preserve">3.19374966621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
     <t xml:space="preserve">3.18981671333313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21029019355774</t>
+    <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
     <t xml:space="preserve">3.10382652282715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06287884712219</t>
+    <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
     <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12839484214783</t>
+    <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783680915833</t>
+    <t xml:space="preserve">3.07106852531433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012108802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03421568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">3.03831052780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02602601051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468940734863</t>
+    <t xml:space="preserve">3.02602624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335280418396</t>
+    <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
     <t xml:space="preserve">3.0751633644104</t>
@@ -2402,46 +2402,46 @@
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460461616516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93594169616699</t>
+    <t xml:space="preserve">2.96460485458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908838272095</t>
+    <t xml:space="preserve">2.9031834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
     <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585690498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87042570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91956281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003629684448</t>
+    <t xml:space="preserve">2.84585666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87042546272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91956257820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9400360584259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404634475708</t>
+    <t xml:space="preserve">2.85404658317566</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624607086182</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490946769714</t>
+    <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89499425888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88270950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87861490249634</t>
+    <t xml:space="preserve">2.89499402046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88270974159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861514091492</t>
   </si>
   <si>
     <t xml:space="preserve">2.87452006340027</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989173412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">2.99736285209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98917365074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2489,34 +2489,34 @@
     <t xml:space="preserve">2.92365717887878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869993209839</t>
+    <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680481910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82947778701782</t>
+    <t xml:space="preserve">2.9318470954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8294780254364</t>
   </si>
   <si>
     <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81719374656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82128834724426</t>
+    <t xml:space="preserve">2.81719350814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82128810882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
+    <t xml:space="preserve">2.84995150566101</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051025390625</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357262611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.83357286453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176230430603</t>
+    <t xml:space="preserve">2.84176206588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2546,34 +2546,34 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978216171265</t>
+    <t xml:space="preserve">2.83766722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081486701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6697826385498</t>
   </si>
   <si>
     <t xml:space="preserve">2.78034067153931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75986671447754</t>
+    <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521360397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387723922729</t>
+    <t xml:space="preserve">2.64521384239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387700080872</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.74348759651184</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939347267151</t>
+    <t xml:space="preserve">2.7271089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939299583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.95615839958191</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303664207458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83155274391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89600372314453</t>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873962402344</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717874526978</t>
+    <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
+    <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
     <t xml:space="preserve">2.5479679107666</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4878134727478</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195605278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35031771659851</t>
+    <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469171524048</t>
@@ -2744,46 +2744,46 @@
     <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883405685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33742737770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28156971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711850166321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10540342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13118386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829352378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110688209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.3546142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898825645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883381843567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33742761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711874008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10540366172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13118410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10110664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08392000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
+    <t xml:space="preserve">2.08391976356506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
   </si>
   <si>
     <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89056658744812</t>
+    <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322503089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041203022003</t>
+    <t xml:space="preserve">1.81322491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041214942932</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">1.67744791507721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65854239463806</t>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416851520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729015350342</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
+    <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">1.93353378772736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97650134563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2876,28 +2876,28 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95931434631348</t>
+    <t xml:space="preserve">1.95931422710419</t>
   </si>
   <si>
     <t xml:space="preserve">2.07962322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08821678161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524946212769</t>
+    <t xml:space="preserve">2.08821654319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17844796180725</t>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2915,67 +2915,67 @@
     <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
+    <t xml:space="preserve">2.06673264503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133830070496</t>
+    <t xml:space="preserve">2.10969996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28586649894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.23000907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28586673736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26438283920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40617537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609815597534</t>
+    <t xml:space="preserve">2.32453751564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40617561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609839439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313059806824</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.427659034729</t>
+    <t xml:space="preserve">2.42765927314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149250030518</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
+    <t xml:space="preserve">2.27297616004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062659263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070405006409</t>
+    <t xml:space="preserve">2.47062635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -69187,7 +69187,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.691099537</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>50200</v>
@@ -69208,6 +69208,32 @@
         <v>1278</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.691087963</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>47826</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1279" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1280">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,46 +38,46 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862012386322</t>
+    <t xml:space="preserve">1.27862000465393</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26823425292969</t>
+    <t xml:space="preserve">1.27977383136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2682341337204</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554013252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861621856689</t>
+    <t xml:space="preserve">1.25554025173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977004528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246037960052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283879756927</t>
+    <t xml:space="preserve">1.24977040290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246026039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437861442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1597592830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784838199615</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.25438630580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746227264404</t>
+    <t xml:space="preserve">1.24746239185333</t>
   </si>
   <si>
     <t xml:space="preserve">1.27285003662109</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.20591866970062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168863773346</t>
+    <t xml:space="preserve">1.21168851852417</t>
   </si>
   <si>
     <t xml:space="preserve">1.21053469181061</t>
@@ -110,100 +110,100 @@
     <t xml:space="preserve">1.19207084178925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2082267999649</t>
+    <t xml:space="preserve">1.20822668075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899854183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476850986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707664012909</t>
+    <t xml:space="preserve">1.22899842262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669774532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900587558746</t>
+    <t xml:space="preserve">1.28669798374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900599479675</t>
   </si>
   <si>
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28438997268677</t>
+    <t xml:space="preserve">1.28439009189606</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323590755463</t>
+    <t xml:space="preserve">1.28323602676392</t>
   </si>
   <si>
     <t xml:space="preserve">1.30054569244385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862379074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093180179596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477962970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208550930023</t>
+    <t xml:space="preserve">1.30862367153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093168258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247173786163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516195297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016360759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362544536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323981285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824158668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016703605652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478341579437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516183376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016348838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362568378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824146747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439742565155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670555591583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35016751289368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478329658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170709133148</t>
   </si>
   <si>
     <t xml:space="preserve">1.34208953380585</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">1.3455513715744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36516928672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324714660645</t>
+    <t xml:space="preserve">1.36516916751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324726581573</t>
   </si>
   <si>
     <t xml:space="preserve">1.38017106056213</t>
@@ -227,94 +227,94 @@
     <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3674772977829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3628613948822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497983455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251530170441</t>
+    <t xml:space="preserve">1.36747682094574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497971534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251518249512</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621198177338</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41099965572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332303524017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427227973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550466537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043408870697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4553633928299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
+    <t xml:space="preserve">1.41099977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427216053009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550454616547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043396949768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536291599274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275722980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48863577842712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5034236907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821112632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162538051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465548038483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039299488068</t>
+    <t xml:space="preserve">1.48863554000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342357158661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821100711823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162526130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574647426605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849426746368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5403927564621</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61433160305023</t>
+    <t xml:space="preserve">1.61433148384094</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707951545715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52437281608582</t>
+    <t xml:space="preserve">1.52437269687653</t>
   </si>
   <si>
     <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55641269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
+    <t xml:space="preserve">1.55641293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077631473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.54655432701111</t>
@@ -323,43 +323,43 @@
     <t xml:space="preserve">1.52190816402435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56257450580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59584712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362416744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006852149963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461462497711</t>
+    <t xml:space="preserve">1.56257462501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5946147441864</t>
   </si>
   <si>
     <t xml:space="preserve">1.64883661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65992736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115975379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661400794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400772571564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950319290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827068805695</t>
+    <t xml:space="preserve">1.65992724895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115987300873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661388874054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400784492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950295448303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827056884766</t>
   </si>
   <si>
     <t xml:space="preserve">1.72523999214172</t>
@@ -368,88 +368,88 @@
     <t xml:space="preserve">1.73756325244904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429050922394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059382915497</t>
+    <t xml:space="preserve">1.70429074764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059370994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.70675539970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71784627437592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851261615753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301714897156</t>
+    <t xml:space="preserve">1.71784639358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
   </si>
   <si>
     <t xml:space="preserve">1.75604784488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78439080715179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206790447235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865412712097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837074756622</t>
+    <t xml:space="preserve">1.78439104557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865424633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7461895942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837110519409</t>
   </si>
   <si>
     <t xml:space="preserve">1.77453255653381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76220953464508</t>
+    <t xml:space="preserve">1.76220941543579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699732780457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76344180107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746247768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855359077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249231815338</t>
+    <t xml:space="preserve">1.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855347156525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249267578125</t>
   </si>
   <si>
     <t xml:space="preserve">1.69443202018738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61186683177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158392906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035190105438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376567840576</t>
+    <t xml:space="preserve">1.61186707019806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447323322296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267480373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376591682434</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049341201782</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">1.63281643390656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309957504272</t>
+    <t xml:space="preserve">1.61309945583344</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556398868561</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">1.61802864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021027088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130138397217</t>
+    <t xml:space="preserve">1.64021039009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760434627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130126476288</t>
   </si>
   <si>
     <t xml:space="preserve">1.65623044967651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926090717316</t>
+    <t xml:space="preserve">1.61926102638245</t>
   </si>
   <si>
     <t xml:space="preserve">1.64513957500458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64144277572632</t>
+    <t xml:space="preserve">1.64144253730774</t>
   </si>
   <si>
     <t xml:space="preserve">1.63404870033264</t>
@@ -494,28 +494,28 @@
     <t xml:space="preserve">1.59091770648956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53546345233917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479734897614</t>
+    <t xml:space="preserve">1.53546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356472492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48247396945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845317363739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503915786743</t>
+    <t xml:space="preserve">1.48247408866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887746810913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884530544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503903865814</t>
   </si>
   <si>
     <t xml:space="preserve">1.53423142433167</t>
@@ -524,157 +524,157 @@
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532194137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120072841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598840236664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105909824371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200846195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338235855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722078800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651323318481</t>
+    <t xml:space="preserve">1.51451420783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532182216644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120060920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598828315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105933666229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338223934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722054958344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651311397552</t>
   </si>
   <si>
     <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499830245972</t>
+    <t xml:space="preserve">1.65499794483185</t>
   </si>
   <si>
     <t xml:space="preserve">1.67594754695892</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67225050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6784120798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073510169983</t>
+    <t xml:space="preserve">1.6722503900528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841219902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073522090912</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717945575714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703806400299</t>
+    <t xml:space="preserve">1.67717969417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703818321228</t>
   </si>
   <si>
     <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538150310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291661262512</t>
+    <t xml:space="preserve">1.71538162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291673183441</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467406749725</t>
+    <t xml:space="preserve">1.76467442512512</t>
   </si>
   <si>
     <t xml:space="preserve">1.75728011131287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74126017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016905784607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330040931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946209907532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742162227631</t>
+    <t xml:space="preserve">1.74126005172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330052852631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946197986603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7474217414856</t>
   </si>
   <si>
     <t xml:space="preserve">1.78069424629211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178488254547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590657234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8176634311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150221824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614838123322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297617435455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762233734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392565727234</t>
+    <t xml:space="preserve">1.79178512096405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590621471405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8669558763504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297641277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762257575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392541885376</t>
   </si>
   <si>
     <t xml:space="preserve">1.94459176063538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980420589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279356956482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687404632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483392715454</t>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279345035553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00867247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838921546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0468738079071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05796432495117</t>
+    <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905555725098</t>
+    <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.13806533813477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14669132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024708747864</t>
+    <t xml:space="preserve">2.14669156074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887307167053</t>
@@ -701,43 +701,43 @@
     <t xml:space="preserve">2.17257022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15655016899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119621276855</t>
+    <t xml:space="preserve">2.15654993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119645118713</t>
   </si>
   <si>
     <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17010521888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640830039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
+    <t xml:space="preserve">2.17010545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531754493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640853881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2181658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2317214012146</t>
+    <t xml:space="preserve">2.17996406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2132363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
     <t xml:space="preserve">2.27978157997131</t>
@@ -749,82 +749,82 @@
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877203941345</t>
+    <t xml:space="preserve">2.35877180099487</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583306312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289408683777</t>
+    <t xml:space="preserve">2.33289432525635</t>
   </si>
   <si>
     <t xml:space="preserve">2.31477952003479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137877464294</t>
+    <t xml:space="preserve">2.25526070594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137901306152</t>
   </si>
   <si>
     <t xml:space="preserve">2.29019570350647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25267291069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973345756531</t>
+    <t xml:space="preserve">2.25267267227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
     <t xml:space="preserve">2.30313444137573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31866121292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33677577972412</t>
+    <t xml:space="preserve">2.31866145133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3367760181427</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806967735291</t>
+    <t xml:space="preserve">2.36782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36136031150818</t>
+    <t xml:space="preserve">2.36135959625244</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065747261047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901263237</t>
+    <t xml:space="preserve">2.34065771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901239395142</t>
   </si>
   <si>
     <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971475601196</t>
+    <t xml:space="preserve">2.34971499443054</t>
   </si>
   <si>
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535187721252</t>
+    <t xml:space="preserve">2.40535259246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642436027527</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">2.29666519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2449095249176</t>
+    <t xml:space="preserve">2.25396656990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26043605804443</t>
+    <t xml:space="preserve">2.26043558120728</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784802436829</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690530776978</t>
+    <t xml:space="preserve">2.26690554618835</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361538887024</t>
@@ -866,28 +866,28 @@
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703507423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903109550476</t>
+    <t xml:space="preserve">2.19703483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197031021118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736755371094</t>
+    <t xml:space="preserve">2.24102759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736731529236</t>
   </si>
   <si>
     <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31348586082458</t>
+    <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
     <t xml:space="preserve">2.29407739639282</t>
@@ -896,40 +896,40 @@
     <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855062484741</t>
+    <t xml:space="preserve">2.27855038642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890156745911</t>
+    <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
     <t xml:space="preserve">2.24879121780396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29278326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041711807251</t>
+    <t xml:space="preserve">2.29278349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041735649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.33548188209534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747814178467</t>
+    <t xml:space="preserve">2.35747838020325</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631377220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819944381714</t>
+    <t xml:space="preserve">2.28631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337455749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819920539856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160042762756</t>
@@ -938,37 +938,37 @@
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572247505188</t>
+    <t xml:space="preserve">2.33418822288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3057222366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359668731689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171101570129</t>
+    <t xml:space="preserve">2.37171053886414</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745944023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38723754882812</t>
+    <t xml:space="preserve">2.41699719429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546341896057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3872377872467</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241361618042</t>
@@ -980,49 +980,49 @@
     <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40793991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3937075138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37688684463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36265349388123</t>
+    <t xml:space="preserve">2.40794038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39370727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37688636779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36265397071838</t>
   </si>
   <si>
     <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31607365608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459493637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076853752136</t>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459469795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429881095886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930828094482</t>
+    <t xml:space="preserve">2.37753367424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3193085193634</t>
   </si>
   <si>
     <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346796989441</t>
+    <t xml:space="preserve">2.04435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258102416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
@@ -1031,37 +1031,37 @@
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993769645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551976203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198877334595</t>
+    <t xml:space="preserve">2.07993721961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198901176453</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699872016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05082488059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966051101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0152428150177</t>
+    <t xml:space="preserve">2.0508246421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847720146179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966063022614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524305343628</t>
   </si>
   <si>
     <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0475902557373</t>
+    <t xml:space="preserve">2.04759001731873</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640670776367</t>
@@ -1076,52 +1076,52 @@
     <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12522435188293</t>
+    <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052923202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905051231384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139723777771</t>
+    <t xml:space="preserve">2.06052899360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376338005066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934592247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
     <t xml:space="preserve">2.11875438690186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12845849990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110158920288</t>
+    <t xml:space="preserve">2.12845873832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962286949158</t>
+    <t xml:space="preserve">2.19962310791016</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050330162048</t>
+    <t xml:space="preserve">2.26755261421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460144996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958495140076</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">2.04932165145874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066558361053</t>
+    <t xml:space="preserve">1.96066582202911</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591202735901</t>
+    <t xml:space="preserve">2.05614161491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591178894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00840353965759</t>
+    <t xml:space="preserve">2.00840330123901</t>
   </si>
   <si>
     <t xml:space="preserve">2.08001017570496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08683013916016</t>
+    <t xml:space="preserve">2.08682990074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.02886247634888</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99135398864746</t>
+    <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
@@ -1202,85 +1202,85 @@
     <t xml:space="preserve">2.01522326469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817395210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794424533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089529037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748530864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384609699249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725560188293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9777147769928</t>
+    <t xml:space="preserve">1.99817419052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089517116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748518943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384573936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725572109222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771513462067</t>
   </si>
   <si>
     <t xml:space="preserve">1.95043587684631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94361639022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820742607117</t>
+    <t xml:space="preserve">1.94361650943756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
     <t xml:space="preserve">2.185715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41417598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663402557373</t>
+    <t xml:space="preserve">2.41417622566223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2880117893219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663450241089</t>
   </si>
   <si>
     <t xml:space="preserve">2.23004388809204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21640467643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889618873596</t>
+    <t xml:space="preserve">2.2164044380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889642715454</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410880088806</t>
+    <t xml:space="preserve">2.11410903930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296110153198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12774848937988</t>
+    <t xml:space="preserve">2.1277482509613</t>
   </si>
   <si>
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12092876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13115835189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584370136261</t>
+    <t xml:space="preserve">2.10387921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092852592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13115811347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15843677520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.15502738952637</t>
@@ -1298,19 +1298,19 @@
     <t xml:space="preserve">2.00499367713928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863288879395</t>
+    <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9811247587204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453450202942</t>
+    <t xml:space="preserve">1.92315709590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.984534740448</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">2.0936496257782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07319068908691</t>
+    <t xml:space="preserve">2.07319045066833</t>
   </si>
   <si>
     <t xml:space="preserve">2.05273151397705</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">2.24027371406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912577629089</t>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.1925356388092</t>
@@ -1349,70 +1349,70 @@
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732231140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.25391268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732278823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483103752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3084704875946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961842536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643838882446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892966270447</t>
+    <t xml:space="preserve">2.29483127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31528997421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30847024917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961866378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233952522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36643815040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892942428589</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32210993766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551980018616</t>
+    <t xml:space="preserve">2.32211017608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32552003860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35279870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37325811386108</t>
+    <t xml:space="preserve">2.35279893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3732578754425</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689708709717</t>
+    <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
     <t xml:space="preserve">2.37666749954224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42099571228027</t>
+    <t xml:space="preserve">2.42099595069885</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804502487183</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122529983521</t>
+    <t xml:space="preserve">2.43122553825378</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827461242676</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306176185608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670121192932</t>
+    <t xml:space="preserve">2.51306200027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5267014503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.54034066200256</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830784797668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558698654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61535739898682</t>
+    <t xml:space="preserve">2.59830808639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558674812317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61535716056824</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855266571045</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61167097091675</t>
+    <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58547902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928778648376</t>
+    <t xml:space="preserve">2.58547925949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928754806519</t>
   </si>
   <si>
     <t xml:space="preserve">2.63037896156311</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">2.71269536018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67153692245483</t>
+    <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657067298889</t>
+    <t xml:space="preserve">2.65657043457031</t>
   </si>
   <si>
     <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160370826721</t>
+    <t xml:space="preserve">2.64160394668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643686294556</t>
+    <t xml:space="preserve">2.71643710136414</t>
   </si>
   <si>
     <t xml:space="preserve">2.72766184806824</t>
@@ -1520,82 +1520,82 @@
     <t xml:space="preserve">2.72017860412598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73140335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262833595276</t>
+    <t xml:space="preserve">2.73140358924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262857437134</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7912700176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120299339294</t>
+    <t xml:space="preserve">2.79126977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8212034702301</t>
   </si>
   <si>
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81371998786926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82494497299194</t>
+    <t xml:space="preserve">2.81371974945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.806236743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82494473457336</t>
   </si>
   <si>
     <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338582038879</t>
+    <t xml:space="preserve">2.96338558197021</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977765083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719410896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331879615784</t>
+    <t xml:space="preserve">2.89977741241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719363212585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
     <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03821849822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09060215950012</t>
+    <t xml:space="preserve">3.03821873664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556817054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12053513526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
+    <t xml:space="preserve">3.10556840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12053489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046811103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169333457947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801790237427</t>
+    <t xml:space="preserve">3.16169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801837921143</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
@@ -1604,49 +1604,49 @@
     <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10931015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434366226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0457022190094</t>
+    <t xml:space="preserve">3.10930991172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434390068054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583579063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97461032867432</t>
+    <t xml:space="preserve">2.98583555221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
+    <t xml:space="preserve">2.91474413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951026916504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00454378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351939201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835206985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209404945374</t>
+    <t xml:space="preserve">3.00454354286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351915359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835230827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467735290527</t>
@@ -1655,43 +1655,43 @@
     <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97086906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964431762695</t>
+    <t xml:space="preserve">2.97086882591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
     <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75011157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.802494764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113644599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84365272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86236119270325</t>
+    <t xml:space="preserve">2.7501118183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80249500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113620758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84365296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86236095428467</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610269546509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848611831665</t>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596912384033</t>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726089477539</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004503250122</t>
+    <t xml:space="preserve">2.79875302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004479408264</t>
   </si>
   <si>
     <t xml:space="preserve">2.76882028579712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80997824668884</t>
+    <t xml:space="preserve">2.80997848510742</t>
   </si>
   <si>
     <t xml:space="preserve">2.76133680343628</t>
@@ -1721,55 +1721,55 @@
     <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03073573112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95590233802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
+    <t xml:space="preserve">3.0307354927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.88481092453003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87358617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78378653526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81746125221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487771034241</t>
+    <t xml:space="preserve">2.87358593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78378677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8174614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487818717957</t>
   </si>
   <si>
     <t xml:space="preserve">2.98957705497742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30761766433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32632565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986703872681</t>
+    <t xml:space="preserve">3.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986727714539</t>
   </si>
   <si>
     <t xml:space="preserve">3.36374187469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42360854148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44979977607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.42360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.26645922660828</t>
@@ -1781,64 +1781,64 @@
     <t xml:space="preserve">3.22530126571655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28142595291138</t>
+    <t xml:space="preserve">3.2814257144928</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2963924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924336433411</t>
+    <t xml:space="preserve">3.29639267921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924360275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305165290833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06440997123718</t>
+    <t xml:space="preserve">3.06441020965576</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093608856201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679339408875</t>
+    <t xml:space="preserve">3.11679315567017</t>
   </si>
   <si>
     <t xml:space="preserve">3.08685994148254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03545689582825</t>
+    <t xml:space="preserve">3.04944324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425451278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03545713424683</t>
   </si>
   <si>
     <t xml:space="preserve">2.2562141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33853054046631</t>
+    <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39091324806213</t>
+    <t xml:space="preserve">2.39091372489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581295013428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942111968994</t>
+    <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438760757446</t>
+    <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574664115906</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">2.4283299446106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40213847160339</t>
+    <t xml:space="preserve">2.40213823318481</t>
   </si>
   <si>
     <t xml:space="preserve">2.51812958717346</t>
@@ -1856,22 +1856,22 @@
     <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465498924255</t>
+    <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710519790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41336297988892</t>
+    <t xml:space="preserve">2.39839673042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710495948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458844184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4133632183075</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
@@ -1883,28 +1883,28 @@
     <t xml:space="preserve">2.4545214176178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4694881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5218710899353</t>
+    <t xml:space="preserve">2.46948790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187085151672</t>
   </si>
   <si>
     <t xml:space="preserve">2.49193787574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935457229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50316286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50690460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7875280380249</t>
+    <t xml:space="preserve">2.52935481071472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50316309928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50690412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
     <t xml:space="preserve">3.15795111656189</t>
@@ -1916,37 +1916,37 @@
     <t xml:space="preserve">3.27768421173096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714436531067</t>
+    <t xml:space="preserve">3.34714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721945762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102353096008</t>
+    <t xml:space="preserve">3.10721969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00102376937866</t>
   </si>
   <si>
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788802146912</t>
+    <t xml:space="preserve">3.06788778305054</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04822182655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968711853027</t>
+    <t xml:space="preserve">3.04822158813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182097434998</t>
+    <t xml:space="preserve">3.0718207359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.96955847740173</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595909118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90269374847412</t>
+    <t xml:space="preserve">2.94989228248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595885276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.86336207389832</t>
@@ -1988,37 +1988,37 @@
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896548271179</t>
+    <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749971389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863120079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456889152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63523650169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
+    <t xml:space="preserve">2.73750019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276907920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109910011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6352367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803844451904</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">2.74143314361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963333129883</t>
+    <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6391704082489</t>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63916993141174</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
@@ -2060,58 +2060,58 @@
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130354881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64703631401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343740463257</t>
+    <t xml:space="preserve">2.63130378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6470365524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65096974372864</t>
+    <t xml:space="preserve">2.59983849525452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
     <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510786056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904057502747</t>
+    <t xml:space="preserve">2.52510738372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
     <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970866203308</t>
+    <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330780982971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50150871276855</t>
+    <t xml:space="preserve">2.5015082359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397613525391</t>
+    <t xml:space="preserve">2.47397637367249</t>
   </si>
   <si>
     <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50937485694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52117443084717</t>
+    <t xml:space="preserve">2.50937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117419242859</t>
   </si>
   <si>
     <t xml:space="preserve">2.4936420917511</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">2.46610999107361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47790932655334</t>
+    <t xml:space="preserve">2.47790956497192</t>
   </si>
   <si>
     <t xml:space="preserve">2.40317893028259</t>
@@ -2129,13 +2129,13 @@
     <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45430994033813</t>
+    <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
     <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37564635276794</t>
+    <t xml:space="preserve">2.37564659118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.3913791179657</t>
@@ -2144,28 +2144,28 @@
     <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024739265442</t>
+    <t xml:space="preserve">2.31271553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36384677886963</t>
+    <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
     <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61557126045227</t>
+    <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.73356652259827</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6903018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7060341835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210123062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482760429382</t>
+    <t xml:space="preserve">2.71783375740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69030165672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70603466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85942840576172</t>
+    <t xml:space="preserve">2.85942888259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449332237244</t>
+    <t xml:space="preserve">2.91449356079102</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562480926514</t>
+    <t xml:space="preserve">2.96562504768372</t>
   </si>
   <si>
     <t xml:space="preserve">2.83976268768311</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">2.82009673118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85156226158142</t>
+    <t xml:space="preserve">2.8515625</t>
   </si>
   <si>
     <t xml:space="preserve">2.88302779197693</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">2.93809247016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90662693977356</t>
+    <t xml:space="preserve">2.90662717819214</t>
   </si>
   <si>
     <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89876055717468</t>
+    <t xml:space="preserve">2.89876079559326</t>
   </si>
   <si>
     <t xml:space="preserve">2.95775842666626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95382523536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87516164779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796335220337</t>
+    <t xml:space="preserve">2.9538254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87516140937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796311378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.86729526519775</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462267875671</t>
+    <t xml:space="preserve">3.01675653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462291717529</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2288,97 +2288,97 @@
     <t xml:space="preserve">2.97349143028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922395706177</t>
+    <t xml:space="preserve">2.98922371864319</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215525627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855587005615</t>
+    <t xml:space="preserve">3.07575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0521547794342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855610847473</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09541988372803</t>
+    <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428839683533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148716926575</t>
+    <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948266983032</t>
+    <t xml:space="preserve">3.1032862663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374966621399</t>
+    <t xml:space="preserve">3.19374990463257</t>
   </si>
   <si>
     <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18981671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21029043197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10382652282715</t>
+    <t xml:space="preserve">3.18981647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21029019355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08744764328003</t>
+    <t xml:space="preserve">3.08744788169861</t>
   </si>
   <si>
     <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05059480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07106852531433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374220848083</t>
+    <t xml:space="preserve">3.05059504508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374197006226</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0055525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831052780151</t>
+    <t xml:space="preserve">3.03421592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783680915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831076622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02602624893188</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0751633644104</t>
+    <t xml:space="preserve">3.08335280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07516360282898</t>
   </si>
   <si>
     <t xml:space="preserve">2.98507881164551</t>
@@ -2402,16 +2402,16 @@
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93594145774841</t>
+    <t xml:space="preserve">2.96460461616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93594169616699</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9031834602356</t>
+    <t xml:space="preserve">2.90318369865417</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9400360584259</t>
+    <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
     <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404658317566</t>
+    <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78853034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80490922927856</t>
+    <t xml:space="preserve">2.78853011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80490946769714</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633086204529</t>
@@ -2459,25 +2459,25 @@
     <t xml:space="preserve">2.89499402046204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88270974159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87861514091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452006340027</t>
+    <t xml:space="preserve">2.88270950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452030181885</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736285209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98917365074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193140983582</t>
+    <t xml:space="preserve">2.99736309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193164825439</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2486,37 +2486,37 @@
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365717887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96869945526123</t>
+    <t xml:space="preserve">2.92365741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96869993209839</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9318470954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680458068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8294780254364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8130989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82128810882568</t>
+    <t xml:space="preserve">2.93184685707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680481910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82947778701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81309866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719374656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82128834724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995150566101</t>
+    <t xml:space="preserve">2.84995198249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051025390625</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357286453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443551063538</t>
+    <t xml:space="preserve">2.83357262611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443574905396</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176206588745</t>
+    <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2546,46 +2546,46 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6697826385498</t>
+    <t xml:space="preserve">2.83766746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978216171265</t>
   </si>
   <si>
     <t xml:space="preserve">2.78034067153931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75986695289612</t>
+    <t xml:space="preserve">2.75986671447754</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521384239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387700080872</t>
+    <t xml:space="preserve">2.64521360397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74348759651184</t>
+    <t xml:space="preserve">2.74348783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7271089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939299583435</t>
+    <t xml:space="preserve">2.76396155357361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72710871696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
     <t xml:space="preserve">2.95615839958191</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170742034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303640365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83155298233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89170718193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303664207458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83155274391174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873962402344</t>
@@ -2621,13 +2621,13 @@
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717898368835</t>
+    <t xml:space="preserve">2.79717874526978</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436610221863</t>
+    <t xml:space="preserve">2.81436586380005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2642,16 +2642,16 @@
     <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90889406204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132132530212</t>
+    <t xml:space="preserve">2.90889430046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132108688354</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968322753906</t>
+    <t xml:space="preserve">2.65968346595764</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952878952026</t>
+    <t xml:space="preserve">2.59952902793884</t>
   </si>
   <si>
     <t xml:space="preserve">2.5479679107666</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195605278015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48781371116638</t>
+    <t xml:space="preserve">2.44914293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4878134727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172415733337</t>
+    <t xml:space="preserve">2.35891127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172439575195</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735015869141</t>
+    <t xml:space="preserve">2.30735039710999</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26867985725403</t>
+    <t xml:space="preserve">2.26867961883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35031795501709</t>
+    <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469171524048</t>
@@ -2744,46 +2744,46 @@
     <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180161476135</t>
+    <t xml:space="preserve">2.37180137634277</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3546142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898825645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883381843567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33742761611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28156995773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711874008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10540366172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13118410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0624361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1225905418396</t>
+    <t xml:space="preserve">2.35461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883405685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33742737770081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28156971931458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711850166321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10540342330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13118386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06243634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829352378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10110688209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12259030342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08391976356506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02376556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197302818298</t>
+    <t xml:space="preserve">2.08392000198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02376532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197290897369</t>
   </si>
   <si>
     <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89056646823883</t>
+    <t xml:space="preserve">1.89056658744812</t>
   </si>
   <si>
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041214942932</t>
+    <t xml:space="preserve">1.81322503089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71869683265686</t>
+    <t xml:space="preserve">1.71869671344757</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2837,13 +2837,13 @@
     <t xml:space="preserve">1.67744791507721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307391643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416851520538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65854227542877</t>
+    <t xml:space="preserve">1.64307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416839599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65854239463806</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729015350342</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92494022846222</t>
+    <t xml:space="preserve">1.9249404668808</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">1.93353378772736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97650122642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087498664856</t>
+    <t xml:space="preserve">1.97650134563446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087522506714</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2876,28 +2876,28 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95931422710419</t>
+    <t xml:space="preserve">1.95931434631348</t>
   </si>
   <si>
     <t xml:space="preserve">2.07962322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08821654319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524922370911</t>
+    <t xml:space="preserve">2.08821678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524946212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17844820022583</t>
+    <t xml:space="preserve">2.17844796180725</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126132011414</t>
+    <t xml:space="preserve">2.16126108169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2915,67 +2915,67 @@
     <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837098121643</t>
+    <t xml:space="preserve">2.19993162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673264503479</t>
+    <t xml:space="preserve">2.06673288345337</t>
   </si>
   <si>
     <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10969996452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133806228638</t>
+    <t xml:space="preserve">2.10970020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133830070496</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28586673736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32024073600769</t>
+    <t xml:space="preserve">2.23000884056091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28586649894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32024049758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860239982605</t>
+    <t xml:space="preserve">2.23860263824463</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594395637512</t>
+    <t xml:space="preserve">2.31594371795654</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453751564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26438307762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609839439392</t>
+    <t xml:space="preserve">2.32453727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26438283920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40617537498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313059806824</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42765927314758</t>
+    <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149250030518</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297616004944</t>
+    <t xml:space="preserve">2.27297639846802</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062635421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070381164551</t>
+    <t xml:space="preserve">2.47062659263611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070405006409</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874121665955</t>
+    <t xml:space="preserve">2.42874097824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.356778383255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280637741089</t>
+    <t xml:space="preserve">2.35677814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280613899231</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237401008606</t>
+    <t xml:space="preserve">2.23084378242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237377166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787624359131</t>
+    <t xml:space="preserve">2.19486260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787648200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337847709656</t>
+    <t xml:space="preserve">2.16337871551514</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189506530762</t>
+    <t xml:space="preserve">2.13189482688904</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06892776489258</t>
+    <t xml:space="preserve">2.068927526474</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591364860535</t>
+    <t xml:space="preserve">2.08691835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591341018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495552062988</t>
+    <t xml:space="preserve">2.01495575904846</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.933997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701138973236</t>
+    <t xml:space="preserve">1.93399751186371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701150894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600704193115</t>
+    <t xml:space="preserve">1.91600692272186</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9115092754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500221729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749057292938</t>
+    <t xml:space="preserve">1.93849527835846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91150915622711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500233650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749045372009</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648574829102</t>
+    <t xml:space="preserve">1.95648598670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050445079803</t>
+    <t xml:space="preserve">1.92050457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902080059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287589550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848340034485</t>
+    <t xml:space="preserve">1.78287577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848328113556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388060092926</t>
+    <t xml:space="preserve">1.77388048171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055126667023</t>
+    <t xml:space="preserve">1.83055114746094</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303938388824</t>
+    <t xml:space="preserve">1.85303950309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347175121307</t>
+    <t xml:space="preserve">1.98347187042236</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246716499329</t>
+    <t xml:space="preserve">1.99246728420258</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844882011414</t>
+    <t xml:space="preserve">2.02844858169556</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194140434265</t>
+    <t xml:space="preserve">2.04194164276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.221848487854</t>
+    <t xml:space="preserve">2.10490894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089059829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22184824943542</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -3849,6 +3849,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.25500011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25</t>
   </si>
 </sst>
 </file>
@@ -69213,7 +69216,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.691087963</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>47826</v>
@@ -69234,6 +69237,32 @@
         <v>1277</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911226852</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>67347</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1282" uniqueCount="1282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="1283">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862012386322</t>
+    <t xml:space="preserve">1.27862000465393</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">1.27977395057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26823401451111</t>
+    <t xml:space="preserve">1.26823389530182</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554037094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861633777618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27515828609467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977004528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246026039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
+    <t xml:space="preserve">1.25554025173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861657619476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27515816688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246037960052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975916385651</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25784826278687</t>
+    <t xml:space="preserve">1.25784838199615</t>
   </si>
   <si>
     <t xml:space="preserve">1.25438618659973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746215343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746593952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2636182308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20591866970062</t>
+    <t xml:space="preserve">1.24746203422546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285015583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746605873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26361811161041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20591855049133</t>
   </si>
   <si>
     <t xml:space="preserve">1.21168863773346</t>
@@ -128,61 +128,61 @@
     <t xml:space="preserve">1.29016005992889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669786453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900599479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439009189606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054569244385</t>
+    <t xml:space="preserve">1.28669798374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208184242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169620990753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862379074097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093168258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477939128876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247149944305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208574771881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30746972560883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016360759735</t>
+    <t xml:space="preserve">1.31093180179596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208562850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30746984481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016372680664</t>
   </si>
   <si>
     <t xml:space="preserve">1.3236255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32708764076233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323957443237</t>
+    <t xml:space="preserve">1.32708752155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824146747589</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">1.35132145881653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34439742565155</t>
+    <t xml:space="preserve">1.34439730644226</t>
   </si>
   <si>
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016715526581</t>
+    <t xml:space="preserve">1.3501672744751</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478341579437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36170697212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208953380585</t>
+    <t xml:space="preserve">1.36170721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
     <t xml:space="preserve">1.34324336051941</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36516904830933</t>
+    <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324714660645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38017082214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786316871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3674772977829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286115646362</t>
+    <t xml:space="preserve">1.38017106056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786304950714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747717857361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286103725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251518249512</t>
+    <t xml:space="preserve">1.39251506328583</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621210098267</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">1.41099977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332291603088</t>
+    <t xml:space="preserve">1.42702007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332303524017</t>
   </si>
   <si>
     <t xml:space="preserve">1.43687856197357</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">1.44427239894867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44550454616547</t>
+    <t xml:space="preserve">1.44550442695618</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043396949768</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">1.4627571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49110019207001</t>
+    <t xml:space="preserve">1.49110043048859</t>
   </si>
   <si>
     <t xml:space="preserve">1.48863554000854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50342345237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5182112455368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162526130676</t>
+    <t xml:space="preserve">1.50342333316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821112632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162514209747</t>
   </si>
   <si>
     <t xml:space="preserve">1.50465559959412</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.4984940290451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5403927564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433184146881</t>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817015171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707927703857</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">1.55641293525696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60077607631683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5465544462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
+    <t xml:space="preserve">1.60077619552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190828323364</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257450580597</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">1.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362428665161</t>
+    <t xml:space="preserve">1.6636244058609</t>
   </si>
   <si>
     <t xml:space="preserve">1.65006899833679</t>
@@ -344,40 +344,40 @@
     <t xml:space="preserve">1.65992736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66115987300873</t>
+    <t xml:space="preserve">1.66115951538086</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661388874054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154271602631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950283527374</t>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950319290161</t>
   </si>
   <si>
     <t xml:space="preserve">1.68827044963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72523987293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756301403046</t>
+    <t xml:space="preserve">1.72523999214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756313323975</t>
   </si>
   <si>
     <t xml:space="preserve">1.70429074764252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059382915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675539970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
+    <t xml:space="preserve">1.70059359073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675528049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784603595734</t>
   </si>
   <si>
     <t xml:space="preserve">1.75851249694824</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">1.79301726818085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439104557037</t>
+    <t xml:space="preserve">1.75604772567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439080715179</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206790447235</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">1.74988603591919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74865400791168</t>
+    <t xml:space="preserve">1.74865412712097</t>
   </si>
   <si>
     <t xml:space="preserve">1.74618947505951</t>
@@ -413,52 +413,52 @@
     <t xml:space="preserve">1.7622092962265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77699720859528</t>
+    <t xml:space="preserve">1.7769969701767</t>
   </si>
   <si>
     <t xml:space="preserve">1.76344168186188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6574627161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855347156525</t>
+    <t xml:space="preserve">1.65746283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855370998383</t>
   </si>
   <si>
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6944317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
+    <t xml:space="preserve">1.69443202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158404827118</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447347164154</t>
+    <t xml:space="preserve">1.60447335243225</t>
   </si>
   <si>
     <t xml:space="preserve">1.63035190105438</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61679625511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267480373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049353122711</t>
+    <t xml:space="preserve">1.6167961359024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376579761505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049317359924</t>
   </si>
   <si>
     <t xml:space="preserve">1.63281643390656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309969425201</t>
+    <t xml:space="preserve">1.61309933662415</t>
   </si>
   <si>
     <t xml:space="preserve">1.6155641078949</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">1.64760410785675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65130126476288</t>
+    <t xml:space="preserve">1.65130114555359</t>
   </si>
   <si>
     <t xml:space="preserve">1.65623021125793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926078796387</t>
+    <t xml:space="preserve">1.61926102638245</t>
   </si>
   <si>
     <t xml:space="preserve">1.64513969421387</t>
@@ -488,19 +488,19 @@
     <t xml:space="preserve">1.64144265651703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63404893875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091746807098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356472492218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479746818542</t>
+    <t xml:space="preserve">1.63404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091794490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546369075775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972653388977</t>
@@ -512,151 +512,151 @@
     <t xml:space="preserve">1.55887758731842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5884530544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503891944885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423130512238</t>
+    <t xml:space="preserve">1.58845317363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423118591309</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726188182831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
+    <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120084762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598852157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105909824371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200870037079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338235855103</t>
+    <t xml:space="preserve">1.57120072841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338247776031</t>
   </si>
   <si>
     <t xml:space="preserve">1.58722078800201</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63651323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66485643386841</t>
+    <t xml:space="preserve">1.63651311397552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
     <t xml:space="preserve">1.65499818325043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67594766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6722503900528</t>
+    <t xml:space="preserve">1.67594718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
   </si>
   <si>
     <t xml:space="preserve">1.67841196060181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978585720062</t>
+    <t xml:space="preserve">1.69073498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978597640991</t>
   </si>
   <si>
     <t xml:space="preserve">1.67717981338501</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68703806400299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552277565002</t>
+    <t xml:space="preserve">1.68703830242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552265644073</t>
   </si>
   <si>
     <t xml:space="preserve">1.71538126468658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71291673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727999210358</t>
+    <t xml:space="preserve">1.71291708946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457341194153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728034973145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74126005172729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946197986603</t>
+    <t xml:space="preserve">1.73016905784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330040931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946162223816</t>
   </si>
   <si>
     <t xml:space="preserve">1.7474217414856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069388866425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8176634311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150221824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614814281464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297593593597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89899611473083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762269496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392518043518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459176063538</t>
+    <t xml:space="preserve">1.78069400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766355037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695599555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899623394012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392553806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459199905396</t>
   </si>
   <si>
     <t xml:space="preserve">1.92980408668518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98279368877411</t>
+    <t xml:space="preserve">1.98279392719269</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838945388794</t>
+    <t xml:space="preserve">2.02838921546936</t>
   </si>
   <si>
     <t xml:space="preserve">2.04687428474426</t>
@@ -665,34 +665,34 @@
     <t xml:space="preserve">2.01483392715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01729846000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796480178833</t>
+    <t xml:space="preserve">2.01729822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796456336975</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303549766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0690553188324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.107257604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09493446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09986352920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13806557655334</t>
+    <t xml:space="preserve">2.06905579566956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10725736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09493398666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0998637676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13806509971619</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669156074524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024708747864</t>
+    <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887307167053</t>
@@ -704,94 +704,94 @@
     <t xml:space="preserve">2.15655016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18119621276855</t>
+    <t xml:space="preserve">2.18119597434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531754493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640877723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
+    <t xml:space="preserve">2.17010569572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640830039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446919441223</t>
   </si>
   <si>
     <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816563606262</t>
+    <t xml:space="preserve">2.17996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2181658744812</t>
   </si>
   <si>
     <t xml:space="preserve">2.20953941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21323657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2317214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27978134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717541694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33030605316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583282470703</t>
+    <t xml:space="preserve">2.2132363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172116279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27978157997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3303062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877203941345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583306312561</t>
   </si>
   <si>
     <t xml:space="preserve">2.33289432525635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
+    <t xml:space="preserve">2.31477975845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526022911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866145133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3367760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100865364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782956123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35489058494568</t>
+    <t xml:space="preserve">2.30313467979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866121292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33677577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782908439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.30054688453674</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">2.33806991577148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34453916549683</t>
+    <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
     <t xml:space="preserve">2.36135983467102</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">2.34065747261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32901239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324550628662</t>
+    <t xml:space="preserve">2.32901263237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842133522034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971499443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.33030652999878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
+    <t xml:space="preserve">2.40535259246826</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642459869385</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">2.3121919631958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537129402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666471481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396656990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2449095249176</t>
+    <t xml:space="preserve">2.29537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
@@ -854,28 +854,28 @@
     <t xml:space="preserve">2.26043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2617301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690554618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361515045166</t>
+    <t xml:space="preserve">2.25784802436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26172971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361562728882</t>
   </si>
   <si>
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197031021118</t>
+    <t xml:space="preserve">2.19703507423401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903109550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319700717926</t>
   </si>
   <si>
     <t xml:space="preserve">2.24102759361267</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">2.31736731529236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32771825790405</t>
+    <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348562240601</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24879097938538</t>
+    <t xml:space="preserve">2.2487907409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.29278349876404</t>
@@ -917,94 +917,94 @@
     <t xml:space="preserve">2.37041711807251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33548212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747838020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28501987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631377220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27337503433228</t>
+    <t xml:space="preserve">2.33548188209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28502011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2863142490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2733747959137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33160042762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418798446655</t>
+    <t xml:space="preserve">2.33160018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
     <t xml:space="preserve">2.3057222366333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35359644889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4674596786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
+    <t xml:space="preserve">2.35359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664649009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699743270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546294212341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3872377872467</t>
+    <t xml:space="preserve">2.47651648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38723802566528</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34195137023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524128913879</t>
+    <t xml:space="preserve">2.34195160865784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40793991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37688660621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36265397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464999198914</t>
+    <t xml:space="preserve">2.3937075138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37688684463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38465023040771</t>
   </si>
   <si>
     <t xml:space="preserve">2.31607341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36459445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076853752136</t>
+    <t xml:space="preserve">2.36459469795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429881095886</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">2.13492798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258078575134</t>
+    <t xml:space="preserve">2.04435539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258054733276</t>
   </si>
   <si>
     <t xml:space="preserve">2.07346796989441</t>
@@ -1037,40 +1037,40 @@
     <t xml:space="preserve">2.07993745803833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11551976203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198877334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06699848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818131446838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966039180756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494740486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04758977890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640694618225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0411205291748</t>
+    <t xml:space="preserve">2.11551952362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198901176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06699872016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0508246421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818155288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847767829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524305343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0475902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04112076759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.07023334503174</t>
@@ -1082,55 +1082,55 @@
     <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10581541061401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06052875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376361846924</t>
+    <t xml:space="preserve">2.10581564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06052923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934568405151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875462532043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845849990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110182762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19962310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28372621536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26755237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2505030632019</t>
+    <t xml:space="preserve">2.10905027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845873832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433645248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19962286949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28372597694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26755261421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050282478333</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230605125427</t>
+    <t xml:space="preserve">2.18230628967285</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322416305542</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">2.16866660118103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13456845283508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433838844299</t>
+    <t xml:space="preserve">2.1345682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433862686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.11751890182495</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">2.1004695892334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08342027664185</t>
+    <t xml:space="preserve">2.08342051506042</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
@@ -1163,28 +1163,28 @@
     <t xml:space="preserve">1.96066534519196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01181316375732</t>
+    <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
     <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227233886719</t>
+    <t xml:space="preserve">2.04591155052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08682990074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886295318604</t>
+    <t xml:space="preserve">2.08001017570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.03909206390381</t>
@@ -1196,34 +1196,34 @@
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09024000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522326469421</t>
+    <t xml:space="preserve">2.09023976325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
     <t xml:space="preserve">1.99817419052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98794448375702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089493274689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9538459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771513462067</t>
+    <t xml:space="preserve">1.98794424533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089517116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748530864716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384573936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725584030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9777147769928</t>
   </si>
   <si>
     <t xml:space="preserve">1.95043587684631</t>
@@ -1238,22 +1238,22 @@
     <t xml:space="preserve">2.14820742607117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18571591377258</t>
+    <t xml:space="preserve">2.185715675354</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801131248474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663426399231</t>
+    <t xml:space="preserve">2.28801155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663402557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.23004412651062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21640467643738</t>
+    <t xml:space="preserve">2.2164044380188</t>
   </si>
   <si>
     <t xml:space="preserve">2.17889618873596</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">2.13797760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410903930664</t>
+    <t xml:space="preserve">2.11410856246948</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296110153198</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">2.1277482509613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09705972671509</t>
+    <t xml:space="preserve">2.09705948829651</t>
   </si>
   <si>
     <t xml:space="preserve">2.10387945175171</t>
@@ -1283,82 +1283,82 @@
     <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15843677520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15502738952637</t>
+    <t xml:space="preserve">2.15843725204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15502762794495</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637120246887</t>
+    <t xml:space="preserve">2.16184663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
     <t xml:space="preserve">2.00499391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863312721252</t>
+    <t xml:space="preserve">2.01863288879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315709590912</t>
+    <t xml:space="preserve">1.92315697669983</t>
   </si>
   <si>
     <t xml:space="preserve">1.98112463951111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98453450202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09365010261536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319045066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299433708191</t>
+    <t xml:space="preserve">1.98453438282013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0766007900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0936496257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273175239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299481391907</t>
   </si>
   <si>
     <t xml:space="preserve">2.24027347564697</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19594573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912553787231</t>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912577629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23345398902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23686337471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.23345375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23686361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391316413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732254981995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506062507629</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165123939514</t>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961818695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643838882446</t>
+    <t xml:space="preserve">2.35961842536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233952522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3664379119873</t>
   </si>
   <si>
     <t xml:space="preserve">2.32892966270447</t>
@@ -1394,61 +1394,61 @@
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32551980018616</t>
+    <t xml:space="preserve">2.32552027702332</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35279870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37325763702393</t>
+    <t xml:space="preserve">2.35279846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37325811386108</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712715148926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38689732551575</t>
+    <t xml:space="preserve">2.38689708709717</t>
   </si>
   <si>
     <t xml:space="preserve">2.37666749954224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42099547386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43463516235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43122553825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44827437400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4619140625</t>
+    <t xml:space="preserve">2.42099595069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804526329041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43463492393494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43122529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46191382408142</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306176185608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919272422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896337509155</t>
+    <t xml:space="preserve">2.5130615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896313667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52670097351074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54034042358398</t>
+    <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171794891357</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">2.59830808639526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62558650970459</t>
+    <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
     <t xml:space="preserve">2.6153576374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88855266571045</t>
+    <t xml:space="preserve">2.88855242729187</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541223526001</t>
@@ -1472,61 +1472,61 @@
     <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56677103042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58547925949097</t>
+    <t xml:space="preserve">2.56677079200745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58547902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928778648376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63037919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71269536018372</t>
+    <t xml:space="preserve">2.63037896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71269512176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6939868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65657019615173</t>
+    <t xml:space="preserve">2.69398713111877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65657091140747</t>
   </si>
   <si>
     <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160418510437</t>
+    <t xml:space="preserve">2.64160370826721</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031193733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643710136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766184806824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772887229919</t>
+    <t xml:space="preserve">2.66031217575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766208648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72017860412598</t>
+    <t xml:space="preserve">2.7201783657074</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262833595276</t>
+    <t xml:space="preserve">2.74262809753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
@@ -1535,64 +1535,64 @@
     <t xml:space="preserve">2.7912700176239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616948127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81371974945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80623626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868647575378</t>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616995811462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81371998786926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.806236743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868623733521</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984467506409</t>
+    <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92971086502075</t>
+    <t xml:space="preserve">2.92971062660217</t>
   </si>
   <si>
     <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93719434738159</t>
+    <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
     <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576900482178</t>
+    <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060215950012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10182666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10556817054749</t>
+    <t xml:space="preserve">3.09060168266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10182690620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053513526917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18040156364441</t>
+    <t xml:space="preserve">3.15046811103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
     <t xml:space="preserve">3.16169285774231</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10931015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434366226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04570198059082</t>
+    <t xml:space="preserve">3.10931038856506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434342384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0457022190094</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706077575684</t>
@@ -1622,34 +1622,34 @@
     <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97461080551147</t>
+    <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07189345359802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0045440196991</t>
+    <t xml:space="preserve">2.91474437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0718936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951050758362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835230827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
+    <t xml:space="preserve">2.97835206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209404945374</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467735290527</t>
@@ -1658,22 +1658,22 @@
     <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97086930274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739470481873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7501118183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.802494764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991098403931</t>
+    <t xml:space="preserve">2.97086906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964407920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84739446640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75011157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80249500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991146087646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85113620758057</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">2.84365296363831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86236095428467</t>
+    <t xml:space="preserve">2.86236143112183</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848611831665</t>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726113319397</t>
+    <t xml:space="preserve">2.92596912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
+    <t xml:space="preserve">2.798752784729</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">2.7613365650177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88106918334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00828552246094</t>
+    <t xml:space="preserve">2.88106942176819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00828576087952</t>
   </si>
   <si>
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590209960938</t>
+    <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.96712708473206</t>
@@ -1739,70 +1739,70 @@
     <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78378653526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81746172904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32632565498352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36374187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">2.78378677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81746125221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487771034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263258934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986680030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3637421131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980025291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3562593460083</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24026799201965</t>
+    <t xml:space="preserve">3.2402675151825</t>
   </si>
   <si>
     <t xml:space="preserve">3.22530102729797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28142619132996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3225839138031</t>
+    <t xml:space="preserve">3.2814257144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
     <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924312591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305165290833</t>
+    <t xml:space="preserve">3.13924336433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
     <t xml:space="preserve">3.06440997123718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94093608856201</t>
+    <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.11679315567017</t>
@@ -1811,49 +1811,49 @@
     <t xml:space="preserve">3.08686017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944324493408</t>
+    <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425403594971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03545689582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2562141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853054046631</t>
+    <t xml:space="preserve">2.03545713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25621438026428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968850135803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39091324806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581318855286</t>
+    <t xml:space="preserve">2.39091348648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581342697144</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445439338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51438784599304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46574640274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42832970619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213823318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812958717346</t>
+    <t xml:space="preserve">2.48445463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51438760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46574664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4283299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213847160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812934875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
+    <t xml:space="preserve">2.39839673042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710472106934</t>
   </si>
   <si>
     <t xml:space="preserve">2.42458820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4133632183075</t>
+    <t xml:space="preserve">2.41336345672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962195396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452117919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4694881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5218710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193835258484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935457229614</t>
+    <t xml:space="preserve">2.40962171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4545214176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46948790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187132835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193787574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935433387756</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5069043636322</t>
+    <t xml:space="preserve">2.50690412521362</t>
   </si>
   <si>
     <t xml:space="preserve">2.59670424461365</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">3.15795135498047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29265093803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714412689209</t>
+    <t xml:space="preserve">3.29265069961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
@@ -1934,16 +1934,16 @@
     <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06788802146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935307502747</t>
+    <t xml:space="preserve">3.06788778305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
     <t xml:space="preserve">3.04822182655334</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07968735694885</t>
+    <t xml:space="preserve">3.07968711853027</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202589988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989204406738</t>
+    <t xml:space="preserve">2.94202542304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989228248596</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742438316345</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91842651367188</t>
+    <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
     <t xml:space="preserve">2.90269374847412</t>
@@ -1979,58 +1979,58 @@
     <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8082971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78076529502869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7964973449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469824790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77289843559265</t>
+    <t xml:space="preserve">2.80829739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78076505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
     <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863143920898</t>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863120079041</t>
   </si>
   <si>
     <t xml:space="preserve">2.74536633491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76109886169434</t>
+    <t xml:space="preserve">2.76109910011292</t>
   </si>
   <si>
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
+    <t xml:space="preserve">2.63523650169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
     <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58803868293762</t>
+    <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6981680393219</t>
+    <t xml:space="preserve">2.69816780090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.74143290519714</t>
@@ -2042,58 +2042,58 @@
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63917016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670250892639</t>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6391704082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670227050781</t>
   </si>
   <si>
     <t xml:space="preserve">2.65490293502808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65883612632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017206192017</t>
+    <t xml:space="preserve">2.65883588790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017230033875</t>
   </si>
   <si>
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130354881287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6470365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343764305115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5959050655365</t>
+    <t xml:space="preserve">2.63130378723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64703631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343716621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59590482711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65096950531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75323247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54084038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970866203308</t>
+    <t xml:space="preserve">2.65096974372864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75323271751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510762214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904057502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54084014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
     <t xml:space="preserve">2.51330804824829</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">2.47397637367249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48577570915222</t>
+    <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.50937485694885</t>
@@ -2117,10 +2117,10 @@
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610999107361</t>
+    <t xml:space="preserve">2.4936420917511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610975265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
@@ -2129,34 +2129,34 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3835129737854</t>
+    <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39137935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.39924550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564635276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3913791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598063468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531278610229</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271576881409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024786949158</t>
+    <t xml:space="preserve">2.31271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631467819214</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230591773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.57230567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70603442192078</t>
+    <t xml:space="preserve">2.7060341835022</t>
   </si>
   <si>
     <t xml:space="preserve">2.70210123062134</t>
@@ -2204,58 +2204,58 @@
     <t xml:space="preserve">2.8594286441803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88696098327637</t>
+    <t xml:space="preserve">2.88696146011353</t>
   </si>
   <si>
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449332237244</t>
+    <t xml:space="preserve">2.91449308395386</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629313468933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0206892490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96169185638428</t>
+    <t xml:space="preserve">3.02068948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9616916179657</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976292610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83189606666565</t>
+    <t xml:space="preserve">2.83976268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83189654350281</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009696960449</t>
+    <t xml:space="preserve">2.82009673118591</t>
   </si>
   <si>
     <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302803039551</t>
+    <t xml:space="preserve">2.88302755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809223175049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90662717819214</t>
+    <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8987603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775866508484</t>
   </si>
   <si>
     <t xml:space="preserve">2.95382523536682</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82796311378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729502677917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022584915161</t>
+    <t xml:space="preserve">2.82796335220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022608757019</t>
   </si>
   <si>
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462291717529</t>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00888991355896</t>
+    <t xml:space="preserve">3.00889015197754</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349119186401</t>
@@ -2300,16 +2300,16 @@
     <t xml:space="preserve">3.07575416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05215549468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855563163757</t>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">3.10328650474548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20948266983032</t>
+    <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441823005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981623649597</t>
+    <t xml:space="preserve">3.19374966621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06287908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.06287884712219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106852531433</t>
+    <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374220848083</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421568870544</t>
+    <t xml:space="preserve">3.03421545028687</t>
   </si>
   <si>
     <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0055525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831052780151</t>
+    <t xml:space="preserve">3.00555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831076622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.02602624893188</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">3.04650020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335304260254</t>
+    <t xml:space="preserve">3.08335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">3.0751633644104</t>
@@ -2402,28 +2402,28 @@
     <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99326825141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96460461616516</t>
+    <t xml:space="preserve">2.99326801300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94822573661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90318369865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137290000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.94822597503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9031834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908862113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727853775024</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9400360584259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8540461063385</t>
+    <t xml:space="preserve">2.94003629684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223578453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624583244324</t>
@@ -2453,25 +2453,25 @@
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490946769714</t>
+    <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89499425888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88270974159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87861490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452006340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775225639343</t>
+    <t xml:space="preserve">2.89499402046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88270998001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861514091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.99736285209656</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97279453277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95232081413269</t>
+    <t xml:space="preserve">2.97279477119446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869969367981</t>
+    <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309866905212</t>
+    <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128858566284</t>
+    <t xml:space="preserve">2.82128834724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995150566101</t>
+    <t xml:space="preserve">2.84995174407959</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051001548767</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">2.83357262611389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2543,22 +2543,22 @@
     <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79262518882751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80900406837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081486701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978240013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034067153931</t>
+    <t xml:space="preserve">2.79262495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80900382995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83766722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034090995789</t>
   </si>
   <si>
     <t xml:space="preserve">2.75986695289612</t>
@@ -2567,25 +2567,25 @@
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521384239197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387723922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805663108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70254039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76396203041077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7271089553833</t>
+    <t xml:space="preserve">2.64521360397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387700080872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805639266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348759651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70254015922546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76396179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72710871696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
@@ -2603,43 +2603,43 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303640365601</t>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82725620269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80577254295349</t>
+    <t xml:space="preserve">2.82725596427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80577230453491</t>
   </si>
   <si>
     <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82295942306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81436610221863</t>
+    <t xml:space="preserve">2.82295966148376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81436586380005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86163020133972</t>
+    <t xml:space="preserve">2.87881684303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.90459752082825</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6983540058136</t>
+    <t xml:space="preserve">2.69835376739502</t>
   </si>
   <si>
     <t xml:space="preserve">2.65968322753906</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64679288864136</t>
+    <t xml:space="preserve">2.64679312705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.59952878952026</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5350775718689</t>
+    <t xml:space="preserve">2.53507781028748</t>
   </si>
   <si>
     <t xml:space="preserve">2.578045129776</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">2.47921991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50929737091064</t>
+    <t xml:space="preserve">2.50929713249207</t>
   </si>
   <si>
     <t xml:space="preserve">2.51359391212463</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
+    <t xml:space="preserve">2.44914293289185</t>
   </si>
   <si>
     <t xml:space="preserve">2.43195581436157</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211049079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41906571388245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35891103744507</t>
+    <t xml:space="preserve">2.49211025238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41906595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35891127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.34172415733337</t>
@@ -2720,37 +2720,37 @@
     <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27727317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.27727341651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34602117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36320781707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3975818157196</t>
+    <t xml:space="preserve">2.36320805549622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469171524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625283241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180161476135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40187883377075</t>
+    <t xml:space="preserve">2.38469195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625259399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40187859535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.35461449623108</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
+    <t xml:space="preserve">2.13118410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2798,22 +2798,22 @@
     <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14407420158386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399722099304</t>
+    <t xml:space="preserve">2.14407396316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322491168976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041214942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78744447231293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.81322503089905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041203022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78744459152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307391643524</t>
+    <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
     <t xml:space="preserve">1.62416839599609</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
@@ -2861,22 +2861,22 @@
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650134563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087498664856</t>
+    <t xml:space="preserve">1.96790754795074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087522506714</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
+    <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07102942466736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17844843864441</t>
+    <t xml:space="preserve">2.07102966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">2.12688708305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13548064231873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18704152107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2128221988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1956353187561</t>
+    <t xml:space="preserve">2.13548040390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18704175949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21282196044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
     <t xml:space="preserve">2.19993185997009</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07532644271851</t>
+    <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
     <t xml:space="preserve">2.06673264503479</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20422863960266</t>
+    <t xml:space="preserve">2.20422840118408</t>
   </si>
   <si>
     <t xml:space="preserve">2.31594395637512</t>
@@ -2972,16 +2972,16 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438307762146</t>
+    <t xml:space="preserve">2.26438283920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609839439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.37609815597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2999,25 +2999,25 @@
     <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22141551971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27297639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24289894104004</t>
+    <t xml:space="preserve">2.22141575813293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27297616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41047239303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062659263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070357322693</t>
+    <t xml:space="preserve">2.41047215461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3858,6 +3858,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.23499989509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32500004768372</t>
   </si>
 </sst>
 </file>
@@ -69300,25 +69303,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6910300926</v>
+        <v>45968.6912962963</v>
       </c>
       <c r="B2505" t="n">
-        <v>297434</v>
+        <v>322627</v>
       </c>
       <c r="C2505" t="n">
-        <v>3.23000001907349</v>
+        <v>3.33500003814697</v>
       </c>
       <c r="D2505" t="n">
-        <v>3.10999989509583</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="E2505" t="n">
-        <v>3.20499992370605</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="F2505" t="n">
-        <v>3.10999989509583</v>
+        <v>3.32500004768372</v>
       </c>
       <c r="G2505" t="s">
-        <v>1236</v>
+        <v>1282</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="1283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="1284">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977383136749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26823401451111</t>
+    <t xml:space="preserve">1.27977406978607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2682341337204</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">1.24861621856689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515804767609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977016448975</t>
+    <t xml:space="preserve">1.27515816688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977028369904</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246037960052</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784069061279</t>
+    <t xml:space="preserve">1.19437861442566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283891677856</t>
+    <t xml:space="preserve">1.18283879756927</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">1.24746239185333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27285015583038</t>
+    <t xml:space="preserve">1.27285003662109</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746593952179</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">1.26361811161041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591866970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168851852417</t>
+    <t xml:space="preserve">1.20591855049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168875694275</t>
   </si>
   <si>
     <t xml:space="preserve">1.21053469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19207084178925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822668075562</t>
+    <t xml:space="preserve">1.19207072257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2082267999649</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130655288696</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">1.22899854183197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2347686290741</t>
+    <t xml:space="preserve">1.23476850986481</t>
   </si>
   <si>
     <t xml:space="preserve">1.23707640171051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29015982151031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669810295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900575637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208196163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28438997268677</t>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900587558746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208184242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28439021110535</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169597148895</t>
@@ -146,118 +146,118 @@
     <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862367153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093168258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477962970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247173786163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208574771881</t>
+    <t xml:space="preserve">1.30054581165314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862355232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093180179596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746984481812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516195297241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016360759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362544536591</t>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516183376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3236255645752</t>
   </si>
   <si>
     <t xml:space="preserve">1.32708764076233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31323981285095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439754486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016739368439</t>
+    <t xml:space="preserve">1.31323969364166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670531749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35016751289368</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478341579437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36170709133148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208929538727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34324359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3455513715744</t>
+    <t xml:space="preserve">1.36170721054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34324336051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
     <t xml:space="preserve">1.36516904830933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37324714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017106056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786304950714</t>
+    <t xml:space="preserve">1.37324750423431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017117977142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786316871643</t>
   </si>
   <si>
     <t xml:space="preserve">1.36747705936432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36286127567291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.394979596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251518249512</t>
+    <t xml:space="preserve">1.36286115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497971534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251494407654</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41099989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332315444946</t>
+    <t xml:space="preserve">1.41099977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42702007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
   </si>
   <si>
     <t xml:space="preserve">1.43687856197357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44427239894867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550442695618</t>
+    <t xml:space="preserve">1.44427227973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550466537476</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043385028839</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">1.45536315441132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46275699138641</t>
+    <t xml:space="preserve">1.46275722980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.49110043048859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48863542079926</t>
+    <t xml:space="preserve">1.48863530158997</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342333316803</t>
@@ -281,25 +281,25 @@
     <t xml:space="preserve">1.51821112632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54162538051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465571880341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574647426605</t>
+    <t xml:space="preserve">1.54162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465559959412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574671268463</t>
   </si>
   <si>
     <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54039287567139</t>
+    <t xml:space="preserve">1.5403927564621</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61433184146881</t>
+    <t xml:space="preserve">1.61433160305023</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707939624786</t>
@@ -308,121 +308,121 @@
     <t xml:space="preserve">1.52437257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958526134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641305446625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
+    <t xml:space="preserve">1.50958502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641281604767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077655315399</t>
   </si>
   <si>
     <t xml:space="preserve">1.5465544462204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190840244293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257450580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362464427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500688791275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461486339569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115987300873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154295444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400784492493</t>
+    <t xml:space="preserve">1.52190828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257462501526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6636244058609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461462497711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883637428284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992724895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115975379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661412715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154307365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
   </si>
   <si>
     <t xml:space="preserve">1.68950307369232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68827068805695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72524011135101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756325244904</t>
+    <t xml:space="preserve">1.68827056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7252402305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
     <t xml:space="preserve">1.70429074764252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059382915497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675504207611</t>
+    <t xml:space="preserve">1.70059394836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675528049469</t>
   </si>
   <si>
     <t xml:space="preserve">1.71784615516663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75851261615753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301714897156</t>
+    <t xml:space="preserve">1.75851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301750659943</t>
   </si>
   <si>
     <t xml:space="preserve">1.75604772567749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78439080715179</t>
+    <t xml:space="preserve">1.78439116477966</t>
   </si>
   <si>
     <t xml:space="preserve">1.77206778526306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74988603591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865388870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618947505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837050914764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220953464508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699732780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344168186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855347156525</t>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865400791168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7461895942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837086677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7745326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7622092962265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344180107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746247768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855335235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.74249243736267</t>
@@ -431,43 +431,43 @@
     <t xml:space="preserve">1.69443202018738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61186718940735</t>
+    <t xml:space="preserve">1.61186730861664</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035190105438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679625511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049317359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309969425201</t>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6426750421524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376591682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281643390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309945583344</t>
   </si>
   <si>
     <t xml:space="preserve">1.6155641078949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61802875995636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021027088165</t>
+    <t xml:space="preserve">1.61802840232849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760410785675</t>
@@ -479,46 +479,46 @@
     <t xml:space="preserve">1.65623033046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513945579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144253730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404881954193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356508255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479711055756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972641468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247385025024</t>
+    <t xml:space="preserve">1.61926102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.645139336586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404858112335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091770648956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546345233917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
     <t xml:space="preserve">1.55887758731842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58845317363739</t>
+    <t xml:space="preserve">1.5884530544281</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503903865814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53423142433167</t>
+    <t xml:space="preserve">1.53423130512238</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726188182831</t>
@@ -536,85 +536,85 @@
     <t xml:space="preserve">1.58598828315735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58105945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200834274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5933825969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722066879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651347160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6648565530777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499830245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225027084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841184139252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073510169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717957496643</t>
+    <t xml:space="preserve">1.58105933666229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338235855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5872209072113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66485643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073498249054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978585720062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717981338501</t>
   </si>
   <si>
     <t xml:space="preserve">1.68703830242157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70552289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7129168510437</t>
+    <t xml:space="preserve">1.7055230140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291673183441</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457353115082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467394828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016929626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75727999210358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125981330872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330017089844</t>
   </si>
   <si>
     <t xml:space="preserve">1.77946186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74742138385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178464412689</t>
+    <t xml:space="preserve">1.74742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069412708282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.76590621471405</t>
@@ -623,58 +623,58 @@
     <t xml:space="preserve">1.8176634311676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81150209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695611476898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297641277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762257575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392565727234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459176063538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92980432510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279345035553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838969230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687404632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729798316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796504020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905555725098</t>
+    <t xml:space="preserve">1.81150186061859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614802360535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899623394012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392529964447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459187984467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00867247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838921546936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687428474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729846000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796456336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303525924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
     <t xml:space="preserve">2.10725736618042</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09986352920532</t>
+    <t xml:space="preserve">2.09986329078674</t>
   </si>
   <si>
     <t xml:space="preserve">2.13806509971619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14669132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024661064148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887331008911</t>
+    <t xml:space="preserve">2.14669156074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024708747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887307167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.17256999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15655016899109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119645118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380237579346</t>
+    <t xml:space="preserve">2.15654993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380213737488</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531754493713</t>
+    <t xml:space="preserve">2.15531778335571</t>
   </si>
   <si>
     <t xml:space="preserve">2.16640853881836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21446847915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17996406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816563606262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953965187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2132363319397</t>
+    <t xml:space="preserve">2.21446919441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18366074562073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1799635887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953917503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.27978157997131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28717517852783</t>
+    <t xml:space="preserve">2.28717541694641</t>
   </si>
   <si>
     <t xml:space="preserve">2.3303062915802</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">2.34583282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289408683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25526022911072</t>
+    <t xml:space="preserve">2.33289432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477975845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137877464294</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">2.25267243385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313467979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3186616897583</t>
+    <t xml:space="preserve">2.23973345756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313444137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.33677577972412</t>
@@ -788,22 +788,22 @@
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782956123352</t>
+    <t xml:space="preserve">2.36782908439636</t>
   </si>
   <si>
     <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806991577148</t>
+    <t xml:space="preserve">2.30054688453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806967735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453916549683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36135983467102</t>
+    <t xml:space="preserve">2.3613600730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">2.34065771102905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32901263237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842085838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971499443054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324550628662</t>
+    <t xml:space="preserve">2.32901215553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.40535259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32642483711243</t>
+    <t xml:space="preserve">2.32642436027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219172477722</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">2.25396633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24490928649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949334144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26043605804443</t>
+    <t xml:space="preserve">2.2449095249176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26043581962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784826278687</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690554618835</t>
+    <t xml:space="preserve">2.26690578460693</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361515045166</t>
@@ -866,34 +866,34 @@
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703483581543</t>
+    <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903157234192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23197031021118</t>
+    <t xml:space="preserve">2.23197054862976</t>
   </si>
   <si>
     <t xml:space="preserve">2.24102735519409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3225429058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348586082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407715797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725696563721</t>
+    <t xml:space="preserve">2.32254314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771825790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348562240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407739639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890156745911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879097938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548188209534</t>
+    <t xml:space="preserve">2.28890180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278302192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041735649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548212051392</t>
   </si>
   <si>
     <t xml:space="preserve">2.35747838020325</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631377220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27337455749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819920539856</t>
+    <t xml:space="preserve">2.28631353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2733747959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819968223572</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160018920898</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">2.33418798446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3057222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359644889832</t>
+    <t xml:space="preserve">2.30572247505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359668731689</t>
   </si>
   <si>
     <t xml:space="preserve">2.37171077728271</t>
@@ -956,28 +956,28 @@
     <t xml:space="preserve">2.41699743270874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46745944023132</t>
+    <t xml:space="preserve">2.46745896339417</t>
   </si>
   <si>
     <t xml:space="preserve">2.44675707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44546318054199</t>
+    <t xml:space="preserve">2.44546294212341</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3872377872467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241313934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34195113182068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36524152755737</t>
+    <t xml:space="preserve">2.38723802566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241361618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34195137023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36524176597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.40794014930725</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">2.36265397071838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38464999198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31607365608215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
+    <t xml:space="preserve">2.38464975357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
+    <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.3193085193634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492798805237</t>
+    <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">2.10258078575134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07346796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788590431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08964157104492</t>
+    <t xml:space="preserve">2.07346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788614273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08964204788208</t>
   </si>
   <si>
     <t xml:space="preserve">2.07993721961975</t>
@@ -1052,28 +1052,28 @@
     <t xml:space="preserve">2.01847720146179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966063022614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524233818054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494716644287</t>
+    <t xml:space="preserve">1.97966027259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0152428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08640670776367</t>
+    <t xml:space="preserve">2.08640718460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670283317566</t>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522387504578</t>
@@ -1082,109 +1082,109 @@
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052875518799</t>
+    <t xml:space="preserve">2.06052923202515</t>
   </si>
   <si>
     <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09934592247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10904979705811</t>
+    <t xml:space="preserve">2.09934616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875438690186</t>
+    <t xml:space="preserve">2.11875414848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110158920288</t>
+    <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28372597694397</t>
+    <t xml:space="preserve">2.19962286949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050330162048</t>
+    <t xml:space="preserve">2.28460168838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230581283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322392463684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13456773757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433862686157</t>
+    <t xml:space="preserve">2.18230605125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1345682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433886528015</t>
   </si>
   <si>
     <t xml:space="preserve">2.11751866340637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11069893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1004695892334</t>
+    <t xml:space="preserve">2.11069941520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342051506042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066558361053</t>
+    <t xml:space="preserve">2.04932188987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96066546440125</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591202735901</t>
+    <t xml:space="preserve">2.05614185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591178894043</t>
   </si>
   <si>
     <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00840353965759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08001041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08682990074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886271476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909206390381</t>
+    <t xml:space="preserve">2.00840306282043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08001017570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886247634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909230232239</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
@@ -1193,139 +1193,139 @@
     <t xml:space="preserve">1.99135410785675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09023976325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
+    <t xml:space="preserve">2.09024024009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06978130340576</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522326469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817395210266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794424533844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089505195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9538459777832</t>
+    <t xml:space="preserve">1.99817407131195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794412612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089517116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748495101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384573936462</t>
   </si>
   <si>
     <t xml:space="preserve">1.95725572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97771465778351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043611526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361650943756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
+    <t xml:space="preserve">1.97771489620209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504359960556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1413881778717</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18571615219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417622566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2880117893219</t>
+    <t xml:space="preserve">2.185715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417574882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801155090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004364967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21640467643738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889642715454</t>
+    <t xml:space="preserve">2.23004388809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2164044380188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889595031738</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410903930664</t>
+    <t xml:space="preserve">2.11410880088806</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296133995056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1277482509613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705948829651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387921333313</t>
+    <t xml:space="preserve">2.12774848937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705972671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115859031677</t>
+    <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502738952637</t>
+    <t xml:space="preserve">2.15502715110779</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637120246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499391555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9231573343277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.984534740448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09364986419678</t>
+    <t xml:space="preserve">2.16184687614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863312721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315709590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112440109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453462123871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0766007900238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0936496257782</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273175239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299457550049</t>
+    <t xml:space="preserve">2.05273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299481391907</t>
   </si>
   <si>
     <t xml:space="preserve">2.24027371406555</t>
@@ -1334,25 +1334,25 @@
     <t xml:space="preserve">2.19594550132751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17207646369934</t>
+    <t xml:space="preserve">2.17207598686218</t>
   </si>
   <si>
     <t xml:space="preserve">2.18912577629089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1925356388092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23345375061035</t>
+    <t xml:space="preserve">2.19253540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23345398902893</t>
   </si>
   <si>
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391268730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
+    <t xml:space="preserve">2.25391316413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506110191345</t>
@@ -1373,46 +1373,46 @@
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961842536926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33233952522278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3391592502594</t>
+    <t xml:space="preserve">2.35961866378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33915948867798</t>
   </si>
   <si>
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32551956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256887435913</t>
+    <t xml:space="preserve">2.32552027702332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3732578754425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39712715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38689732551575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099595069885</t>
+    <t xml:space="preserve">2.37325763702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39712691307068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38689708709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37666773796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099547386169</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804502487183</t>
@@ -1421,115 +1421,115 @@
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122553825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44827461242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46191382408142</t>
+    <t xml:space="preserve">2.43122529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44827437400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4619140625</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942231178284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306200027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48919272422791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896337509155</t>
+    <t xml:space="preserve">2.51306176185608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48919320106506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896313667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52670121192932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54034090042114</t>
+    <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830808639526</t>
+    <t xml:space="preserve">2.59830832481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.62558698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61535716056824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855290412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61541223526001</t>
+    <t xml:space="preserve">2.61535739898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61541247367859</t>
   </si>
   <si>
     <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56677079200745</t>
+    <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55928754806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63037919998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71269512176514</t>
+    <t xml:space="preserve">2.55928778648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63037896156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71269536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69398713111877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65657043457031</t>
+    <t xml:space="preserve">2.69398665428162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65657067298889</t>
   </si>
   <si>
     <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160370826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405367851257</t>
+    <t xml:space="preserve">2.64160394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405344009399</t>
   </si>
   <si>
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643710136414</t>
+    <t xml:space="preserve">2.71643686294556</t>
   </si>
   <si>
     <t xml:space="preserve">2.72766184806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69772839546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7052116394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72017884254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73140358924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262833595276</t>
+    <t xml:space="preserve">2.69772887229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70521187782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72017860412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73140382766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262857437134</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79126977920532</t>
+    <t xml:space="preserve">2.7912700176239</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120323181152</t>
@@ -1538,13 +1538,13 @@
     <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81371974945068</t>
+    <t xml:space="preserve">2.8137195110321</t>
   </si>
   <si>
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868599891663</t>
+    <t xml:space="preserve">2.82868623733521</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338534355164</t>
+    <t xml:space="preserve">2.96338558197021</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977741241455</t>
+    <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
@@ -1568,16 +1568,16 @@
     <t xml:space="preserve">2.99331879615784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576900482178</t>
+    <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060215950012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10182666778564</t>
+    <t xml:space="preserve">3.09060192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10182690620422</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556840896606</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169333457947</t>
+    <t xml:space="preserve">3.16169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801814079285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06066846847534</t>
+    <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
     <t xml:space="preserve">3.07937669754028</t>
@@ -1607,91 +1607,91 @@
     <t xml:space="preserve">3.10930991172791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09434342384338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0457022190094</t>
+    <t xml:space="preserve">3.09434366226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04570174217224</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583579063416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97461032867432</t>
+    <t xml:space="preserve">2.98583555221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
     <t xml:space="preserve">2.91100287437439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07189345359802</t>
+    <t xml:space="preserve">2.91474461555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0718936920166</t>
   </si>
   <si>
     <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951026916504</t>
+    <t xml:space="preserve">3.01951050758362</t>
   </si>
   <si>
     <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90351963043213</t>
+    <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
     <t xml:space="preserve">2.97835254669189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98209404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467759132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841885566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086906433105</t>
+    <t xml:space="preserve">2.98209381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841933250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086930274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84739470481873</t>
+    <t xml:space="preserve">2.84739446640015</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80249452590942</t>
+    <t xml:space="preserve">2.80249500274658</t>
   </si>
   <si>
     <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85113620758057</t>
+    <t xml:space="preserve">2.85113644599915</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365296363831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86236095428467</t>
+    <t xml:space="preserve">2.86236119270325</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848635673523</t>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596912384033</t>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726089477539</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
+    <t xml:space="preserve">2.79875302314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">2.76882004737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80997824668884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7613365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106966018677</t>
+    <t xml:space="preserve">2.80997800827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76133704185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590233802795</t>
+    <t xml:space="preserve">2.95590281486511</t>
   </si>
   <si>
     <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88481092453003</t>
+    <t xml:space="preserve">2.88481116294861</t>
   </si>
   <si>
     <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78378677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8174614906311</t>
+    <t xml:space="preserve">2.78378653526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81746125221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.85487794876099</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">2.98957705497742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30761766433716</t>
+    <t xml:space="preserve">3.30761742591858</t>
   </si>
   <si>
     <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3263258934021</t>
+    <t xml:space="preserve">3.32632565498352</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986703872681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36374187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360854148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44979977607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625863075256</t>
+    <t xml:space="preserve">3.3637421131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360806465149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.26645922660828</t>
@@ -1781,43 +1781,43 @@
     <t xml:space="preserve">3.22530126571655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2814257144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258439064026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2963924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924360275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1130518913269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440997123718</t>
+    <t xml:space="preserve">3.28142595291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3225839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639267921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924336433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305141448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06441020965576</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679315567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08685994148254</t>
+    <t xml:space="preserve">3.11679339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08686017990112</t>
   </si>
   <si>
     <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57425427436829</t>
+    <t xml:space="preserve">2.57425451278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2562141418457</t>
+    <t xml:space="preserve">2.25621438026428</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853054046631</t>
@@ -1832,7 +1832,7 @@
     <t xml:space="preserve">2.43581318855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942135810852</t>
+    <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">2.46574664115906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42833018302917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812958717346</t>
+    <t xml:space="preserve">2.42832970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213847160339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812934875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465498924255</t>
+    <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
     <t xml:space="preserve">2.35723853111267</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962147712708</t>
+    <t xml:space="preserve">2.40962195396423</t>
   </si>
   <si>
     <t xml:space="preserve">2.4545214176178</t>
@@ -1886,52 +1886,52 @@
     <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5218710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935457229614</t>
+    <t xml:space="preserve">2.52187132835388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193787574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5069043636322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670424461365</t>
+    <t xml:space="preserve">2.50690460205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795087814331</t>
+    <t xml:space="preserve">3.15795111656189</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27768445014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714460372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17801690101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10721945762634</t>
+    <t xml:space="preserve">3.27768421173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17801713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1072199344635</t>
   </si>
   <si>
     <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99709010124207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788778305054</t>
+    <t xml:space="preserve">2.99709057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788754463196</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12295246124268</t>
+    <t xml:space="preserve">3.12295269966125</t>
   </si>
   <si>
     <t xml:space="preserve">3.07182097434998</t>
@@ -1952,34 +1952,34 @@
     <t xml:space="preserve">2.96955823898315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92235994338989</t>
+    <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.94202542304993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9498918056488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595861434937</t>
+    <t xml:space="preserve">2.94989228248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742438316345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90269374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336207389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8082971572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78076505661011</t>
+    <t xml:space="preserve">2.9026939868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80829739570618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78076481819153</t>
   </si>
   <si>
     <t xml:space="preserve">2.79649782180786</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896524429321</t>
+    <t xml:space="preserve">2.76896548271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749971389771</t>
+    <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
     <t xml:space="preserve">2.66276907920837</t>
@@ -2006,22 +2006,22 @@
     <t xml:space="preserve">2.74536633491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76109886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456889152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737035751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803844451904</t>
+    <t xml:space="preserve">2.76109910011292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63523697853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737059593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74143314361572</t>
+    <t xml:space="preserve">2.74143290519714</t>
   </si>
   <si>
     <t xml:space="preserve">2.72963356971741</t>
@@ -2039,22 +2039,22 @@
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6391704082489</t>
+    <t xml:space="preserve">2.68243551254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63917016983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65490293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883612632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017206192017</t>
+    <t xml:space="preserve">2.6549026966095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017230033875</t>
   </si>
   <si>
     <t xml:space="preserve">2.58410549163818</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64703679084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343764305115</t>
+    <t xml:space="preserve">2.6470365524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343716621399</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983849525452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65096974372864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75323247909546</t>
+    <t xml:space="preserve">2.59983825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65096950531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
     <t xml:space="preserve">2.52510762214661</t>
@@ -2087,19 +2087,19 @@
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084062576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150847434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544166564941</t>
+    <t xml:space="preserve">2.54084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330828666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397613525391</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610975265503</t>
+    <t xml:space="preserve">2.49364185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610999107361</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
@@ -2126,34 +2126,34 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38351273536682</t>
+    <t xml:space="preserve">2.38351249694824</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39924550056458</t>
+    <t xml:space="preserve">2.399245262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3913791179657</t>
+    <t xml:space="preserve">2.39137935638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.35598063468933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.340247631073</t>
+    <t xml:space="preserve">2.31271553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34024786949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631443977356</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">2.36384677886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557126045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.57230591773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356628417969</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783399581909</t>
+    <t xml:space="preserve">2.71783375740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70603442192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210123062134</t>
+    <t xml:space="preserve">2.70603466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210099220276</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2207,37 +2207,37 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449356079102</t>
+    <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02068948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562480926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83976268768311</t>
+    <t xml:space="preserve">3.0206892490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9616916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562504768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8476288318634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156226158142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302779197693</t>
+    <t xml:space="preserve">2.84762907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910560131073</t>
+    <t xml:space="preserve">2.91055989265442</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876055717468</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82796335220337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022608757019</t>
+    <t xml:space="preserve">2.82796311378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729502677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022632598877</t>
   </si>
   <si>
     <t xml:space="preserve">3.00495648384094</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">3.01675653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02462291717529</t>
+    <t xml:space="preserve">3.02462244033813</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2288,31 +2288,31 @@
     <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922395706177</t>
+    <t xml:space="preserve">2.98922371864319</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0521547794342</t>
+    <t xml:space="preserve">3.07575440406799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215501785278</t>
   </si>
   <si>
     <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06002116203308</t>
+    <t xml:space="preserve">3.06002163887024</t>
   </si>
   <si>
     <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04428839683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148693084717</t>
+    <t xml:space="preserve">3.04428863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688565254211</t>
@@ -2327,28 +2327,28 @@
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374990463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1544177532196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21029019355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10382652282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06287884712219</t>
+    <t xml:space="preserve">3.19374966621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441823005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21029043197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10382676124573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
     <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12839484214783</t>
+    <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2360,7 +2360,7 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106852531433</t>
+    <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374197006226</t>
@@ -2369,34 +2369,34 @@
     <t xml:space="preserve">3.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00555276870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602601051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468940734863</t>
+    <t xml:space="preserve">3.03421568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783680915833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0055525302887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335304260254</t>
+    <t xml:space="preserve">3.08335280418396</t>
   </si>
   <si>
     <t xml:space="preserve">3.0751633644104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98507881164551</t>
+    <t xml:space="preserve">2.98507857322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">2.96460461616516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93594169616699</t>
+    <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7762463092804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80490946769714</t>
+    <t xml:space="preserve">2.77624607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633062362671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89499425888062</t>
+    <t xml:space="preserve">2.89499402046204</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
@@ -2465,28 +2465,28 @@
     <t xml:space="preserve">2.87861514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87452006340027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775201797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989173412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193140983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9727942943573</t>
+    <t xml:space="preserve">2.87452030181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775225639343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99736285209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98917365074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193164825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97279453277588</t>
   </si>
   <si>
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365717887878</t>
+    <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
     <t xml:space="preserve">2.96869969367981</t>
@@ -2495,37 +2495,37 @@
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184685707092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680481910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8294780254364</t>
+    <t xml:space="preserve">2.93184661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680458068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
     <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81719350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82128834724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85814118385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84995150566101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91546773910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357262611389</t>
+    <t xml:space="preserve">2.81719374656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82128810882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85814142227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84995174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051001548767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91546750068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,16 +2534,16 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215123176575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84176230430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79262495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80900406837463</t>
+    <t xml:space="preserve">2.77215099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84176206588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79262518882751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80900430679321</t>
   </si>
   <si>
     <t xml:space="preserve">2.83766746520996</t>
@@ -2555,25 +2555,25 @@
     <t xml:space="preserve">2.66978240013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034090995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6943507194519</t>
+    <t xml:space="preserve">2.78034067153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986695289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69435095787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.64521384239197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67387747764587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805663108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74348759651184</t>
+    <t xml:space="preserve">2.67387723922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.743488073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7271089553833</t>
+    <t xml:space="preserve">2.72710871696472</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95615839958191</t>
+    <t xml:space="preserve">2.95615863800049</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83155274391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89600372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84873962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725596427917</t>
+    <t xml:space="preserve">2.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89600396156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84873986244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725620269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717874526978</t>
+    <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
@@ -2633,19 +2633,19 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881684303284</t>
+    <t xml:space="preserve">2.87881708145142</t>
   </si>
   <si>
     <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90459752082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.90459775924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5479679107666</t>
+    <t xml:space="preserve">2.59952878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54796767234802</t>
   </si>
   <si>
     <t xml:space="preserve">2.53507781028748</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
+    <t xml:space="preserve">2.44914269447327</t>
   </si>
   <si>
     <t xml:space="preserve">2.43195581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4878134727478</t>
+    <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2720,10 +2720,10 @@
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602117538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.34602093696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39758205413818</t>
+    <t xml:space="preserve">2.3975818157196</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469171524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625259399414</t>
+    <t xml:space="preserve">2.38469195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625283241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
@@ -2759,28 +2759,28 @@
     <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33742737770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28156971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711850166321</t>
+    <t xml:space="preserve">2.33742761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118386268616</t>
+    <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
     <t xml:space="preserve">2.06243634223938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11829352378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110688209534</t>
+    <t xml:space="preserve">2.11829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
     <t xml:space="preserve">2.12259030342102</t>
@@ -2792,16 +2792,16 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985464096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14407396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08392000198364</t>
+    <t xml:space="preserve">2.16985487937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14407420158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399722099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
     <t xml:space="preserve">2.02376532554626</t>
@@ -2810,22 +2810,22 @@
     <t xml:space="preserve">1.88197290897369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94212746620178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89056658744812</t>
+    <t xml:space="preserve">1.94212734699249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322503089905</t>
+    <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744459152222</t>
+    <t xml:space="preserve">1.78744447231293</t>
   </si>
   <si>
     <t xml:space="preserve">1.71869671344757</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67744791507721</t>
+    <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
     <t xml:space="preserve">1.64307403564453</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">1.62416839599609</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65854239463806</t>
+    <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729015350342</t>
@@ -2858,13 +2858,13 @@
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790778636932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353378772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650134563446</t>
+    <t xml:space="preserve">1.96790766716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353366851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650110721588</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04954600334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95931434631348</t>
+    <t xml:space="preserve">2.0495457649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95931422710419</t>
   </si>
   <si>
     <t xml:space="preserve">2.07962322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08821678161621</t>
+    <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.04524946212769</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17844796180725</t>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21282196044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19563508033752</t>
+    <t xml:space="preserve">2.2128221988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1956353187561</t>
   </si>
   <si>
     <t xml:space="preserve">2.19993162155151</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">2.06673288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09681010246277</t>
+    <t xml:space="preserve">2.09681034088135</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2942,10 +2942,10 @@
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28586649894714</t>
+    <t xml:space="preserve">2.23000907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
     <t xml:space="preserve">2.32024049758911</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438283920288</t>
+    <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313059806824</t>
+    <t xml:space="preserve">2.33313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750483512878</t>
+    <t xml:space="preserve">2.36750507354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.427659034729</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39328527450562</t>
+    <t xml:space="preserve">2.39328503608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41047215461731</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">2.47062659263611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50070405006409</t>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3861,6 +3861,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.38000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32999992370605</t>
   </si>
 </sst>
 </file>
@@ -69381,13 +69384,13 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6912615741</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>233320</v>
       </c>
       <c r="C2508" t="n">
-        <v>3.375</v>
+        <v>3.38000011444092</v>
       </c>
       <c r="D2508" t="n">
         <v>3.28500008583069</v>
@@ -69402,6 +69405,32 @@
         <v>1282</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6911805556</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>179685</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>3.32999992370605</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>1283</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27862024307251</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2682341337204</t>
+    <t xml:space="preserve">1.27977383136749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26823401451111</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977028369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246037960052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437861442566</t>
+    <t xml:space="preserve">1.24977040290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.19784080982208</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283879756927</t>
+    <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.25438630580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746239185333</t>
+    <t xml:space="preserve">1.24746215343475</t>
   </si>
   <si>
     <t xml:space="preserve">1.27285003662109</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">1.20591855049133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168875694275</t>
+    <t xml:space="preserve">1.21168863773346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21053469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899854183197</t>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130643367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899866104126</t>
   </si>
   <si>
     <t xml:space="preserve">1.23476850986481</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">1.23707640171051</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2901599407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669786453247</t>
+    <t xml:space="preserve">1.29016005992889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28208184242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439021110535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169597148895</t>
+    <t xml:space="preserve">1.28208208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438985347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169620990753</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054581165314</t>
+    <t xml:space="preserve">1.30054593086243</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862355232239</t>
@@ -164,16 +164,16 @@
     <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30746984481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32593369483948</t>
+    <t xml:space="preserve">1.3074699640274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
     <t xml:space="preserve">1.30516183376312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32016372680664</t>
+    <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.3236255645752</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">1.32708764076233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31323969364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824158668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
+    <t xml:space="preserve">1.31323957443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3282413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132133960724</t>
   </si>
   <si>
     <t xml:space="preserve">1.34439730644226</t>
@@ -197,100 +197,100 @@
     <t xml:space="preserve">1.34670531749725</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016751289368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478341579437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208941459656</t>
+    <t xml:space="preserve">1.3501672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478329658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170709133148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208953380585</t>
   </si>
   <si>
     <t xml:space="preserve">1.34324336051941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516904830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324750423431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017117977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786316871643</t>
+    <t xml:space="preserve">1.34555160999298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516892910004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786293029785</t>
   </si>
   <si>
     <t xml:space="preserve">1.36747705936432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36286115646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251494407654</t>
+    <t xml:space="preserve">1.3628613948822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.394979596138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251518249512</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41099977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42702007293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687856197357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427227973938</t>
+    <t xml:space="preserve">1.41099989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687868118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427251815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043385028839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46275722980499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110043048859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863530158997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342333316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821112632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574671268463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849414825439</t>
+    <t xml:space="preserve">1.45043408870697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536327362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4627571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110054969788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863565921783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821100711823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162538051605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465571880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574647426605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4984940290451</t>
   </si>
   <si>
     <t xml:space="preserve">1.5403927564621</t>
@@ -299,91 +299,91 @@
     <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61433160305023</t>
+    <t xml:space="preserve">1.61433172225952</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707939624786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52437257766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958502292633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641281604767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077655315399</t>
+    <t xml:space="preserve">1.5243729352951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958514213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641305446625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077631473541</t>
   </si>
   <si>
     <t xml:space="preserve">1.5465544462204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52190828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257462501526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59584701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6636244058609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006899833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461462497711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883637428284</t>
+    <t xml:space="preserve">1.52190792560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584677219391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006852149963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5946147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883661270142</t>
   </si>
   <si>
     <t xml:space="preserve">1.65992724895477</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66115975379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661412715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400772571564</t>
+    <t xml:space="preserve">1.66115963459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661353111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7215428352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400760650635</t>
   </si>
   <si>
     <t xml:space="preserve">1.68950307369232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68827056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7252402305603</t>
+    <t xml:space="preserve">1.68827044963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523999214172</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429074764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059394836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675528049469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301750659943</t>
+    <t xml:space="preserve">1.70429062843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7067551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784627437592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
   </si>
   <si>
     <t xml:space="preserve">1.75604772567749</t>
@@ -392,34 +392,34 @@
     <t xml:space="preserve">1.78439116477966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77206778526306</t>
+    <t xml:space="preserve">1.77206754684448</t>
   </si>
   <si>
     <t xml:space="preserve">1.74988615512848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74865400791168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7461895942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837086677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7745326757431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7622092962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699720859528</t>
+    <t xml:space="preserve">1.74865388870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618947505951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837074756622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453243732452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220965385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699732780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.76344180107117</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65746247768402</t>
+    <t xml:space="preserve">1.6574627161026</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855335235596</t>
@@ -428,94 +428,94 @@
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443202018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186730861664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158416748047</t>
+    <t xml:space="preserve">1.69443213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186718940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158404827118</t>
   </si>
   <si>
     <t xml:space="preserve">1.60447335243225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
+    <t xml:space="preserve">1.6303516626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6167961359024</t>
   </si>
   <si>
     <t xml:space="preserve">1.6426750421524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376591682434</t>
+    <t xml:space="preserve">1.65376555919647</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63281643390656</t>
+    <t xml:space="preserve">1.63281655311584</t>
   </si>
   <si>
     <t xml:space="preserve">1.61309945583344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6155641078949</t>
+    <t xml:space="preserve">1.61556386947632</t>
   </si>
   <si>
     <t xml:space="preserve">1.61802840232849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021039009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130114555359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623033046722</t>
+    <t xml:space="preserve">1.64021027088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760422706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130126476288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623044967651</t>
   </si>
   <si>
     <t xml:space="preserve">1.61926102638245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.645139336586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091770648956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546345233917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972653388977</t>
+    <t xml:space="preserve">1.64513957500458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144265651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091782569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479711055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972629547119</t>
   </si>
   <si>
     <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5884530544281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503903865814</t>
+    <t xml:space="preserve">1.55887734889984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845317363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
   </si>
   <si>
     <t xml:space="preserve">1.53423130512238</t>
@@ -524,19 +524,19 @@
     <t xml:space="preserve">1.49726188182831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532206058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120072841644</t>
+    <t xml:space="preserve">1.51451420783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532194137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120060920715</t>
   </si>
   <si>
     <t xml:space="preserve">1.58598828315735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58105933666229</t>
+    <t xml:space="preserve">1.58105909824371</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
@@ -545,61 +545,61 @@
     <t xml:space="preserve">1.59338235855103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5872209072113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66485643386841</t>
+    <t xml:space="preserve">1.58722078800201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6365133523941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
     <t xml:space="preserve">1.65499818325043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67594766616821</t>
+    <t xml:space="preserve">1.67594742774963</t>
   </si>
   <si>
     <t xml:space="preserve">1.67225062847137</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67841196060181</t>
+    <t xml:space="preserve">1.67841184139252</t>
   </si>
   <si>
     <t xml:space="preserve">1.69073498249054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66978585720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703830242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7055230140686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538126468658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457353115082</t>
+    <t xml:space="preserve">1.66978597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717945575714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552289485931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291661262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457341194153</t>
   </si>
   <si>
     <t xml:space="preserve">1.76467418670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75727999210358</t>
+    <t xml:space="preserve">1.75728034973145</t>
   </si>
   <si>
     <t xml:space="preserve">1.74125981330872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016917705536</t>
+    <t xml:space="preserve">1.73016953468323</t>
   </si>
   <si>
     <t xml:space="preserve">1.77330017089844</t>
@@ -608,82 +608,82 @@
     <t xml:space="preserve">1.77946186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74742162227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069412708282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8176634311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150186061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614802360535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
+    <t xml:space="preserve">1.7474217414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7806943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178512096405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590645313263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614814281464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695611476898</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89899623394012</t>
+    <t xml:space="preserve">1.8989964723587</t>
   </si>
   <si>
     <t xml:space="preserve">1.9076224565506</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90392529964447</t>
+    <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
     <t xml:space="preserve">1.94459187984467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980408668518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279333114624</t>
+    <t xml:space="preserve">1.92980420589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279345035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867247581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687428474426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729846000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796456336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303525924683</t>
+    <t xml:space="preserve">2.02838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0468738079071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729822158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10725736618042</t>
+    <t xml:space="preserve">2.107257604599</t>
   </si>
   <si>
     <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09986329078674</t>
+    <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.13806509971619</t>
@@ -695,67 +695,67 @@
     <t xml:space="preserve">2.16024708747864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16887307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17256999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15654993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380213737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531778335571</t>
+    <t xml:space="preserve">2.16887331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1725697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15655016899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119645118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010521888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531754493713</t>
   </si>
   <si>
     <t xml:space="preserve">2.16640853881836</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21446919441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18366074562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1799635887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816611289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323657035828</t>
+    <t xml:space="preserve">2.21446895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18366098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17996406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2132363319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978157997131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717541694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3303062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877203941345</t>
+    <t xml:space="preserve">2.27978134155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33030652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289432525635</t>
+    <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
     <t xml:space="preserve">2.31477975845337</t>
@@ -764,52 +764,52 @@
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137877464294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019522666931</t>
+    <t xml:space="preserve">2.25137829780579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019570350647</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267243385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973345756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313444137573</t>
+    <t xml:space="preserve">2.23973393440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33677577972412</t>
+    <t xml:space="preserve">2.3367760181427</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806967735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34453916549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3613600730896</t>
+    <t xml:space="preserve">2.36782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34453940391541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065771102905</t>
+    <t xml:space="preserve">2.34065723419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.32901215553284</t>
@@ -818,49 +818,49 @@
     <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324526786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40535259246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642436027527</t>
+    <t xml:space="preserve">2.34971499443054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40535187721252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642483711243</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537081718445</t>
+    <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">2.29666519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2449095249176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26949310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26043581962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26172995567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361515045166</t>
+    <t xml:space="preserve">2.25396680831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490904808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26949334144592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26043605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784802436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26172971725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361562728882</t>
   </si>
   <si>
     <t xml:space="preserve">2.2060923576355</t>
@@ -869,70 +869,70 @@
     <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21903157234192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197054862976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102735519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771825790405</t>
+    <t xml:space="preserve">2.21903133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102711677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3225429058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725648880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855062484741</t>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725672721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855038642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278302192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041735649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548212051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747838020325</t>
+    <t xml:space="preserve">2.28890204429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879097938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548188209534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747790336609</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819968223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160018920898</t>
+    <t xml:space="preserve">2.28631377220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337527275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160066604614</t>
   </si>
   <si>
     <t xml:space="preserve">2.30960392951965</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">2.33418798446655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30572247505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359668731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745896339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
+    <t xml:space="preserve">2.3057222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359644889832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171101570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664601325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699719429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546294212341</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38723802566528</t>
+    <t xml:space="preserve">2.38723754882812</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241361618042</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524176597595</t>
+    <t xml:space="preserve">2.36524152755737</t>
   </si>
   <si>
     <t xml:space="preserve">2.40794014930725</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">2.39370727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37688636779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36265397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464975357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
+    <t xml:space="preserve">2.37688660621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38465023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607341766357</t>
   </si>
   <si>
     <t xml:space="preserve">2.36459445953369</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37429904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37753343582153</t>
+    <t xml:space="preserve">2.37429881095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.3193085193634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492822647095</t>
+    <t xml:space="preserve">2.13492798805237</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346773147583</t>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788614273071</t>
@@ -1031,40 +1031,40 @@
     <t xml:space="preserve">2.08964204788208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993721961975</t>
+    <t xml:space="preserve">2.07993745803833</t>
   </si>
   <si>
     <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12198925018311</t>
+    <t xml:space="preserve">2.12198877334595</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699848175049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847720146179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966027259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0152428150177</t>
+    <t xml:space="preserve">2.05082488059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966051101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524305343628</t>
   </si>
   <si>
     <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0475902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640718460083</t>
+    <t xml:space="preserve">2.04759001731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640646934509</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07670259475708</t>
+    <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522387504578</t>
@@ -1082,31 +1082,31 @@
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052923202515</t>
+    <t xml:space="preserve">2.06052899360657</t>
   </si>
   <si>
     <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09934616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875414848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845849990845</t>
+    <t xml:space="preserve">2.09934568405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905051231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139771461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845826148987</t>
   </si>
   <si>
     <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15433645248413</t>
+    <t xml:space="preserve">2.15433669090271</t>
   </si>
   <si>
     <t xml:space="preserve">2.19962286949158</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755261421204</t>
+    <t xml:space="preserve">2.26755237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.28460168838501</t>
@@ -1124,46 +1124,46 @@
     <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20958495140076</t>
+    <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22322416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433886528015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751866340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069941520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10046935081482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08342051506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04932188987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066546440125</t>
+    <t xml:space="preserve">2.223224401474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1004695892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08342027664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04932165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96066534519196</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614185333252</t>
+    <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.04591178894043</t>
@@ -1172,73 +1172,73 @@
     <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00840306282043</t>
+    <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
     <t xml:space="preserve">2.08001017570496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08683013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909230232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04250192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99135410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09024024009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978130340576</t>
+    <t xml:space="preserve">2.08682990074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0425021648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99135458469391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09024000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522326469421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817407131195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794412612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089517116547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384573936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771489620209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504359960556</t>
+    <t xml:space="preserve">1.99817395210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089529037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748566627502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9538459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725548267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771513462067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043611526489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94361627101898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1413881778717</t>
+    <t xml:space="preserve">2.14138770103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.185715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417574882507</t>
+    <t xml:space="preserve">2.18571591377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
     <t xml:space="preserve">2.28801155090332</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">2.2164044380188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17889595031738</t>
+    <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11410880088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296133995056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12774848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387945175171</t>
+    <t xml:space="preserve">2.11410903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296110153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12774872779846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705996513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387969017029</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1584370136261</t>
+    <t xml:space="preserve">2.15843677520752</t>
   </si>
   <si>
     <t xml:space="preserve">2.15502715110779</t>
@@ -1289,52 +1289,52 @@
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499367713928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863312721252</t>
+    <t xml:space="preserve">2.16184711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637120246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499391555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01863288879395</t>
   </si>
   <si>
     <t xml:space="preserve">2.05955123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112440109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453462123871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0766007900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0936496257782</t>
+    <t xml:space="preserve">1.92315685749054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112463951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453450202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07660055160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09364986419678</t>
   </si>
   <si>
     <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299481391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24027371406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594550132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207598686218</t>
+    <t xml:space="preserve">2.05273175239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24027347564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207622528076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18912577629089</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">2.19253540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23345398902893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23686361312866</t>
+    <t xml:space="preserve">2.23345375061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23686337471008</t>
   </si>
   <si>
     <t xml:space="preserve">2.25391316413879</t>
@@ -1355,43 +1355,43 @@
     <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506110191345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29824113845825</t>
+    <t xml:space="preserve">2.30506086349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
     <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961866378784</t>
+    <t xml:space="preserve">2.35961818695068</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233976364136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33915948867798</t>
+    <t xml:space="preserve">2.36643815040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32552027702332</t>
+    <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">2.38689708709717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37666773796082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099547386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
+    <t xml:space="preserve">2.37666726112366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099595069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804478645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44827437400818</t>
+    <t xml:space="preserve">2.43122553825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44827461242676</t>
   </si>
   <si>
     <t xml:space="preserve">2.4619140625</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">2.51306176185608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48919320106506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670121192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034066200256</t>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896337509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034042358398</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171794891357</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">2.59830832481384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62558698654175</t>
+    <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
     <t xml:space="preserve">2.61535739898682</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">2.88855266571045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61541247367859</t>
+    <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
     <t xml:space="preserve">2.61167073249817</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58547925949097</t>
+    <t xml:space="preserve">2.58547902107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928778648376</t>
@@ -1481,13 +1481,13 @@
     <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269536018372</t>
+    <t xml:space="preserve">2.71269512176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69398665428162</t>
+    <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
     <t xml:space="preserve">2.65657067298889</t>
@@ -1499,52 +1499,52 @@
     <t xml:space="preserve">2.64160394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66405344009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031217575073</t>
+    <t xml:space="preserve">2.66405367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031241416931</t>
   </si>
   <si>
     <t xml:space="preserve">2.71643686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72766184806824</t>
+    <t xml:space="preserve">2.72766208648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772887229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70521187782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72017860412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73140382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262857437134</t>
+    <t xml:space="preserve">2.70521211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7201783657074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73140358924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262833595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7912700176239</t>
+    <t xml:space="preserve">2.79126977920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120323181152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83616948127747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8137195110321</t>
+    <t xml:space="preserve">2.83616971969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868623733521</t>
+    <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
@@ -1553,22 +1553,22 @@
     <t xml:space="preserve">2.86984443664551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92971086502075</t>
+    <t xml:space="preserve">2.96338582038879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92971062660217</t>
   </si>
   <si>
     <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93719410896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331879615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">2.93719434738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331903457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576900482178</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">3.09060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10182690620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10556840896606</t>
+    <t xml:space="preserve">3.10182666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10556817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053489685059</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">3.16169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12801814079285</t>
+    <t xml:space="preserve">3.12801790237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07937669754028</t>
+    <t xml:space="preserve">3.0793764591217</t>
   </si>
   <si>
     <t xml:space="preserve">3.10930991172791</t>
@@ -1610,64 +1610,64 @@
     <t xml:space="preserve">3.09434366226196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04570174217224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99706053733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583555221558</t>
+    <t xml:space="preserve">3.04570198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583579063416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100287437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951050758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00454378128052</t>
+    <t xml:space="preserve">2.91100239753723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951003074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0045440196991</t>
   </si>
   <si>
     <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
+    <t xml:space="preserve">2.97835206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209404945374</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841933250427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086930274963</t>
+    <t xml:space="preserve">2.94841909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086906433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84739446640015</t>
+    <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
     <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80249500274658</t>
+    <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
     <t xml:space="preserve">2.83991122245789</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848587989807</t>
+    <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596936225891</t>
+    <t xml:space="preserve">2.92596912384033</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726089477539</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004479408264</t>
+    <t xml:space="preserve">2.79875326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004455566406</t>
   </si>
   <si>
     <t xml:space="preserve">2.76882004737854</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">2.80997800827026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76133704185486</t>
+    <t xml:space="preserve">2.7613365650177</t>
   </si>
   <si>
     <t xml:space="preserve">2.88106942176819</t>
@@ -1721,16 +1721,16 @@
     <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0307354927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95590281486511</t>
+    <t xml:space="preserve">3.03073573112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95590209960938</t>
   </si>
   <si>
     <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88481116294861</t>
+    <t xml:space="preserve">2.88481092453003</t>
   </si>
   <si>
     <t xml:space="preserve">2.87358617782593</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">2.78378653526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81746125221252</t>
+    <t xml:space="preserve">2.81746172904968</t>
   </si>
   <si>
     <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98957705497742</t>
+    <t xml:space="preserve">2.989577293396</t>
   </si>
   <si>
     <t xml:space="preserve">3.30761742591858</t>
@@ -1754,31 +1754,31 @@
     <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632565498352</t>
+    <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986703872681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3637421131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360806465149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980001449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26645922660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530126571655</t>
+    <t xml:space="preserve">3.36374187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44979977607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664589881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530078887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.28142595291138</t>
@@ -1790,112 +1790,112 @@
     <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924336433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06441020965576</t>
+    <t xml:space="preserve">3.13924312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06440997123718</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679339408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944348335266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425451278687</t>
+    <t xml:space="preserve">3.11679315567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08685994148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944324493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425403594971</t>
   </si>
   <si>
     <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25621438026428</t>
+    <t xml:space="preserve">2.2562141418457</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091348648071</t>
+    <t xml:space="preserve">2.37968850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581318855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942111968994</t>
+    <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
     <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51438784599304</t>
+    <t xml:space="preserve">2.51438760757446</t>
   </si>
   <si>
     <t xml:space="preserve">2.46574664115906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42832970619202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812934875488</t>
+    <t xml:space="preserve">2.4283299446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39465522766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35723853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839673042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4133632183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43207168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40962195396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4545214176178</t>
+    <t xml:space="preserve">2.39465498924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35723876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839696884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710519790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41336297988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43207144737244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40962147712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45452117919922</t>
   </si>
   <si>
     <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187132835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935481071472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50316286087036</t>
+    <t xml:space="preserve">2.5218710899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935457229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50316309928894</t>
   </si>
   <si>
     <t xml:space="preserve">2.50690460205078</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78752827644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15795111656189</t>
+    <t xml:space="preserve">2.7875280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17801713943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1072199344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709057807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788754463196</t>
+    <t xml:space="preserve">3.17801690101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10721945762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0010232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788802146912</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
@@ -1955,10 +1955,10 @@
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202542304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989228248596</t>
+    <t xml:space="preserve">2.94202589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742438316345</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076481819153</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896548271179</t>
+    <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749995231628</t>
+    <t xml:space="preserve">2.73749971389771</t>
   </si>
   <si>
     <t xml:space="preserve">2.66276907920837</t>
@@ -2003,10 +2003,10 @@
     <t xml:space="preserve">2.78863143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74536633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109910011292</t>
+    <t xml:space="preserve">2.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.67456912994385</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62737059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803868293762</t>
+    <t xml:space="preserve">2.62737035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
@@ -2030,7 +2030,7 @@
     <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74143290519714</t>
+    <t xml:space="preserve">2.7414333820343</t>
   </si>
   <si>
     <t xml:space="preserve">2.72963356971741</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243551254272</t>
+    <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.63917016983032</t>
@@ -2048,10 +2048,10 @@
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6549026966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883636474609</t>
+    <t xml:space="preserve">2.65490293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883612632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6470365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343716621399</t>
+    <t xml:space="preserve">2.64703631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343764305115</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323271751404</t>
+    <t xml:space="preserve">2.75323247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.52510762214661</t>
@@ -2087,22 +2087,22 @@
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084038734436</t>
+    <t xml:space="preserve">2.54084062576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970866203308</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51330828666687</t>
+    <t xml:space="preserve">2.51330780982971</t>
   </si>
   <si>
     <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50544142723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397613525391</t>
+    <t xml:space="preserve">2.50544166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397637367249</t>
   </si>
   <si>
     <t xml:space="preserve">2.48577570915222</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364185333252</t>
+    <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
     <t xml:space="preserve">2.46610999107361</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38351249694824</t>
+    <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
+    <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39137935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598063468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531230926514</t>
+    <t xml:space="preserve">2.3913791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598039627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531254768372</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34024786949158</t>
+    <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631443977356</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">2.57230591773987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356628417969</t>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783375740051</t>
+    <t xml:space="preserve">2.71783399581909</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
@@ -2186,10 +2186,10 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70603466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210099220276</t>
+    <t xml:space="preserve">2.70603442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594286441803</t>
+    <t xml:space="preserve">2.85942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2216,16 +2216,16 @@
     <t xml:space="preserve">3.0206892490387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9616916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562504768372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83976292610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83189630508423</t>
+    <t xml:space="preserve">2.96169185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83976268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83189606666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">2.82009673118591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809247016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90662693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055989265442</t>
+    <t xml:space="preserve">2.85156226158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809223175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90662670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876055717468</t>
@@ -2255,28 +2255,28 @@
     <t xml:space="preserve">2.95775818824768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95382523536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87516140937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796311378479</t>
+    <t xml:space="preserve">2.9538254737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87516164779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
     <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93022632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495648384094</t>
+    <t xml:space="preserve">2.93022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
     <t xml:space="preserve">3.01675653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02462244033813</t>
+    <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922371864319</t>
+    <t xml:space="preserve">2.98922419548035</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575440406799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002163887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.07575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855563163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002140045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
@@ -2315,13 +2315,13 @@
     <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12688565254211</t>
+    <t xml:space="preserve">3.12688541412354</t>
   </si>
   <si>
     <t xml:space="preserve">3.10328650474548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
@@ -2330,16 +2330,16 @@
     <t xml:space="preserve">3.19374966621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15441823005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981647491455</t>
+    <t xml:space="preserve">3.15441799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382676124573</t>
+    <t xml:space="preserve">3.10382652282715</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
@@ -2360,43 +2360,43 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374197006226</t>
+    <t xml:space="preserve">3.07106852531433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374220848083</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421568870544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01783680915833</t>
+    <t xml:space="preserve">3.03421592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602624893188</t>
+    <t xml:space="preserve">3.03831052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602601051331</t>
   </si>
   <si>
     <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04649996757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0751633644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507857322693</t>
+    <t xml:space="preserve">3.04650020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08335304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07516360282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
+    <t xml:space="preserve">2.9031834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89089918136597</t>
+    <t xml:space="preserve">2.89089941978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.84585666656494</t>
@@ -2435,13 +2435,13 @@
     <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94003629684448</t>
+    <t xml:space="preserve">2.9400360584259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85404634475708</t>
+    <t xml:space="preserve">2.85404658317566</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624607086182</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633062362671</t>
+    <t xml:space="preserve">2.80490946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
     <t xml:space="preserve">2.89499402046204</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">2.87861514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87452030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775225639343</t>
+    <t xml:space="preserve">2.87452006340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.99736285209656</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365741729736</t>
+    <t xml:space="preserve">2.92365717887878</t>
   </si>
   <si>
     <t xml:space="preserve">2.96869969367981</t>
@@ -2495,46 +2495,46 @@
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
+    <t xml:space="preserve">2.93184685707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82947778701782</t>
+    <t xml:space="preserve">2.8294780254364</t>
   </si>
   <si>
     <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81719374656677</t>
+    <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.82128810882568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85814142227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051001548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91546750068665</t>
+    <t xml:space="preserve">2.85814118385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84995150566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
     <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
+    <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
     <t xml:space="preserve">2.84176206588745</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">2.79262518882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80900430679321</t>
+    <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80081462860107</t>
+    <t xml:space="preserve">2.80081486701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69435095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521384239197</t>
+    <t xml:space="preserve">2.69435048103333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521408081055</t>
   </si>
   <si>
     <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
+    <t xml:space="preserve">2.76805663108826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
+    <t xml:space="preserve">2.7271089553833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95615863800049</t>
+    <t xml:space="preserve">2.95615839958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">2.89170718193054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85303664207458</t>
+    <t xml:space="preserve">2.85303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">2.87881708145142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86162996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90459775924683</t>
+    <t xml:space="preserve">2.86163020133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
     <t xml:space="preserve">2.90889406204224</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2666,10 +2666,10 @@
     <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54796767234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53507781028748</t>
+    <t xml:space="preserve">2.5479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5350775718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.578045129776</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49211025238037</t>
+    <t xml:space="preserve">2.49211049079895</t>
   </si>
   <si>
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">2.34602093696594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26867985725403</t>
+    <t xml:space="preserve">2.26867961883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36320805549622</t>
+    <t xml:space="preserve">2.36320781707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.3975818157196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35031771659851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38469195365906</t>
+    <t xml:space="preserve">2.35031795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38469171524048</t>
   </si>
   <si>
     <t xml:space="preserve">2.43625283241272</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118410110474</t>
+    <t xml:space="preserve">2.13118386268616</t>
   </si>
   <si>
     <t xml:space="preserve">2.06243634223938</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985487937927</t>
+    <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.14407420158386</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83041203022003</t>
+    <t xml:space="preserve">1.83041214942932</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744447231293</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">1.6774480342865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307403564453</t>
+    <t xml:space="preserve">1.64307391643524</t>
   </si>
   <si>
     <t xml:space="preserve">1.62416839599609</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
+    <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">1.93353366851807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97650110721588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">1.97650134563446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524946212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17844820022583</t>
+    <t xml:space="preserve">2.04524922370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102942466736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17844843864441</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">2.13548064231873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18704175949097</t>
+    <t xml:space="preserve">2.18704152107239</t>
   </si>
   <si>
     <t xml:space="preserve">2.2128221988678</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">2.1956353187561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07532620429993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06673288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681034088135</t>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07532644271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06673264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">2.40617537498474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37609815597534</t>
+    <t xml:space="preserve">2.37609839439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313083648682</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.427659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149250030518</t>
+    <t xml:space="preserve">2.36750483512878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42765927314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">2.27297639846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24289917945862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39328503608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41047215461731</t>
+    <t xml:space="preserve">2.24289894104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39328527450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41047239303589</t>
   </si>
   <si>
     <t xml:space="preserve">2.47062659263611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50070381164551</t>
+    <t xml:space="preserve">2.50070357322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -69410,7 +69410,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6911805556</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>179685</v>
@@ -69431,6 +69431,32 @@
         <v>1283</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911805556</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>173996</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>3.29500007629395</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>3.34500002861023</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>3.32500004768372</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27862012386322</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
@@ -47,70 +47,70 @@
     <t xml:space="preserve">1.27977383136749</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2682341337204</t>
+    <t xml:space="preserve">1.26823425292969</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554037094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861621856689</t>
+    <t xml:space="preserve">1.25554049015045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246049880981</t>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246026039124</t>
   </si>
   <si>
     <t xml:space="preserve">1.19437885284424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19784092903137</t>
+    <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975916385651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283879756927</t>
+    <t xml:space="preserve">1.18283867835999</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438606739044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746215343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285015583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
+    <t xml:space="preserve">1.25438642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746239185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746593952179</t>
   </si>
   <si>
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591855049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168863773346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053469181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822668075562</t>
+    <t xml:space="preserve">1.20591843128204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822656154633</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130643367767</t>
@@ -119,34 +119,34 @@
     <t xml:space="preserve">1.22899842262268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23476839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707640171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29016005992889</t>
+    <t xml:space="preserve">1.23476827144623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707628250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29016017913818</t>
   </si>
   <si>
     <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28900599479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2820817232132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439021110535</t>
+    <t xml:space="preserve">1.28900611400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208196163177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438997268677</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323602676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054569244385</t>
+    <t xml:space="preserve">1.28323590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054557323456</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862367153168</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247161865234</t>
+    <t xml:space="preserve">1.32247173786163</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208562850952</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.30746984481812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593357563019</t>
+    <t xml:space="preserve">1.32593369483948</t>
   </si>
   <si>
     <t xml:space="preserve">1.30516171455383</t>
@@ -176,40 +176,40 @@
     <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362544536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708740234375</t>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708764076233</t>
   </si>
   <si>
     <t xml:space="preserve">1.31323981285095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439754486084</t>
+    <t xml:space="preserve">1.3282413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439730644226</t>
   </si>
   <si>
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016715526581</t>
+    <t xml:space="preserve">1.35016739368439</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478329658508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36170732975006</t>
+    <t xml:space="preserve">1.36170721054077</t>
   </si>
   <si>
     <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3432434797287</t>
+    <t xml:space="preserve">1.34324336051941</t>
   </si>
   <si>
     <t xml:space="preserve">1.34555149078369</t>
@@ -218,106 +218,106 @@
     <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37324726581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017094135284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786316871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747694015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286127567291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497983455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251506328583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621198177338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701971530914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332279682159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427239894867</t>
+    <t xml:space="preserve">1.37324702739716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017106056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786304950714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747705936432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497971534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099965572357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427227973938</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550466537476</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043396949768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536327362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49110054969788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863565921783</t>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536315441132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275722980499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110019207001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863530158997</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51821100711823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162538051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574671268463</t>
+    <t xml:space="preserve">1.51821136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162526130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5046558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574659347534</t>
   </si>
   <si>
     <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5403927564621</t>
+    <t xml:space="preserve">1.54039263725281</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61433172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707927703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52437269687653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50958478450775</t>
+    <t xml:space="preserve">1.61433160305023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707951545715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52437281608582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
     <t xml:space="preserve">1.55641305446625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60077655315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655456542969</t>
+    <t xml:space="preserve">1.60077619552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5465544462204</t>
   </si>
   <si>
     <t xml:space="preserve">1.52190816402435</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">1.56257450580597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500688791275</t>
+    <t xml:space="preserve">1.59584677219391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362392902374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006864070892</t>
   </si>
   <si>
     <t xml:space="preserve">1.59461462497711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64883649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992748737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115963459015</t>
+    <t xml:space="preserve">1.64883661270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992724895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115975379944</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
@@ -356,67 +356,67 @@
     <t xml:space="preserve">1.72400760650635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68950295448303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523999214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059359073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675539970398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
+    <t xml:space="preserve">1.68950307369232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756289482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7042909860611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059382915497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7067551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784627437592</t>
   </si>
   <si>
     <t xml:space="preserve">1.75851249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79301726818085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206790447235</t>
+    <t xml:space="preserve">1.79301738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604808330536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439104557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206814289093</t>
   </si>
   <si>
     <t xml:space="preserve">1.74988627433777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7486537694931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7461895942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837086677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453255653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76220941543579</t>
+    <t xml:space="preserve">1.74865412712097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7683709859848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7745326757431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7622092962265</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699720859528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76344168186188</t>
+    <t xml:space="preserve">1.7634414434433</t>
   </si>
   <si>
     <t xml:space="preserve">1.6574627161026</t>
@@ -425,25 +425,25 @@
     <t xml:space="preserve">1.66855347156525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74249231815338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
+    <t xml:space="preserve">1.74249243736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443237781525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186718940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158392906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447323322296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035190105438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679637432098</t>
   </si>
   <si>
     <t xml:space="preserve">1.64267492294312</t>
@@ -458,49 +458,49 @@
     <t xml:space="preserve">1.63281631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61309933662415</t>
+    <t xml:space="preserve">1.61309921741486</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556398868561</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61802864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021027088165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760410785675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65130126476288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65623033046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513957500458</t>
+    <t xml:space="preserve">1.61802840232849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760434627533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6513010263443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623044967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513969421387</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144241809845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63404881954193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091794490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546369075775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479722976685</t>
+    <t xml:space="preserve">1.63404870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091782569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972653388977</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55887758731842</t>
+    <t xml:space="preserve">1.55887746810913</t>
   </si>
   <si>
     <t xml:space="preserve">1.5884530544281</t>
@@ -518,52 +518,52 @@
     <t xml:space="preserve">1.56503927707672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53423118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49726176261902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51451444625854</t>
+    <t xml:space="preserve">1.53423154354095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726188182831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
     <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120072841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598864078522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105909824371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200870037079</t>
+    <t xml:space="preserve">1.57120048999786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598828315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105933666229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
   </si>
   <si>
     <t xml:space="preserve">1.59338223934174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58722078800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6365133523941</t>
+    <t xml:space="preserve">1.58722066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651323318481</t>
   </si>
   <si>
     <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
+    <t xml:space="preserve">1.65499794483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594730854034</t>
   </si>
   <si>
     <t xml:space="preserve">1.67225050926208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6784120798111</t>
+    <t xml:space="preserve">1.67841219902039</t>
   </si>
   <si>
     <t xml:space="preserve">1.69073522090912</t>
@@ -572,79 +572,79 @@
     <t xml:space="preserve">1.66978597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717957496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703818321228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291661262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457341194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467430591583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126017093658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016953468323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330040931702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946197986603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742162227631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178488254547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766355037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614838123322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695611476898</t>
+    <t xml:space="preserve">1.67717969417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703830242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552277565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291673183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6845737695694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016905784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330029010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946162223816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74742150306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069412708282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590621471405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766331195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695635318756</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297605514526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89899611473083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762221813202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392553806305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459199905396</t>
+    <t xml:space="preserve">1.89899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459176063538</t>
   </si>
   <si>
     <t xml:space="preserve">1.92980420589447</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">1.98279356956482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00867199897766</t>
+    <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
     <t xml:space="preserve">2.02838921546936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04687404632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01483392715454</t>
+    <t xml:space="preserve">2.04687428474426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01483368873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.01729822158813</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303573608398</t>
+    <t xml:space="preserve">2.05303549766541</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10725736618042</t>
+    <t xml:space="preserve">2.107257604599</t>
   </si>
   <si>
     <t xml:space="preserve">2.0949342250824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0998637676239</t>
+    <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.13806533813477</t>
@@ -692,13 +692,13 @@
     <t xml:space="preserve">2.14669132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17256999015808</t>
+    <t xml:space="preserve">2.16024661064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1725697517395</t>
   </si>
   <si>
     <t xml:space="preserve">2.15654993057251</t>
@@ -707,34 +707,34 @@
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380261421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010569572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531754493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640877723694</t>
+    <t xml:space="preserve">2.17380237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366098403931</t>
+    <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
     <t xml:space="preserve">2.17996382713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21816539764404</t>
+    <t xml:space="preserve">2.2181658744812</t>
   </si>
   <si>
     <t xml:space="preserve">2.20953965187073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21323680877686</t>
+    <t xml:space="preserve">2.21323657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">2.28717517852783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3303062915802</t>
+    <t xml:space="preserve">2.33030652999878</t>
   </si>
   <si>
     <t xml:space="preserve">2.35877203941345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34583306312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289384841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477975845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019522666931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23973369598389</t>
+    <t xml:space="preserve">2.34583330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289408683777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526022911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137877464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23973345756531</t>
   </si>
   <si>
     <t xml:space="preserve">2.30313444137573</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">2.33677577972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35100865364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35489082336426</t>
+    <t xml:space="preserve">2.35100889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3548903465271</t>
   </si>
   <si>
     <t xml:space="preserve">2.30054664611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33806991577148</t>
+    <t xml:space="preserve">2.33807015419006</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453916549683</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.3613600730896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653566360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34065723419189</t>
+    <t xml:space="preserve">2.36653542518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065747261047</t>
   </si>
   <si>
     <t xml:space="preserve">2.32901263237</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">2.34324550628662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
+    <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31219172477722</t>
+    <t xml:space="preserve">2.3121919631958</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537105560303</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">2.29666495323181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25396633148193</t>
+    <t xml:space="preserve">2.25396656990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.24490904808044</t>
@@ -851,52 +851,52 @@
     <t xml:space="preserve">2.26043605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25784802436829</t>
+    <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2060923576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703507423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903133392334</t>
+    <t xml:space="preserve">2.26690554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361562728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20609259605408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903109550476</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197031021118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24102759361267</t>
+    <t xml:space="preserve">2.24102735519409</t>
   </si>
   <si>
     <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31736779212952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771849632263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348586082458</t>
+    <t xml:space="preserve">2.31736731529236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
     <t xml:space="preserve">2.29407715797424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27725672721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855062484741</t>
+    <t xml:space="preserve">2.27725648880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855038642883</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431751251221</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24879097938538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.2487907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">2.33548212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747790336609</t>
+    <t xml:space="preserve">2.35747838020325</t>
   </si>
   <si>
     <t xml:space="preserve">2.28501987457275</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">2.28631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27337503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819968223572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160018920898</t>
+    <t xml:space="preserve">2.27337527275085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160042762756</t>
   </si>
   <si>
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418798446655</t>
+    <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
     <t xml:space="preserve">2.3057222366333</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">2.40664601325989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699743270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745920181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651648521423</t>
+    <t xml:space="preserve">2.41699767112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4674596786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">2.38723802566528</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">2.34195160865784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524128913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40793991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39370727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37688660621643</t>
+    <t xml:space="preserve">2.36524176597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40794014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3937075138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37688636779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.3626537322998</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31607341766357</t>
+    <t xml:space="preserve">2.31607365608215</t>
   </si>
   <si>
     <t xml:space="preserve">2.36459445953369</t>
@@ -1010,22 +1010,22 @@
     <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31930804252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13492774963379</t>
+    <t xml:space="preserve">2.31930828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435563087463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346796989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788614273071</t>
+    <t xml:space="preserve">2.10258078575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346820831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
     <t xml:space="preserve">2.08964157104492</t>
@@ -1037,31 +1037,31 @@
     <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12198925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06699824333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05082488059998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818179130554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966015338898</t>
+    <t xml:space="preserve">2.12198901176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06699848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818155288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966063022614</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494716644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04759001731873</t>
+    <t xml:space="preserve">2.02494692802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640694618225</t>
@@ -1070,28 +1070,28 @@
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023358345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522387504578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10581588745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06052875518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522411346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10581564903259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06052899360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0637640953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934592247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905003547668</t>
+    <t xml:space="preserve">2.10905027389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139723777771</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">2.11875462532043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12845826148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110230445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433621406555</t>
+    <t xml:space="preserve">2.12845873832703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
     <t xml:space="preserve">2.19962310791016</t>
@@ -1115,73 +1115,73 @@
     <t xml:space="preserve">2.28372597694397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755285263062</t>
+    <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
     <t xml:space="preserve">2.28460144996643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25050282478333</t>
+    <t xml:space="preserve">2.25050330162048</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
+    <t xml:space="preserve">2.18230605125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.223224401474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456797599792</t>
   </si>
   <si>
     <t xml:space="preserve">2.12433838844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11751866340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1004695892334</t>
+    <t xml:space="preserve">2.11751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04932188987732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066546440125</t>
+    <t xml:space="preserve">2.0493221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96066558361053</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614161491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591155052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227257728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00840330123901</t>
+    <t xml:space="preserve">2.05614137649536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
     <t xml:space="preserve">2.08001041412354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.086829662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886247634888</t>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
   </si>
   <si>
     <t xml:space="preserve">2.03909206390381</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99135410785675</t>
+    <t xml:space="preserve">1.99135422706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
@@ -1202,16 +1202,16 @@
     <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817407131195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794436454773</t>
+    <t xml:space="preserve">1.99817383289337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794424533844</t>
   </si>
   <si>
     <t xml:space="preserve">1.97089540958405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96748542785645</t>
+    <t xml:space="preserve">1.96748554706573</t>
   </si>
   <si>
     <t xml:space="preserve">1.95384573936462</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">1.95725572109222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97771489620209</t>
+    <t xml:space="preserve">1.97771513462067</t>
   </si>
   <si>
     <t xml:space="preserve">1.9504359960556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94361627101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1413881778717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18571591377258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417574882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801155090332</t>
+    <t xml:space="preserve">1.94361615180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820742607117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18571615219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801131248474</t>
   </si>
   <si>
     <t xml:space="preserve">2.22663426399231</t>
@@ -1250,37 +1250,37 @@
     <t xml:space="preserve">2.23004388809204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2164044380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13797807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410880088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296157836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12774848937988</t>
+    <t xml:space="preserve">2.21640467643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889618873596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13797783851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410903930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296110153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1277482509613</t>
   </si>
   <si>
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387969017029</t>
+    <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115811347961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584370136261</t>
+    <t xml:space="preserve">2.13115787506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15843725204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.15502738952637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184687614441</t>
+    <t xml:space="preserve">2.16184711456299</t>
   </si>
   <si>
     <t xml:space="preserve">2.06637096405029</t>
@@ -1298,19 +1298,19 @@
     <t xml:space="preserve">2.00499367713928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0186333656311</t>
+    <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453438282013</t>
+    <t xml:space="preserve">1.9231573343277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9811247587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453450202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
@@ -1322,31 +1322,31 @@
     <t xml:space="preserve">2.07319068908691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05273151397705</t>
+    <t xml:space="preserve">2.05273175239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253540039062</t>
+    <t xml:space="preserve">2.24027371406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345398902893</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686385154724</t>
+    <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25391292572021</t>
@@ -1355,43 +1355,43 @@
     <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29824113845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29483103752136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30847072601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961866378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3323392868042</t>
+    <t xml:space="preserve">2.30506110191345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29824090003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29483127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31529021263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3084704875946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961842536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33233952522278</t>
   </si>
   <si>
     <t xml:space="preserve">2.3664379119873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32892966270447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3391592502594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32210969924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551980018616</t>
+    <t xml:space="preserve">2.32892942428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33915901184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32210993766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32552003860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37325763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39712691307068</t>
+    <t xml:space="preserve">2.3732578754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3971266746521</t>
   </si>
   <si>
     <t xml:space="preserve">2.38689708709717</t>
@@ -1430,37 +1430,37 @@
     <t xml:space="preserve">2.4619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51306176185608</t>
+    <t xml:space="preserve">2.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5130615234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.48919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47896337509155</t>
+    <t xml:space="preserve">2.47896313667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52670121192932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54034042358398</t>
+    <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830832481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558698654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61535739898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88855242729187</t>
+    <t xml:space="preserve">2.59830784797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558674812317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61535716056824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88855266571045</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541247367859</t>
@@ -1472,28 +1472,28 @@
     <t xml:space="preserve">2.56677079200745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58547902107239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928778648376</t>
+    <t xml:space="preserve">2.58547925949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928754806519</t>
   </si>
   <si>
     <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269512176514</t>
+    <t xml:space="preserve">2.71269536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6939868927002</t>
+    <t xml:space="preserve">2.69398713111877</t>
   </si>
   <si>
     <t xml:space="preserve">2.65657043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64908742904663</t>
+    <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
     <t xml:space="preserve">2.64160394668579</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">2.66405391693115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031241416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766160964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772863388062</t>
+    <t xml:space="preserve">2.66031217575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643710136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766184806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772839546204</t>
   </si>
   <si>
     <t xml:space="preserve">2.70521187782288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72017860412598</t>
+    <t xml:space="preserve">2.7201783657074</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">2.79126977920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616971969604</t>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82494473457336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86984467506409</t>
+    <t xml:space="preserve">2.82494497299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86984419822693</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92971086502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89977741241455</t>
+    <t xml:space="preserve">2.92971062660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03821897506714</t>
+    <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.09060168266296</t>
@@ -1583,37 +1583,37 @@
     <t xml:space="preserve">3.10556840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12053489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18040156364441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16169285774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801814079285</t>
+    <t xml:space="preserve">3.12053513526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046811103821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18040132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801790237427</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07937669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10930991172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09434342384338</t>
+    <t xml:space="preserve">3.0793764591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10931015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09434366226196</t>
   </si>
   <si>
     <t xml:space="preserve">3.0457022190094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706077575684</t>
+    <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583579063416</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474413871765</t>
+    <t xml:space="preserve">2.91100287437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.0718936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06815195083618</t>
+    <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951050758362</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835230827332</t>
+    <t xml:space="preserve">2.97835254669189</t>
   </si>
   <si>
     <t xml:space="preserve">2.98209404945374</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086906433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964384078979</t>
+    <t xml:space="preserve">2.94841933250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086930274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
     <t xml:space="preserve">2.84739470481873</t>
@@ -1673,25 +1673,25 @@
     <t xml:space="preserve">2.83991146087646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85113644599915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84365296363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86236143112183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86610269546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848611831665</t>
+    <t xml:space="preserve">2.85113596916199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84365272521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86236119270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86610245704651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596912384033</t>
+    <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
     <t xml:space="preserve">2.90726089477539</t>
@@ -1706,28 +1706,28 @@
     <t xml:space="preserve">2.78004479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76882004737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7613365650177</t>
+    <t xml:space="preserve">2.76882028579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997800827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76133704185486</t>
   </si>
   <si>
     <t xml:space="preserve">2.88106918334961</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00828576087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03073573112488</t>
+    <t xml:space="preserve">3.00828552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
     <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96712708473206</t>
+    <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.88481116294861</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">2.87358593940735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78378653526306</t>
+    <t xml:space="preserve">2.78378629684448</t>
   </si>
   <si>
     <t xml:space="preserve">2.8174614906311</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98957705497742</t>
+    <t xml:space="preserve">2.989577293396</t>
   </si>
   <si>
     <t xml:space="preserve">3.30761766433716</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632541656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986703872681</t>
+    <t xml:space="preserve">3.32632565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986680030823</t>
   </si>
   <si>
     <t xml:space="preserve">3.3637421131134</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2664589881897</t>
+    <t xml:space="preserve">3.26645922660828</t>
   </si>
   <si>
     <t xml:space="preserve">3.24026775360107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22530126571655</t>
+    <t xml:space="preserve">3.22530078887939</t>
   </si>
   <si>
     <t xml:space="preserve">3.28142595291138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3225839138031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29639267921448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924336433411</t>
+    <t xml:space="preserve">3.32258415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924312591553</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305141448975</t>
@@ -1802,31 +1802,31 @@
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679315567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
+    <t xml:space="preserve">3.11679339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08685994148254</t>
   </si>
   <si>
     <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57425427436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03545665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621438026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853054046631</t>
+    <t xml:space="preserve">2.57425403594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03545689582825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2562141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853006362915</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39091324806213</t>
+    <t xml:space="preserve">2.39091348648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581342697144</t>
@@ -1835,22 +1835,22 @@
     <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445439338684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51438784599304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46574664115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4283299446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213847160339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812934875488</t>
+    <t xml:space="preserve">2.48445463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51438760757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46574687957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42832970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213823318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343024253845</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839673042297</t>
+    <t xml:space="preserve">2.39839696884155</t>
   </si>
   <si>
     <t xml:space="preserve">2.41710495948792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42458844184875</t>
+    <t xml:space="preserve">2.42458820343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.4133632183075</t>
@@ -1880,40 +1880,40 @@
     <t xml:space="preserve">2.40962171554565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45452165603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4694881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52187132835388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935433387756</t>
+    <t xml:space="preserve">2.4545214176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46948838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5218710899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690412521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670376777649</t>
+    <t xml:space="preserve">2.5069043636322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670400619507</t>
   </si>
   <si>
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795159339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
+    <t xml:space="preserve">3.15795111656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265093803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.34714436531067</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">3.06788778305054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09935307502747</t>
+    <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
     <t xml:space="preserve">3.04822182655334</t>
@@ -1943,37 +1943,37 @@
     <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1229522228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182121276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96955800056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92235970497131</t>
+    <t xml:space="preserve">3.12295246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182097434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96955823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92235994338989</t>
   </si>
   <si>
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989228248596</t>
+    <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94595909118652</t>
+    <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90269374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
+    <t xml:space="preserve">2.9026939868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
     <t xml:space="preserve">2.80829739570618</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">2.76896548271179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77289843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73749995231628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276931762695</t>
+    <t xml:space="preserve">2.77289891242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73750019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
     <t xml:space="preserve">2.78863143920898</t>
@@ -2012,58 +2012,58 @@
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6352367401123</t>
+    <t xml:space="preserve">2.63523697853088</t>
   </si>
   <si>
     <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62737059593201</t>
+    <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69816780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74143290519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72963333129883</t>
+    <t xml:space="preserve">2.60770440101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6981680393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74143314361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63917016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65490293502808</t>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63916993141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670250892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65490245819092</t>
   </si>
   <si>
     <t xml:space="preserve">2.65883612632751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58017253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58410573005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63130378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64703679084778</t>
+    <t xml:space="preserve">2.58017206192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58410549163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63130354881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64703631401062</t>
   </si>
   <si>
     <t xml:space="preserve">2.62343716621399</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983825683594</t>
+    <t xml:space="preserve">2.59983801841736</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096950531006</t>
@@ -2081,28 +2081,28 @@
     <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510762214661</t>
+    <t xml:space="preserve">2.52510738372803</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084014892578</t>
+    <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
     <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51330804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544142723083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397613525391</t>
+    <t xml:space="preserve">2.51330828666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150847434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397637367249</t>
   </si>
   <si>
     <t xml:space="preserve">2.4857759475708</t>
@@ -2114,67 +2114,67 @@
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610999107361</t>
+    <t xml:space="preserve">2.4936420917511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610975265503</t>
   </si>
   <si>
     <t xml:space="preserve">2.47790932655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40317893028259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38351249694824</t>
+    <t xml:space="preserve">2.40317869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3835129737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
+    <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564635276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3913791179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.39137935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598063468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271553039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
+    <t xml:space="preserve">2.31271529197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340247631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230591773987</t>
+    <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
     <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73356652259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7571656703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503205299377</t>
+    <t xml:space="preserve">2.73356676101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503252983093</t>
   </si>
   <si>
     <t xml:space="preserve">2.71783399581909</t>
@@ -2186,13 +2186,13 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70603466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210123062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482736587524</t>
+    <t xml:space="preserve">2.70603442192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482760429382</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02068948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96169185638428</t>
+    <t xml:space="preserve">3.0206892490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96169209480286</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976268768311</t>
+    <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009673118591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8515625</t>
+    <t xml:space="preserve">2.82009696960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88302779197693</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">2.93809247016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90662693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055989265442</t>
+    <t xml:space="preserve">2.90662670135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876055717468</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">2.87516140937805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82796311378479</t>
+    <t xml:space="preserve">2.82796335220337</t>
   </si>
   <si>
     <t xml:space="preserve">2.86729526519775</t>
@@ -2270,64 +2270,64 @@
     <t xml:space="preserve">2.93022632598877</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00495672225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01675629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462267875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00889015197754</t>
+    <t xml:space="preserve">3.00495648384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01675653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035544395447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349095344543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922371864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98529076576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575464248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">2.98922395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98529100418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855563163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002163887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148693084717</t>
+    <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10328650474548</t>
+    <t xml:space="preserve">3.1032862663269</t>
   </si>
   <si>
     <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2055492401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19374990463257</t>
+    <t xml:space="preserve">3.20554900169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19374966621399</t>
   </si>
   <si>
     <t xml:space="preserve">3.15441823005676</t>
@@ -2336,31 +2336,31 @@
     <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2102906703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10382676124573</t>
+    <t xml:space="preserve">3.21029019355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10382652282715</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287932395935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925820350647</t>
+    <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08744740486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06697392463684</t>
+    <t xml:space="preserve">3.08744764328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06697368621826</t>
   </si>
   <si>
     <t xml:space="preserve">3.05059456825256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
+    <t xml:space="preserve">3.07106852531433</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374220848083</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">3.03831076622009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02602624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468940734863</t>
+    <t xml:space="preserve">3.02602601051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.04649996757507</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07516360282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507857322693</t>
+    <t xml:space="preserve">3.0751633644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
@@ -2411,13 +2411,13 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9031834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908862113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137290000916</t>
+    <t xml:space="preserve">2.90318369865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.90727806091309</t>
@@ -2432,13 +2432,13 @@
     <t xml:space="preserve">2.87042546272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91956281661987</t>
+    <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223554611206</t>
+    <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8786153793335</t>
+    <t xml:space="preserve">2.87861514091492</t>
   </si>
   <si>
     <t xml:space="preserve">2.87452030181885</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
+    <t xml:space="preserve">2.93184685707092</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8130989074707</t>
+    <t xml:space="preserve">2.81309914588928</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
@@ -2516,16 +2516,16 @@
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
+    <t xml:space="preserve">2.84995150566101</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9154679775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357262611389</t>
+    <t xml:space="preserve">2.91546773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215123176575</t>
+    <t xml:space="preserve">2.77215099334717</t>
   </si>
   <si>
     <t xml:space="preserve">2.84176206588745</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">2.79262518882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80900406837463</t>
+    <t xml:space="preserve">2.80900430679321</t>
   </si>
   <si>
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8008143901825</t>
+    <t xml:space="preserve">2.80081462860107</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">2.78034090995789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69435095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521360397339</t>
+    <t xml:space="preserve">2.75986695289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6943507194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521384239197</t>
   </si>
   <si>
     <t xml:space="preserve">2.67387723922729</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7271089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939323425293</t>
+    <t xml:space="preserve">2.72710871696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939299583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.95615839958191</t>
@@ -2597,25 +2597,25 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897128105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303664207458</t>
+    <t xml:space="preserve">2.93897151947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84873986244202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725620269775</t>
+    <t xml:space="preserve">2.89600396156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84873962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725596427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">2.87881684303284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86163020133972</t>
+    <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
     <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
@@ -2657,46 +2657,46 @@
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405698776245</t>
+    <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
+    <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
     <t xml:space="preserve">2.5479679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5350775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57804489135742</t>
+    <t xml:space="preserve">2.53507781028748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.578045129776</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47922015190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929713249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359415054321</t>
+    <t xml:space="preserve">2.47921991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929737091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359391212463</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195557594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4878134727478</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195605278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35031771659851</t>
+    <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469171524048</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883405685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33742737770081</t>
+    <t xml:space="preserve">2.3546142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898825645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883381843567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33742761611938</t>
   </si>
   <si>
     <t xml:space="preserve">2.28156995773315</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10540342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13118386268616</t>
+    <t xml:space="preserve">2.10540366172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
     <t xml:space="preserve">2.0624361038208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11829352378845</t>
+    <t xml:space="preserve">2.11829376220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10110664367676</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14407420158386</t>
+    <t xml:space="preserve">2.14407396316528</t>
   </si>
   <si>
     <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08392000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02376532554626</t>
+    <t xml:space="preserve">2.08391976356506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02376556396484</t>
   </si>
   <si>
     <t xml:space="preserve">1.88197302818298</t>
@@ -2816,37 +2816,37 @@
     <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85619246959686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81322503089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041203022003</t>
+    <t xml:space="preserve">1.85619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81322491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041214942932</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6774480342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6241682767868</t>
+    <t xml:space="preserve">1.67744791507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416851520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84330236911774</t>
+    <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
     <t xml:space="preserve">1.96790778636932</t>
@@ -2864,10 +2864,10 @@
     <t xml:space="preserve">1.93353378772736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97650134563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2876,19 +2876,19 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9593141078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0796229839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08821678161621</t>
+    <t xml:space="preserve">1.95931422710419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07962322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07102942466736</t>
+    <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
     <t xml:space="preserve">2.17844820022583</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2128221988678</t>
+    <t xml:space="preserve">2.21282196044922</t>
   </si>
   <si>
     <t xml:space="preserve">2.19563508033752</t>
@@ -2933,16 +2933,16 @@
     <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133830070496</t>
+    <t xml:space="preserve">2.10969996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
+    <t xml:space="preserve">2.23000907897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.28586673736572</t>
@@ -2954,28 +2954,28 @@
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26438283920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40617537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609815597534</t>
+    <t xml:space="preserve">2.32453751564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40617561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609839439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313059806824</t>
@@ -2990,10 +2990,10 @@
     <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.427659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25149273872375</t>
+    <t xml:space="preserve">2.42765927314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25149250030518</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
@@ -3002,13 +3002,13 @@
     <t xml:space="preserve">2.27297616004944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2428994178772</t>
+    <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
     <t xml:space="preserve">2.39328527450562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41047239303589</t>
+    <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
     <t xml:space="preserve">2.47062635421753</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -69546,7 +69546,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6923842593</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>58088</v>
@@ -69567,6 +69567,32 @@
         <v>1283</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6922106482</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>65292</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>3.25500011444092</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27861988544464</t>
+    <t xml:space="preserve">1.27862000465393</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977395057678</t>
+    <t xml:space="preserve">1.27977406978607</t>
   </si>
   <si>
     <t xml:space="preserve">1.2682341337204</t>
@@ -53,43 +53,43 @@
     <t xml:space="preserve">1.26938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554013252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861633777618</t>
+    <t xml:space="preserve">1.25554025173187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861645698547</t>
   </si>
   <si>
     <t xml:space="preserve">1.27515816688538</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246026039124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437861442566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975904464722</t>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246037960052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784080982208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975916385651</t>
   </si>
   <si>
     <t xml:space="preserve">1.18283879756927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25784826278687</t>
+    <t xml:space="preserve">1.25784814357758</t>
   </si>
   <si>
     <t xml:space="preserve">1.25438618659973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285015583038</t>
+    <t xml:space="preserve">1.24746215343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285027503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746593952179</t>
@@ -98,46 +98,46 @@
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591855049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168875694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899842262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476850986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707640171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29015982151031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669810295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900599479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208208084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439009189606</t>
+    <t xml:space="preserve">1.20591878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2105348110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130643367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2370765209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900587558746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208196163177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438985347748</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169597148895</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">1.30054569244385</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862379074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093168258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32477951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247161865234</t>
+    <t xml:space="preserve">1.30862367153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093192100525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32477962970734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247138023376</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208574771881</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016372680664</t>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516159534454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.3236255645752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32708752155304</t>
+    <t xml:space="preserve">1.32708740234375</t>
   </si>
   <si>
     <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
+    <t xml:space="preserve">1.32824182510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132145881653</t>
   </si>
   <si>
     <t xml:space="preserve">1.34439730644226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34670567512512</t>
+    <t xml:space="preserve">1.34670519828796</t>
   </si>
   <si>
     <t xml:space="preserve">1.35016739368439</t>
@@ -203,199 +203,199 @@
     <t xml:space="preserve">1.35478329658508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208929538727</t>
+    <t xml:space="preserve">1.36170709133148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
     <t xml:space="preserve">1.3432434797287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3455513715744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516916751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324726581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017129898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786304950714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747694015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286103725433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497971534729</t>
+    <t xml:space="preserve">1.34555149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786293029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747705936432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.394979596138</t>
   </si>
   <si>
     <t xml:space="preserve">1.39251518249512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39621198177338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099977493286</t>
+    <t xml:space="preserve">1.39621210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099989414215</t>
   </si>
   <si>
     <t xml:space="preserve">1.42701983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42332291603088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687844276428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427239894867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550478458405</t>
+    <t xml:space="preserve">1.42332279682159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427263736725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550442695618</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043408870697</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536303520203</t>
+    <t xml:space="preserve">1.45536315441132</t>
   </si>
   <si>
     <t xml:space="preserve">1.4627571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49110043048859</t>
+    <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
     <t xml:space="preserve">1.48863554000854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50342357158661</t>
+    <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
     <t xml:space="preserve">1.51821112632751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54162526130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849390983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5403927564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433160305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707939624786</t>
+    <t xml:space="preserve">1.54162538051605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465548038483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849414825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6081702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707915782928</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437281608582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958514213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641305446625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077655315399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655432701111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190828323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5625741481781</t>
+    <t xml:space="preserve">1.50958502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6007764339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190792560577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257438659668</t>
   </si>
   <si>
     <t xml:space="preserve">1.5958468914032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66362428665161</t>
+    <t xml:space="preserve">1.66362452507019</t>
   </si>
   <si>
     <t xml:space="preserve">1.65006875991821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59461462497711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883661270142</t>
+    <t xml:space="preserve">1.5946147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883685112</t>
   </si>
   <si>
     <t xml:space="preserve">1.65992736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66115951538086</t>
+    <t xml:space="preserve">1.66115975379944</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400736808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950283527374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523963451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756313323975</t>
+    <t xml:space="preserve">1.72154319286346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827092647552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523987293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
     <t xml:space="preserve">1.70429074764252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059359073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675551891327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784627437592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604748725891</t>
+    <t xml:space="preserve">1.70059394836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7067551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784615516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851261615753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301714897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604808330536</t>
   </si>
   <si>
     <t xml:space="preserve">1.78439080715179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77206778526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988615512848</t>
+    <t xml:space="preserve">1.77206790447235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.74865388870239</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">1.7461895942688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76837122440338</t>
+    <t xml:space="preserve">1.76837074756622</t>
   </si>
   <si>
     <t xml:space="preserve">1.7745326757431</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">1.76220941543579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77699720859528</t>
+    <t xml:space="preserve">1.77699732780457</t>
   </si>
   <si>
     <t xml:space="preserve">1.76344168186188</t>
@@ -422,76 +422,76 @@
     <t xml:space="preserve">1.6574627161026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66855335235596</t>
+    <t xml:space="preserve">1.66855323314667</t>
   </si>
   <si>
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443202018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186730861664</t>
+    <t xml:space="preserve">1.69443190097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186683177948</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447347164154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035190105438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267492294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376579761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309933662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556398868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6180282831192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021027088165</t>
+    <t xml:space="preserve">1.60447311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6167961359024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267468452454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376543998718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049329280853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281643390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6155641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802852153778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021015167236</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65130090713501</t>
+    <t xml:space="preserve">1.6513010263443</t>
   </si>
   <si>
     <t xml:space="preserve">1.65623021125793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513957500458</t>
+    <t xml:space="preserve">1.61926102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513945579529</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144265651703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63404881954193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091758728027</t>
+    <t xml:space="preserve">1.63404893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091770648956</t>
   </si>
   <si>
     <t xml:space="preserve">1.53546369075775</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49972641468048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247420787811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887746810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503927707672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5342310667038</t>
+    <t xml:space="preserve">1.49972653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247408866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887758731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845293521881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423130512238</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451432704926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532206058502</t>
+    <t xml:space="preserve">1.51451396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532194137573</t>
   </si>
   <si>
     <t xml:space="preserve">1.57120072841644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58598816394806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105933666229</t>
+    <t xml:space="preserve">1.58598828315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
   </si>
   <si>
     <t xml:space="preserve">1.6020085811615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59338223934174</t>
+    <t xml:space="preserve">1.5933825969696</t>
   </si>
   <si>
     <t xml:space="preserve">1.58722078800201</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">1.6648565530777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499806404114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594754695892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6722503900528</t>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594730854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225050926208</t>
   </si>
   <si>
     <t xml:space="preserve">1.6784120798111</t>
@@ -569,97 +569,97 @@
     <t xml:space="preserve">1.69073534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717945575714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703830242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552277565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538150310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457341194153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467442512512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75727999210358</t>
+    <t xml:space="preserve">1.66978573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717969417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7055230140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291661262512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457329273224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728023052216</t>
   </si>
   <si>
     <t xml:space="preserve">1.74125993251801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73016929626465</t>
+    <t xml:space="preserve">1.73016977310181</t>
   </si>
   <si>
     <t xml:space="preserve">1.77330029010773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77946174144745</t>
+    <t xml:space="preserve">1.77946186065674</t>
   </si>
   <si>
     <t xml:space="preserve">1.74742162227631</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7806943655014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178488254547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590645313263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8115017414093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8361485004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8669558763504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297629356384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89899623394012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762257575989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392529964447</t>
+    <t xml:space="preserve">1.78069424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590609550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766355037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695611476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899599552155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
     <t xml:space="preserve">1.94459187984467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980408668518</t>
+    <t xml:space="preserve">1.9298038482666</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279356956482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687428474426</t>
+    <t xml:space="preserve">2.0086727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687404632568</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483392715454</t>
@@ -671,37 +671,37 @@
     <t xml:space="preserve">2.05796480178833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303525924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905579566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10725736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09493446350098</t>
+    <t xml:space="preserve">2.05303549766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.107257604599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0949342250824</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806509971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669132232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024708747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887307167053</t>
+    <t xml:space="preserve">2.13806533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669108390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024684906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887283325195</t>
   </si>
   <si>
     <t xml:space="preserve">2.17256999015808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15655016899109</t>
+    <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18119621276855</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17010521888733</t>
+    <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.15531754493713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16640853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18366074562073</t>
+    <t xml:space="preserve">2.16640830039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446847915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18366098403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.17996406555176</t>
@@ -731,79 +731,79 @@
     <t xml:space="preserve">2.21816539764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323680877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23172116279602</t>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2132363319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2317214012146</t>
   </si>
   <si>
     <t xml:space="preserve">2.27978157997131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28717541694641</t>
+    <t xml:space="preserve">2.28717517852783</t>
   </si>
   <si>
     <t xml:space="preserve">2.33030652999878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877180099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583282470703</t>
+    <t xml:space="preserve">2.35877203941345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583306312561</t>
   </si>
   <si>
     <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477975845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
+    <t xml:space="preserve">2.31477952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526022911072</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137853622437</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866145133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3367760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100865364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782908439636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
+    <t xml:space="preserve">2.30313467979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866121292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33677577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782932281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
   </si>
   <si>
     <t xml:space="preserve">2.30054664611816</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33806991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34453940391541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36135983467102</t>
+    <t xml:space="preserve">2.33806943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34453916549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3613600730896</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">2.34065747261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32901215553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842133522034</t>
+    <t xml:space="preserve">2.32901239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.34971475601196</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535259246826</t>
+    <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642483711243</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31219148635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29537081718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24490904808044</t>
+    <t xml:space="preserve">2.3121919631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666495323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396656990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949334144592</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26172971725464</t>
+    <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
     <t xml:space="preserve">2.26690554618835</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">2.24361538887024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20609259605408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703531265259</t>
+    <t xml:space="preserve">2.2060923576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23197054862976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102759361267</t>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102783203125</t>
   </si>
   <si>
     <t xml:space="preserve">2.3225429058075</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">2.31348586082458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2940776348114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725648880005</t>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855038642883</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890204429626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041735649109</t>
+    <t xml:space="preserve">2.28890180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879097938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041711807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.33548212051392</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">2.35747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28502035140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631377220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
+    <t xml:space="preserve">2.28502011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337503433228</t>
   </si>
   <si>
     <t xml:space="preserve">2.26819944381714</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">2.33160042762756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30960416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418774604797</t>
+    <t xml:space="preserve">2.30960392951965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
     <t xml:space="preserve">2.3057222366333</t>
@@ -962,31 +962,31 @@
     <t xml:space="preserve">2.46745920181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44675731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38723802566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241337776184</t>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651648521423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3872377872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241313934326</t>
   </si>
   <si>
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524128913879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40794038772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.36524152755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40794014930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3937075138092</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688660621643</t>
@@ -995,37 +995,37 @@
     <t xml:space="preserve">2.3626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38464999198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459445953369</t>
+    <t xml:space="preserve">2.38465023040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607365608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076853752136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37429881095886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37753343582153</t>
+    <t xml:space="preserve">2.37429904937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492798805237</t>
+    <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
     <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346796989441</t>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
@@ -1034,85 +1034,85 @@
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11552000045776</t>
+    <t xml:space="preserve">2.07993721961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
     <t xml:space="preserve">2.12198901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699848175049</t>
+    <t xml:space="preserve">2.06699824333191</t>
   </si>
   <si>
     <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02818179130554</t>
+    <t xml:space="preserve">2.02818202972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.01847720146179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966027259827</t>
+    <t xml:space="preserve">1.97966039180756</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494716644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0475902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640670776367</t>
+    <t xml:space="preserve">2.02494692802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04758977890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640694618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023358345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522411346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10581564903259</t>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670283317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522387504578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
     <t xml:space="preserve">2.06052899360657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06376385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934568405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905027389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14139747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875414848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845873832703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433645248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19962286949158</t>
+    <t xml:space="preserve">2.06376361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934592247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905051231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14139771461487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875462532043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845849990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15110182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433669090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19962310791016</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050282478333</t>
+    <t xml:space="preserve">2.28460144996643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2505030632019</t>
   </si>
   <si>
     <t xml:space="preserve">2.20958471298218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18230628967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.223224401474</t>
+    <t xml:space="preserve">2.18230581283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22322463989258</t>
   </si>
   <si>
     <t xml:space="preserve">2.16866660118103</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">2.11069917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1004695892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08342051506042</t>
+    <t xml:space="preserve">2.10046935081482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066570281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0118134021759</t>
+    <t xml:space="preserve">1.96066558361053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01181364059448</t>
   </si>
   <si>
     <t xml:space="preserve">2.05614161491394</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">2.00840330123901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001017570496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.086829662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02886247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909230232239</t>
+    <t xml:space="preserve">2.08001041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02886271476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
     <t xml:space="preserve">2.04250192642212</t>
@@ -1196,109 +1196,109 @@
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09023976325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522302627563</t>
+    <t xml:space="preserve">2.09024000167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522326469421</t>
   </si>
   <si>
     <t xml:space="preserve">1.99817407131195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98794460296631</t>
+    <t xml:space="preserve">1.98794436454773</t>
   </si>
   <si>
     <t xml:space="preserve">1.97089517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96748495101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384573936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771489620209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9504359960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361627101898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1413881778717</t>
+    <t xml:space="preserve">1.96748554706573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384585857391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771513462067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043611526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361639022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820742607117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.185715675354</t>
+    <t xml:space="preserve">2.18571591377258</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417598724365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663450241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2164044380188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17889618873596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13797807693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410880088806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06296133995056</t>
+    <t xml:space="preserve">2.28801131248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004388809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21640467643738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17889595031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13797783851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410856246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06296110153198</t>
   </si>
   <si>
     <t xml:space="preserve">2.1277482509613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09705996513367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387969017029</t>
+    <t xml:space="preserve">2.09705972671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
     <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115787506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1584370136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15502738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15161728858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16184687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499367713928</t>
+    <t xml:space="preserve">2.13115811347961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15843677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15502715110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1516170501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16184711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637120246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499391555786</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863312721252</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315709590912</t>
+    <t xml:space="preserve">1.9231573343277</t>
   </si>
   <si>
     <t xml:space="preserve">1.98112463951111</t>
@@ -1316,16 +1316,16 @@
     <t xml:space="preserve">1.98453462123871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07660055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09364938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273127555847</t>
+    <t xml:space="preserve">2.07660031318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09364986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319092750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273175239563</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
@@ -1334,19 +1334,19 @@
     <t xml:space="preserve">2.24027371406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19594526290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912553787231</t>
+    <t xml:space="preserve">2.19594550132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912577629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23345375061035</t>
+    <t xml:space="preserve">2.23345398902893</t>
   </si>
   <si>
     <t xml:space="preserve">2.23686361312866</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483103752136</t>
+    <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
     <t xml:space="preserve">2.31529021263123</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">2.35961866378784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233952522278</t>
+    <t xml:space="preserve">2.33233976364136</t>
   </si>
   <si>
     <t xml:space="preserve">2.3664379119873</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">2.32210993766785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32552003860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256887435913</t>
+    <t xml:space="preserve">2.32551980018616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
     <t xml:space="preserve">2.35279893875122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37325763702393</t>
+    <t xml:space="preserve">2.3732578754425</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37666749954224</t>
+    <t xml:space="preserve">2.37666773796082</t>
   </si>
   <si>
     <t xml:space="preserve">2.42099571228027</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122553825378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44827461242676</t>
+    <t xml:space="preserve">2.43122529983521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44827437400818</t>
   </si>
   <si>
     <t xml:space="preserve">2.4619140625</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">2.51306176185608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48919272422791</t>
+    <t xml:space="preserve">2.48919296264648</t>
   </si>
   <si>
     <t xml:space="preserve">2.47896313667297</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">2.60171794891357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59830832481384</t>
+    <t xml:space="preserve">2.59830784797668</t>
   </si>
   <si>
     <t xml:space="preserve">2.62558698654175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61535739898682</t>
+    <t xml:space="preserve">2.61535716056824</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855266571045</t>
@@ -1469,55 +1469,55 @@
     <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61167049407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56677079200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58547902107239</t>
+    <t xml:space="preserve">2.61167073249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56677103042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58547949790955</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928778648376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63037896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71269536018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67153739929199</t>
+    <t xml:space="preserve">2.63037919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71269512176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67153716087341</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657019615173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766184806824</t>
+    <t xml:space="preserve">2.65657043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160418510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031241416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643710136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766208648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70521187782288</t>
+    <t xml:space="preserve">2.70521211624146</t>
   </si>
   <si>
     <t xml:space="preserve">2.7201783657074</t>
@@ -1526,43 +1526,43 @@
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262857437134</t>
+    <t xml:space="preserve">2.74262833595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7912700176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616971969604</t>
+    <t xml:space="preserve">2.79126977920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.8137195110321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868647575378</t>
+    <t xml:space="preserve">2.80623626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868623733521</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86984467506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96338582038879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92971086502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89977741241455</t>
+    <t xml:space="preserve">2.86984443664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96338558197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92971062660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
@@ -1571,37 +1571,37 @@
     <t xml:space="preserve">2.99331879615784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576852798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03821849822998</t>
+    <t xml:space="preserve">3.0157687664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
     <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10182690620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10556817054749</t>
+    <t xml:space="preserve">3.10182666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10556864738464</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046811103821</t>
+    <t xml:space="preserve">3.15046834945679</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169309616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12801814079285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06066846847534</t>
+    <t xml:space="preserve">3.16169333457947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12801837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
     <t xml:space="preserve">3.0793764591217</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706053733826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98583579063416</t>
+    <t xml:space="preserve">2.99706077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100287437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474461555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06815195083618</t>
+    <t xml:space="preserve">2.91100263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951026916504</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835230827332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209404945374</t>
+    <t xml:space="preserve">2.97835254669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841933250427</t>
+    <t xml:space="preserve">2.94841909408569</t>
   </si>
   <si>
     <t xml:space="preserve">2.97086906433105</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75011157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80249500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84365272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86236119270325</t>
+    <t xml:space="preserve">2.7501118183136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.802494764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113596916199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84365296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86236095428467</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610269546509</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89603590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92596936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726089477539</t>
+    <t xml:space="preserve">2.89603567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92596888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
+    <t xml:space="preserve">2.79875302314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
@@ -1727,67 +1727,67 @@
     <t xml:space="preserve">3.03073573112488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481116294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78378653526306</t>
+    <t xml:space="preserve">2.95590233802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481092453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358593940735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78378677368164</t>
   </si>
   <si>
     <t xml:space="preserve">2.81746125221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85487771034241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619208335876</t>
+    <t xml:space="preserve">2.85487794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761742591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619184494019</t>
   </si>
   <si>
     <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41986703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3637421131134</t>
+    <t xml:space="preserve">3.41986727714539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36374187469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.42360854148865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44980025291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625910758972</t>
+    <t xml:space="preserve">3.44979977607727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2814257144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258439064026</t>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28142595291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3225839138031</t>
   </si>
   <si>
     <t xml:space="preserve">3.29639267921448</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">3.13924336433411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11305165290833</t>
+    <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
     <t xml:space="preserve">3.06441020965576</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">3.08686017990112</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04944348335266</t>
+    <t xml:space="preserve">3.04944324493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425427436829</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968850135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091348648071</t>
+    <t xml:space="preserve">2.37968873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581342697144</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445463180542</t>
+    <t xml:space="preserve">2.48445439338684</t>
   </si>
   <si>
     <t xml:space="preserve">2.51438784599304</t>
@@ -1847,22 +1847,22 @@
     <t xml:space="preserve">2.46574664115906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4283299446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40213823318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51812934875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38343024253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465546607971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35723829269409</t>
+    <t xml:space="preserve">2.42832970619202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40213871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51812958717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38343000411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465498924255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
     <t xml:space="preserve">2.39839673042297</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50316286087036</t>
+    <t xml:space="preserve">2.50316262245178</t>
   </si>
   <si>
     <t xml:space="preserve">2.5069043636322</t>
@@ -1913,37 +1913,37 @@
     <t xml:space="preserve">3.15795135498047</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17801713943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1072199344635</t>
+    <t xml:space="preserve">3.29265093803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17801690101624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10721945762634</t>
   </si>
   <si>
     <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99709057807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788778305054</t>
+    <t xml:space="preserve">2.99709010124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788802146912</t>
   </si>
   <si>
     <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04822158813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968735694885</t>
+    <t xml:space="preserve">3.04822182655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968711853027</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989228248596</t>
+    <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742438316345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94595909118652</t>
+    <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842651367188</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79649758338928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469824790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896524429321</t>
+    <t xml:space="preserve">2.79649782180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896548271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
@@ -2000,43 +2000,43 @@
     <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66276931762695</t>
+    <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
     <t xml:space="preserve">2.78863143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74536609649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109910011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803868293762</t>
+    <t xml:space="preserve">2.74536633491516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6352367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770440101624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69816780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74143290519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72963356971741</t>
+    <t xml:space="preserve">2.6981680393219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74143314361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72963333129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6549026966095</t>
+    <t xml:space="preserve">2.65490293502808</t>
   </si>
   <si>
     <t xml:space="preserve">2.65883636474609</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63130402565002</t>
+    <t xml:space="preserve">2.63130354881287</t>
   </si>
   <si>
     <t xml:space="preserve">2.6470365524292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62343716621399</t>
+    <t xml:space="preserve">2.62343764305115</t>
   </si>
   <si>
     <t xml:space="preserve">2.5959050655365</t>
@@ -2084,34 +2084,34 @@
     <t xml:space="preserve">2.75323271751404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52510738372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904081344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54084014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330828666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150847434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4857759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50937485694885</t>
+    <t xml:space="preserve">2.52510786056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904057502747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330780982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150871276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544142723083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397589683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48577570915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50937461853027</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117443084717</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">2.47790932655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40317893028259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38351249694824</t>
+    <t xml:space="preserve">2.40317869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38351273536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.45430994033813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564635276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3913791179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598063468933</t>
+    <t xml:space="preserve">2.39924550056458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39137935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
     <t xml:space="preserve">2.39531230926514</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31271529197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36384677886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57230591773987</t>
+    <t xml:space="preserve">2.31271553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.340247631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36384701728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
     <t xml:space="preserve">2.61557102203369</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75716614723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503205299377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71783375740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390080451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69030165672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70603466033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210099220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482736587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87909460067749</t>
+    <t xml:space="preserve">2.75716590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503229141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71783399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6903018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7060341835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210123062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482760429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87909483909607</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449332237244</t>
+    <t xml:space="preserve">2.91449356079102</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629313468933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02068948745728</t>
+    <t xml:space="preserve">3.0206892490387</t>
   </si>
   <si>
     <t xml:space="preserve">2.9616916179657</t>
@@ -2231,28 +2231,28 @@
     <t xml:space="preserve">2.83189630508423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84762907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302803039551</t>
+    <t xml:space="preserve">2.84762930870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302779197693</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90662670135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91055989265442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
+    <t xml:space="preserve">2.90662693977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91056036949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89876055717468</t>
   </si>
   <si>
     <t xml:space="preserve">2.95775818824768</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">2.95382523536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516140937805</t>
+    <t xml:space="preserve">2.87516164779663</t>
   </si>
   <si>
     <t xml:space="preserve">2.82796311378479</t>
@@ -2270,88 +2270,88 @@
     <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93022632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01675653457642</t>
+    <t xml:space="preserve">2.93022608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495672225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01675629615784</t>
   </si>
   <si>
     <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04035544395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00889015197754</t>
+    <t xml:space="preserve">3.04035520553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888967514038</t>
   </si>
   <si>
     <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922371864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98529076576233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575440406799</t>
+    <t xml:space="preserve">2.98922395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98529052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575392723083</t>
   </si>
   <si>
     <t xml:space="preserve">3.05215501785278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02855587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002163887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04428863525391</t>
+    <t xml:space="preserve">3.02855563163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002140045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09541988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04428839683533</t>
   </si>
   <si>
     <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12688541412354</t>
+    <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
     <t xml:space="preserve">3.10328650474548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374966621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441823005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981647491455</t>
+    <t xml:space="preserve">3.19374990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382676124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06287932395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925820350647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12839531898499</t>
+    <t xml:space="preserve">3.10382652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06287908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106876373291</t>
+    <t xml:space="preserve">3.07106852531433</t>
   </si>
   <si>
     <t xml:space="preserve">3.01374220848083</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03421592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0178370475769</t>
+    <t xml:space="preserve">3.03421568870544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831076622009</t>
+    <t xml:space="preserve">3.03831052780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.02602624893188</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07516360282898</t>
+    <t xml:space="preserve">3.0751633644104</t>
   </si>
   <si>
     <t xml:space="preserve">2.98507881164551</t>
@@ -2408,22 +2408,22 @@
     <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93594169616699</t>
+    <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
+    <t xml:space="preserve">2.9031834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137290000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.91137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">2.84585666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87042570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91956281661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003629684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86223554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85404634475708</t>
+    <t xml:space="preserve">2.87042546272278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91956257820129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9400360584259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86223578453064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85404658317566</t>
   </si>
   <si>
     <t xml:space="preserve">2.77624607086182</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">2.87861514091492</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87452030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775225639343</t>
+    <t xml:space="preserve">2.87452006340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.99736285209656</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2489,40 +2489,40 @@
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365741729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96869993209839</t>
+    <t xml:space="preserve">2.92365717887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
+    <t xml:space="preserve">2.9318470954895</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82947778701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81309866905212</t>
+    <t xml:space="preserve">2.8294780254364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128834724426</t>
+    <t xml:space="preserve">2.82128810882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051001548767</t>
+    <t xml:space="preserve">2.84995150566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051025390625</t>
   </si>
   <si>
     <t xml:space="preserve">2.91546773910522</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2549,46 +2549,46 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978240013123</t>
+    <t xml:space="preserve">2.83766722679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081486701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6697826385498</t>
   </si>
   <si>
     <t xml:space="preserve">2.78034067153931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75986671447754</t>
+    <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
     <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521360397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387723922729</t>
+    <t xml:space="preserve">2.64521384239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387700080872</t>
   </si>
   <si>
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.74348759651184</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76396155357361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72710871696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939323425293</t>
+    <t xml:space="preserve">2.76396179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7271089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939299583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.95615839958191</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170718193054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303664207458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83155274391174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89600372314453</t>
+    <t xml:space="preserve">2.89170742034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303640365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83155298233032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873962402344</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79717874526978</t>
+    <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">2.90459752082825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
+    <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
     <t xml:space="preserve">2.5479679107666</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4878134727478</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195605278015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172439575195</t>
+    <t xml:space="preserve">2.35891103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172415733337</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">2.34602117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35031771659851</t>
+    <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
     <t xml:space="preserve">2.38469171524048</t>
@@ -2747,46 +2747,46 @@
     <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180137634277</t>
+    <t xml:space="preserve">2.37180161476135</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883405685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33742737770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28156971931458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21711850166321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10540342330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13118386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829352378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10110688209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.3546142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898825645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883381843567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33742761611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28156995773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21711874008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10540366172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13118410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829376220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10110664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2804,34 +2804,34 @@
     <t xml:space="preserve">2.11399698257446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08392000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02376532554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197290897369</t>
+    <t xml:space="preserve">2.08391976356506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197302818298</t>
   </si>
   <si>
     <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89056658744812</t>
+    <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322503089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041203022003</t>
+    <t xml:space="preserve">1.81322491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041214942932</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71869671344757</t>
+    <t xml:space="preserve">1.71869683265686</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">1.67744791507721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416839599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65854239463806</t>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416851520538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
     <t xml:space="preserve">1.72729015350342</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
+    <t xml:space="preserve">1.92494022846222</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">1.93353378772736</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97650134563446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">1.97650122642517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2879,28 +2879,28 @@
     <t xml:space="preserve">2.04954600334167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95931434631348</t>
+    <t xml:space="preserve">1.95931422710419</t>
   </si>
   <si>
     <t xml:space="preserve">2.07962322235107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08821678161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524946212769</t>
+    <t xml:space="preserve">2.08821654319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524922370911</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17844796180725</t>
+    <t xml:space="preserve">2.17844820022583</t>
   </si>
   <si>
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2918,67 +2918,67 @@
     <t xml:space="preserve">2.19563508033752</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
+    <t xml:space="preserve">2.06673264503479</t>
   </si>
   <si>
     <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133830070496</t>
+    <t xml:space="preserve">2.10969996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28586649894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.23000907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28586673736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860263824463</t>
+    <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26438283920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40617537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609815597534</t>
+    <t xml:space="preserve">2.32453751564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40617561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609839439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313059806824</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.427659034729</t>
+    <t xml:space="preserve">2.42765927314758</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149250030518</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
+    <t xml:space="preserve">2.27297616004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062659263611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50070405006409</t>
+    <t xml:space="preserve">2.47062635421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50070381164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.42424345016479</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874097824097</t>
+    <t xml:space="preserve">2.42874121665955</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35677814483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280613899231</t>
+    <t xml:space="preserve">2.356778383255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280637741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3062,10 +3062,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084378242493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237377166748</t>
+    <t xml:space="preserve">2.23084354400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237401008606</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3086,16 +3086,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486260414124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787648200989</t>
+    <t xml:space="preserve">2.19486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337871551514</t>
+    <t xml:space="preserve">2.16337847709656</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189482688904</t>
+    <t xml:space="preserve">2.13189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3134,7 +3134,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.068927526474</t>
+    <t xml:space="preserve">2.06892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3143,10 +3143,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591341018677</t>
+    <t xml:space="preserve">2.08691811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591364860535</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495575904846</t>
+    <t xml:space="preserve">2.01495552062988</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93399751186371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701150894165</t>
+    <t xml:space="preserve">1.933997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701138973236</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3176,28 +3176,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600692272186</t>
+    <t xml:space="preserve">1.91600704193115</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849527835846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91150915622711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500233650208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749045372009</t>
+    <t xml:space="preserve">1.93849515914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9115092754364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500221729279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749057292938</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648598670959</t>
+    <t xml:space="preserve">1.95648574829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050457000732</t>
+    <t xml:space="preserve">1.92050445079803</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88902080059052</t>
+    <t xml:space="preserve">1.8890209197998</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287577629089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848328113556</t>
+    <t xml:space="preserve">1.78287589550018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848340034485</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3242,13 +3242,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388048171997</t>
+    <t xml:space="preserve">1.77388060092926</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055114746094</t>
+    <t xml:space="preserve">1.83055126667023</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303950309753</t>
+    <t xml:space="preserve">1.85303938388824</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3275,13 +3275,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347187042236</t>
+    <t xml:space="preserve">1.98347175121307</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246728420258</t>
+    <t xml:space="preserve">1.99246716499329</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844858169556</t>
+    <t xml:space="preserve">2.02844882011414</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194164276123</t>
+    <t xml:space="preserve">2.04194140434265</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089059829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22184824943542</t>
+    <t xml:space="preserve">2.10490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089035987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.221848487854</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -69604,7 +69604,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6910763889</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>94214</v>
@@ -69625,6 +69625,32 @@
         <v>1287</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6910069444</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>68661</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>3.3050000667572</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>3.24499988555908</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>3.26999998092651</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>3.32500004768372</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.27977406978607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2682341337204</t>
+    <t xml:space="preserve">1.26823401451111</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938819885254</t>
@@ -56,64 +56,64 @@
     <t xml:space="preserve">1.25554025173187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24861621856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27515816688538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977040290833</t>
+    <t xml:space="preserve">1.24861633777618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2751579284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977016448975</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
+    <t xml:space="preserve">1.19437897205353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283867835999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25784814357758</t>
+    <t xml:space="preserve">1.18283891677856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25784838199615</t>
   </si>
   <si>
     <t xml:space="preserve">1.25438630580902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285027503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26361835002899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20591855049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168863773346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2105348110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822668075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130667209625</t>
+    <t xml:space="preserve">1.24746215343475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746593952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2636182308197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20591878890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168875694275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053457260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207084178925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2082267999649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130655288696</t>
   </si>
   <si>
     <t xml:space="preserve">1.22899854183197</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">1.23476850986481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23707664012909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29015970230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669786453247</t>
+    <t xml:space="preserve">1.23707640171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669798374176</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
@@ -137,52 +137,52 @@
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28438985347748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169609069824</t>
+    <t xml:space="preserve">1.28438997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169597148895</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054557323456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862379074097</t>
+    <t xml:space="preserve">1.30054569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862367153168</t>
   </si>
   <si>
     <t xml:space="preserve">1.31093168258667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32477962970734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32247173786163</t>
+    <t xml:space="preserve">1.32477951049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32247161865234</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30746960639954</t>
+    <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
     <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516183376312</t>
+    <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
     <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362544536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708764076233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323981285095</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824170589447</t>
@@ -197,130 +197,130 @@
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016739368439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478317737579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208929538727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34324336051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555149078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516928672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324738502502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017117977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786304950714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286127567291</t>
+    <t xml:space="preserve">1.35016715526581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478341579437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170709133148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3432434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555160999298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516916751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324726581573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786328792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747694015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286103725433</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251530170441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621198177338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099989414215</t>
+    <t xml:space="preserve">1.39251518249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621210098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099965572357</t>
   </si>
   <si>
     <t xml:space="preserve">1.42701983451843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42332303524017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687832355499</t>
+    <t xml:space="preserve">1.42332315444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687868118286</t>
   </si>
   <si>
     <t xml:space="preserve">1.44427251815796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44550454616547</t>
+    <t xml:space="preserve">1.44550442695618</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043396949768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536327362061</t>
+    <t xml:space="preserve">1.45536303520203</t>
   </si>
   <si>
     <t xml:space="preserve">1.46275699138641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49110043048859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863542079926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342357158661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5182112455368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162538051605</t>
+    <t xml:space="preserve">1.4911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863554000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342345237732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821100711823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162526130676</t>
   </si>
   <si>
     <t xml:space="preserve">1.50465559959412</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51574647426605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849426746368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039263725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433148384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707939624786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5243729352951</t>
+    <t xml:space="preserve">1.51574659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4984940290451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039311408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817015171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433184146881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707927703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52437257766724</t>
   </si>
   <si>
     <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55641293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6007764339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5465544462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
+    <t xml:space="preserve">1.55641269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077619552612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655468463898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190828323364</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257438659668</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">1.59584701061249</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6636244058609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006864070892</t>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006875991821</t>
   </si>
   <si>
     <t xml:space="preserve">1.59461462497711</t>
@@ -341,28 +341,28 @@
     <t xml:space="preserve">1.64883661270142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65992736816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115963459015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661365032196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154295444489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400796413422</t>
+    <t xml:space="preserve">1.65992712974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115975379944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661412715912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154307365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400760650635</t>
   </si>
   <si>
     <t xml:space="preserve">1.68950295448303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68827068805695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523999214172</t>
+    <t xml:space="preserve">1.68827044963837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523975372314</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756313323975</t>
@@ -371,82 +371,82 @@
     <t xml:space="preserve">1.70429062843323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70059359073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70675551891327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301750659943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7560476064682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439104557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206766605377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988639354706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865388870239</t>
+    <t xml:space="preserve">1.7005934715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7067551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784579753876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851261615753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604796409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7843906879425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206778526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988615512848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865400791168</t>
   </si>
   <si>
     <t xml:space="preserve">1.74618947505951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76837086677551</t>
+    <t xml:space="preserve">1.76837122440338</t>
   </si>
   <si>
     <t xml:space="preserve">1.77453255653381</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76220941543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77699744701385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344192028046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855347156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158392906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447323322296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035202026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267528057098</t>
+    <t xml:space="preserve">1.7622092962265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699708938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746295452118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855370998383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249243736267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186683177948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158404827118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679625511169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267480373383</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376567840576</t>
@@ -455,64 +455,64 @@
     <t xml:space="preserve">1.62049341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63281643390656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556398868561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802864074707</t>
+    <t xml:space="preserve">1.63281667232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309945583344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6155641078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802852153778</t>
   </si>
   <si>
     <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64760398864746</t>
+    <t xml:space="preserve">1.64760422706604</t>
   </si>
   <si>
     <t xml:space="preserve">1.65130126476288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6562305688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513957500458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144241809845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356496334076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479734897614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972653388977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247408866882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887734889984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845317363739</t>
+    <t xml:space="preserve">1.65623033046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513969421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144265651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404881954193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091782569885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546369075775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356484413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972641468048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247385025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887758731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58845329284668</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503903865814</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532206058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120072841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598840236664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.581059217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200810432434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338235855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722078800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6365133523941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66485631465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225050926208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841219902039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073510169983</t>
+    <t xml:space="preserve">1.54532194137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120048999786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105909824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338223934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66485643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499794483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6784120798111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073498249054</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978585720062</t>
@@ -575,79 +575,79 @@
     <t xml:space="preserve">1.67717957496643</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68703818321228</t>
+    <t xml:space="preserve">1.68703830242157</t>
   </si>
   <si>
     <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291673183441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467394828796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728011131287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016941547394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946174144745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742138385773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178500175476</t>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457353115082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467406749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75728023052216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125993251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016917705536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330005168915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74742150306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78069400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178488254547</t>
   </si>
   <si>
     <t xml:space="preserve">1.76590621471405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8176634311676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150186061859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614838123322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297617435455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762221813202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392541885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459211826324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92980408668518</t>
+    <t xml:space="preserve">1.81766355037689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614814281464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695599555969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297653198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899623394012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762233734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392553806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459199905396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980420589447</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279356956482</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838969230652</t>
+    <t xml:space="preserve">2.02838921546936</t>
   </si>
   <si>
     <t xml:space="preserve">2.04687404632568</t>
@@ -668,25 +668,25 @@
     <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05796480178833</t>
+    <t xml:space="preserve">2.05796456336975</t>
   </si>
   <si>
     <t xml:space="preserve">2.05303597450256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905579566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10725736618042</t>
+    <t xml:space="preserve">2.0690553188324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.107257604599</t>
   </si>
   <si>
     <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09986329078674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13806533813477</t>
+    <t xml:space="preserve">2.09986352920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13806509971619</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669132232666</t>
@@ -713,43 +713,43 @@
     <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531754493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1664080619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18366098403931</t>
+    <t xml:space="preserve">2.15531778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640877723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446895599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
     <t xml:space="preserve">2.17996406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21816563606262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953941345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323657035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23172092437744</t>
+    <t xml:space="preserve">2.2181658744812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323680877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
     <t xml:space="preserve">2.27978134155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28717517852783</t>
+    <t xml:space="preserve">2.28717541694641</t>
   </si>
   <si>
     <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35877203941345</t>
+    <t xml:space="preserve">2.35877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583306312561</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477975845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137853622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019522666931</t>
+    <t xml:space="preserve">2.31477952003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526022911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137877464294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973345756531</t>
+    <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
     <t xml:space="preserve">2.30313444137573</t>
@@ -782,19 +782,19 @@
     <t xml:space="preserve">2.3186616897583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3367760181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100865364075</t>
+    <t xml:space="preserve">2.33677577972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100841522217</t>
   </si>
   <si>
     <t xml:space="preserve">2.36782932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35489010810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054664611816</t>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054712295532</t>
   </si>
   <si>
     <t xml:space="preserve">2.33806967735291</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3613600730896</t>
+    <t xml:space="preserve">2.36136031150818</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
@@ -812,43 +812,43 @@
     <t xml:space="preserve">2.34065771102905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32901215553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842085838318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34971451759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324526786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4053521156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642483711243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31219148635864</t>
+    <t xml:space="preserve">2.32901239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40535235404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642459869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666543006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396656990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2449095249176</t>
+    <t xml:space="preserve">2.29666519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26043581962585</t>
+    <t xml:space="preserve">2.26043605804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784826278687</t>
@@ -869,43 +869,43 @@
     <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21903133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197054862976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102759361267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3225429058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736731529236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771873474121</t>
+    <t xml:space="preserve">2.21903109550476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319700717926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254338264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771849632263</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725625038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855038642883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26431751251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28890204429626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879121780396</t>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725672721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855062484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26431775093079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28890180587769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2487907409668</t>
   </si>
   <si>
     <t xml:space="preserve">2.29278326034546</t>
@@ -920,55 +920,55 @@
     <t xml:space="preserve">2.35747814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28502011299133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631377220154</t>
+    <t xml:space="preserve">2.28501987457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">2.2733747959137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26819920539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160042762756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418774604797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572247505188</t>
+    <t xml:space="preserve">2.26819944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960392951965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3057222366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171101570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699767112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46745896339417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44675707817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546294212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651648521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38723802566528</t>
+    <t xml:space="preserve">2.37171077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699719429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46745944023132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4467568397522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546318054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3872377872467</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241337776184</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524152755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40793991088867</t>
+    <t xml:space="preserve">2.36524176597595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
     <t xml:space="preserve">2.39370703697205</t>
@@ -989,70 +989,70 @@
     <t xml:space="preserve">2.37688660621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36265397071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38464999198914</t>
+    <t xml:space="preserve">2.3626537322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38465023040771</t>
   </si>
   <si>
     <t xml:space="preserve">2.31607341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36459445953369</t>
+    <t xml:space="preserve">2.36459469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37429904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37753319740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3193085193634</t>
+    <t xml:space="preserve">2.37429881095886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37753367424011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930804252625</t>
   </si>
   <si>
     <t xml:space="preserve">2.13492798805237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258102416992</t>
+    <t xml:space="preserve">2.04435539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258054733276</t>
   </si>
   <si>
     <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03788614273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08964204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07993745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11552000045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12198901176453</t>
+    <t xml:space="preserve">2.03788590431213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0896418094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07993769645691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551928520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12198925018311</t>
   </si>
   <si>
     <t xml:space="preserve">2.06699872016907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05082511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818131446838</t>
+    <t xml:space="preserve">2.05082488059998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818155288696</t>
   </si>
   <si>
     <t xml:space="preserve">2.01847743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966051101685</t>
+    <t xml:space="preserve">1.97966063022614</t>
   </si>
   <si>
     <t xml:space="preserve">2.01524257659912</t>
@@ -1061,49 +1061,49 @@
     <t xml:space="preserve">2.02494716644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04759001731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640694618225</t>
+    <t xml:space="preserve">2.0475902557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640718460083</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1252236366272</t>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670283317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052899360657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0637640953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934592247009</t>
+    <t xml:space="preserve">2.06052923202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376385688782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934616088867</t>
   </si>
   <si>
     <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14139771461487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11875438690186</t>
+    <t xml:space="preserve">2.14139747619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11875414848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110158920288</t>
+    <t xml:space="preserve">2.15110182762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433645248413</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755261421204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460168838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2505030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958471298218</t>
+    <t xml:space="preserve">2.26755237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230605125427</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">2.22322416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16866660118103</t>
+    <t xml:space="preserve">2.16866683959961</t>
   </si>
   <si>
     <t xml:space="preserve">2.1345682144165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12433838844299</t>
+    <t xml:space="preserve">2.12433862686157</t>
   </si>
   <si>
     <t xml:space="preserve">2.11751866340637</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">2.11069917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10046935081482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08342051506042</t>
+    <t xml:space="preserve">2.10046982765198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066522598267</t>
+    <t xml:space="preserve">1.96066582202911</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05614161491394</t>
+    <t xml:space="preserve">2.05614137649536</t>
   </si>
   <si>
     <t xml:space="preserve">2.04591178894043</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08682990074158</t>
+    <t xml:space="preserve">2.08001065254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
     <t xml:space="preserve">2.02886247634888</t>
@@ -1190,46 +1190,46 @@
     <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99135410785675</t>
+    <t xml:space="preserve">1.99135398864746</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06978106498718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99817407131195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794436454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089517116547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748518943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384573936462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771465778351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043623447418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436160326004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138793945312</t>
+    <t xml:space="preserve">2.0697808265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522326469421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99817419052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794448375702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089505195618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748530864716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95384585857391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95725560188293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9777147769928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95043611526489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361615180969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138770103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820742607117</t>
@@ -1238,7 +1238,7 @@
     <t xml:space="preserve">2.185715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41417598724365</t>
+    <t xml:space="preserve">2.41417622566223</t>
   </si>
   <si>
     <t xml:space="preserve">2.28801155090332</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">2.22663426399231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23004388809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21640419960022</t>
+    <t xml:space="preserve">2.23004364967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2164044380188</t>
   </si>
   <si>
     <t xml:space="preserve">2.17889618873596</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">2.09705972671509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387969017029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12092852592468</t>
+    <t xml:space="preserve">2.10387945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1209282875061</t>
   </si>
   <si>
     <t xml:space="preserve">2.13115811347961</t>
@@ -1283,52 +1283,52 @@
     <t xml:space="preserve">2.1584370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502762794495</t>
+    <t xml:space="preserve">2.15502738952637</t>
   </si>
   <si>
     <t xml:space="preserve">2.15161728858948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16184687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637096405029</t>
+    <t xml:space="preserve">2.16184711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637072563171</t>
   </si>
   <si>
     <t xml:space="preserve">2.00499391555786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01863312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955171585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315709590912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453438282013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0766007900238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09364986419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319045066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273151397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299457550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24027371406555</t>
+    <t xml:space="preserve">2.01863288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315721511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9811247587204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453450202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07660055160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0936496257782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273175239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299481391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24027347564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.19594550132751</t>
@@ -1337,34 +1337,34 @@
     <t xml:space="preserve">2.17207646369934</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18912601470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19253540039062</t>
+    <t xml:space="preserve">2.18912577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
     <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686385154724</t>
+    <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.25391292572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25732278823853</t>
+    <t xml:space="preserve">2.25732254981995</t>
   </si>
   <si>
     <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29824113845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29483079910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31529021263123</t>
+    <t xml:space="preserve">2.29824090003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29483127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3152904510498</t>
   </si>
   <si>
     <t xml:space="preserve">2.30165076255798</t>
@@ -1373,34 +1373,34 @@
     <t xml:space="preserve">2.3084704875946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35961866378784</t>
+    <t xml:space="preserve">2.35961842536926</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233976364136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36643815040588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33915901184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32210993766785</t>
+    <t xml:space="preserve">2.3664379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892966270447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3391592502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32211017608643</t>
   </si>
   <si>
     <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34256887435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35279893875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732578754425</t>
+    <t xml:space="preserve">2.34256911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35279870033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37325763702393</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37666773796082</t>
+    <t xml:space="preserve">2.37666749954224</t>
   </si>
   <si>
     <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43804526329041</t>
+    <t xml:space="preserve">2.43804502487183</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">2.44827437400818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46191430091858</t>
+    <t xml:space="preserve">2.46191382408142</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942231178284</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">2.48919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47896337509155</t>
+    <t xml:space="preserve">2.47896313667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.52670121192932</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">2.54034066200256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.601717710495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830808639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62558698654175</t>
+    <t xml:space="preserve">2.60171794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830784797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
     <t xml:space="preserve">2.61535739898682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88855290412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61541271209717</t>
+    <t xml:space="preserve">2.88855242729187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
     <t xml:space="preserve">2.61167097091675</t>
@@ -1472,34 +1472,34 @@
     <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58547925949097</t>
+    <t xml:space="preserve">2.58547878265381</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928778648376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63037919998169</t>
+    <t xml:space="preserve">2.63037896156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.71269536018372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67153716087341</t>
+    <t xml:space="preserve">2.67153692245483</t>
   </si>
   <si>
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657043457031</t>
+    <t xml:space="preserve">2.65657067298889</t>
   </si>
   <si>
     <t xml:space="preserve">2.64908695220947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160370826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405391693115</t>
+    <t xml:space="preserve">2.64160346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
     <t xml:space="preserve">2.66031217575073</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">2.72766184806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69772839546204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70521187782288</t>
+    <t xml:space="preserve">2.69772863388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70521211624146</t>
   </si>
   <si>
     <t xml:space="preserve">2.72017884254456</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79126977920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83616948127747</t>
+    <t xml:space="preserve">2.7912700176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120299339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371998786926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80623626708984</t>
+    <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
     <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82494497299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86984443664551</t>
+    <t xml:space="preserve">2.82494473457336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86984467506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.96338582038879</t>
@@ -1559,34 +1559,34 @@
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977741241455</t>
+    <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.93719410896301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99331879615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">2.99331903457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576900482178</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060192108154</t>
+    <t xml:space="preserve">3.09060144424438</t>
   </si>
   <si>
     <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556817054749</t>
+    <t xml:space="preserve">3.10556864738464</t>
   </si>
   <si>
     <t xml:space="preserve">3.12053513526917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046811103821</t>
+    <t xml:space="preserve">3.15046834945679</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07937669754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10930991172791</t>
+    <t xml:space="preserve">3.0793764591217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
     <t xml:space="preserve">3.09434342384338</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583579063416</t>
+    <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
@@ -1625,97 +1625,97 @@
     <t xml:space="preserve">2.91100263595581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91474461555481</t>
+    <t xml:space="preserve">2.91474413871765</t>
   </si>
   <si>
     <t xml:space="preserve">3.0718936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06815195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951050758362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00454354286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90351939201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841885566711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086930274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964384078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739446640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75011134147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80249452590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83991122245789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113596916199</t>
+    <t xml:space="preserve">3.0681517124176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00454378128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835206985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467711448669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086882591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964407920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84739470481873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75011157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80249500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83991146087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365272521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86236119270325</t>
+    <t xml:space="preserve">2.86236143112183</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848635673523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89603567123413</t>
+    <t xml:space="preserve">2.91848587989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
     <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726089477539</t>
+    <t xml:space="preserve">2.90726113319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004479408264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76882028579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997800827026</t>
+    <t xml:space="preserve">2.79875302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004503250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76882004737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
     <t xml:space="preserve">2.76133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88106966018677</t>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712732315063</t>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712708473206</t>
   </si>
   <si>
     <t xml:space="preserve">2.88481116294861</t>
@@ -1736,97 +1736,97 @@
     <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78378677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81746172904968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487771034241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957705497742</t>
+    <t xml:space="preserve">2.78378653526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8174614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98957681655884</t>
   </si>
   <si>
     <t xml:space="preserve">3.30761766433716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38619208335876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986680030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36374187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44979977607727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625863075256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26645922660828</t>
+    <t xml:space="preserve">3.38619184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632541656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986703872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3637421131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980025291443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
     <t xml:space="preserve">3.2402675151825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28142595291138</t>
+    <t xml:space="preserve">3.22530102729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2814257144928</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29639220237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13924336433411</t>
+    <t xml:space="preserve">3.29639267921448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13924360275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305141448975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06441020965576</t>
+    <t xml:space="preserve">3.06440997123718</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425451278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03545689582825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25621438026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853030204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37968897819519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091324806213</t>
+    <t xml:space="preserve">3.11679339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08685994148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944372177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425427436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03545665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2562141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853054046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37968873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091348648071</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581342697144</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">2.49942111968994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.484454870224</t>
+    <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51438784599304</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51812958717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38343024253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39465498924255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35723853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839649200439</t>
+    <t xml:space="preserve">2.51812934875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38343000411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39465522766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35723876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839673042297</t>
   </si>
   <si>
     <t xml:space="preserve">2.41710495948792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42458820343018</t>
+    <t xml:space="preserve">2.42458844184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.41336345672607</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">2.40962195396423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4545214176178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46948838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5218710899353</t>
+    <t xml:space="preserve">2.45452165603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4694881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187132835388</t>
   </si>
   <si>
     <t xml:space="preserve">2.49193787574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935457229614</t>
+    <t xml:space="preserve">2.52935433387756</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
@@ -1901,28 +1901,28 @@
     <t xml:space="preserve">2.5069043636322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59670400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78752827644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15795111656189</t>
+    <t xml:space="preserve">2.59670376777649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7875280380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15795159339905</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265069961548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27768468856812</t>
+    <t xml:space="preserve">3.27768421173096</t>
   </si>
   <si>
     <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17801690101624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1072199344635</t>
+    <t xml:space="preserve">3.17801713943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10721969604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.00102353096008</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04822182655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07968735694885</t>
+    <t xml:space="preserve">3.04822206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07968711853027</t>
   </si>
   <si>
     <t xml:space="preserve">3.12295246124268</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">3.07182097434998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96955823898315</t>
+    <t xml:space="preserve">2.96955800056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202542304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989204406738</t>
+    <t xml:space="preserve">2.94202589988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989228248596</t>
   </si>
   <si>
     <t xml:space="preserve">2.97742462158203</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91842651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8082971572876</t>
+    <t xml:space="preserve">2.91842675209045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80829739570618</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73750019073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536609649658</t>
+    <t xml:space="preserve">2.73749995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536633491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.76109910011292</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">2.67456912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
+    <t xml:space="preserve">2.6352367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
   </si>
   <si>
     <t xml:space="preserve">2.62737059593201</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60770440101624</t>
+    <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">2.74143290519714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963356971741</t>
+    <t xml:space="preserve">2.72963333129883</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63916993141174</t>
+    <t xml:space="preserve">2.63917016983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6549026966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883636474609</t>
+    <t xml:space="preserve">2.65490293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883612632751</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6470365524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62343716621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59590530395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59983825683594</t>
+    <t xml:space="preserve">2.64703631401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62343740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5959050655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59983801841736</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323271751404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510762214661</t>
+    <t xml:space="preserve">2.75323247909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510786056519</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
@@ -2090,40 +2090,40 @@
     <t xml:space="preserve">2.54084014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970866203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330828666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150871276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50544166564941</t>
+    <t xml:space="preserve">2.48970890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330780982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150847434998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4857759475708</t>
+    <t xml:space="preserve">2.48577618598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117419242859</t>
+    <t xml:space="preserve">2.52117466926575</t>
   </si>
   <si>
     <t xml:space="preserve">2.4936420917511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46610999107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47790932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40317893028259</t>
+    <t xml:space="preserve">2.46610951423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47790956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40317869186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.38351273536682</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698276519775</t>
+    <t xml:space="preserve">2.39531254768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698252677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34024786949158</t>
+    <t xml:space="preserve">2.340247631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631467819214</t>
@@ -2162,19 +2162,19 @@
     <t xml:space="preserve">2.36384677886963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356652259827</t>
+    <t xml:space="preserve">2.57230591773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356676101685</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503205299377</t>
+    <t xml:space="preserve">2.76503252983093</t>
   </si>
   <si>
     <t xml:space="preserve">2.71783375740051</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6903018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70603442192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482736587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87909436225891</t>
+    <t xml:space="preserve">2.69030141830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7060341835022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210123062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482760429382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
     <t xml:space="preserve">2.8594286441803</t>
@@ -2207,19 +2207,19 @@
     <t xml:space="preserve">2.87122845649719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91449356079102</t>
+    <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0206892490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9616916179657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562480926514</t>
+    <t xml:space="preserve">3.02068948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96169185638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562457084656</t>
   </si>
   <si>
     <t xml:space="preserve">2.83976268768311</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009720802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85156273841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302826881409</t>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302755355835</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
@@ -2246,49 +2246,49 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91055989265442</t>
+    <t xml:space="preserve">2.91056036949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876079559326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.95775866508484</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516140937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796311378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93022632598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00495648384094</t>
+    <t xml:space="preserve">2.87516164779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796335220337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729502677917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93022584915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
     <t xml:space="preserve">3.01675653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02462291717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035544395447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00889015197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97349119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98922371864319</t>
+    <t xml:space="preserve">3.02462267875671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00888991355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97349095344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529100418091</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">3.07575416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05215501785278</t>
+    <t xml:space="preserve">3.05215525627136</t>
   </si>
   <si>
     <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06002163887024</t>
+    <t xml:space="preserve">3.06002140045166</t>
   </si>
   <si>
     <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04428839683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09148693084717</t>
+    <t xml:space="preserve">3.04428863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688541412354</t>
@@ -2327,46 +2327,46 @@
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374966621399</t>
+    <t xml:space="preserve">3.19374990463257</t>
   </si>
   <si>
     <t xml:space="preserve">3.15441799163818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18981671333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21029043197632</t>
+    <t xml:space="preserve">3.18981647491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2102906703949</t>
   </si>
   <si>
     <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06287908554077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.06287932395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08744764328003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06697368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05059480667114</t>
+    <t xml:space="preserve">3.08744740486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06697392463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05059456825256</t>
   </si>
   <si>
     <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01374197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012084960938</t>
+    <t xml:space="preserve">3.01374220848083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
@@ -2384,16 +2384,16 @@
     <t xml:space="preserve">3.02602624893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05468964576721</t>
+    <t xml:space="preserve">3.05468940734863</t>
   </si>
   <si>
     <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08335280418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0751633644104</t>
+    <t xml:space="preserve">3.08335304260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07516360282898</t>
   </si>
   <si>
     <t xml:space="preserve">2.98507857322693</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460461616516</t>
+    <t xml:space="preserve">2.96460485458374</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
@@ -2411,34 +2411,34 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318369865417</t>
+    <t xml:space="preserve">2.9031834602356</t>
   </si>
   <si>
     <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.91137290000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585666656494</t>
+    <t xml:space="preserve">2.84585690498352</t>
   </si>
   <si>
     <t xml:space="preserve">2.87042546272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91956257820129</t>
+    <t xml:space="preserve">2.91956281661987</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223578453064</t>
+    <t xml:space="preserve">2.86223554611206</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87861514091492</t>
+    <t xml:space="preserve">2.8786153793335</t>
   </si>
   <si>
     <t xml:space="preserve">2.87452030181885</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2507,13 +2507,13 @@
     <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81719374656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82128810882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85814142227173</t>
+    <t xml:space="preserve">2.81719350814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82128834724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.84995174407959</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91546750068665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357286453247</t>
+    <t xml:space="preserve">2.9154679775238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357262611389</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
+    <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
     <t xml:space="preserve">2.84176206588745</t>
@@ -2543,37 +2543,37 @@
     <t xml:space="preserve">2.79262518882751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80900430679321</t>
+    <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80081462860107</t>
+    <t xml:space="preserve">2.8008143901825</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034067153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986695289612</t>
+    <t xml:space="preserve">2.78034090995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986671447754</t>
   </si>
   <si>
     <t xml:space="preserve">2.69435095787048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64521384239197</t>
+    <t xml:space="preserve">2.64521360397339</t>
   </si>
   <si>
     <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
+    <t xml:space="preserve">2.76805663108826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
+    <t xml:space="preserve">2.7271089553833</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95615863800049</t>
+    <t xml:space="preserve">2.95615839958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897151947021</t>
+    <t xml:space="preserve">2.93897128105164</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
@@ -2633,70 +2633,70 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86162996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90459775924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90889406204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132132530212</t>
+    <t xml:space="preserve">2.87881684303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86163020133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90459752082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90889430046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132108688354</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405722618103</t>
+    <t xml:space="preserve">2.69405698776245</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54796767234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53507781028748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.578045129776</t>
+    <t xml:space="preserve">2.59952902793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5350775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929737091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359391212463</t>
+    <t xml:space="preserve">2.47922015190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929713249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48781371116638</t>
+    <t xml:space="preserve">2.44914293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195557594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4878134727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867985725403</t>
+    <t xml:space="preserve">2.34602117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867961883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3975818157196</t>
+    <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469195365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625283241272</t>
+    <t xml:space="preserve">2.38469171524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33742761611938</t>
+    <t xml:space="preserve">2.33742737770081</t>
   </si>
   <si>
     <t xml:space="preserve">2.28156995773315</t>
@@ -2771,19 +2771,19 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829376220703</t>
+    <t xml:space="preserve">2.13118386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829352378845</t>
   </si>
   <si>
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985487937927</t>
+    <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.14407420158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399722099304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08391976356506</t>
+    <t xml:space="preserve">2.11399698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08392000198364</t>
   </si>
   <si>
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85619258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81322491168976</t>
+    <t xml:space="preserve">1.85619246959686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81322503089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744447231293</t>
+    <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
     <t xml:space="preserve">1.71869671344757</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62416839599609</t>
+    <t xml:space="preserve">1.6241682767868</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84330224990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650110721588</t>
+    <t xml:space="preserve">1.92494022846222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84330236911774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96790778636932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650134563446</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,22 +2873,22 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95931422710419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07962322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08821654319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524946212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102966308594</t>
+    <t xml:space="preserve">2.04954600334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593141078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0796229839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08821678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524922370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102942466736</t>
   </si>
   <si>
     <t xml:space="preserve">2.17844820022583</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126132011414</t>
+    <t xml:space="preserve">2.16126108169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">2.2128221988678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1956353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.19563508033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681034088135</t>
+    <t xml:space="preserve">2.06673264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000907897949</t>
+    <t xml:space="preserve">2.23000884056091</t>
   </si>
   <si>
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594395637512</t>
+    <t xml:space="preserve">2.31594371795654</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438307762146</t>
+    <t xml:space="preserve">2.26438283920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750507354736</t>
+    <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
     <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149250030518</t>
+    <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24289917945862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39328503608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41047215461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062659263611</t>
+    <t xml:space="preserve">2.27297616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2428994178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39328527450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41047239303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062635421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -69656,7 +69656,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.6912615741</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>107849</v>
@@ -69677,6 +69677,32 @@
         <v>1287</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6911458333</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>57184</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="1289">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,52 +44,52 @@
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977406978607</t>
+    <t xml:space="preserve">1.27977395057678</t>
   </si>
   <si>
     <t xml:space="preserve">1.26823401451111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26938819885254</t>
+    <t xml:space="preserve">1.26938807964325</t>
   </si>
   <si>
     <t xml:space="preserve">1.25554025173187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24861633777618</t>
+    <t xml:space="preserve">1.24861621856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.2751579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
+    <t xml:space="preserve">1.24977004528046</t>
   </si>
   <si>
     <t xml:space="preserve">1.23246049880981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19437897205353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784069061279</t>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
     <t xml:space="preserve">1.15975904464722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.18283891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25784838199615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25438630580902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746215343475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285003662109</t>
+    <t xml:space="preserve">1.18283879756927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25784826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25438618659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285027503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746593952179</t>
@@ -98,31 +98,31 @@
     <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168875694275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053457260132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207084178925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2082267999649</t>
+    <t xml:space="preserve">1.20591855049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207072257996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20822668075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899854183197</t>
+    <t xml:space="preserve">1.22899842262268</t>
   </si>
   <si>
     <t xml:space="preserve">1.23476850986481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23707640171051</t>
+    <t xml:space="preserve">1.23707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28438997268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169597148895</t>
+    <t xml:space="preserve">1.28439009189606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169620990753</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323590755463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054569244385</t>
+    <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
     <t xml:space="preserve">1.30862367153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093168258667</t>
+    <t xml:space="preserve">1.31093192100525</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208562850952</t>
+    <t xml:space="preserve">1.32247149944305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208574771881</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746972560883</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016360759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3236255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708764076233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323981285095</t>
+    <t xml:space="preserve">1.30516183376312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32362568378448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824170589447</t>
@@ -197,112 +197,112 @@
     <t xml:space="preserve">1.34670543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35016715526581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478341579437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170709133148</t>
+    <t xml:space="preserve">1.35016751289368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3547830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170721054077</t>
   </si>
   <si>
     <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3432434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555160999298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516916751862</t>
+    <t xml:space="preserve">1.34324336051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3455513715744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516928672791</t>
   </si>
   <si>
     <t xml:space="preserve">1.37324726581573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38017094135284</t>
+    <t xml:space="preserve">1.38017106056213</t>
   </si>
   <si>
     <t xml:space="preserve">1.37786328792572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36747694015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286103725433</t>
+    <t xml:space="preserve">1.36747705936432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
     <t xml:space="preserve">1.39497971534729</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39251518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621210098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41099965572357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332315444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43687868118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44427251815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44550442695618</t>
+    <t xml:space="preserve">1.39251494407654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621198177338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41099989414215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43687856197357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44427239894867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44550478458405</t>
   </si>
   <si>
     <t xml:space="preserve">1.45043396949768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45536303520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46275699138641</t>
+    <t xml:space="preserve">1.45536315441132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4627571105957</t>
   </si>
   <si>
     <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48863554000854</t>
+    <t xml:space="preserve">1.48863565921783</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51821100711823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162526130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
+    <t xml:space="preserve">1.5182112455368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162514209747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465571880341</t>
   </si>
   <si>
     <t xml:space="preserve">1.51574659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4984940290451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039311408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817015171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433184146881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707927703857</t>
+    <t xml:space="preserve">1.49849414825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039263725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817003250122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433148384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707939624786</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437257766724</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55641269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655468463898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190828323364</t>
+    <t xml:space="preserve">1.55641293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6007764339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655420780182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190816402435</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59584701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006875991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59461462497711</t>
+    <t xml:space="preserve">1.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362416744232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5946147441864</t>
   </si>
   <si>
     <t xml:space="preserve">1.64883661270142</t>
@@ -347,52 +347,52 @@
     <t xml:space="preserve">1.66115975379944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71661412715912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72154307365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72400760650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950295448303</t>
+    <t xml:space="preserve">1.71661376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72154295444489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72400772571564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950283527374</t>
   </si>
   <si>
     <t xml:space="preserve">1.68827044963837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72523975372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7005934715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784579753876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851261615753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604796409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7843906879425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206778526306</t>
+    <t xml:space="preserve">1.72523999214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756289482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059359073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675539970398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784627437592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301750659943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604784488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439104557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206790447235</t>
   </si>
   <si>
     <t xml:space="preserve">1.74988615512848</t>
@@ -404,58 +404,58 @@
     <t xml:space="preserve">1.74618947505951</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76837122440338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453255653381</t>
+    <t xml:space="preserve">1.76837110519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453279495239</t>
   </si>
   <si>
     <t xml:space="preserve">1.7622092962265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77699708938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344156265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746295452118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855370998383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249243736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443213939667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186683177948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158404827118</t>
+    <t xml:space="preserve">1.77699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344168186188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855359077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249255657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443225860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
     <t xml:space="preserve">1.60447335243225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679625511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267480373383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281667232513</t>
+    <t xml:space="preserve">1.6303516626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267492294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376579761505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049353122711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281655311584</t>
   </si>
   <si>
     <t xml:space="preserve">1.61309945583344</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">1.61802852153778</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021039009094</t>
+    <t xml:space="preserve">1.64021015167236</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760422706604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65130126476288</t>
+    <t xml:space="preserve">1.65130114555359</t>
   </si>
   <si>
     <t xml:space="preserve">1.65623033046722</t>
@@ -482,31 +482,31 @@
     <t xml:space="preserve">1.61926090717316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64513969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144265651703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404881954193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091782569885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546369075775</t>
+    <t xml:space="preserve">1.64513945579529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091794490814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546357154846</t>
   </si>
   <si>
     <t xml:space="preserve">1.49356484413147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49479722976685</t>
+    <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48247385025024</t>
+    <t xml:space="preserve">1.48247420787811</t>
   </si>
   <si>
     <t xml:space="preserve">1.55887758731842</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">1.56503903865814</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53423130512238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49726188182831</t>
+    <t xml:space="preserve">1.53423118591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
     <t xml:space="preserve">1.51451420783997</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">1.54532194137573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57120048999786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598852157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105909824371</t>
+    <t xml:space="preserve">1.57120072841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598828315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">1.59338223934174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58722066879272</t>
+    <t xml:space="preserve">1.58722078800201</t>
   </si>
   <si>
     <t xml:space="preserve">1.63651323318481</t>
@@ -557,64 +557,64 @@
     <t xml:space="preserve">1.65499794483185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67594754695892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225062847137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6784120798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073498249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978585720062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717957496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703830242157</t>
+    <t xml:space="preserve">1.67594766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225027084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073522090912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717945575714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703818321228</t>
   </si>
   <si>
     <t xml:space="preserve">1.70552289485931</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538126468658</t>
+    <t xml:space="preserve">1.71538150310516</t>
   </si>
   <si>
     <t xml:space="preserve">1.7129168510437</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68457353115082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76467406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728023052216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125993251801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016917705536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330005168915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946186065674</t>
+    <t xml:space="preserve">1.68457365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76467418670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75727999210358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126029014587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016905784607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330029010773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946174144745</t>
   </si>
   <si>
     <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78069400787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178488254547</t>
+    <t xml:space="preserve">1.78069424629211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178500175476</t>
   </si>
   <si>
     <t xml:space="preserve">1.76590621471405</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">1.81766355037689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81150209903717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614814281464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695599555969</t>
+    <t xml:space="preserve">1.81150197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614826202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695623397827</t>
   </si>
   <si>
     <t xml:space="preserve">1.88297653198242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89899623394012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762233734131</t>
+    <t xml:space="preserve">1.8989964723587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762269496918</t>
   </si>
   <si>
     <t xml:space="preserve">1.90392553806305</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">1.94459199905396</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980420589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279356956482</t>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279368877411</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">2.02838921546936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04687404632568</t>
+    <t xml:space="preserve">2.04687428474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483368873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01729846000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796456336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303597450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0690553188324</t>
+    <t xml:space="preserve">2.01729869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796480178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303549766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905579566956</t>
   </si>
   <si>
     <t xml:space="preserve">2.107257604599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09493446350098</t>
+    <t xml:space="preserve">2.09493398666382</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806509971619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669132232666</t>
+    <t xml:space="preserve">2.13806557655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669156074524</t>
   </si>
   <si>
     <t xml:space="preserve">2.16024684906006</t>
@@ -698,61 +698,61 @@
     <t xml:space="preserve">2.16887283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17256999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15654993057251</t>
+    <t xml:space="preserve">2.17257022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15655040740967</t>
   </si>
   <si>
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640877723694</t>
+    <t xml:space="preserve">2.17380213737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010521888733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531754493713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640853881836</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366074562073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17996406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2181658744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20953965187073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323680877686</t>
+    <t xml:space="preserve">2.18366098403931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17996382713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816563606262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20953941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2132363319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978134155273</t>
+    <t xml:space="preserve">2.27978110313416</t>
   </si>
   <si>
     <t xml:space="preserve">2.28717541694641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3303062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877227783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583306312561</t>
+    <t xml:space="preserve">2.33030652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583282470703</t>
   </si>
   <si>
     <t xml:space="preserve">2.33289408683777</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">2.31477952003479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25526022911072</t>
+    <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137877464294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019546508789</t>
+    <t xml:space="preserve">2.29019522666931</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267267227173</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">2.23973369598389</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30313444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3186616897583</t>
+    <t xml:space="preserve">2.30313420295715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.33677577972412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35100841522217</t>
+    <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
     <t xml:space="preserve">2.36782932281494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35489058494568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054712295532</t>
+    <t xml:space="preserve">2.3548903465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054688453674</t>
   </si>
   <si>
     <t xml:space="preserve">2.33806967735291</t>
@@ -803,52 +803,52 @@
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36136031150818</t>
+    <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842109680176</t>
+    <t xml:space="preserve">2.34065747261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901263237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842133522034</t>
   </si>
   <si>
     <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34324550628662</t>
+    <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
     <t xml:space="preserve">2.40535235404968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32642459869385</t>
+    <t xml:space="preserve">2.32642436027527</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537105560303</t>
+    <t xml:space="preserve">2.29537129402161</t>
   </si>
   <si>
     <t xml:space="preserve">2.29666519165039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25396633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24490928649902</t>
+    <t xml:space="preserve">2.25396656990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2449095249176</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26043605804443</t>
+    <t xml:space="preserve">2.26043581962585</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784826278687</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.26172995567322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26690554618835</t>
+    <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361538887024</t>
@@ -866,64 +866,64 @@
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703507423401</t>
+    <t xml:space="preserve">2.19703531265259</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903109550476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319700717926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24102783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254338264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32771849632263</t>
+    <t xml:space="preserve">2.23197031021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24102759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3225429058075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736707687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">2.31348562240601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29407715797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725672721863</t>
+    <t xml:space="preserve">2.29407739639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725648880005</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26431775093079</t>
+    <t xml:space="preserve">2.26431798934937</t>
   </si>
   <si>
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2487907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041687965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548188209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28501987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631401062012</t>
+    <t xml:space="preserve">2.24879121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278349876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747838020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28502011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631377220154</t>
   </si>
   <si>
     <t xml:space="preserve">2.2733747959137</t>
@@ -932,22 +932,22 @@
     <t xml:space="preserve">2.26819944381714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33160018920898</t>
+    <t xml:space="preserve">2.33160042762756</t>
   </si>
   <si>
     <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33418798446655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3057222366333</t>
+    <t xml:space="preserve">2.33418822288513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30572247505188</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171077728271</t>
+    <t xml:space="preserve">2.37171101570129</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664625167847</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">2.41699719429016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46745944023132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546318054199</t>
+    <t xml:space="preserve">2.46745920181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546270370483</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3872377872467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241337776184</t>
+    <t xml:space="preserve">2.38723802566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241361618042</t>
   </si>
   <si>
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524176597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40794014930725</t>
+    <t xml:space="preserve">2.36524128913879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40793991088867</t>
   </si>
   <si>
     <t xml:space="preserve">2.39370703697205</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">2.3626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38465023040771</t>
+    <t xml:space="preserve">2.38464999198914</t>
   </si>
   <si>
     <t xml:space="preserve">2.31607341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36459469795227</t>
+    <t xml:space="preserve">2.36459445953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
@@ -1010,31 +1010,31 @@
     <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31930804252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13492798805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258054733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346820831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788590431213</t>
+    <t xml:space="preserve">2.31930828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13492822647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435563087463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258078575134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346773147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788566589355</t>
   </si>
   <si>
     <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07993769645691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11551928520203</t>
+    <t xml:space="preserve">2.07993745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11551952362061</t>
   </si>
   <si>
     <t xml:space="preserve">2.12198925018311</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966063022614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524257659912</t>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847767829895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966074943542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0152428150177</t>
   </si>
   <si>
     <t xml:space="preserve">2.02494716644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0475902557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08640718460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0411205291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07023334503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670283317566</t>
+    <t xml:space="preserve">2.04759001731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08640694618225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04112076759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07023358345032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.12522387504578</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">2.10581541061401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06052923202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06376385688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09934616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10905003547668</t>
+    <t xml:space="preserve">2.06052899360657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06376361846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09934592247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10905027389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875414848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12845849990845</t>
+    <t xml:space="preserve">2.11875438690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12845826148987</t>
   </si>
   <si>
     <t xml:space="preserve">2.15110182762146</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962286949158</t>
+    <t xml:space="preserve">2.19962310791016</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">2.26755237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460121154785</t>
+    <t xml:space="preserve">2.28460144996643</t>
   </si>
   <si>
     <t xml:space="preserve">2.25050330162048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20958495140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18230605125427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22322416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866683959961</t>
+    <t xml:space="preserve">2.20958471298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18230628967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.223224401474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866660118103</t>
   </si>
   <si>
     <t xml:space="preserve">2.1345682144165</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">2.11069917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10046982765198</t>
+    <t xml:space="preserve">2.1004695892334</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342027664185</t>
@@ -1160,94 +1160,94 @@
     <t xml:space="preserve">1.96066582202911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0118134021759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05614137649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227257728577</t>
+    <t xml:space="preserve">2.01181364059448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05614185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591202735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227233886719</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001065254211</t>
+    <t xml:space="preserve">2.08001017570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02886247634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03909182548523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04250192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99135398864746</t>
+    <t xml:space="preserve">2.02886271476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03909206390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0425021648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99135410785675</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0697808265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522326469421</t>
+    <t xml:space="preserve">2.06978106498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
     <t xml:space="preserve">1.99817419052124</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98794448375702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089505195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748530864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384585857391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95725560188293</t>
+    <t xml:space="preserve">1.98794424533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089517116547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748507022858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9538459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9572559595108</t>
   </si>
   <si>
     <t xml:space="preserve">1.9777147769928</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95043611526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361615180969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820742607117</t>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361650943756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
     <t xml:space="preserve">2.185715675354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41417622566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663426399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004364967346</t>
+    <t xml:space="preserve">2.41417574882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801107406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663450241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.2164044380188</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13797783851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11410880088806</t>
+    <t xml:space="preserve">2.13797807693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11410903930664</t>
   </si>
   <si>
     <t xml:space="preserve">2.06296110153198</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">2.1209282875061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13115811347961</t>
+    <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15161728858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16184711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637072563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499391555786</t>
+    <t xml:space="preserve">2.15502762794495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15161752700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16184687614441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637096405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499367713928</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863288879395</t>
@@ -1307,37 +1307,37 @@
     <t xml:space="preserve">1.92315721511841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9811247587204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453450202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0936496257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319068908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273175239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21299481391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24027347564697</t>
+    <t xml:space="preserve">1.98112440109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453462123871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07660031318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09364986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319045066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21299457550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24027371406555</t>
   </si>
   <si>
     <t xml:space="preserve">2.19594550132751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17207646369934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912577629089</t>
+    <t xml:space="preserve">2.17207622528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.1925356388092</t>
@@ -1346,16 +1346,16 @@
     <t xml:space="preserve">2.23345375061035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23686361312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732254981995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.23686385154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391316413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732278823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
@@ -1364,7 +1364,7 @@
     <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3152904510498</t>
+    <t xml:space="preserve">2.31529021263123</t>
   </si>
   <si>
     <t xml:space="preserve">2.30165076255798</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">2.35961842536926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3664379119873</t>
+    <t xml:space="preserve">2.33233952522278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36643815040588</t>
   </si>
   <si>
     <t xml:space="preserve">2.32892966270447</t>
@@ -1391,73 +1391,73 @@
     <t xml:space="preserve">2.32211017608643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32551980018616</t>
+    <t xml:space="preserve">2.32552003860474</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35279870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37325763702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39712691307068</t>
+    <t xml:space="preserve">2.35279893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3732578754425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3971266746521</t>
   </si>
   <si>
     <t xml:space="preserve">2.38689732551575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42099571228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43804502487183</t>
+    <t xml:space="preserve">2.37666773796082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42099595069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43804478645325</t>
   </si>
   <si>
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122529983521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44827437400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46191382408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942231178284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51306176185608</t>
+    <t xml:space="preserve">2.43122553825378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44827461242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942255020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51306200027466</t>
   </si>
   <si>
     <t xml:space="preserve">2.48919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47896313667297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670121192932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034066200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171794891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830784797668</t>
+    <t xml:space="preserve">2.47896289825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670097351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171818733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830832481384</t>
   </si>
   <si>
     <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61535739898682</t>
+    <t xml:space="preserve">2.6153576374054</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855242729187</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">2.61541223526001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61167097091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56677103042603</t>
+    <t xml:space="preserve">2.61167073249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56677079200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.58547878265381</t>
@@ -1493,43 +1493,43 @@
     <t xml:space="preserve">2.65657067298889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64908695220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160346984863</t>
+    <t xml:space="preserve">2.64908719062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160394668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66031217575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643710136414</t>
+    <t xml:space="preserve">2.66031193733215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643733978271</t>
   </si>
   <si>
     <t xml:space="preserve">2.72766184806824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69772863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70521211624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72017884254456</t>
+    <t xml:space="preserve">2.69772887229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70521187782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72017812728882</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262833595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7912700176239</t>
+    <t xml:space="preserve">2.74262857437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861921310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79126977920532</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
@@ -1538,55 +1538,55 @@
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81371998786926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80623650550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82868647575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82494473457336</t>
+    <t xml:space="preserve">2.8137195110321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.806236743927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82868623733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
     <t xml:space="preserve">2.86984467506409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338582038879</t>
+    <t xml:space="preserve">2.96338605880737</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977765083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719410896301</t>
+    <t xml:space="preserve">2.89977788925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719387054443</t>
   </si>
   <si>
     <t xml:space="preserve">2.99331903457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01576900482178</t>
+    <t xml:space="preserve">3.0157687664032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060144424438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10182666778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10556864738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12053513526917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
+    <t xml:space="preserve">3.09060168266296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10182690620422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10556840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12053489685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046811103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
@@ -1595,22 +1595,22 @@
     <t xml:space="preserve">3.16169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12801837921143</t>
+    <t xml:space="preserve">3.12801814079285</t>
   </si>
   <si>
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0793764591217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10931015014648</t>
+    <t xml:space="preserve">3.07937669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10931038856506</t>
   </si>
   <si>
     <t xml:space="preserve">3.09434342384338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04570174217224</t>
+    <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706053733826</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100263595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474413871765</t>
+    <t xml:space="preserve">2.91100287437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.0718936920166</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951026916504</t>
+    <t xml:space="preserve">3.01951050758362</t>
   </si>
   <si>
     <t xml:space="preserve">3.00454378128052</t>
@@ -1643,49 +1643,49 @@
     <t xml:space="preserve">2.90351963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97835206985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209381103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467711448669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086882591248</t>
+    <t xml:space="preserve">2.97835230827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209357261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467759132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841933250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086930274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964407920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84739470481873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75011157989502</t>
+    <t xml:space="preserve">2.84739446640015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7501118183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.80249500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991146087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85113620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84365272521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86236143112183</t>
+    <t xml:space="preserve">2.83991122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85113644599915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84365296363831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86236119270325</t>
   </si>
   <si>
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848587989807</t>
+    <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726113319397</t>
+    <t xml:space="preserve">2.90726065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">2.79875302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78004503250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76882004737854</t>
+    <t xml:space="preserve">2.78004479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76881980895996</t>
   </si>
   <si>
     <t xml:space="preserve">2.80997824668884</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">2.76133680343628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88106942176819</t>
+    <t xml:space="preserve">2.88106918334961</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590257644653</t>
+    <t xml:space="preserve">2.95590233802795</t>
   </si>
   <si>
     <t xml:space="preserve">2.96712708473206</t>
@@ -1733,34 +1733,34 @@
     <t xml:space="preserve">2.88481116294861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87358617782593</t>
+    <t xml:space="preserve">2.87358593940735</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8174614906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487794876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957681655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761766433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32632541656494</t>
+    <t xml:space="preserve">2.81746125221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487818717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98957705497742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761742591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986703872681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3637421131134</t>
+    <t xml:space="preserve">3.36374187469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.42360830307007</t>
@@ -1769,16 +1769,16 @@
     <t xml:space="preserve">3.44980025291443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35625910758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2664589881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530102729797</t>
+    <t xml:space="preserve">3.3562593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26645922660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530126571655</t>
   </si>
   <si>
     <t xml:space="preserve">3.2814257144928</t>
@@ -1790,37 +1790,37 @@
     <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924360275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440997123718</t>
+    <t xml:space="preserve">3.13924336433411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06441020965576</t>
   </si>
   <si>
     <t xml:space="preserve">2.94093585014343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11679339408875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08685994148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944372177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57425427436829</t>
+    <t xml:space="preserve">3.11679315567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08686017990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944348335266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57425451278687</t>
   </si>
   <si>
     <t xml:space="preserve">2.03545665740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2562141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853054046631</t>
+    <t xml:space="preserve">2.25621438026428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853030204773</t>
   </si>
   <si>
     <t xml:space="preserve">2.37968873977661</t>
@@ -1829,19 +1829,19 @@
     <t xml:space="preserve">2.39091348648071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48445463180542</t>
+    <t xml:space="preserve">2.43581318855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942135810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48445439338684</t>
   </si>
   <si>
     <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46574664115906</t>
+    <t xml:space="preserve">2.4657461643219</t>
   </si>
   <si>
     <t xml:space="preserve">2.4283299446106</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51812934875488</t>
+    <t xml:space="preserve">2.51812958717346</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35723876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839673042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710495948792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458844184875</t>
+    <t xml:space="preserve">2.35723853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710472106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458820343018</t>
   </si>
   <si>
     <t xml:space="preserve">2.41336345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43207168579102</t>
+    <t xml:space="preserve">2.43207144737244</t>
   </si>
   <si>
     <t xml:space="preserve">2.40962195396423</t>
@@ -1886,22 +1886,22 @@
     <t xml:space="preserve">2.4694881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52187132835388</t>
+    <t xml:space="preserve">2.5218710899353</t>
   </si>
   <si>
     <t xml:space="preserve">2.49193787574768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52935433387756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50316286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5069043636322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670376777649</t>
+    <t xml:space="preserve">2.52935481071472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50316309928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50690460205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670448303223</t>
   </si>
   <si>
     <t xml:space="preserve">2.7875280380249</t>
@@ -1910,58 +1910,58 @@
     <t xml:space="preserve">3.15795159339905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29265069961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768421173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17801713943481</t>
+    <t xml:space="preserve">3.29265093803406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768397331238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714388847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.10721969604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788778305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935331344604</t>
+    <t xml:space="preserve">3.00102376937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709057807922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788802146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935355186462</t>
   </si>
   <si>
     <t xml:space="preserve">3.04822206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07968711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12295246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07182097434998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96955800056458</t>
+    <t xml:space="preserve">3.07968735694885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12295269966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0718207359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96955823898315</t>
   </si>
   <si>
     <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94202589988708</t>
+    <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
     <t xml:space="preserve">2.94989228248596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742462158203</t>
+    <t xml:space="preserve">2.97742438316345</t>
   </si>
   <si>
     <t xml:space="preserve">2.94595909118652</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">2.91842675209045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90269374847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336207389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
+    <t xml:space="preserve">2.9026939868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896548271179</t>
+    <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
@@ -1997,43 +1997,43 @@
     <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66276931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863120079041</t>
+    <t xml:space="preserve">2.66276907920837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863143920898</t>
   </si>
   <si>
     <t xml:space="preserve">2.74536633491516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76109910011292</t>
+    <t xml:space="preserve">2.76109886169434</t>
   </si>
   <si>
     <t xml:space="preserve">2.67456912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
+    <t xml:space="preserve">2.63523697853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
     <t xml:space="preserve">2.62737059593201</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58803868293762</t>
+    <t xml:space="preserve">2.58803844451904</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6981680393219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74143290519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72963333129883</t>
+    <t xml:space="preserve">2.69816780090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74143314361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72963380813599</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
@@ -2042,28 +2042,28 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63917016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670250892639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65490293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883612632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017230033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58410549163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63130378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64703631401062</t>
+    <t xml:space="preserve">2.63916993141174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6549026966095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017253875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58410573005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63130402565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6470365524292</t>
   </si>
   <si>
     <t xml:space="preserve">2.62343740463257</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983801841736</t>
+    <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52510786056519</t>
+    <t xml:space="preserve">2.75323271751404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52510762214661</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904081344604</t>
@@ -2090,13 +2090,13 @@
     <t xml:space="preserve">2.54084014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330780982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150847434998</t>
+    <t xml:space="preserve">2.48970866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330804824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
@@ -2105,25 +2105,25 @@
     <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48577618598938</t>
+    <t xml:space="preserve">2.4857759475708</t>
   </si>
   <si>
     <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52117466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4936420917511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47790956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40317869186401</t>
+    <t xml:space="preserve">2.52117419242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49364185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47790932655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40317893028259</t>
   </si>
   <si>
     <t xml:space="preserve">2.38351273536682</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39924550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564635276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39137935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35598039627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39531254768372</t>
+    <t xml:space="preserve">2.399245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3913791179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35598063468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39531230926514</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698252677917</t>
@@ -2153,52 +2153,52 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340247631073</t>
+    <t xml:space="preserve">2.34024786949158</t>
   </si>
   <si>
     <t xml:space="preserve">2.33631467819214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36384677886963</t>
+    <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
     <t xml:space="preserve">2.57230591773987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61557126045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356676101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503252983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71783375740051</t>
+    <t xml:space="preserve">2.61557102203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356652259827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75716614723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503205299377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71783351898193</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69030141830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7060341835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70210123062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89482760429382</t>
+    <t xml:space="preserve">2.69030165672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70603466033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70210099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89482736587524</t>
   </si>
   <si>
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594286441803</t>
+    <t xml:space="preserve">2.85942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02068948745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96169185638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96562457084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83976268768311</t>
+    <t xml:space="preserve">3.0206892490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9616916179657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96562480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009673118591</t>
+    <t xml:space="preserve">2.82009696960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.8515625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302755355835</t>
+    <t xml:space="preserve">2.88302803039551</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809247016907</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">2.90662693977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91056036949158</t>
+    <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
     <t xml:space="preserve">2.89876079559326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95775866508484</t>
+    <t xml:space="preserve">2.95775818824768</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516164779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796335220337</t>
+    <t xml:space="preserve">2.87516140937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796311378479</t>
   </si>
   <si>
     <t xml:space="preserve">2.86729502677917</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">2.93022584915161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00495672225952</t>
+    <t xml:space="preserve">3.00495648384094</t>
   </si>
   <si>
     <t xml:space="preserve">3.01675653457642</t>
@@ -2279,49 +2279,49 @@
     <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04035568237305</t>
+    <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349095344543</t>
+    <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98529100418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575416564941</t>
+    <t xml:space="preserve">2.98529076576233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575440406799</t>
   </si>
   <si>
     <t xml:space="preserve">3.05215525627136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02855587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002140045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542012214661</t>
+    <t xml:space="preserve">3.02855563163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002163887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09542036056519</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148716926575</t>
+    <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.1032862663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
@@ -2336,37 +2336,37 @@
     <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2102906703949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10382676124573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06287932395935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07925820350647</t>
+    <t xml:space="preserve">3.21029043197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10382652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06287908554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08744740486145</t>
+    <t xml:space="preserve">3.08744764328003</t>
   </si>
   <si>
     <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05059456825256</t>
+    <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
     <t xml:space="preserve">3.07106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01374220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012108802795</t>
+    <t xml:space="preserve">3.01374197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012084960938</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
@@ -2378,34 +2378,34 @@
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831076622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602624893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04649996757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08335304260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07516360282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507857322693</t>
+    <t xml:space="preserve">3.03831052780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602601051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468964576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04650020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08335280418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0751633644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96460485458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93594145774841</t>
+    <t xml:space="preserve">2.96460461616516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93594169616699</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
@@ -2417,19 +2417,19 @@
     <t xml:space="preserve">2.89908862113953</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137290000916</t>
+    <t xml:space="preserve">2.91137313842773</t>
   </si>
   <si>
     <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89089918136597</t>
+    <t xml:space="preserve">2.89089941978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.84585690498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87042546272278</t>
+    <t xml:space="preserve">2.87042570114136</t>
   </si>
   <si>
     <t xml:space="preserve">2.91956281661987</t>
@@ -2438,37 +2438,37 @@
     <t xml:space="preserve">2.94003629684448</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223554611206</t>
+    <t xml:space="preserve">2.86223578453064</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624607086182</t>
+    <t xml:space="preserve">2.77624583244324</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86633062362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499402046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88270974159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8786153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452030181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92775225639343</t>
+    <t xml:space="preserve">2.80490946769714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86633086204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499425888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88270950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452006340027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.99736285209656</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">2.98917365074158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02193140983582</t>
+    <t xml:space="preserve">3.02193188667297</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365741729736</t>
+    <t xml:space="preserve">2.92365717887878</t>
   </si>
   <si>
     <t xml:space="preserve">2.96869969367981</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8130989074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719350814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82128834724426</t>
+    <t xml:space="preserve">2.81309866905212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719374656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82128810882568</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">2.84995174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96051001548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9154679775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357262611389</t>
+    <t xml:space="preserve">2.96051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91546773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357286453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8008143901825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66978240013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78034090995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69435095787048</t>
+    <t xml:space="preserve">2.80081462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66978216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78034067153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986695289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6943507194519</t>
   </si>
   <si>
     <t xml:space="preserve">2.64521360397339</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805663108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.76805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.743488073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7271089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95615839958191</t>
+    <t xml:space="preserve">2.72710871696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939347267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95615863800049</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897128105164</t>
+    <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600372314453</t>
+    <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
@@ -2633,70 +2633,70 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881684303284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86163020133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90459752082825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90889430046082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132108688354</t>
+    <t xml:space="preserve">2.87881708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86162996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90459775924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90889406204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968322753906</t>
+    <t xml:space="preserve">2.65968346595764</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405698776245</t>
+    <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952902793884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5479679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5350775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57804489135742</t>
+    <t xml:space="preserve">2.59952878952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54796767234802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53507781028748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.578045129776</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47922015190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929713249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359415054321</t>
+    <t xml:space="preserve">2.47921991348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929737091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359391212463</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195557594299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4878134727478</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48781371116638</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735015869141</t>
+    <t xml:space="preserve">2.30735039710999</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602117538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867961883545</t>
+    <t xml:space="preserve">2.34602093696594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867985725403</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39758205413818</t>
+    <t xml:space="preserve">2.3975818157196</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469171524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625259399414</t>
+    <t xml:space="preserve">2.38469195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625283241272</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33742737770081</t>
+    <t xml:space="preserve">2.33742761611938</t>
   </si>
   <si>
     <t xml:space="preserve">2.28156995773315</t>
@@ -2771,19 +2771,19 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118386268616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0624361038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829352378845</t>
+    <t xml:space="preserve">2.13118410110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06243634223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829376220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1225905418396</t>
+    <t xml:space="preserve">2.12259030342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985464096069</t>
+    <t xml:space="preserve">2.16985487937927</t>
   </si>
   <si>
     <t xml:space="preserve">2.14407420158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399698257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08392000198364</t>
+    <t xml:space="preserve">2.11399722099304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197302818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212746620178</t>
+    <t xml:space="preserve">1.88197290897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212734699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85619246959686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81322503089905</t>
+    <t xml:space="preserve">1.85619258880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744459152222</t>
+    <t xml:space="preserve">1.78744447231293</t>
   </si>
   <si>
     <t xml:space="preserve">1.71869671344757</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6241682767868</t>
+    <t xml:space="preserve">1.62416839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92494022846222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84330236911774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96790778636932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353378772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650134563446</t>
+    <t xml:space="preserve">1.9249404668808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84330224990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96790766716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353366851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650110721588</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,22 +2873,22 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04954600334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9593141078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0796229839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08821678161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524922370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102942466736</t>
+    <t xml:space="preserve">2.0495457649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95931422710419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07962322235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08821654319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524946212769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102966308594</t>
   </si>
   <si>
     <t xml:space="preserve">2.17844820022583</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126108169556</t>
+    <t xml:space="preserve">2.16126132011414</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">2.2128221988678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19563508033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837098121643</t>
+    <t xml:space="preserve">2.1956353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681010246277</t>
+    <t xml:space="preserve">2.06673288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681034088135</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000884056091</t>
+    <t xml:space="preserve">2.23000907897949</t>
   </si>
   <si>
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024073600769</t>
+    <t xml:space="preserve">2.32024049758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594371795654</t>
+    <t xml:space="preserve">2.31594395637512</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438283920288</t>
+    <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313059806824</t>
+    <t xml:space="preserve">2.33313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750483512878</t>
+    <t xml:space="preserve">2.36750507354736</t>
   </si>
   <si>
     <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149273872375</t>
+    <t xml:space="preserve">2.25149250030518</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2428994178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39328527450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41047239303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062635421753</t>
+    <t xml:space="preserve">2.27297639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24289917945862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39328503608704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41047215461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062659263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -3876,6 +3876,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.29500007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27999997138977</t>
   </si>
 </sst>
 </file>
@@ -69682,7 +69685,7 @@
     </row>
     <row r="2519">
       <c r="A2519" s="1" t="n">
-        <v>45986.6911458333</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2519" t="n">
         <v>57184</v>
@@ -69703,6 +69706,32 @@
         <v>1273</v>
       </c>
       <c r="H2519" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>45987.6910763889</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>72581</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>3.21499991416931</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2520" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H2520" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27862012386322</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
@@ -47,184 +47,184 @@
     <t xml:space="preserve">1.27977395057678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26823401451111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26938807964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25554025173187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24861621856689</t>
+    <t xml:space="preserve">1.2682341337204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26938819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25554013252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.2751579284668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977004528046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437885284424</t>
+    <t xml:space="preserve">1.24977028369904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246026039124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
   </si>
   <si>
     <t xml:space="preserve">1.19784080982208</t>
   </si>
   <si>
-    <t xml:space="preserve">1.15975904464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283879756927</t>
+    <t xml:space="preserve">1.15975916385651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283903598785</t>
   </si>
   <si>
     <t xml:space="preserve">1.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25438618659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285027503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746593952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2636182308197</t>
+    <t xml:space="preserve">1.25438630580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746239185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285015583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746605873108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26361811161041</t>
   </si>
   <si>
     <t xml:space="preserve">1.20591855049133</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21168851852417</t>
+    <t xml:space="preserve">1.21168863773346</t>
   </si>
   <si>
     <t xml:space="preserve">1.21053469181061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.19207072257996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20822668075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899842262268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476850986481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707628250122</t>
+    <t xml:space="preserve">1.19207096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2082267999649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23130667209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899854183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2370765209198</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669798374176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900587558746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28208196163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28439009189606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27169620990753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28323590755463</t>
+    <t xml:space="preserve">1.28669786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900575637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28208184242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438985347748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27169609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28323602676392</t>
   </si>
   <si>
     <t xml:space="preserve">1.30054581165314</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30862367153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093192100525</t>
+    <t xml:space="preserve">1.30862379074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093168258667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247149944305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31208574771881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30746972560883</t>
+    <t xml:space="preserve">1.32247161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31208550930023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30746960639954</t>
   </si>
   <si>
     <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516183376312</t>
+    <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
     <t xml:space="preserve">1.32016372680664</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32362568378448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708752155304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32824170589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132133960724</t>
+    <t xml:space="preserve">1.32362544536591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708764076233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323981285095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32824158668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132122039795</t>
   </si>
   <si>
     <t xml:space="preserve">1.34439742565155</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34670543670654</t>
+    <t xml:space="preserve">1.34670531749725</t>
   </si>
   <si>
     <t xml:space="preserve">1.35016751289368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3547830581665</t>
+    <t xml:space="preserve">1.35478353500366</t>
   </si>
   <si>
     <t xml:space="preserve">1.36170721054077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34208941459656</t>
+    <t xml:space="preserve">1.34208953380585</t>
   </si>
   <si>
     <t xml:space="preserve">1.34324336051941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3455513715744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36516928672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324726581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017106056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786328792572</t>
+    <t xml:space="preserve">1.34555149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36516916751862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
     <t xml:space="preserve">1.36747705936432</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39497971534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251494407654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39621198177338</t>
+    <t xml:space="preserve">1.39497983455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251530170441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39621186256409</t>
   </si>
   <si>
     <t xml:space="preserve">1.41099989414215</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">1.42332291603088</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43687856197357</t>
+    <t xml:space="preserve">1.43687844276428</t>
   </si>
   <si>
     <t xml:space="preserve">1.44427239894867</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44550478458405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45043396949768</t>
+    <t xml:space="preserve">1.44550454616547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45043408870697</t>
   </si>
   <si>
     <t xml:space="preserve">1.45536315441132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4627571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4911003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863565921783</t>
+    <t xml:space="preserve">1.46275699138641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49110043048859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863542079926</t>
   </si>
   <si>
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5182112455368</t>
+    <t xml:space="preserve">1.51821100711823</t>
   </si>
   <si>
     <t xml:space="preserve">1.54162514209747</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">1.51574659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49849414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039263725281</t>
+    <t xml:space="preserve">1.4984940290451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039299488068</t>
   </si>
   <si>
     <t xml:space="preserve">1.60817003250122</t>
@@ -302,175 +302,175 @@
     <t xml:space="preserve">1.61433148384094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59707939624786</t>
+    <t xml:space="preserve">1.59707927703857</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437257766724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958502292633</t>
+    <t xml:space="preserve">1.50958478450775</t>
   </si>
   <si>
     <t xml:space="preserve">1.55641293525696</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6007764339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655420780182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362416744232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006899833679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883661270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115975379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71661376953125</t>
+    <t xml:space="preserve">1.60077631473541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54655432701111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6636244058609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006875991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883673191071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992748737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115963459015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71661400794983</t>
   </si>
   <si>
     <t xml:space="preserve">1.72154295444489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72400772571564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68950283527374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827044963837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523999214172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429039001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059359073639</t>
+    <t xml:space="preserve">1.72400760650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68950319290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827068805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7252402305603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429062843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059370994568</t>
   </si>
   <si>
     <t xml:space="preserve">1.70675539970398</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71784627437592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851273536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301750659943</t>
+    <t xml:space="preserve">1.71784615516663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301726818085</t>
   </si>
   <si>
     <t xml:space="preserve">1.75604784488678</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78439104557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206790447235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988615512848</t>
+    <t xml:space="preserve">1.78439080715179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206778526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988603591919</t>
   </si>
   <si>
     <t xml:space="preserve">1.74865400791168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74618947505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837110519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453279495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7622092962265</t>
+    <t xml:space="preserve">1.74618923664093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837086677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453243732452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76220941543579</t>
   </si>
   <si>
     <t xml:space="preserve">1.77699720859528</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76344168186188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746283531189</t>
+    <t xml:space="preserve">1.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
   </si>
   <si>
     <t xml:space="preserve">1.66855359077454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74249255657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443225860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186695098877</t>
+    <t xml:space="preserve">1.74249267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443202018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186718940735</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6303516626358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679649353027</t>
+    <t xml:space="preserve">1.60447323322296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6167961359024</t>
   </si>
   <si>
     <t xml:space="preserve">1.64267492294312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376579761505</t>
+    <t xml:space="preserve">1.65376567840576</t>
   </si>
   <si>
     <t xml:space="preserve">1.62049353122711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309945583344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6155641078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61802852153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021015167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760422706604</t>
+    <t xml:space="preserve">1.63281679153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309933662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61556398868561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61802864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021027088165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760410785675</t>
   </si>
   <si>
     <t xml:space="preserve">1.65130114555359</t>
@@ -479,193 +479,193 @@
     <t xml:space="preserve">1.65623033046722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513945579529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404893875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091794490814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479734897614</t>
+    <t xml:space="preserve">1.61926114559174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513957500458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144253730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091770648956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356496334076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479711055756</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972641468048</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48247420787811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887758731842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503903865814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423118591309</t>
+    <t xml:space="preserve">1.48247396945953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884530544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503891944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423094749451</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726176261902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451420783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532194137573</t>
+    <t xml:space="preserve">1.51451408863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
     <t xml:space="preserve">1.57120072841644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58598828315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.581059217453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60200846195221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338223934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722078800201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63651323318481</t>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105909824371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200834274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5933825969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722066879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63651311397552</t>
   </si>
   <si>
     <t xml:space="preserve">1.66485643386841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65499794483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594766616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225027084351</t>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
   </si>
   <si>
     <t xml:space="preserve">1.67841196060181</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073522090912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717945575714</t>
+    <t xml:space="preserve">1.69073510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6771799325943</t>
   </si>
   <si>
     <t xml:space="preserve">1.68703818321228</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70552289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538150310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7129168510437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457365036011</t>
+    <t xml:space="preserve">1.70552265644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291673183441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457353115082</t>
   </si>
   <si>
     <t xml:space="preserve">1.76467418670654</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75727999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74126029014587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016905784607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77330029010773</t>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126017093658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016929626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77330040931702</t>
   </si>
   <si>
     <t xml:space="preserve">1.77946174144745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74742150306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78069424629211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590621471405</t>
+    <t xml:space="preserve">1.74742162227631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7806943655014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79178488254547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590633392334</t>
   </si>
   <si>
     <t xml:space="preserve">1.81766355037689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81150197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614826202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297653198242</t>
+    <t xml:space="preserve">1.81150186061859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86695611476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297617435455</t>
   </si>
   <si>
     <t xml:space="preserve">1.8989964723587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90762269496918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392553806305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94459199905396</t>
+    <t xml:space="preserve">1.9076224565506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392541885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94459176063538</t>
   </si>
   <si>
     <t xml:space="preserve">1.92980408668518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98279368877411</t>
+    <t xml:space="preserve">1.98279345035553</t>
   </si>
   <si>
     <t xml:space="preserve">2.00867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02838921546936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687428474426</t>
+    <t xml:space="preserve">2.02838897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0468738079071</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483368873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01729869842529</t>
+    <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796480178833</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">2.05303549766541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06905579566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.107257604599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09493398666382</t>
+    <t xml:space="preserve">2.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10725736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986352920532</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">2.13806557655334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14669156074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16024684906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16887283325195</t>
+    <t xml:space="preserve">2.14669132232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16024661064148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16887307167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.17257022857666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15655040740967</t>
+    <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
     <t xml:space="preserve">2.18119621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17380213737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010521888733</t>
+    <t xml:space="preserve">2.17380237579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.15531754493713</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18366098403931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17996382713318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21816563606262</t>
+    <t xml:space="preserve">2.18366122245789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17996406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21816515922546</t>
   </si>
   <si>
     <t xml:space="preserve">2.20953941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2132363319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23172116279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27978110313416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717541694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33030652999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877180099487</t>
+    <t xml:space="preserve">2.21323609352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23172092437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27978157997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3303062915802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877227783203</t>
   </si>
   <si>
     <t xml:space="preserve">2.34583282470703</t>
@@ -758,46 +758,46 @@
     <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31477952003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
+    <t xml:space="preserve">2.31477928161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526022911072</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137877464294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29019522666931</t>
+    <t xml:space="preserve">2.29019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313420295715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31866145133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33677577972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100865364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782932281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3548903465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806967735291</t>
+    <t xml:space="preserve">2.23973345756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313467979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3186616897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3367760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100889205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782956123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35489058494568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453940391541</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653542518616</t>
+    <t xml:space="preserve">2.36653518676758</t>
   </si>
   <si>
     <t xml:space="preserve">2.34065747261047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32901263237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842133522034</t>
+    <t xml:space="preserve">2.32901215553284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.34971475601196</t>
@@ -824,91 +824,91 @@
     <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642436027527</t>
+    <t xml:space="preserve">2.40535259246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
     <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537129402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396656990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2449095249176</t>
+    <t xml:space="preserve">2.29537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666495323181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26043581962585</t>
+    <t xml:space="preserve">2.26043629646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.25784826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26172995567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690530776978</t>
+    <t xml:space="preserve">2.2617301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690554618835</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361538887024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2060923576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19703531265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21903109550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23197031021118</t>
+    <t xml:space="preserve">2.20609211921692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19703483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21903133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2319700717926</t>
   </si>
   <si>
     <t xml:space="preserve">2.24102759361267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3225429058075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31736707687378</t>
+    <t xml:space="preserve">2.32254314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31736755371094</t>
   </si>
   <si>
     <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31348562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407739639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725648880005</t>
+    <t xml:space="preserve">2.31348586082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407715797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
     <t xml:space="preserve">2.27855062484741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26431798934937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28890180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24879121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
+    <t xml:space="preserve">2.26431751251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28890156745911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879097938538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278373718262</t>
   </si>
   <si>
     <t xml:space="preserve">2.37041711807251</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">2.33548212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35747838020325</t>
+    <t xml:space="preserve">2.35747790336609</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631377220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819944381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160042762756</t>
+    <t xml:space="preserve">2.28631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337455749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819920539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160018920898</t>
   </si>
   <si>
     <t xml:space="preserve">2.30960392951965</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30572247505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35359644889832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37171101570129</t>
+    <t xml:space="preserve">2.30572199821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35359668731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37171077728271</t>
   </si>
   <si>
     <t xml:space="preserve">2.40664625167847</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">2.46745920181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44675707817078</t>
+    <t xml:space="preserve">2.44675731658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546270370483</t>
@@ -968,25 +968,25 @@
     <t xml:space="preserve">2.47651672363281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38723802566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241361618042</t>
+    <t xml:space="preserve">2.38723754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36524128913879</t>
+    <t xml:space="preserve">2.36524176597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.40793991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370703697205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37688660621643</t>
+    <t xml:space="preserve">2.3937075138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37688684463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.3626537322998</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">2.31607341766357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36459445953369</t>
+    <t xml:space="preserve">2.36459469795227</t>
   </si>
   <si>
     <t xml:space="preserve">2.38076829910278</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">2.37429881095886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
+    <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435563087463</t>
+    <t xml:space="preserve">2.13492774963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435539245605</t>
   </si>
   <si>
     <t xml:space="preserve">2.10258078575134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07346773147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03788566589355</t>
+    <t xml:space="preserve">2.07346796989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
     <t xml:space="preserve">2.0896418094635</t>
@@ -1034,49 +1034,49 @@
     <t xml:space="preserve">2.07993745803833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11551952362061</t>
+    <t xml:space="preserve">2.11551976203918</t>
   </si>
   <si>
     <t xml:space="preserve">2.12198925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699872016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05082488059998</t>
+    <t xml:space="preserve">2.06699824333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05082511901855</t>
   </si>
   <si>
     <t xml:space="preserve">2.02818179130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01847767829895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966074943542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0152428150177</t>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966063022614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01524257659912</t>
   </si>
   <si>
     <t xml:space="preserve">2.02494716644287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04759001731873</t>
+    <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640694618225</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04112076759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07023358345032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12522387504578</t>
+    <t xml:space="preserve">2.0411205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07023334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07670283317566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12522411346436</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">2.06052899360657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06376361846924</t>
+    <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.09934592247009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905027389526</t>
+    <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">2.11875438690186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12845826148987</t>
+    <t xml:space="preserve">2.12845873832703</t>
   </si>
   <si>
     <t xml:space="preserve">2.15110182762146</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.15433645248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962310791016</t>
+    <t xml:space="preserve">2.19962334632874</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">2.26755237579346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28460144996643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25050330162048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958471298218</t>
+    <t xml:space="preserve">2.28460121154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25050282478333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958495140076</t>
   </si>
   <si>
     <t xml:space="preserve">2.18230628967285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.223224401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433862686157</t>
+    <t xml:space="preserve">2.22322392463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866636276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456797599792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433838844299</t>
   </si>
   <si>
     <t xml:space="preserve">2.11751866340637</t>
@@ -1157,19 +1157,19 @@
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066582202911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01181364059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05614185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04591202735901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227233886719</t>
+    <t xml:space="preserve">1.96066534519196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01181316375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05614161491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04591155052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">2.03909206390381</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0425021648407</t>
+    <t xml:space="preserve">2.04250168800354</t>
   </si>
   <si>
     <t xml:space="preserve">1.99135410785675</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06978106498718</t>
+    <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522302627563</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">1.98794424533844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97089517116547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748507022858</t>
+    <t xml:space="preserve">1.97089540958405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748542785645</t>
   </si>
   <si>
     <t xml:space="preserve">1.9538459777832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9572559595108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9777147769928</t>
+    <t xml:space="preserve">1.95725548267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771513462067</t>
   </si>
   <si>
     <t xml:space="preserve">1.95043587684631</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">1.94361650943756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14138793945312</t>
+    <t xml:space="preserve">2.14138770103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.185715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417574882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801107406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663450241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004412651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2164044380188</t>
+    <t xml:space="preserve">2.18571591377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004364967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
     <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13797807693481</t>
+    <t xml:space="preserve">2.13797783851624</t>
   </si>
   <si>
     <t xml:space="preserve">2.11410903930664</t>
@@ -1274,28 +1274,28 @@
     <t xml:space="preserve">2.10387945175171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1209282875061</t>
+    <t xml:space="preserve">2.12092852592468</t>
   </si>
   <si>
     <t xml:space="preserve">2.13115835189819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1584370136261</t>
+    <t xml:space="preserve">2.15843725204468</t>
   </si>
   <si>
     <t xml:space="preserve">2.15502762794495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15161752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16184687614441</t>
+    <t xml:space="preserve">2.15161728858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16184711456299</t>
   </si>
   <si>
     <t xml:space="preserve">2.06637096405029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00499367713928</t>
+    <t xml:space="preserve">2.00499415397644</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863288879395</t>
@@ -1304,16 +1304,16 @@
     <t xml:space="preserve">2.05955147743225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92315721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98112440109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453462123871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660031318665</t>
+    <t xml:space="preserve">1.92315697669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112463951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453450202942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07660055160522</t>
   </si>
   <si>
     <t xml:space="preserve">2.09364986419678</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027371406555</t>
+    <t xml:space="preserve">2.24027347564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.19594550132751</t>
@@ -1337,19 +1337,19 @@
     <t xml:space="preserve">2.17207622528076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18912553787231</t>
+    <t xml:space="preserve">2.18912577629089</t>
   </si>
   <si>
     <t xml:space="preserve">2.1925356388092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23345375061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23686385154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25391316413879</t>
+    <t xml:space="preserve">2.23345351219177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23686361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25391292572021</t>
   </si>
   <si>
     <t xml:space="preserve">2.25732278823853</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483127593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
+    <t xml:space="preserve">2.29483103752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
   </si>
   <si>
     <t xml:space="preserve">2.3084704875946</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">2.32211017608643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32552003860474</t>
+    <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
     <t xml:space="preserve">2.34256911277771</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">2.3732578754425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3971266746521</t>
+    <t xml:space="preserve">2.39712691307068</t>
   </si>
   <si>
     <t xml:space="preserve">2.38689732551575</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.37666773796082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42099595069885</t>
+    <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804478645325</t>
@@ -1421,43 +1421,43 @@
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122553825378</t>
+    <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827461242676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942255020142</t>
+    <t xml:space="preserve">2.46191382408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942207336426</t>
   </si>
   <si>
     <t xml:space="preserve">2.51306200027466</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47896289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52670097351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54034042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171818733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59830832481384</t>
+    <t xml:space="preserve">2.48919272422791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47896361351013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52670121192932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54034066200256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171794891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59830784797668</t>
   </si>
   <si>
     <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6153576374054</t>
+    <t xml:space="preserve">2.61535739898682</t>
   </si>
   <si>
     <t xml:space="preserve">2.88855242729187</t>
@@ -1469,19 +1469,19 @@
     <t xml:space="preserve">2.61167073249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56677079200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58547878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55928778648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63037896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71269536018372</t>
+    <t xml:space="preserve">2.56677103042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58547925949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55928754806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63037919998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71269512176514</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153692245483</t>
@@ -1490,46 +1490,46 @@
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657067298889</t>
+    <t xml:space="preserve">2.65657043457031</t>
   </si>
   <si>
     <t xml:space="preserve">2.64908719062805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66405367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66031193733215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71643733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766184806824</t>
+    <t xml:space="preserve">2.64160370826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66405391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66031241416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71643710136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766160964966</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772887229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70521187782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72017812728882</t>
+    <t xml:space="preserve">2.70521211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72017884254456</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262857437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85861921310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79126977920532</t>
+    <t xml:space="preserve">2.74262809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85861945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79126954078674</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">2.83616971969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8137195110321</t>
+    <t xml:space="preserve">2.81371974945068</t>
   </si>
   <si>
     <t xml:space="preserve">2.806236743927</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">2.82868623733521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82494497299194</t>
+    <t xml:space="preserve">2.82494473457336</t>
   </si>
   <si>
     <t xml:space="preserve">2.86984467506409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96338605880737</t>
+    <t xml:space="preserve">2.96338534355164</t>
   </si>
   <si>
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977788925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331903457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">2.89977765083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719434738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331879615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576924324036</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821873664856</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">3.09060168266296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10182690620422</t>
+    <t xml:space="preserve">3.10182666778564</t>
   </si>
   <si>
     <t xml:space="preserve">3.10556840896606</t>
@@ -1586,19 +1586,19 @@
     <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15046811103821</t>
+    <t xml:space="preserve">3.15046834945679</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169309616089</t>
+    <t xml:space="preserve">3.16169285774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801814079285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06066870689392</t>
+    <t xml:space="preserve">3.06066846847534</t>
   </si>
   <si>
     <t xml:space="preserve">3.07937669754028</t>
@@ -1610,70 +1610,70 @@
     <t xml:space="preserve">3.09434342384338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04570198059082</t>
+    <t xml:space="preserve">3.0457022190094</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706053733826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98583555221558</t>
+    <t xml:space="preserve">2.98583579063416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9746105670929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91100287437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91474437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0681517124176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01951050758362</t>
+    <t xml:space="preserve">2.91100263595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91474413871765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07189345359802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06815195083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01951026916504</t>
   </si>
   <si>
     <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90351963043213</t>
+    <t xml:space="preserve">2.90351939201355</t>
   </si>
   <si>
     <t xml:space="preserve">2.97835230827332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98209357261658</t>
+    <t xml:space="preserve">2.98209381103516</t>
   </si>
   <si>
     <t xml:space="preserve">2.94467759132385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94841933250427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086930274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95964407920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84739446640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7501118183136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80249500274658</t>
+    <t xml:space="preserve">2.94841909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086906433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95964384078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84739470481873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75011157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
     <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85113644599915</t>
+    <t xml:space="preserve">2.85113596916199</t>
   </si>
   <si>
     <t xml:space="preserve">2.84365296363831</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">2.86610293388367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848611831665</t>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
@@ -1694,28 +1694,28 @@
     <t xml:space="preserve">2.92596936225891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229440689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79875302314758</t>
+    <t xml:space="preserve">2.90726113319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229464530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79875326156616</t>
   </si>
   <si>
     <t xml:space="preserve">2.78004479408264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76881980895996</t>
+    <t xml:space="preserve">2.76882028579712</t>
   </si>
   <si>
     <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106918334961</t>
+    <t xml:space="preserve">2.7613365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">3.0307354927063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95590233802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
   </si>
   <si>
     <t xml:space="preserve">2.88481116294861</t>
@@ -1739,49 +1739,49 @@
     <t xml:space="preserve">2.78378653526306</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81746125221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85487818717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98957705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761742591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619232177734</t>
+    <t xml:space="preserve">2.8174614906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85487794876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989577293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619208335876</t>
   </si>
   <si>
     <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41986703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36374187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360830307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980025291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3562593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26645922660828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24026775360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2814257144928</t>
+    <t xml:space="preserve">3.41986680030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3637421131134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360854148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2664589881897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2402675151825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530102729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28142595291138</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">3.29639267921448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924336433411</t>
+    <t xml:space="preserve">3.13924360275269</t>
   </si>
   <si>
     <t xml:space="preserve">3.11305165290833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06441020965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679315567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
+    <t xml:space="preserve">3.06440997123718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679339408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08685994148254</t>
   </si>
   <si>
     <t xml:space="preserve">3.04944348335266</t>
@@ -1817,40 +1817,40 @@
     <t xml:space="preserve">2.03545665740967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25621438026428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33853030204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37968873977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091348648071</t>
+    <t xml:space="preserve">2.25621461868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33853054046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37968850135803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091324806213</t>
   </si>
   <si>
     <t xml:space="preserve">2.43581318855286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942135810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48445439338684</t>
+    <t xml:space="preserve">2.49942111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51438784599304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4657461643219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4283299446106</t>
+    <t xml:space="preserve">2.46574664115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42833018302917</t>
   </si>
   <si>
     <t xml:space="preserve">2.40213847160339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51812958717346</t>
+    <t xml:space="preserve">2.51812934875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.38343000411987</t>
@@ -1859,46 +1859,46 @@
     <t xml:space="preserve">2.39465522766113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35723853111267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39839649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41710472106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42458820343018</t>
+    <t xml:space="preserve">2.35723876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39839673042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41710495948792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42458844184875</t>
   </si>
   <si>
     <t xml:space="preserve">2.41336345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43207144737244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40962195396423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45452165603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4694881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5218710899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49193787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935481071472</t>
+    <t xml:space="preserve">2.43207168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40962147712708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4545214176178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46948790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52187085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49193811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935457229614</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316309928894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50690460205078</t>
+    <t xml:space="preserve">2.5069043636322</t>
   </si>
   <si>
     <t xml:space="preserve">2.59670448303223</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">2.7875280380249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795159339905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29265093803406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27768397331238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34714388847351</t>
+    <t xml:space="preserve">3.15795135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29265069961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27768445014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
@@ -1925,28 +1925,28 @@
     <t xml:space="preserve">3.10721969604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00102376937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709057807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06788802146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09935355186462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04822206497192</t>
+    <t xml:space="preserve">3.00102353096008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709010124207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06788778305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09935331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04822182655334</t>
   </si>
   <si>
     <t xml:space="preserve">3.07968735694885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12295269966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0718207359314</t>
+    <t xml:space="preserve">3.12295246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07182097434998</t>
   </si>
   <si>
     <t xml:space="preserve">2.96955823898315</t>
@@ -1961,19 +1961,19 @@
     <t xml:space="preserve">2.94989228248596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742438316345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595909118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91842675209045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9026939868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86336183547974</t>
+    <t xml:space="preserve">2.97742462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595885276794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91842699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90269374847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
     <t xml:space="preserve">2.8082971572876</t>
@@ -1982,85 +1982,85 @@
     <t xml:space="preserve">2.78076505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79649758338928</t>
+    <t xml:space="preserve">2.79649782180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.78469800949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76896524429321</t>
+    <t xml:space="preserve">2.76896548271179</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73749995231628</t>
+    <t xml:space="preserve">2.73750019073486</t>
   </si>
   <si>
     <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78863143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109886169434</t>
+    <t xml:space="preserve">2.78863120079041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109910011292</t>
   </si>
   <si>
     <t xml:space="preserve">2.67456912994385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523697853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803844451904</t>
+    <t xml:space="preserve">2.6352367401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58803868293762</t>
   </si>
   <si>
     <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69816780090332</t>
+    <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
     <t xml:space="preserve">2.74143314361572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72963380813599</t>
+    <t xml:space="preserve">2.72963356971741</t>
   </si>
   <si>
     <t xml:space="preserve">2.686368227005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68243527412415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63916993141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66670227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6549026966095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58017253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58410573005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63130402565002</t>
+    <t xml:space="preserve">2.68243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63917016983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66670250892639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65490317344666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883612632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58017230033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58410549163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63130378723145</t>
   </si>
   <si>
     <t xml:space="preserve">2.6470365524292</t>
@@ -2072,13 +2072,13 @@
     <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59983825683594</t>
+    <t xml:space="preserve">2.59983849525452</t>
   </si>
   <si>
     <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75323271751404</t>
+    <t xml:space="preserve">2.75323247909546</t>
   </si>
   <si>
     <t xml:space="preserve">2.52510762214661</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">2.52904081344604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54084014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48970866203308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330804824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150871276855</t>
+    <t xml:space="preserve">2.54084038734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48970913887024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330780982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5015082359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
@@ -2105,25 +2105,25 @@
     <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4857759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50937485694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52117419242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49364185333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610999107361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47790932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40317893028259</t>
+    <t xml:space="preserve">2.48577618598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50937461853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49364233016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610975265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47790956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40317869186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.38351273536682</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.399245262146</t>
+    <t xml:space="preserve">2.39924550056458</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564659118652</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">2.3913791179657</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35598063468933</t>
+    <t xml:space="preserve">2.35598015785217</t>
   </si>
   <si>
     <t xml:space="preserve">2.39531230926514</t>
@@ -2153,43 +2153,43 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34024786949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631467819214</t>
+    <t xml:space="preserve">2.340247631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230591773987</t>
+    <t xml:space="preserve">2.57230567932129</t>
   </si>
   <si>
     <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73356652259827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75716614723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76503205299377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71783351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390080451965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69030165672302</t>
+    <t xml:space="preserve">2.73356676101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7571656703949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76503229141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71783375740051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69030141830444</t>
   </si>
   <si>
     <t xml:space="preserve">2.70603466033936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210099220276</t>
+    <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85942840576172</t>
+    <t xml:space="preserve">2.85942888259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0206892490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9616916179657</t>
+    <t xml:space="preserve">3.02068948745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
     <t xml:space="preserve">2.96562480926514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83976292610168</t>
+    <t xml:space="preserve">2.83976268768311</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189630508423</t>
@@ -2231,28 +2231,28 @@
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88302803039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809247016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90662693977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910560131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775818824768</t>
+    <t xml:space="preserve">2.82009673118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85156226158142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88302755355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809223175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90662717819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91056036949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775842666626</t>
   </si>
   <si>
     <t xml:space="preserve">2.9538254737854</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">3.01675653457642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02462267875671</t>
+    <t xml:space="preserve">3.02462291717529</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98922395706177</t>
+    <t xml:space="preserve">2.98922371864319</t>
   </si>
   <si>
     <t xml:space="preserve">2.98529076576233</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">3.07575440406799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05215525627136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855563163757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002163887024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09542036056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04428863525391</t>
+    <t xml:space="preserve">3.05215501785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002140045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09542012214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04428839683533</t>
   </si>
   <si>
     <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12688541412354</t>
+    <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
     <t xml:space="preserve">3.1032862663269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20948266983032</t>
+    <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
@@ -2339,16 +2339,16 @@
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382652282715</t>
+    <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12839508056641</t>
+    <t xml:space="preserve">3.07925820350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12839484214783</t>
   </si>
   <si>
     <t xml:space="preserve">3.08744764328003</t>
@@ -2366,37 +2366,37 @@
     <t xml:space="preserve">3.01374197006226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03012084960938</t>
+    <t xml:space="preserve">3.03012108802795</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01783680915833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0055525302887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03831052780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02602601051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05468964576721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04650020599365</t>
+    <t xml:space="preserve">3.01783657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00555276870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03831076622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02602624893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05468940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04649996757507</t>
   </si>
   <si>
     <t xml:space="preserve">3.08335280418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0751633644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507881164551</t>
+    <t xml:space="preserve">3.07516360282898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507857322693</t>
   </si>
   <si>
     <t xml:space="preserve">2.99326825141907</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">2.96460461616516</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93594169616699</t>
+    <t xml:space="preserve">2.93594145774841</t>
   </si>
   <si>
     <t xml:space="preserve">2.94822573661804</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89089941978455</t>
+    <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.84585690498352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87042570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91956281661987</t>
+    <t xml:space="preserve">2.8704252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
     <t xml:space="preserve">2.94003629684448</t>
@@ -2444,40 +2444,40 @@
     <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624583244324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78853034973145</t>
+    <t xml:space="preserve">2.77624607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78853011131287</t>
   </si>
   <si>
     <t xml:space="preserve">2.80490946769714</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86633086204529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499425888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88270950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87861490249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452006340027</t>
+    <t xml:space="preserve">2.86633062362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499402046204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88270974159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87861514091492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452030181885</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775201797485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736285209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98917365074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193188667297</t>
+    <t xml:space="preserve">2.99736309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">2.95232057571411</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92365717887878</t>
+    <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
     <t xml:space="preserve">2.96869969367981</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93184661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680458068848</t>
+    <t xml:space="preserve">2.93184685707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680481910706</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309866905212</t>
+    <t xml:space="preserve">2.8130989074707</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719374656677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82128810882568</t>
+    <t xml:space="preserve">2.82128834724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
+    <t xml:space="preserve">2.84995198249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.96051025390625</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">2.91546773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357286453247</t>
+    <t xml:space="preserve">2.83357238769531</t>
   </si>
   <si>
     <t xml:space="preserve">2.78443574905396</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176206588745</t>
+    <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2549,19 +2549,19 @@
     <t xml:space="preserve">2.83766746520996</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80081462860107</t>
+    <t xml:space="preserve">2.8008143901825</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978216171265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034067153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986695289612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6943507194519</t>
+    <t xml:space="preserve">2.78034090995789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69435095787048</t>
   </si>
   <si>
     <t xml:space="preserve">2.64521360397339</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">2.67387723922729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76805686950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.743488073349</t>
+    <t xml:space="preserve">2.76805663108826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74348783493042</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939347267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95615863800049</t>
+    <t xml:space="preserve">2.7271089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95615839958191</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.96904850006104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93897151947021</t>
+    <t xml:space="preserve">2.93897128105164</t>
   </si>
   <si>
     <t xml:space="preserve">2.89170718193054</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600396156311</t>
+    <t xml:space="preserve">2.89600372314453</t>
   </si>
   <si>
     <t xml:space="preserve">2.84873986244202</t>
@@ -2633,70 +2633,70 @@
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86162996292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90459775924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90889406204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74132132530212</t>
+    <t xml:space="preserve">2.87881684303284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86163020133972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90459752082825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90889430046082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74132108688354</t>
   </si>
   <si>
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968346595764</t>
+    <t xml:space="preserve">2.65968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69405722618103</t>
+    <t xml:space="preserve">2.69405698776245</t>
   </si>
   <si>
     <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59952878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54796767234802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53507781028748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.578045129776</t>
+    <t xml:space="preserve">2.59952902793884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5479679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5350775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">2.5952320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47921991348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50929737091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51359391212463</t>
+    <t xml:space="preserve">2.47922015190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50929713249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914269447327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48781371116638</t>
+    <t xml:space="preserve">2.44914293289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195557594299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4878134727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.49211025238037</t>
@@ -2714,16 +2714,16 @@
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735039710999</t>
+    <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602093696594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26867985725403</t>
+    <t xml:space="preserve">2.34602117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26867961883545</t>
   </si>
   <si>
     <t xml:space="preserve">2.25578951835632</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3975818157196</t>
+    <t xml:space="preserve">2.39758205413818</t>
   </si>
   <si>
     <t xml:space="preserve">2.35031771659851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469195365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625283241272</t>
+    <t xml:space="preserve">2.38469171524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
     <t xml:space="preserve">2.37180137634277</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33742761611938</t>
+    <t xml:space="preserve">2.33742737770081</t>
   </si>
   <si>
     <t xml:space="preserve">2.28156995773315</t>
@@ -2771,19 +2771,19 @@
     <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13118410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06243634223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11829376220703</t>
+    <t xml:space="preserve">2.13118386268616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0624361038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11829352378845</t>
   </si>
   <si>
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12259030342102</t>
+    <t xml:space="preserve">2.1225905418396</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985487937927</t>
+    <t xml:space="preserve">2.16985464096069</t>
   </si>
   <si>
     <t xml:space="preserve">2.14407420158386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11399722099304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08391976356506</t>
+    <t xml:space="preserve">2.11399698257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08392000198364</t>
   </si>
   <si>
     <t xml:space="preserve">2.02376532554626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88197290897369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212734699249</t>
+    <t xml:space="preserve">1.88197302818298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212746620178</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85619258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81322491168976</t>
+    <t xml:space="preserve">1.85619246959686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81322503089905</t>
   </si>
   <si>
     <t xml:space="preserve">1.83041203022003</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78744447231293</t>
+    <t xml:space="preserve">1.78744459152222</t>
   </si>
   <si>
     <t xml:space="preserve">1.71869671344757</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">1.64307403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62416839599609</t>
+    <t xml:space="preserve">1.6241682767868</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729015350342</t>
+    <t xml:space="preserve">1.72729027271271</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9249404668808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84330224990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96790766716003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353366851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650110721588</t>
+    <t xml:space="preserve">1.92494022846222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84330236911774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96790778636932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353378772736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650134563446</t>
   </si>
   <si>
     <t xml:space="preserve">2.01087522506714</t>
@@ -2873,22 +2873,22 @@
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0495457649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95931422710419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07962322235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08821654319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04524946212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07102966308594</t>
+    <t xml:space="preserve">2.04954600334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9593141078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0796229839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08821678161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04524922370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07102942466736</t>
   </si>
   <si>
     <t xml:space="preserve">2.17844820022583</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.18274474143982</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16126132011414</t>
+    <t xml:space="preserve">2.16126108169556</t>
   </si>
   <si>
     <t xml:space="preserve">2.12688708305359</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">2.2128221988678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1956353187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993162155151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415118217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837074279785</t>
+    <t xml:space="preserve">2.19563508033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993185997009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837098121643</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681034088135</t>
+    <t xml:space="preserve">2.06673264503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
     <t xml:space="preserve">2.10970020294189</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">2.15696430206299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23000907897949</t>
+    <t xml:space="preserve">2.23000884056091</t>
   </si>
   <si>
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024049758911</t>
+    <t xml:space="preserve">2.32024073600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31594395637512</t>
+    <t xml:space="preserve">2.31594371795654</t>
   </si>
   <si>
     <t xml:space="preserve">2.30305361747742</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26438307762146</t>
+    <t xml:space="preserve">2.26438283920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.40617537498474</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">2.37609815597534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33313083648682</t>
+    <t xml:space="preserve">2.33313059806824</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,31 +2987,31 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750507354736</t>
+    <t xml:space="preserve">2.36750483512878</t>
   </si>
   <si>
     <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149250030518</t>
+    <t xml:space="preserve">2.25149273872375</t>
   </si>
   <si>
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24289917945862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39328503608704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41047215461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062659263611</t>
+    <t xml:space="preserve">2.27297616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2428994178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39328527450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41047239303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062635421753</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -69711,7 +69711,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6910763889</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>72581</v>
@@ -69732,6 +69732,32 @@
         <v>1288</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6911342593</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>58163</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>3.31500005722046</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>3.29500007629395</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27862012386322</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27977395057678</t>
+    <t xml:space="preserve">1.27977406978607</t>
   </si>
   <si>
     <t xml:space="preserve">1.26823401451111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26938807964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25554037094116</t>
+    <t xml:space="preserve">1.26938819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25554025173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515780925751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977028369904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246037960052</t>
+    <t xml:space="preserve">1.27515828609467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246049880981</t>
   </si>
   <si>
     <t xml:space="preserve">1.19437873363495</t>
@@ -80,79 +80,79 @@
     <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25784838199615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25438642501831</t>
+    <t xml:space="preserve">1.25784814357758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25438618659973</t>
   </si>
   <si>
     <t xml:space="preserve">1.24746227264404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27285003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746593952179</t>
+    <t xml:space="preserve">1.27285015583038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746605873108</t>
   </si>
   <si>
     <t xml:space="preserve">1.26361811161041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.20591878890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168863773346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21053469181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207084178925</t>
+    <t xml:space="preserve">1.20591866970062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168851852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2105348110199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207072257996</t>
   </si>
   <si>
     <t xml:space="preserve">1.2082267999649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23130655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899854183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707640171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29016005992889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669798374176</t>
+    <t xml:space="preserve">1.23130667209625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899866104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476874828339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2370765209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2901599407196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669810295105</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28208196163177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28438985347748</t>
+    <t xml:space="preserve">1.28208208084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28438997268677</t>
   </si>
   <si>
     <t xml:space="preserve">1.27169620990753</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28323590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30054593086243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862355232239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093180179596</t>
+    <t xml:space="preserve">1.28323602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30054581165314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862367153168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093192100525</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">1.30746972560883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593357563019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30516171455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32016372680664</t>
+    <t xml:space="preserve">1.32593369483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30516195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32016360759735</t>
   </si>
   <si>
     <t xml:space="preserve">1.32362544536591</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">1.31323969364166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824170589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439718723297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35016739368439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478317737579</t>
+    <t xml:space="preserve">1.32824146747589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132145881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670531749725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3501672744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478341579437</t>
   </si>
   <si>
     <t xml:space="preserve">1.36170721054077</t>
@@ -209,34 +209,34 @@
     <t xml:space="preserve">1.34208929538727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34324336051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3455513715744</t>
+    <t xml:space="preserve">1.3432434797287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555125236511</t>
   </si>
   <si>
     <t xml:space="preserve">1.36516916751862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37324726581573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017117977142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786316871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747694015503</t>
+    <t xml:space="preserve">1.37324714660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017106056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786304950714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36747717857361</t>
   </si>
   <si>
     <t xml:space="preserve">1.36286127567291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.394979596138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251530170441</t>
+    <t xml:space="preserve">1.39497983455658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251518249512</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621210098267</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">1.44550454616547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4504337310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536315441132</t>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536327362061</t>
   </si>
   <si>
     <t xml:space="preserve">1.4627571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4911003112793</t>
+    <t xml:space="preserve">1.49110019207001</t>
   </si>
   <si>
     <t xml:space="preserve">1.48863542079926</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">1.50342345237732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51821136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162514209747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50465559959412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574647426605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4984940290451</t>
+    <t xml:space="preserve">1.51821088790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162538051605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5046558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849414825439</t>
   </si>
   <si>
     <t xml:space="preserve">1.54039299488068</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60817003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433184146881</t>
+    <t xml:space="preserve">1.6081702709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707939624786</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">1.52437269687653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50958478450775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55641281604767</t>
+    <t xml:space="preserve">1.50958502292633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55641317367554</t>
   </si>
   <si>
     <t xml:space="preserve">1.60077619552612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5465544462204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190828323364</t>
+    <t xml:space="preserve">1.54655468463898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190816402435</t>
   </si>
   <si>
     <t xml:space="preserve">1.56257438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59584701061249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6636244058609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65006911754608</t>
+    <t xml:space="preserve">1.5958468914032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6500688791275</t>
   </si>
   <si>
     <t xml:space="preserve">1.5946147441864</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">1.64883673191071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65992724895477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115963459015</t>
+    <t xml:space="preserve">1.65992712974548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115987300873</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7215428352356</t>
+    <t xml:space="preserve">1.72154295444489</t>
   </si>
   <si>
     <t xml:space="preserve">1.72400772571564</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">1.68827056884766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72523963451385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756301403046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059370994568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784615516663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301714897156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604796409607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439092636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206814289093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988615512848</t>
+    <t xml:space="preserve">1.72523987293243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756289482117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429039001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059359073639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675528049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784603595734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851237773895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301738739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560476064682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206790447235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988627433777</t>
   </si>
   <si>
     <t xml:space="preserve">1.74865388870239</t>
@@ -404,88 +404,88 @@
     <t xml:space="preserve">1.74618935585022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7683709859848</t>
+    <t xml:space="preserve">1.76837050914764</t>
   </si>
   <si>
     <t xml:space="preserve">1.77453243732452</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7622092962265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7769969701767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7634414434433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6574627161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855347156525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249243736267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69443213939667</t>
+    <t xml:space="preserve">1.76220917701721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746259689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855359077454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249255657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69443202018738</t>
   </si>
   <si>
     <t xml:space="preserve">1.61186695098877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63158404827118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447299480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035178184509</t>
+    <t xml:space="preserve">1.63158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6303516626358</t>
   </si>
   <si>
     <t xml:space="preserve">1.61679637432098</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6426750421524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65376579761505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049317359924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281655311584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309945583344</t>
+    <t xml:space="preserve">1.64267480373383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65376555919647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281643390656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309933662415</t>
   </si>
   <si>
     <t xml:space="preserve">1.61556386947632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61802852153778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64021039009094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64760422706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6513010263443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6562305688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926078796387</t>
+    <t xml:space="preserve">1.61802864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64021015167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64760410785675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65130126476288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65623033046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926102638245</t>
   </si>
   <si>
     <t xml:space="preserve">1.64513969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64144265651703</t>
+    <t xml:space="preserve">1.64144277572632</t>
   </si>
   <si>
     <t xml:space="preserve">1.63404858112335</t>
@@ -494,28 +494,28 @@
     <t xml:space="preserve">1.59091782569885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53546369075775</t>
+    <t xml:space="preserve">1.53546357154846</t>
   </si>
   <si>
     <t xml:space="preserve">1.49356484413147</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49479734897614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49972629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48247396945953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55887746810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58845341205597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56503903865814</t>
+    <t xml:space="preserve">1.49479711055756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49972653388977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48247385025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55887758731842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5884530544281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56503915786743</t>
   </si>
   <si>
     <t xml:space="preserve">1.53423130512238</t>
@@ -527,118 +527,118 @@
     <t xml:space="preserve">1.51451420783997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54532206058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120060920715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598828315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105933666229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6020085811615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59338247776031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58722078800201</t>
+    <t xml:space="preserve">1.54532217979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120072841644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60200846195221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59338223934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722102642059</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6648565530777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499842166901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594742774963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225050926208</t>
+    <t xml:space="preserve">1.66485631465912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499830245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6722503900528</t>
   </si>
   <si>
     <t xml:space="preserve">1.6784120798111</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69073498249054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717969417572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703806400299</t>
+    <t xml:space="preserve">1.69073510169983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978561878204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717957496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6870379447937</t>
   </si>
   <si>
     <t xml:space="preserve">1.70552277565002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291708946228</t>
+    <t xml:space="preserve">1.71538150310516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291697025299</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457353115082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467406749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75728034973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125981330872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73016929626465</t>
+    <t xml:space="preserve">1.76467394828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75727999210358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74125993251801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73016941547394</t>
   </si>
   <si>
     <t xml:space="preserve">1.77330029010773</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77946162223816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74742150306702</t>
+    <t xml:space="preserve">1.77946174144745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7474217414856</t>
   </si>
   <si>
     <t xml:space="preserve">1.78069412708282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178500175476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590669155121</t>
+    <t xml:space="preserve">1.79178512096405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590609550476</t>
   </si>
   <si>
     <t xml:space="preserve">1.81766355037689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81150197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83614814281464</t>
+    <t xml:space="preserve">1.81150209903717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
     <t xml:space="preserve">1.86695599555969</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88297641277313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89899623394012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762257575989</t>
+    <t xml:space="preserve">1.88297617435455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8989964723587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762209892273</t>
   </si>
   <si>
     <t xml:space="preserve">1.90392541885376</t>
@@ -647,52 +647,52 @@
     <t xml:space="preserve">1.94459187984467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980432510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279392719269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00867199897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838945388794</t>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98279345035553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838969230652</t>
   </si>
   <si>
     <t xml:space="preserve">2.04687404632568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01483345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01729822158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05796480178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05303549766541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905579566956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10725736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09493470191956</t>
+    <t xml:space="preserve">2.01483392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01729869842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05796456336975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05303573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905603408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.107257604599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806509971619</t>
+    <t xml:space="preserve">2.13806533813477</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669156074524</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024708747864</t>
+    <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887331008911</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">2.15654993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18119645118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380261421204</t>
+    <t xml:space="preserve">2.18119621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010545730591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531754493713</t>
+    <t xml:space="preserve">2.15531778335571</t>
   </si>
   <si>
     <t xml:space="preserve">2.16640853881836</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996406555176</t>
+    <t xml:space="preserve">2.1799635887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953941345215</t>
+    <t xml:space="preserve">2.20953917503357</t>
   </si>
   <si>
     <t xml:space="preserve">2.2132363319397</t>
@@ -746,82 +746,82 @@
     <t xml:space="preserve">2.28717517852783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33030652999878</t>
+    <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.35877203941345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34583306312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289408683777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477952003479</t>
+    <t xml:space="preserve">2.34583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289384841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477928161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25137877464294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019594192505</t>
+    <t xml:space="preserve">2.25137901306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019546508789</t>
   </si>
   <si>
     <t xml:space="preserve">2.25267267227173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23973369598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30313444137573</t>
+    <t xml:space="preserve">2.23973345756531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
     <t xml:space="preserve">2.31866121292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33677577972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35100889205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36782908439636</t>
+    <t xml:space="preserve">2.3367760181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35100865364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36782956123352</t>
   </si>
   <si>
     <t xml:space="preserve">2.35489058494568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054688453674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806991577148</t>
+    <t xml:space="preserve">2.30054664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806943893433</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453940391541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3613600730896</t>
+    <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
     <t xml:space="preserve">2.36653542518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34065771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901239395142</t>
+    <t xml:space="preserve">2.34065747261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901215553284</t>
   </si>
   <si>
     <t xml:space="preserve">2.34842085838318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34971451759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34324526786804</t>
+    <t xml:space="preserve">2.34971475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34324502944946</t>
   </si>
   <si>
     <t xml:space="preserve">2.4053521156311</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">2.32642459869385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3121919631958</t>
+    <t xml:space="preserve">2.31219172477722</t>
   </si>
   <si>
     <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29666519165039</t>
+    <t xml:space="preserve">2.29666495323181</t>
   </si>
   <si>
     <t xml:space="preserve">2.25396633148193</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">2.2060923576355</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19703531265259</t>
+    <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
     <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2319700717926</t>
+    <t xml:space="preserve">2.23197054862976</t>
   </si>
   <si>
     <t xml:space="preserve">2.24102759361267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3225429058075</t>
+    <t xml:space="preserve">2.32254314422607</t>
   </si>
   <si>
     <t xml:space="preserve">2.31736755371094</t>
@@ -896,64 +896,64 @@
     <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855062484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26431751251221</t>
+    <t xml:space="preserve">2.27855038642883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
     <t xml:space="preserve">2.28890180587769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24879121780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29278349876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37041711807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548188209534</t>
+    <t xml:space="preserve">2.2487907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29278326034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37041759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548164367676</t>
   </si>
   <si>
     <t xml:space="preserve">2.35747790336609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28501987457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27337503433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819944381714</t>
+    <t xml:space="preserve">2.28502011299133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28631353378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2733747959137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819920539856</t>
   </si>
   <si>
     <t xml:space="preserve">2.33160018920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30960416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418822288513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30572199821472</t>
+    <t xml:space="preserve">2.30960369110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418798446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3057222366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171101570129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699719429016</t>
+    <t xml:space="preserve">2.37171077728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664649009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699767112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.46745920181274</t>
@@ -962,19 +962,19 @@
     <t xml:space="preserve">2.44675707817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44546294212341</t>
+    <t xml:space="preserve">2.44546341896057</t>
   </si>
   <si>
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3872377872467</t>
+    <t xml:space="preserve">2.38723802566528</t>
   </si>
   <si>
     <t xml:space="preserve">2.39241361618042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34195137023926</t>
+    <t xml:space="preserve">2.34195160865784</t>
   </si>
   <si>
     <t xml:space="preserve">2.36524152755737</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.3937075138092</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688660621643</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">2.3626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38464999198914</t>
+    <t xml:space="preserve">2.38465023040771</t>
   </si>
   <si>
     <t xml:space="preserve">2.31607341766357</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">2.36459469795227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38076829910278</t>
+    <t xml:space="preserve">2.38076853752136</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753367424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930804252625</t>
+    <t xml:space="preserve">2.37753391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
     <t xml:space="preserve">2.13492822647095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04435563087463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10258078575134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07346820831299</t>
+    <t xml:space="preserve">2.04435539245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10258054733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07346773147583</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08964157104492</t>
+    <t xml:space="preserve">2.0896418094635</t>
   </si>
   <si>
     <t xml:space="preserve">2.07993745803833</t>
@@ -1040,43 +1040,43 @@
     <t xml:space="preserve">2.12198901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699824333191</t>
+    <t xml:space="preserve">2.06699848175049</t>
   </si>
   <si>
     <t xml:space="preserve">2.05082488059998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02818155288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01847743988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966039180756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01524257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494716644287</t>
+    <t xml:space="preserve">2.02818179130554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01847696304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966063022614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0152428150177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494692802429</t>
   </si>
   <si>
     <t xml:space="preserve">2.04759001731873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08640670776367</t>
+    <t xml:space="preserve">2.08640694618225</t>
   </si>
   <si>
     <t xml:space="preserve">2.0411205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07023310661316</t>
+    <t xml:space="preserve">2.07023334503174</t>
   </si>
   <si>
     <t xml:space="preserve">2.07670283317566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12522411346436</t>
+    <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
     <t xml:space="preserve">2.10581541061401</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">2.06376385688782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09934592247009</t>
+    <t xml:space="preserve">2.09934568405151</t>
   </si>
   <si>
     <t xml:space="preserve">2.10905027389526</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875414848328</t>
+    <t xml:space="preserve">2.11875438690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15433645248413</t>
+    <t xml:space="preserve">2.15110182762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15433669090271</t>
   </si>
   <si>
     <t xml:space="preserve">2.19962310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28372597694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26755237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28460144996643</t>
+    <t xml:space="preserve">2.28372621536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26755285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28460168838501</t>
   </si>
   <si>
     <t xml:space="preserve">2.2505030632019</t>
@@ -1130,34 +1130,34 @@
     <t xml:space="preserve">2.18230581283569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.223224401474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16866660118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1345682144165</t>
+    <t xml:space="preserve">2.22322416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16866683959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13456797599792</t>
   </si>
   <si>
     <t xml:space="preserve">2.12433838844299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11751890182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1004695892334</t>
+    <t xml:space="preserve">2.11751866340637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
     <t xml:space="preserve">2.08342027664185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04932165145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96066534519196</t>
+    <t xml:space="preserve">2.04932188987732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96066582202911</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
@@ -1169,82 +1169,82 @@
     <t xml:space="preserve">2.04591178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03227233886719</t>
+    <t xml:space="preserve">2.03227257728577</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001041412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08682990074158</t>
+    <t xml:space="preserve">2.08001065254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08683013916016</t>
   </si>
   <si>
     <t xml:space="preserve">2.02886271476746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03909206390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04250192642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99135422706604</t>
+    <t xml:space="preserve">2.03909230232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0425021648407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
     <t xml:space="preserve">2.09024000167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06978058815002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01522278785706</t>
+    <t xml:space="preserve">2.06978106498718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
     <t xml:space="preserve">1.99817407131195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98794424533844</t>
+    <t xml:space="preserve">1.98794448375702</t>
   </si>
   <si>
     <t xml:space="preserve">1.97089517116547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96748507022858</t>
+    <t xml:space="preserve">1.96748530864716</t>
   </si>
   <si>
     <t xml:space="preserve">1.95384573936462</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95725572109222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97771465778351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95043575763702</t>
+    <t xml:space="preserve">1.95725548267365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97771489620209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9504359960556</t>
   </si>
   <si>
     <t xml:space="preserve">1.94361639022827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14138746261597</t>
+    <t xml:space="preserve">2.14138770103455</t>
   </si>
   <si>
     <t xml:space="preserve">2.14820742607117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18571615219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41417622566223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28801155090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22663426399231</t>
+    <t xml:space="preserve">2.18571591377258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41417574882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28801131248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22663450241089</t>
   </si>
   <si>
     <t xml:space="preserve">2.23004388809204</t>
@@ -1253,28 +1253,28 @@
     <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17889595031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13797783851624</t>
+    <t xml:space="preserve">2.17889642715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13797807693481</t>
   </si>
   <si>
     <t xml:space="preserve">2.11410880088806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06296110153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12774848937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09705972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10387945175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1209282875061</t>
+    <t xml:space="preserve">2.0629608631134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1277482509613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09705996513367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10387921333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092876434326</t>
   </si>
   <si>
     <t xml:space="preserve">2.13115835189819</t>
@@ -1286,49 +1286,49 @@
     <t xml:space="preserve">2.15502738952637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1516170501709</t>
+    <t xml:space="preserve">2.15161752700806</t>
   </si>
   <si>
     <t xml:space="preserve">2.16184687614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06637096405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00499367713928</t>
+    <t xml:space="preserve">2.06637120246887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0049934387207</t>
   </si>
   <si>
     <t xml:space="preserve">2.01863312721252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05955123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315697669983</t>
+    <t xml:space="preserve">2.05955147743225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315721511841</t>
   </si>
   <si>
     <t xml:space="preserve">1.9811247587204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.984534740448</t>
+    <t xml:space="preserve">1.98453450202942</t>
   </si>
   <si>
     <t xml:space="preserve">2.07660055160522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0936496257782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07319092750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05273175239563</t>
+    <t xml:space="preserve">2.09364986419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07319068908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05273151397705</t>
   </si>
   <si>
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027371406555</t>
+    <t xml:space="preserve">2.24027347564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.19594550132751</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">2.25732278823853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30506086349487</t>
+    <t xml:space="preserve">2.30506110191345</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">2.29483127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30847024917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35961866378784</t>
+    <t xml:space="preserve">2.31529021263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165076255798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30847072601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35961842536926</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233976364136</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">2.32551980018616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34256958961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35279846191406</t>
+    <t xml:space="preserve">2.34256911277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35279870033264</t>
   </si>
   <si>
     <t xml:space="preserve">2.3732578754425</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">2.37666749954224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42099595069885</t>
+    <t xml:space="preserve">2.42099571228027</t>
   </si>
   <si>
     <t xml:space="preserve">2.43804502487183</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">2.43463516235352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43122553825378</t>
+    <t xml:space="preserve">2.43122529983521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44827461242676</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">2.49942207336426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51306200027466</t>
+    <t xml:space="preserve">2.5130615234375</t>
   </si>
   <si>
     <t xml:space="preserve">2.48919296264648</t>
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve">2.59830808639526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62558722496033</t>
+    <t xml:space="preserve">2.62558698654175</t>
   </si>
   <si>
     <t xml:space="preserve">2.6153576374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88855242729187</t>
+    <t xml:space="preserve">2.88855290412903</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541223526001</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">2.56677103042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58547902107239</t>
+    <t xml:space="preserve">2.58547925949097</t>
   </si>
   <si>
     <t xml:space="preserve">2.55928778648376</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">2.6939868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65657067298889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64908742904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64160370826721</t>
+    <t xml:space="preserve">2.65657043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64908695220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64160394668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
@@ -1505,16 +1505,16 @@
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643710136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766184806824</t>
+    <t xml:space="preserve">2.71643733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766208648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.69772863388062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70521187782288</t>
+    <t xml:space="preserve">2.70521211624146</t>
   </si>
   <si>
     <t xml:space="preserve">2.7201783657074</t>
@@ -1529,13 +1529,13 @@
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7912700176239</t>
+    <t xml:space="preserve">2.79127025604248</t>
   </si>
   <si>
     <t xml:space="preserve">2.82120299339294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83616995811462</t>
+    <t xml:space="preserve">2.83616948127747</t>
   </si>
   <si>
     <t xml:space="preserve">2.81371974945068</t>
@@ -1544,10 +1544,10 @@
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868623733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82494473457336</t>
+    <t xml:space="preserve">2.82868599891663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82494497299194</t>
   </si>
   <si>
     <t xml:space="preserve">2.86984467506409</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">2.92971086502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89977788925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93719410896301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331903457642</t>
+    <t xml:space="preserve">2.89977765083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93719387054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331879615784</t>
   </si>
   <si>
     <t xml:space="preserve">3.0157687664032</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">3.10182690620422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10556840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12053513526917</t>
+    <t xml:space="preserve">3.10556864738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12053489685059</t>
   </si>
   <si>
     <t xml:space="preserve">3.15046834945679</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169285774231</t>
+    <t xml:space="preserve">3.16169333457947</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801814079285</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">3.06066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07937669754028</t>
+    <t xml:space="preserve">3.0793764591217</t>
   </si>
   <si>
     <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0943431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0457022190094</t>
+    <t xml:space="preserve">3.09434342384338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
     <t xml:space="preserve">2.99706053733826</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">3.0718936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06815195083618</t>
+    <t xml:space="preserve">3.06815147399902</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951050758362</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90351939201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835206985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209404945374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086906433105</t>
+    <t xml:space="preserve">2.90351963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835254669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209357261658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467759132385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841933250427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086882591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964407920837</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">2.84739470481873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7501118183136</t>
+    <t xml:space="preserve">2.75011157989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991146087646</t>
+    <t xml:space="preserve">2.83991122245789</t>
   </si>
   <si>
     <t xml:space="preserve">2.85113620758057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84365272521973</t>
+    <t xml:space="preserve">2.84365296363831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86236119270325</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">2.86610269546509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91848587989807</t>
+    <t xml:space="preserve">2.91848611831665</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">2.92596912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90726089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89229464530945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79875302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004479408264</t>
+    <t xml:space="preserve">2.90726065635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89229440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79875326156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004503250122</t>
   </si>
   <si>
     <t xml:space="preserve">2.76882004737854</t>
@@ -1712,28 +1712,28 @@
     <t xml:space="preserve">2.80997824668884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76133680343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88106966018677</t>
+    <t xml:space="preserve">2.76133704185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88106942176819</t>
   </si>
   <si>
     <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0307354927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95590233802795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712708473206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88481092453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87358617782593</t>
+    <t xml:space="preserve">3.03073573112488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95590257644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712732315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88481116294861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87358593940735</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1745,31 +1745,31 @@
     <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98957705497742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3076171875</t>
+    <t xml:space="preserve">2.98957753181458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761766433716</t>
   </si>
   <si>
     <t xml:space="preserve">3.38619184494019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632541656494</t>
+    <t xml:space="preserve">3.3263258934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.41986680030823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36374187469482</t>
+    <t xml:space="preserve">3.3637421131134</t>
   </si>
   <si>
     <t xml:space="preserve">3.42360854148865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44980025291443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3562593460083</t>
+    <t xml:space="preserve">3.44980049133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625886917114</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">3.22530102729797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2814257144928</t>
+    <t xml:space="preserve">3.28142619132996</t>
   </si>
   <si>
     <t xml:space="preserve">3.32258415222168</t>
@@ -1790,19 +1790,19 @@
     <t xml:space="preserve">3.2963924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13924336433411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11305141448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06440997123718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94093608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679291725159</t>
+    <t xml:space="preserve">3.13924312591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11305165290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06441020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94093585014343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679363250732</t>
   </si>
   <si>
     <t xml:space="preserve">3.08686017990112</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">3.04944348335266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57425403594971</t>
+    <t xml:space="preserve">2.57425427436829</t>
   </si>
   <si>
     <t xml:space="preserve">2.03545689582825</t>
@@ -1823,25 +1823,25 @@
     <t xml:space="preserve">2.33853054046631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37968850135803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39091324806213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581318855286</t>
+    <t xml:space="preserve">2.37968873977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39091372489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581342697144</t>
   </si>
   <si>
     <t xml:space="preserve">2.49942135810852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48445463180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51438760757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46574664115906</t>
+    <t xml:space="preserve">2.484454870224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51438784599304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46574640274048</t>
   </si>
   <si>
     <t xml:space="preserve">2.42832970619202</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839696884155</t>
+    <t xml:space="preserve">2.39839673042297</t>
   </si>
   <si>
     <t xml:space="preserve">2.41710495948792</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">2.42458844184875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4133632183075</t>
+    <t xml:space="preserve">2.41336345672607</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">2.5218710899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49193787574768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52935457229614</t>
+    <t xml:space="preserve">2.4919376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
     <t xml:space="preserve">2.50316286087036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5069043636322</t>
+    <t xml:space="preserve">2.50690460205078</t>
   </si>
   <si>
     <t xml:space="preserve">2.59670400619507</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">2.78752827644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15795135498047</t>
+    <t xml:space="preserve">3.15795111656189</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27768445014954</t>
+    <t xml:space="preserve">3.27768421173096</t>
   </si>
   <si>
     <t xml:space="preserve">3.34714436531067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17801713943481</t>
+    <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
     <t xml:space="preserve">3.10721969604492</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">3.00102353096008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99709033966064</t>
+    <t xml:space="preserve">2.99709010124207</t>
   </si>
   <si>
     <t xml:space="preserve">3.06788778305054</t>
@@ -1937,7 +1937,7 @@
     <t xml:space="preserve">3.09935331344604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04822206497192</t>
+    <t xml:space="preserve">3.04822182655334</t>
   </si>
   <si>
     <t xml:space="preserve">3.07968735694885</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">3.07182121276855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96955800056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92235970497131</t>
+    <t xml:space="preserve">2.96955847740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92235994338989</t>
   </si>
   <si>
     <t xml:space="preserve">2.94202566146851</t>
@@ -1961,34 +1961,34 @@
     <t xml:space="preserve">2.94989204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97742438316345</t>
+    <t xml:space="preserve">2.97742462158203</t>
   </si>
   <si>
     <t xml:space="preserve">2.94595885276794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91842675209045</t>
+    <t xml:space="preserve">2.91842651367188</t>
   </si>
   <si>
     <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86336207389832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80829739570618</t>
+    <t xml:space="preserve">2.86336183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8082971572876</t>
   </si>
   <si>
     <t xml:space="preserve">2.78076505661011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79649782180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78469824790955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76896548271179</t>
+    <t xml:space="preserve">2.79649758338928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78469800949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76896524429321</t>
   </si>
   <si>
     <t xml:space="preserve">2.77289867401123</t>
@@ -1997,34 +1997,34 @@
     <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66276907920837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78863120079041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74536633491516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76109910011292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67456912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6352367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950397491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62737059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58803844451904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60770463943481</t>
+    <t xml:space="preserve">2.66276931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74536609649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76109886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67456889152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63523721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950421333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62737035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5880389213562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60770440101624</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
@@ -2042,22 +2042,22 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63917016983032</t>
+    <t xml:space="preserve">2.63916993141174</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65490293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65883612632751</t>
+    <t xml:space="preserve">2.6549026966095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65883636474609</t>
   </si>
   <si>
     <t xml:space="preserve">2.58017230033875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58410573005676</t>
+    <t xml:space="preserve">2.58410549163818</t>
   </si>
   <si>
     <t xml:space="preserve">2.63130378723145</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">2.6470365524292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62343716621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5959050655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59983801841736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65096950531006</t>
+    <t xml:space="preserve">2.62343740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59590530395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59983825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65096974372864</t>
   </si>
   <si>
     <t xml:space="preserve">2.75323247909546</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">2.48970890045166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51330780982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50150847434998</t>
+    <t xml:space="preserve">2.51330828666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50150871276855</t>
   </si>
   <si>
     <t xml:space="preserve">2.50544142723083</t>
@@ -2105,37 +2105,37 @@
     <t xml:space="preserve">2.47397613525391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48577618598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50937485694885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52117466926575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4936420917511</t>
+    <t xml:space="preserve">2.4857759475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50937509536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52117443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49364233016968</t>
   </si>
   <si>
     <t xml:space="preserve">2.46610975265503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47790932655334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40317893028259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38351273536682</t>
+    <t xml:space="preserve">2.47790956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40317869186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3835129737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.45431017875671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39924550056458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37564635276794</t>
+    <t xml:space="preserve">2.39924573898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37564659118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.39137935638428</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531254768372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29698252677917</t>
+    <t xml:space="preserve">2.39531230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29698276519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.31271553039551</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">2.33631443977356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36384677886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57230591773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557126045227</t>
+    <t xml:space="preserve">2.36384701728821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57230567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557102203369</t>
   </si>
   <si>
     <t xml:space="preserve">2.73356676101685</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">2.75716590881348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76503252983093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71783375740051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71390056610107</t>
+    <t xml:space="preserve">2.76503229141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71783399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71390080451965</t>
   </si>
   <si>
     <t xml:space="preserve">2.69030165672302</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.7060341835022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70210146903992</t>
+    <t xml:space="preserve">2.70210123062134</t>
   </si>
   <si>
     <t xml:space="preserve">2.89482736587524</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8594286441803</t>
+    <t xml:space="preserve">2.85942888259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.88696122169495</t>
@@ -2213,43 +2213,43 @@
     <t xml:space="preserve">2.92629289627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02068948745728</t>
+    <t xml:space="preserve">3.0206892490387</t>
   </si>
   <si>
     <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562480926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83976292610168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83189630508423</t>
+    <t xml:space="preserve">2.96562457084656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83976268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83189606666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.84762907028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82009673118591</t>
+    <t xml:space="preserve">2.82009696960449</t>
   </si>
   <si>
     <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302755355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809247016907</t>
+    <t xml:space="preserve">2.88302779197693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809270858765</t>
   </si>
   <si>
     <t xml:space="preserve">2.90662670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91056036949158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89876079559326</t>
+    <t xml:space="preserve">2.910560131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8987603187561</t>
   </si>
   <si>
     <t xml:space="preserve">2.95775842666626</t>
@@ -2258,13 +2258,13 @@
     <t xml:space="preserve">2.9538254737854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87516164779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82796359062195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.87516140937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82796311378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86729526519775</t>
   </si>
   <si>
     <t xml:space="preserve">2.93022608757019</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675653457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462267875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04035568237305</t>
+    <t xml:space="preserve">3.01675629615784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462291717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04035544395447</t>
   </si>
   <si>
     <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349119186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98922371864319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98529100418091</t>
+    <t xml:space="preserve">2.97349095344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98922395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98529076576233</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575416564941</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">3.05215501785278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02855610847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06002140045166</t>
+    <t xml:space="preserve">3.02855563163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06002163887024</t>
   </si>
   <si>
     <t xml:space="preserve">3.09541988372803</t>
@@ -2315,37 +2315,37 @@
     <t xml:space="preserve">3.09148716926575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12688541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10328650474548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948266983032</t>
+    <t xml:space="preserve">3.12688565254211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1032862663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948243141174</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19374966621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15441823005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981623649597</t>
+    <t xml:space="preserve">3.19374990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15441799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981671333313</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382676124573</t>
+    <t xml:space="preserve">3.10382652282715</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925796508789</t>
+    <t xml:space="preserve">3.07925820350647</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2354,16 +2354,16 @@
     <t xml:space="preserve">3.08744764328003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06697368621826</t>
+    <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
     <t xml:space="preserve">3.05059480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07106852531433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374197006226</t>
+    <t xml:space="preserve">3.07106828689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374220848083</t>
   </si>
   <si>
     <t xml:space="preserve">3.03012108802795</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">3.03421568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01783680915833</t>
+    <t xml:space="preserve">3.01783657073975</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">3.03831076622009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02602601051331</t>
+    <t xml:space="preserve">3.02602624893188</t>
   </si>
   <si>
     <t xml:space="preserve">3.05468964576721</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">3.08335304260254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07516360282898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98507857322693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99326825141907</t>
+    <t xml:space="preserve">3.0751633644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98507881164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99326801300049</t>
   </si>
   <si>
     <t xml:space="preserve">2.96460485458374</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">2.89908885955811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91137313842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727829933167</t>
+    <t xml:space="preserve">2.91137290000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727806091309</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">2.87042546272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91956257820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94003629684448</t>
+    <t xml:space="preserve">2.91956281661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9400360584259</t>
   </si>
   <si>
     <t xml:space="preserve">2.86223578453064</t>
@@ -2453,31 +2453,31 @@
     <t xml:space="preserve">2.80490922927856</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86633062362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89499402046204</t>
+    <t xml:space="preserve">2.86633086204529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89499425888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8786153793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87452030181885</t>
+    <t xml:space="preserve">2.87861490249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87452006340027</t>
   </si>
   <si>
     <t xml:space="preserve">2.92775225639343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736285209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98917365074158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193164825439</t>
+    <t xml:space="preserve">2.99736309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989173412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193140983582</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">2.96869945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94413137435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93184661865234</t>
+    <t xml:space="preserve">2.94413113594055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9318470954895</t>
   </si>
   <si>
     <t xml:space="preserve">2.88680458068848</t>
@@ -2504,10 +2504,10 @@
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81309914588928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81719350814819</t>
+    <t xml:space="preserve">2.8130989074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81719374656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.82128834724426</t>
@@ -2516,28 +2516,28 @@
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051001548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91546773910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83357286453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443574905396</t>
+    <t xml:space="preserve">2.84995150566101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91546750068665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83357262611389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443551063538</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77215099334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84176206588745</t>
+    <t xml:space="preserve">2.77215123176575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84176230430603</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2555,16 +2555,16 @@
     <t xml:space="preserve">2.66978240013123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78034090995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75986671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6943507194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521384239197</t>
+    <t xml:space="preserve">2.78034067153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75986695289612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69435095787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521360397339</t>
   </si>
   <si>
     <t xml:space="preserve">2.67387700080872</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">2.76805663108826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74348783493042</t>
+    <t xml:space="preserve">2.74348759651184</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,10 +2582,10 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72710871696472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939323425293</t>
+    <t xml:space="preserve">2.7271089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939299583435</t>
   </si>
   <si>
     <t xml:space="preserve">2.95615839958191</t>
@@ -2603,31 +2603,31 @@
     <t xml:space="preserve">2.89170742034912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85303664207458</t>
+    <t xml:space="preserve">2.85303640365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89600372314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84873986244202</t>
+    <t xml:space="preserve">2.89600396156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84873962402344</t>
   </si>
   <si>
     <t xml:space="preserve">2.82725596427917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80577230453491</t>
+    <t xml:space="preserve">2.80577254295349</t>
   </si>
   <si>
     <t xml:space="preserve">2.79717898368835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82295966148376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81436586380005</t>
+    <t xml:space="preserve">2.82295942306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">2.74132132530212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69835376739502</t>
+    <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
     <t xml:space="preserve">2.65968322753906</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">2.69405722618103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64679312705994</t>
+    <t xml:space="preserve">2.64679288864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.59952878952026</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">2.47921991348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50929713249207</t>
+    <t xml:space="preserve">2.50929737091064</t>
   </si>
   <si>
     <t xml:space="preserve">2.51359391212463</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">2.42336225509644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44914293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43195581436157</t>
+    <t xml:space="preserve">2.44914269447327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43195605278015</t>
   </si>
   <si>
     <t xml:space="preserve">2.48781371116638</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">2.49211025238037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41906595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35891127586365</t>
+    <t xml:space="preserve">2.41906571388245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35891103744507</t>
   </si>
   <si>
     <t xml:space="preserve">2.34172415733337</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">2.30735015869141</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27727341651917</t>
+    <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
     <t xml:space="preserve">2.34602117538452</t>
@@ -2738,25 +2738,25 @@
     <t xml:space="preserve">2.35031795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38469195365906</t>
+    <t xml:space="preserve">2.38469171524048</t>
   </si>
   <si>
     <t xml:space="preserve">2.43625259399414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37180137634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40187859535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883405685425</t>
+    <t xml:space="preserve">2.37180161476135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40187883377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3546142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898825645447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883381843567</t>
   </si>
   <si>
     <t xml:space="preserve">2.33742761611938</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10540342330933</t>
+    <t xml:space="preserve">2.10540366172791</t>
   </si>
   <si>
     <t xml:space="preserve">2.13118410110474</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">1.85619258880615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81322503089905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83041203022003</t>
+    <t xml:space="preserve">1.81322491168976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83041214942932</t>
   </si>
   <si>
     <t xml:space="preserve">1.78744459152222</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6774480342865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64307403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416839599609</t>
+    <t xml:space="preserve">1.67744791507721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64307391643524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416851520538</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72729027271271</t>
+    <t xml:space="preserve">1.72729015350342</t>
   </si>
   <si>
     <t xml:space="preserve">1.79174137115479</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790754795074</t>
+    <t xml:space="preserve">1.96790778636932</t>
   </si>
   <si>
     <t xml:space="preserve">1.93353378772736</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">1.97650122642517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01087522506714</t>
+    <t xml:space="preserve">2.01087498664856</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">2.12688708305359</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13548040390015</t>
+    <t xml:space="preserve">2.13548064231873</t>
   </si>
   <si>
     <t xml:space="preserve">2.18704175949097</t>
@@ -2933,10 +2933,10 @@
     <t xml:space="preserve">2.09681010246277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10970020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133830070496</t>
+    <t xml:space="preserve">2.10969996452332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133806228638</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">2.23860239982605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20422840118408</t>
+    <t xml:space="preserve">2.20422863960266</t>
   </si>
   <si>
     <t xml:space="preserve">2.31594395637512</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26438283920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40617537498474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609815597534</t>
+    <t xml:space="preserve">2.32453751564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26438307762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40617561340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609839439392</t>
   </si>
   <si>
     <t xml:space="preserve">2.33313059806824</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">2.42765927314758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25149273872375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22141575813293</t>
+    <t xml:space="preserve">2.25149250030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
     <t xml:space="preserve">2.27297616004944</t>
@@ -69789,7 +69789,7 @@
     </row>
     <row r="2523">
       <c r="A2523" s="1" t="n">
-        <v>45992.6912731481</v>
+        <v>45992.3333333333</v>
       </c>
       <c r="B2523" t="n">
         <v>53258</v>
@@ -69810,6 +69810,32 @@
         <v>1275</v>
       </c>
       <c r="H2523" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="1" t="n">
+        <v>45993.691099537</v>
+      </c>
+      <c r="B2524" t="n">
+        <v>35198</v>
+      </c>
+      <c r="C2524" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2524" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E2524" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F2524" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H2524" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862012386322</t>
+    <t xml:space="preserve">1.27862000465393</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.27977406978607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26823401451111</t>
+    <t xml:space="preserve">1.2682341337204</t>
   </si>
   <si>
     <t xml:space="preserve">1.26938819885254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25554025173187</t>
+    <t xml:space="preserve">1.25554049015045</t>
   </si>
   <si>
     <t xml:space="preserve">1.24861633777618</t>
@@ -62,85 +62,85 @@
     <t xml:space="preserve">1.27515828609467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.24977016448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23246049880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437873363495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784069061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975904464722</t>
+    <t xml:space="preserve">1.24977040290833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2324606180191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437885284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784080982208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975916385651</t>
   </si>
   <si>
     <t xml:space="preserve">1.18283891677856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.25784814357758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25438618659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746227264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285015583038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27746605873108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26361811161041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20591866970062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.21168851852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2105348110199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19207072257996</t>
+    <t xml:space="preserve">1.25784802436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25438630580902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746239185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27746593952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26361799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20591855049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21168863773346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21053469181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19207084178925</t>
   </si>
   <si>
     <t xml:space="preserve">1.2082267999649</t>
   </si>
   <si>
-    <t xml:space="preserve">1.23130667209625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22899866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476874828339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2370765209198</t>
+    <t xml:space="preserve">1.23130643367767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22899854183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707628250122</t>
   </si>
   <si>
     <t xml:space="preserve">1.2901599407196</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28669810295105</t>
+    <t xml:space="preserve">1.28669786453247</t>
   </si>
   <si>
     <t xml:space="preserve">1.28900587558746</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28208208084106</t>
+    <t xml:space="preserve">1.28208196163177</t>
   </si>
   <si>
     <t xml:space="preserve">1.28438997268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27169620990753</t>
+    <t xml:space="preserve">1.27169585227966</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323602676392</t>
@@ -152,25 +152,25 @@
     <t xml:space="preserve">1.30862367153168</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31093192100525</t>
+    <t xml:space="preserve">1.31093180179596</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32247161865234</t>
+    <t xml:space="preserve">1.32247149944305</t>
   </si>
   <si>
     <t xml:space="preserve">1.31208562850952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30746972560883</t>
+    <t xml:space="preserve">1.30746984481812</t>
   </si>
   <si>
     <t xml:space="preserve">1.32593369483948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30516195297241</t>
+    <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
     <t xml:space="preserve">1.32016360759735</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">1.32362544536591</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32708740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31323969364166</t>
+    <t xml:space="preserve">1.32708764076233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31323957443237</t>
   </si>
   <si>
     <t xml:space="preserve">1.32824146747589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35132145881653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439730644226</t>
+    <t xml:space="preserve">1.35132122039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439742565155</t>
   </si>
   <si>
     <t xml:space="preserve">1.34670531749725</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">1.34208929538727</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3432434797287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34555125236511</t>
+    <t xml:space="preserve">1.34324359893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
     <t xml:space="preserve">1.36516916751862</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">1.37786304950714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36747717857361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36286127567291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39497983455658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39251518249512</t>
+    <t xml:space="preserve">1.36747705936432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36286115646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39497971534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39251506328583</t>
   </si>
   <si>
     <t xml:space="preserve">1.39621210098267</t>
@@ -245,61 +245,61 @@
     <t xml:space="preserve">1.41099989414215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42701983451843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332303524017</t>
+    <t xml:space="preserve">1.42702007293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332291603088</t>
   </si>
   <si>
     <t xml:space="preserve">1.43687844276428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44427239894867</t>
+    <t xml:space="preserve">1.44427251815796</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550454616547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043385028839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536327362061</t>
+    <t xml:space="preserve">1.45043408870697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536315441132</t>
   </si>
   <si>
     <t xml:space="preserve">1.4627571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49110019207001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48863542079926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342345237732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821088790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162538051605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5046558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51574659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849414825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54039299488068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6081702709198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433172225952</t>
+    <t xml:space="preserve">1.4911003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48863554000854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342333316803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821112632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50465571880341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51574683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849390983582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5403927564621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60817015171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433160305023</t>
   </si>
   <si>
     <t xml:space="preserve">1.59707939624786</t>
@@ -311,25 +311,25 @@
     <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55641317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077619552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54655468463898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52190816402435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56257438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5958468914032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362428665161</t>
+    <t xml:space="preserve">1.55641293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077631473541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5465544462204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52190828323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56257450580597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584677219391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362452507019</t>
   </si>
   <si>
     <t xml:space="preserve">1.6500688791275</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">1.5946147441864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64883673191071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992712974548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115987300873</t>
+    <t xml:space="preserve">1.64883649349213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992748737335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115975379944</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154295444489</t>
+    <t xml:space="preserve">1.72154307365417</t>
   </si>
   <si>
     <t xml:space="preserve">1.72400772571564</t>
@@ -362,112 +362,112 @@
     <t xml:space="preserve">1.68827056884766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72523987293243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73756289482117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70429039001465</t>
+    <t xml:space="preserve">1.72523975372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73756301403046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70429062843323</t>
   </si>
   <si>
     <t xml:space="preserve">1.70059359073639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70675528049469</t>
+    <t xml:space="preserve">1.7067551612854</t>
   </si>
   <si>
     <t xml:space="preserve">1.71784603595734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75851237773895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301738739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7560476064682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206790447235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988627433777</t>
+    <t xml:space="preserve">1.75851273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301702976227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75604784488678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439104557037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988615512848</t>
   </si>
   <si>
     <t xml:space="preserve">1.74865388870239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74618935585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837050914764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77453243732452</t>
+    <t xml:space="preserve">1.74618947505951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76837086677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7745326757431</t>
   </si>
   <si>
     <t xml:space="preserve">1.76220917701721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77699720859528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344156265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65746259689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855359077454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74249255657196</t>
+    <t xml:space="preserve">1.77699732780457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344180107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6574627161026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855323314667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
     <t xml:space="preserve">1.69443202018738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61186695098877</t>
+    <t xml:space="preserve">1.61186707019806</t>
   </si>
   <si>
     <t xml:space="preserve">1.63158416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60447335243225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6303516626358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679637432098</t>
+    <t xml:space="preserve">1.60447299480438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63035178184509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679625511169</t>
   </si>
   <si>
     <t xml:space="preserve">1.64267480373383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65376555919647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281643390656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309933662415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61556386947632</t>
+    <t xml:space="preserve">1.65376591682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62049329280853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281619548798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309945583344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6155641078949</t>
   </si>
   <si>
     <t xml:space="preserve">1.61802864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64021015167236</t>
+    <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
     <t xml:space="preserve">1.64760410785675</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">1.65130126476288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65623033046722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926102638245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513969421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64144277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63404858112335</t>
+    <t xml:space="preserve">1.6562305688858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926090717316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513981342316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64144265651703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63404870033264</t>
   </si>
   <si>
     <t xml:space="preserve">1.59091782569885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49356484413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49479711055756</t>
+    <t xml:space="preserve">1.53546369075775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49356472492218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49479734897614</t>
   </si>
   <si>
     <t xml:space="preserve">1.49972653388977</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">1.5884530544281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56503915786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53423130512238</t>
+    <t xml:space="preserve">1.56503903865814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53423118591309</t>
   </si>
   <si>
     <t xml:space="preserve">1.49726188182831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451420783997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532217979431</t>
+    <t xml:space="preserve">1.51451408863068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532206058502</t>
   </si>
   <si>
     <t xml:space="preserve">1.57120072841644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58598852157593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105945587158</t>
+    <t xml:space="preserve">1.58598840236664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58105933666229</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
@@ -545,70 +545,70 @@
     <t xml:space="preserve">1.59338223934174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58722102642059</t>
+    <t xml:space="preserve">1.5872209072113</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66485631465912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499830245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594754695892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6722503900528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6784120798111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69073510169983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978561878204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67717957496643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6870379447937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552277565002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538150310516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291697025299</t>
+    <t xml:space="preserve">1.66485643386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499818325043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594730854034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225086688995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67841219902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69073522090912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978585720062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67717981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703830242157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552265644073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538138389587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71291661262512</t>
   </si>
   <si>
     <t xml:space="preserve">1.68457353115082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76467394828796</t>
+    <t xml:space="preserve">1.76467430591583</t>
   </si>
   <si>
     <t xml:space="preserve">1.75727999210358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74125993251801</t>
+    <t xml:space="preserve">1.74125981330872</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016941547394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77330029010773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77946174144745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7474217414856</t>
+    <t xml:space="preserve">1.77330017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77946186065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74742150306702</t>
   </si>
   <si>
     <t xml:space="preserve">1.78069412708282</t>
@@ -617,64 +617,64 @@
     <t xml:space="preserve">1.79178512096405</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76590609550476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766355037689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150209903717</t>
+    <t xml:space="preserve">1.76590633392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766331195831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150221824646</t>
   </si>
   <si>
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695599555969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297617435455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8989964723587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90762209892273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90392541885376</t>
+    <t xml:space="preserve">1.86695623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297641277313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90762221813202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
     <t xml:space="preserve">1.94459187984467</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92980408668518</t>
+    <t xml:space="preserve">1.9298038482666</t>
   </si>
   <si>
     <t xml:space="preserve">1.98279345035553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00867223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838969230652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687404632568</t>
+    <t xml:space="preserve">2.00867247581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838945388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04687428474426</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483392715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01729869842529</t>
+    <t xml:space="preserve">2.01729846000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.05796456336975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06905603408813</t>
+    <t xml:space="preserve">2.05303549766541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
     <t xml:space="preserve">2.107257604599</t>
@@ -686,46 +686,46 @@
     <t xml:space="preserve">2.09986352920532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13806533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14669156074524</t>
+    <t xml:space="preserve">2.13806509971619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14669132232666</t>
   </si>
   <si>
     <t xml:space="preserve">2.16024684906006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16887331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17256999015808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15654993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18119621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380237579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17010545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15531778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640853881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21446871757507</t>
+    <t xml:space="preserve">2.16887307167053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1725697517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15655016899109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18119645118713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380261421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17010569572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15531730651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640830039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21446895599365</t>
   </si>
   <si>
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1799635887146</t>
+    <t xml:space="preserve">2.17996382713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">2.20953917503357</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2132363319397</t>
+    <t xml:space="preserve">2.21323657035828</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
@@ -743,34 +743,34 @@
     <t xml:space="preserve">2.27978134155273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28717517852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3303062915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35877203941345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33289384841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31477928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2552604675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25137901306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29019546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25267267227173</t>
+    <t xml:space="preserve">2.28717541694641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33030652999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35877180099487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34583306312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33289432525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31477975845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25526070594788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25137853622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29019570350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25267243385315</t>
   </si>
   <si>
     <t xml:space="preserve">2.23973345756531</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31866121292114</t>
+    <t xml:space="preserve">2.31866145133972</t>
   </si>
   <si>
     <t xml:space="preserve">2.3367760181427</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">2.35489058494568</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30054664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33806943893433</t>
+    <t xml:space="preserve">2.30054688453674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33806991577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.34453940391541</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653542518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34065747261047</t>
+    <t xml:space="preserve">2.36653566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065723419189</t>
   </si>
   <si>
     <t xml:space="preserve">2.32901215553284</t>
@@ -821,46 +821,46 @@
     <t xml:space="preserve">2.34971475601196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34324502944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4053521156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31219172477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29537105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29666495323181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25396633148193</t>
+    <t xml:space="preserve">2.34324526786804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40535235404968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32642483711243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31219148635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29537129402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29666519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25396656990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.24490904808044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26949334144592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26043581962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26172971725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24361515045166</t>
+    <t xml:space="preserve">2.26949310302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26043605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784802436829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26172995567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690554618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24361538887024</t>
   </si>
   <si>
     <t xml:space="preserve">2.2060923576355</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21903133392334</t>
+    <t xml:space="preserve">2.21903157234192</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197054862976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24102759361267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254314422607</t>
+    <t xml:space="preserve">2.24102711677551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32254266738892</t>
   </si>
   <si>
     <t xml:space="preserve">2.31736755371094</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">2.32771873474121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31348562240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407739639282</t>
+    <t xml:space="preserve">2.31348609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407715797424</t>
   </si>
   <si>
     <t xml:space="preserve">2.27725672721863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27855038642883</t>
+    <t xml:space="preserve">2.27855086326599</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890180587769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2487907409668</t>
+    <t xml:space="preserve">2.28890204429626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24879097938538</t>
   </si>
   <si>
     <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37041759490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548164367676</t>
+    <t xml:space="preserve">2.37041687965393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548188209534</t>
   </si>
   <si>
     <t xml:space="preserve">2.35747790336609</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631353378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2733747959137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26819920539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33160018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30960369110107</t>
+    <t xml:space="preserve">2.28631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27337503433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26819944381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33160042762756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30960392951965</t>
   </si>
   <si>
     <t xml:space="preserve">2.33418798446655</t>
@@ -947,19 +947,19 @@
     <t xml:space="preserve">2.35359644889832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37171077728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40664649009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41699767112732</t>
+    <t xml:space="preserve">2.37171101570129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40664625167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41699743270874</t>
   </si>
   <si>
     <t xml:space="preserve">2.46745920181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44675707817078</t>
+    <t xml:space="preserve">2.4467568397522</t>
   </si>
   <si>
     <t xml:space="preserve">2.44546341896057</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">2.47651648521423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38723802566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241361618042</t>
+    <t xml:space="preserve">2.38723754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241337776184</t>
   </si>
   <si>
     <t xml:space="preserve">2.34195160865784</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3937075138092</t>
+    <t xml:space="preserve">2.39370727539062</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688660621643</t>
@@ -992,37 +992,37 @@
     <t xml:space="preserve">2.3626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38465023040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31607341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459469795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076853752136</t>
+    <t xml:space="preserve">2.38465046882629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.316073179245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459445953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38076829910278</t>
   </si>
   <si>
     <t xml:space="preserve">2.37429904937744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37753391265869</t>
+    <t xml:space="preserve">2.37753367424011</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13492822647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04435539245605</t>
+    <t xml:space="preserve">2.13492798805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04435563087463</t>
   </si>
   <si>
     <t xml:space="preserve">2.10258054733276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07346773147583</t>
+    <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.03788590431213</t>
@@ -1040,28 +1040,28 @@
     <t xml:space="preserve">2.12198901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699848175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05082488059998</t>
+    <t xml:space="preserve">2.06699872016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0508246421814</t>
   </si>
   <si>
     <t xml:space="preserve">2.02818179130554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01847696304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97966063022614</t>
+    <t xml:space="preserve">2.01847743988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97966027259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.0152428150177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494692802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04759001731873</t>
+    <t xml:space="preserve">2.02494716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0475902557373</t>
   </si>
   <si>
     <t xml:space="preserve">2.08640694618225</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.12522387504578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10581541061401</t>
+    <t xml:space="preserve">2.10581564903259</t>
   </si>
   <si>
     <t xml:space="preserve">2.06052899360657</t>
@@ -1091,73 +1091,73 @@
     <t xml:space="preserve">2.09934568405151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10905027389526</t>
+    <t xml:space="preserve">2.10905003547668</t>
   </si>
   <si>
     <t xml:space="preserve">2.14139747619629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11875438690186</t>
+    <t xml:space="preserve">2.11875486373901</t>
   </si>
   <si>
     <t xml:space="preserve">2.12845849990845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15110182762146</t>
+    <t xml:space="preserve">2.15110158920288</t>
   </si>
   <si>
     <t xml:space="preserve">2.15433669090271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19962310791016</t>
+    <t xml:space="preserve">2.199622631073</t>
   </si>
   <si>
     <t xml:space="preserve">2.28372621536255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26755285263062</t>
+    <t xml:space="preserve">2.26755261421204</t>
   </si>
   <si>
     <t xml:space="preserve">2.28460168838501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2505030632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20958495140076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18230581283569</t>
+    <t xml:space="preserve">2.25050330162048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20958471298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18230605125427</t>
   </si>
   <si>
     <t xml:space="preserve">2.22322416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16866683959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13456797599792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12433838844299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11751866340637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11069917678833</t>
+    <t xml:space="preserve">2.16866660118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1345682144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12433862686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11751890182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11069893836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.10046935081482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08342027664185</t>
+    <t xml:space="preserve">2.08342051506042</t>
   </si>
   <si>
     <t xml:space="preserve">2.04932188987732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96066582202911</t>
+    <t xml:space="preserve">1.96066558361053</t>
   </si>
   <si>
     <t xml:space="preserve">2.0118134021759</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">2.05614161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04591178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03227257728577</t>
+    <t xml:space="preserve">2.04591202735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03227233886719</t>
   </si>
   <si>
     <t xml:space="preserve">2.00840353965759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08001065254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08683013916016</t>
+    <t xml:space="preserve">2.08001041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08682990074158</t>
   </si>
   <si>
     <t xml:space="preserve">2.02886271476746</t>
@@ -1187,34 +1187,34 @@
     <t xml:space="preserve">2.03909230232239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0425021648407</t>
+    <t xml:space="preserve">2.04250192642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.99135434627533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09024000167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06978106498718</t>
+    <t xml:space="preserve">2.09023976325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0697808265686</t>
   </si>
   <si>
     <t xml:space="preserve">2.01522302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99817407131195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98794448375702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97089517116547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96748530864716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95384573936462</t>
+    <t xml:space="preserve">1.99817395210266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98794424533844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97089493274689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96748518943787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9538459777832</t>
   </si>
   <si>
     <t xml:space="preserve">1.95725548267365</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">1.97771489620209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9504359960556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94361639022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14138770103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14820742607117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18571591377258</t>
+    <t xml:space="preserve">1.95043587684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94361627101898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14138793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14820766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18571615219116</t>
   </si>
   <si>
     <t xml:space="preserve">2.41417574882507</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">2.28801131248474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22663450241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23004388809204</t>
+    <t xml:space="preserve">2.22663426399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23004412651062</t>
   </si>
   <si>
     <t xml:space="preserve">2.21640467643738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17889642715454</t>
+    <t xml:space="preserve">2.17889618873596</t>
   </si>
   <si>
     <t xml:space="preserve">2.13797807693481</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">2.11410880088806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0629608631134</t>
+    <t xml:space="preserve">2.06296133995056</t>
   </si>
   <si>
     <t xml:space="preserve">2.1277482509613</t>
@@ -1271,49 +1271,49 @@
     <t xml:space="preserve">2.09705996513367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10387921333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12092876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13115835189819</t>
+    <t xml:space="preserve">2.10387945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12092852592468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13115787506104</t>
   </si>
   <si>
     <t xml:space="preserve">2.1584370136261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15502738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15161752700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16184687614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06637120246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0049934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01863312721252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05955147743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92315721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9811247587204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98453450202942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07660055160522</t>
+    <t xml:space="preserve">2.15502715110779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15161728858948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16184711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06637072563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00499367713928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0186333656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05955171585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92315709590912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98112487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98453426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0766007900238</t>
   </si>
   <si>
     <t xml:space="preserve">2.09364986419678</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">2.21299457550049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24027347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19594550132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17207622528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18912577629089</t>
+    <t xml:space="preserve">2.24027371406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19594526290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17207646369934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18912553787231</t>
   </si>
   <si>
     <t xml:space="preserve">2.19253540039062</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">2.23686361312866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25732278823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30506110191345</t>
+    <t xml:space="preserve">2.25391268730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25732231140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30506086349487</t>
   </si>
   <si>
     <t xml:space="preserve">2.29824090003967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29483127593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31529021263123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30165076255798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30847072601318</t>
+    <t xml:space="preserve">2.29483151435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30165100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30847024917603</t>
   </si>
   <si>
     <t xml:space="preserve">2.35961842536926</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">2.33233976364136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3664379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32892942428589</t>
+    <t xml:space="preserve">2.36643815040588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32892990112305</t>
   </si>
   <si>
     <t xml:space="preserve">2.3391592502594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32211017608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32551980018616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34256911277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35279870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3732578754425</t>
+    <t xml:space="preserve">2.32210969924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32552003860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34256887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35279846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37325763702393</t>
   </si>
   <si>
     <t xml:space="preserve">2.39712691307068</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">2.4619140625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49942207336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5130615234375</t>
+    <t xml:space="preserve">2.49942231178284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51306200027466</t>
   </si>
   <si>
     <t xml:space="preserve">2.48919296264648</t>
@@ -1445,22 +1445,22 @@
     <t xml:space="preserve">2.52670121192932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54034066200256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60171794891357</t>
+    <t xml:space="preserve">2.54034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60171818733215</t>
   </si>
   <si>
     <t xml:space="preserve">2.59830808639526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62558698654175</t>
+    <t xml:space="preserve">2.62558674812317</t>
   </si>
   <si>
     <t xml:space="preserve">2.6153576374054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88855290412903</t>
+    <t xml:space="preserve">2.88855266571045</t>
   </si>
   <si>
     <t xml:space="preserve">2.61541223526001</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">2.63037919998169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71269512176514</t>
+    <t xml:space="preserve">2.71269536018372</t>
   </si>
   <si>
     <t xml:space="preserve">2.67153716087341</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">2.64908695220947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64160394668579</t>
+    <t xml:space="preserve">2.64160418510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.66405367851257</t>
@@ -1505,34 +1505,34 @@
     <t xml:space="preserve">2.66031217575073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71643733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72766208648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69772863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70521211624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7201783657074</t>
+    <t xml:space="preserve">2.71643710136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72766184806824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69772887229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70521187782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72017860412598</t>
   </si>
   <si>
     <t xml:space="preserve">2.73140358924866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262809753418</t>
+    <t xml:space="preserve">2.74262857437134</t>
   </si>
   <si>
     <t xml:space="preserve">2.85861945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79127025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82120299339294</t>
+    <t xml:space="preserve">2.7912700176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82120323181152</t>
   </si>
   <si>
     <t xml:space="preserve">2.83616948127747</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">2.80623650550842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82868599891663</t>
+    <t xml:space="preserve">2.82868647575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.82494497299194</t>
@@ -1562,76 +1562,76 @@
     <t xml:space="preserve">2.89977765083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93719387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99331879615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0157687664032</t>
+    <t xml:space="preserve">2.93719434738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99331903457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01576900482178</t>
   </si>
   <si>
     <t xml:space="preserve">3.03821849822998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09060168266296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10182690620422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10556864738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12053489685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15046834945679</t>
+    <t xml:space="preserve">3.09060192108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10182666778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10556817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12053513526917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15046811103821</t>
   </si>
   <si>
     <t xml:space="preserve">3.18040132522583</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16169333457947</t>
+    <t xml:space="preserve">3.16169285774231</t>
   </si>
   <si>
     <t xml:space="preserve">3.12801814079285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06066870689392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0793764591217</t>
+    <t xml:space="preserve">3.06066846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07937669754028</t>
   </si>
   <si>
     <t xml:space="preserve">3.10931015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09434342384338</t>
+    <t xml:space="preserve">3.09434366226196</t>
   </si>
   <si>
     <t xml:space="preserve">3.04570198059082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99706053733826</t>
+    <t xml:space="preserve">2.99706077575684</t>
   </si>
   <si>
     <t xml:space="preserve">2.98583555221558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9746105670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91100263595581</t>
+    <t xml:space="preserve">2.97461080551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91100287437439</t>
   </si>
   <si>
     <t xml:space="preserve">2.91474437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0718936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06815147399902</t>
+    <t xml:space="preserve">3.07189321517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0681517124176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951050758362</t>
@@ -1640,22 +1640,22 @@
     <t xml:space="preserve">3.00454378128052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90351963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97835254669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98209357261658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94467759132385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94841933250427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97086882591248</t>
+    <t xml:space="preserve">2.90351939201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97835230827332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98209381103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94467735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94841909408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97086930274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.95964407920837</t>
@@ -1670,7 +1670,7 @@
     <t xml:space="preserve">2.802494764328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83991122245789</t>
+    <t xml:space="preserve">2.83991098403931</t>
   </si>
   <si>
     <t xml:space="preserve">2.85113620758057</t>
@@ -1679,40 +1679,40 @@
     <t xml:space="preserve">2.84365296363831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86236119270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86610269546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91848611831665</t>
+    <t xml:space="preserve">2.86236095428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86610293388367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91848587989807</t>
   </si>
   <si>
     <t xml:space="preserve">2.89603590965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92596912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90726065635681</t>
+    <t xml:space="preserve">2.92596936225891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90726113319397</t>
   </si>
   <si>
     <t xml:space="preserve">2.89229440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79875326156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78004503250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76882004737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80997824668884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76133704185486</t>
+    <t xml:space="preserve">2.79875302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78004479408264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76881980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80997800827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76133680343628</t>
   </si>
   <si>
     <t xml:space="preserve">2.88106942176819</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">3.00828552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03073573112488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95590257644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96712732315063</t>
+    <t xml:space="preserve">3.0307354927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95590233802795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96712708473206</t>
   </si>
   <si>
     <t xml:space="preserve">2.88481116294861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87358593940735</t>
+    <t xml:space="preserve">2.87358617782593</t>
   </si>
   <si>
     <t xml:space="preserve">2.78378653526306</t>
@@ -1745,49 +1745,49 @@
     <t xml:space="preserve">2.85487794876099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98957753181458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30761766433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38619184494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3263258934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41986680030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3637421131134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42360854148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44980049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35625886917114</t>
+    <t xml:space="preserve">2.98957681655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30761742591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38619208335876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32632565498352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41986703872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36374187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42360830307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44980001449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35625910758972</t>
   </si>
   <si>
     <t xml:space="preserve">3.2664589881897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402675151825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22530102729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28142619132996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32258415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2963924407959</t>
+    <t xml:space="preserve">3.24026775360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22530126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2814257144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3225839138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29639291763306</t>
   </si>
   <si>
     <t xml:space="preserve">3.13924312591553</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">3.06441020965576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94093585014343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11679363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08686017990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04944348335266</t>
+    <t xml:space="preserve">2.94093608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11679315567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0868604183197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04944324493408</t>
   </si>
   <si>
     <t xml:space="preserve">2.57425427436829</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">2.03545689582825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25621438026428</t>
+    <t xml:space="preserve">2.2562141418457</t>
   </si>
   <si>
     <t xml:space="preserve">2.33853054046631</t>
@@ -1826,16 +1826,16 @@
     <t xml:space="preserve">2.37968873977661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39091372489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43581342697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49942135810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.484454870224</t>
+    <t xml:space="preserve">2.39091324806213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43581318855286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49942111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48445463180542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51438784599304</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">2.35723853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39839673042297</t>
+    <t xml:space="preserve">2.39839696884155</t>
   </si>
   <si>
     <t xml:space="preserve">2.41710495948792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42458844184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41336345672607</t>
+    <t xml:space="preserve">2.42458820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4133632183075</t>
   </si>
   <si>
     <t xml:space="preserve">2.43207168579102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40962171554565</t>
+    <t xml:space="preserve">2.40962195396423</t>
   </si>
   <si>
     <t xml:space="preserve">2.4545214176178</t>
@@ -1889,25 +1889,25 @@
     <t xml:space="preserve">2.5218710899353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4919376373291</t>
+    <t xml:space="preserve">2.49193811416626</t>
   </si>
   <si>
     <t xml:space="preserve">2.52935481071472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50316286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50690460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59670400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78752827644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15795111656189</t>
+    <t xml:space="preserve">2.50316309928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5069043636322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59670424461365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78752851486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15795135498047</t>
   </si>
   <si>
     <t xml:space="preserve">3.29265093803406</t>
@@ -1916,25 +1916,25 @@
     <t xml:space="preserve">3.27768421173096</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34714436531067</t>
+    <t xml:space="preserve">3.34714412689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.17801690101624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10721969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00102353096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99709010124207</t>
+    <t xml:space="preserve">3.1072199344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0010232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99709033966064</t>
   </si>
   <si>
     <t xml:space="preserve">3.06788778305054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09935331344604</t>
+    <t xml:space="preserve">3.09935307502747</t>
   </si>
   <si>
     <t xml:space="preserve">3.04822182655334</t>
@@ -1946,25 +1946,25 @@
     <t xml:space="preserve">3.12295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07182121276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96955847740173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92235994338989</t>
+    <t xml:space="preserve">3.0718207359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96955823898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92235970497131</t>
   </si>
   <si>
     <t xml:space="preserve">2.94202566146851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94989204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97742462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94595885276794</t>
+    <t xml:space="preserve">2.94989228248596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97742414474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94595909118652</t>
   </si>
   <si>
     <t xml:space="preserve">2.91842651367188</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">2.9026939868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86336183547974</t>
+    <t xml:space="preserve">2.86336207389832</t>
   </si>
   <si>
     <t xml:space="preserve">2.8082971572876</t>
@@ -1997,13 +1997,13 @@
     <t xml:space="preserve">2.73749995231628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66276931762695</t>
+    <t xml:space="preserve">2.66276907920837</t>
   </si>
   <si>
     <t xml:space="preserve">2.78863143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74536609649658</t>
+    <t xml:space="preserve">2.74536633491516</t>
   </si>
   <si>
     <t xml:space="preserve">2.76109886169434</t>
@@ -2012,25 +2012,25 @@
     <t xml:space="preserve">2.67456889152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63523721694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61950421333313</t>
+    <t xml:space="preserve">2.63523697853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61950397491455</t>
   </si>
   <si>
     <t xml:space="preserve">2.62737035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5880389213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60770440101624</t>
+    <t xml:space="preserve">2.58803868293762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60770463943481</t>
   </si>
   <si>
     <t xml:space="preserve">2.6981680393219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74143290519714</t>
+    <t xml:space="preserve">2.74143314361572</t>
   </si>
   <si>
     <t xml:space="preserve">2.72963333129883</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">2.68243527412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63916993141174</t>
+    <t xml:space="preserve">2.63917016983032</t>
   </si>
   <si>
     <t xml:space="preserve">2.66670250892639</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">2.62343740463257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59590530395508</t>
+    <t xml:space="preserve">2.5959050655365</t>
   </si>
   <si>
     <t xml:space="preserve">2.59983825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65096974372864</t>
+    <t xml:space="preserve">2.65096950531006</t>
   </si>
   <si>
     <t xml:space="preserve">2.75323247909546</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">2.54084038734436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48970890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51330828666687</t>
+    <t xml:space="preserve">2.48970866203308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51330804824829</t>
   </si>
   <si>
     <t xml:space="preserve">2.50150871276855</t>
@@ -2102,37 +2102,37 @@
     <t xml:space="preserve">2.50544142723083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4857759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50937509536743</t>
+    <t xml:space="preserve">2.47397637367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48577570915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50937485694885</t>
   </si>
   <si>
     <t xml:space="preserve">2.52117443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49364233016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46610975265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47790956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40317869186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3835129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45431017875671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39924573898315</t>
+    <t xml:space="preserve">2.4936420917511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46610999107361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47790932655334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40317893028259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38351273536682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45431041717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.399245262146</t>
   </si>
   <si>
     <t xml:space="preserve">2.37564659118652</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">2.35598039627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39531230926514</t>
+    <t xml:space="preserve">2.39531254768372</t>
   </si>
   <si>
     <t xml:space="preserve">2.29698276519775</t>
@@ -2153,22 +2153,22 @@
     <t xml:space="preserve">2.31271553039551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.340247631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33631443977356</t>
+    <t xml:space="preserve">2.34024786949158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33631467819214</t>
   </si>
   <si>
     <t xml:space="preserve">2.36384701728821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57230567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61557102203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73356676101685</t>
+    <t xml:space="preserve">2.57230591773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61557126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73356652259827</t>
   </si>
   <si>
     <t xml:space="preserve">2.75716590881348</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.76503229141235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71783399581909</t>
+    <t xml:space="preserve">2.71783375740051</t>
   </si>
   <si>
     <t xml:space="preserve">2.71390080451965</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">2.69030165672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7060341835022</t>
+    <t xml:space="preserve">2.70603466033936</t>
   </si>
   <si>
     <t xml:space="preserve">2.70210123062134</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">2.87909460067749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85942888259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88696122169495</t>
+    <t xml:space="preserve">2.8594286441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88696098327637</t>
   </si>
   <si>
     <t xml:space="preserve">2.87122845649719</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">2.91449332237244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92629289627075</t>
+    <t xml:space="preserve">2.92629313468933</t>
   </si>
   <si>
     <t xml:space="preserve">3.0206892490387</t>
@@ -2219,10 +2219,10 @@
     <t xml:space="preserve">2.96169185638428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96562457084656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83976268768311</t>
+    <t xml:space="preserve">2.96562480926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83976292610168</t>
   </si>
   <si>
     <t xml:space="preserve">2.83189606666565</t>
@@ -2237,25 +2237,25 @@
     <t xml:space="preserve">2.85156226158142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88302779197693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93809270858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90662670135498</t>
+    <t xml:space="preserve">2.88302826881409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93809223175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90662717819214</t>
   </si>
   <si>
     <t xml:space="preserve">2.910560131073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8987603187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95775842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9538254737854</t>
+    <t xml:space="preserve">2.89876055717468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95775818824768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95382523536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.87516140937805</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">2.82796311378479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729526519775</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.93022608757019</t>
@@ -2273,10 +2273,10 @@
     <t xml:space="preserve">3.00495672225952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01675629615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02462291717529</t>
+    <t xml:space="preserve">3.01675653457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02462267875671</t>
   </si>
   <si>
     <t xml:space="preserve">3.04035544395447</t>
@@ -2285,43 +2285,43 @@
     <t xml:space="preserve">3.00888991355896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97349095344543</t>
+    <t xml:space="preserve">2.97349119186401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98922395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98529076576233</t>
+    <t xml:space="preserve">2.98529100418091</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05215501785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02855563163757</t>
+    <t xml:space="preserve">3.05215525627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02855587005615</t>
   </si>
   <si>
     <t xml:space="preserve">3.06002163887024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09541988372803</t>
+    <t xml:space="preserve">3.09542012214661</t>
   </si>
   <si>
     <t xml:space="preserve">3.04428863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09148716926575</t>
+    <t xml:space="preserve">3.09148693084717</t>
   </si>
   <si>
     <t xml:space="preserve">3.12688565254211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1032862663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20948243141174</t>
+    <t xml:space="preserve">3.10328650474548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20948266983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.2055492401123</t>
@@ -2330,22 +2330,22 @@
     <t xml:space="preserve">3.19374990463257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15441799163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18981671333313</t>
+    <t xml:space="preserve">3.15441823005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18981647491455</t>
   </si>
   <si>
     <t xml:space="preserve">3.21029043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10382652282715</t>
+    <t xml:space="preserve">3.10382676124573</t>
   </si>
   <si>
     <t xml:space="preserve">3.06287908554077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07925820350647</t>
+    <t xml:space="preserve">3.07925796508789</t>
   </si>
   <si>
     <t xml:space="preserve">3.12839508056641</t>
@@ -2357,28 +2357,28 @@
     <t xml:space="preserve">3.06697392463684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05059480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07106828689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01374220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03012108802795</t>
+    <t xml:space="preserve">3.05059504508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01374197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03012084960938</t>
   </si>
   <si>
     <t xml:space="preserve">3.03421568870544</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01783657073975</t>
+    <t xml:space="preserve">3.01783680915833</t>
   </si>
   <si>
     <t xml:space="preserve">3.0055525302887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03831076622009</t>
+    <t xml:space="preserve">3.03831052780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.02602624893188</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">3.05468964576721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04649996757507</t>
+    <t xml:space="preserve">3.04650020599365</t>
   </si>
   <si>
     <t xml:space="preserve">3.08335304260254</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">2.98507881164551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99326801300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96460485458374</t>
+    <t xml:space="preserve">2.99326825141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96460461616516</t>
   </si>
   <si>
     <t xml:space="preserve">2.93594145774841</t>
@@ -2411,52 +2411,52 @@
     <t xml:space="preserve">2.94822573661804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9031834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89908885955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91137290000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90727806091309</t>
+    <t xml:space="preserve">2.90318369865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89908862113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91137313842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90727829933167</t>
   </si>
   <si>
     <t xml:space="preserve">2.89089918136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84585690498352</t>
+    <t xml:space="preserve">2.84585666656494</t>
   </si>
   <si>
     <t xml:space="preserve">2.87042546272278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91956281661987</t>
+    <t xml:space="preserve">2.91956257820129</t>
   </si>
   <si>
     <t xml:space="preserve">2.9400360584259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86223578453064</t>
+    <t xml:space="preserve">2.86223602294922</t>
   </si>
   <si>
     <t xml:space="preserve">2.85404634475708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77624607086182</t>
+    <t xml:space="preserve">2.77624583244324</t>
   </si>
   <si>
     <t xml:space="preserve">2.78853034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80490922927856</t>
+    <t xml:space="preserve">2.80490946769714</t>
   </si>
   <si>
     <t xml:space="preserve">2.86633086204529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89499425888062</t>
+    <t xml:space="preserve">2.89499402046204</t>
   </si>
   <si>
     <t xml:space="preserve">2.88270974159241</t>
@@ -2471,40 +2471,40 @@
     <t xml:space="preserve">2.92775225639343</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99736309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989173412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02193140983582</t>
+    <t xml:space="preserve">2.99736285209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98917365074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02193164825439</t>
   </si>
   <si>
     <t xml:space="preserve">2.97279453277588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95232057571411</t>
+    <t xml:space="preserve">2.95232081413269</t>
   </si>
   <si>
     <t xml:space="preserve">2.92365741729736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96869945526123</t>
+    <t xml:space="preserve">2.96869969367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.94413113594055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9318470954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88680458068848</t>
+    <t xml:space="preserve">2.93184661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88680481910706</t>
   </si>
   <si>
     <t xml:space="preserve">2.82947778701782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8130989074707</t>
+    <t xml:space="preserve">2.81309866905212</t>
   </si>
   <si>
     <t xml:space="preserve">2.81719374656677</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">2.85814118385315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84995150566101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96051025390625</t>
+    <t xml:space="preserve">2.84995174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96051001548767</t>
   </si>
   <si>
     <t xml:space="preserve">2.91546750068665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83357262611389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78443551063538</t>
+    <t xml:space="preserve">2.83357286453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78443574905396</t>
   </si>
   <si>
     <t xml:space="preserve">2.79671955108643</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.77215123176575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84176230430603</t>
+    <t xml:space="preserve">2.84176206588745</t>
   </si>
   <si>
     <t xml:space="preserve">2.79262518882751</t>
@@ -2546,10 +2546,10 @@
     <t xml:space="preserve">2.80900406837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83766722679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80081462860107</t>
+    <t xml:space="preserve">2.83766746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80081486701965</t>
   </si>
   <si>
     <t xml:space="preserve">2.66978240013123</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">2.75986695289612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69435095787048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64521360397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67387700080872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76805663108826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74348759651184</t>
+    <t xml:space="preserve">2.6943507194519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64521384239197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67387723922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76805686950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.743488073349</t>
   </si>
   <si>
     <t xml:space="preserve">2.70254039764404</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">2.76396179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7271089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939299583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95615839958191</t>
+    <t xml:space="preserve">2.72710871696472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95615863800049</t>
   </si>
   <si>
     <t xml:space="preserve">2.92178463935852</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">2.93897151947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89170742034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85303640365601</t>
+    <t xml:space="preserve">2.89170718193054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85303664207458</t>
   </si>
   <si>
     <t xml:space="preserve">2.83155298233032</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">2.89600396156311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84873962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82725596427917</t>
+    <t xml:space="preserve">2.84873986244202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82725620269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.80577254295349</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">2.82295942306519</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81436610221863</t>
+    <t xml:space="preserve">2.81436586380005</t>
   </si>
   <si>
     <t xml:space="preserve">2.80147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87881684303284</t>
+    <t xml:space="preserve">2.87881708145142</t>
   </si>
   <si>
     <t xml:space="preserve">2.86162996292114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90459752082825</t>
+    <t xml:space="preserve">2.90459775924683</t>
   </si>
   <si>
     <t xml:space="preserve">2.90889406204224</t>
@@ -2651,7 +2651,7 @@
     <t xml:space="preserve">2.6983540058136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65968322753906</t>
+    <t xml:space="preserve">2.65968346595764</t>
   </si>
   <si>
     <t xml:space="preserve">2.74991488456726</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">2.59952878952026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5479679107666</t>
+    <t xml:space="preserve">2.54796767234802</t>
   </si>
   <si>
     <t xml:space="preserve">2.53507781028748</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.44914269447327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43195605278015</t>
+    <t xml:space="preserve">2.43195581436157</t>
   </si>
   <si>
     <t xml:space="preserve">2.48781371116638</t>
@@ -2705,22 +2705,22 @@
     <t xml:space="preserve">2.41906571388245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35891103744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34172415733337</t>
+    <t xml:space="preserve">2.35891127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34172439575195</t>
   </si>
   <si>
     <t xml:space="preserve">2.31164717674255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30735015869141</t>
+    <t xml:space="preserve">2.30735039710999</t>
   </si>
   <si>
     <t xml:space="preserve">2.27727317810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34602117538452</t>
+    <t xml:space="preserve">2.34602093696594</t>
   </si>
   <si>
     <t xml:space="preserve">2.26867985725403</t>
@@ -2732,31 +2732,31 @@
     <t xml:space="preserve">2.36320805549622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35031795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38469171524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43625259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37180161476135</t>
+    <t xml:space="preserve">2.3975818157196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35031771659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38469195365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43625283241272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37180137634277</t>
   </si>
   <si>
     <t xml:space="preserve">2.40187883377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3546142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38898825645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32883381843567</t>
+    <t xml:space="preserve">2.35461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38898849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32883405685425</t>
   </si>
   <si>
     <t xml:space="preserve">2.33742761611938</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">2.21711874008179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10540366172791</t>
+    <t xml:space="preserve">2.10540342330933</t>
   </si>
   <si>
     <t xml:space="preserve">2.13118410110474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0624361038208</t>
+    <t xml:space="preserve">2.06243634223938</t>
   </si>
   <si>
     <t xml:space="preserve">2.11829376220703</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">2.10110664367676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1225905418396</t>
+    <t xml:space="preserve">2.12259030342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.13977742195129</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">2.152667760849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16985464096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14407396316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11399698257446</t>
+    <t xml:space="preserve">2.16985487937927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14407420158386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11399722099304</t>
   </si>
   <si>
     <t xml:space="preserve">2.08391976356506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02376556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88197302818298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94212746620178</t>
+    <t xml:space="preserve">2.02376532554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88197290897369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94212734699249</t>
   </si>
   <si>
     <t xml:space="preserve">1.89056646823883</t>
@@ -2822,25 +2822,25 @@
     <t xml:space="preserve">1.81322491168976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83041214942932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78744459152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71869683265686</t>
+    <t xml:space="preserve">1.83041203022003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78744447231293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71869671344757</t>
   </si>
   <si>
     <t xml:space="preserve">1.70150971412659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67744791507721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64307391643524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62416851520538</t>
+    <t xml:space="preserve">1.6774480342865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64307403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62416839599609</t>
   </si>
   <si>
     <t xml:space="preserve">1.65854227542877</t>
@@ -2852,28 +2852,28 @@
     <t xml:space="preserve">1.79174137115479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92494022846222</t>
+    <t xml:space="preserve">1.9249404668808</t>
   </si>
   <si>
     <t xml:space="preserve">1.84330224990845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96790778636932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93353378772736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97650122642517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01087498664856</t>
+    <t xml:space="preserve">1.96790766716003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93353366851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97650110721588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01087522506714</t>
   </si>
   <si>
     <t xml:space="preserve">2.05813932418823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04954600334167</t>
+    <t xml:space="preserve">2.0495457649231</t>
   </si>
   <si>
     <t xml:space="preserve">1.95931422710419</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">2.08821654319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04524922370911</t>
+    <t xml:space="preserve">2.04524946212769</t>
   </si>
   <si>
     <t xml:space="preserve">2.07102966308594</t>
@@ -2909,34 +2909,34 @@
     <t xml:space="preserve">2.18704175949097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21282196044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19563508033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19993185997009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17415142059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14837098121643</t>
+    <t xml:space="preserve">2.2128221988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1956353187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19993162155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17415118217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">2.07532620429993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06673264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09681010246277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10969996452332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19133806228638</t>
+    <t xml:space="preserve">2.06673288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09681034088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10970020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19133830070496</t>
   </si>
   <si>
     <t xml:space="preserve">2.15696430206299</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">2.28586673736572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32024073600769</t>
+    <t xml:space="preserve">2.32024049758911</t>
   </si>
   <si>
     <t xml:space="preserve">2.29875683784485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23860239982605</t>
+    <t xml:space="preserve">2.23860263824463</t>
   </si>
   <si>
     <t xml:space="preserve">2.20422863960266</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">2.30305361747742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32453751564026</t>
+    <t xml:space="preserve">2.32453727722168</t>
   </si>
   <si>
     <t xml:space="preserve">2.26438307762146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40617561340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37609839439392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33313059806824</t>
+    <t xml:space="preserve">2.40617537498474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37609815597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33313083648682</t>
   </si>
   <si>
     <t xml:space="preserve">2.26008629798889</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">2.29016351699829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36750483512878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42765927314758</t>
+    <t xml:space="preserve">2.36750507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.427659034729</t>
   </si>
   <si>
     <t xml:space="preserve">2.25149250030518</t>
@@ -2999,19 +2999,19 @@
     <t xml:space="preserve">2.22141551971436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27297616004944</t>
+    <t xml:space="preserve">2.27297639846802</t>
   </si>
   <si>
     <t xml:space="preserve">2.24289917945862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39328527450562</t>
+    <t xml:space="preserve">2.39328503608704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41047215461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47062635421753</t>
+    <t xml:space="preserve">2.47062659263611</t>
   </si>
   <si>
     <t xml:space="preserve">2.50070381164551</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">2.36577391624451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42874121665955</t>
+    <t xml:space="preserve">2.42874097824097</t>
   </si>
   <si>
     <t xml:space="preserve">2.43773651123047</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">2.45572710037231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.356778383255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30280637741089</t>
+    <t xml:space="preserve">2.35677814483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30280613899231</t>
   </si>
   <si>
     <t xml:space="preserve">2.33429002761841</t>
@@ -3059,10 +3059,10 @@
     <t xml:space="preserve">2.17687177658081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23084354400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17237401008606</t>
+    <t xml:space="preserve">2.23084378242493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17237377166748</t>
   </si>
   <si>
     <t xml:space="preserve">2.20385766029358</t>
@@ -3083,16 +3083,16 @@
     <t xml:space="preserve">2.19935989379883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16787624359131</t>
+    <t xml:space="preserve">2.19486260414124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16787648200989</t>
   </si>
   <si>
     <t xml:space="preserve">2.19036459922791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16337847709656</t>
+    <t xml:space="preserve">2.16337871551514</t>
   </si>
   <si>
     <t xml:space="preserve">2.14538788795471</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">2.13639259338379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13189506530762</t>
+    <t xml:space="preserve">2.13189482688904</t>
   </si>
   <si>
     <t xml:space="preserve">2.12739729881287</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">2.06442999839783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06892776489258</t>
+    <t xml:space="preserve">2.068927526474</t>
   </si>
   <si>
     <t xml:space="preserve">2.03744411468506</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">2.09141612052917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08691811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09591364860535</t>
+    <t xml:space="preserve">2.08691835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09591341018677</t>
   </si>
   <si>
     <t xml:space="preserve">2.05993223190308</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">2.0554347038269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01495552062988</t>
+    <t xml:space="preserve">2.01495575904846</t>
   </si>
   <si>
     <t xml:space="preserve">1.97447657585144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.933997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90701138973236</t>
+    <t xml:space="preserve">1.93399751186371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90701150894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.92949986457825</t>
@@ -3173,28 +3173,28 @@
     <t xml:space="preserve">1.90251386165619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91600704193115</t>
+    <t xml:space="preserve">1.91600692272186</t>
   </si>
   <si>
     <t xml:space="preserve">1.94299304485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93849515914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9115092754364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92500221729279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94749057292938</t>
+    <t xml:space="preserve">1.93849527835846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91150915622711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92500233650208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94749045372009</t>
   </si>
   <si>
     <t xml:space="preserve">1.96548116207123</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95648574829102</t>
+    <t xml:space="preserve">1.95648598670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.00146245956421</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">1.95198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92050445079803</t>
+    <t xml:space="preserve">1.92050457000732</t>
   </si>
   <si>
     <t xml:space="preserve">1.89801609516144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8890209197998</t>
+    <t xml:space="preserve">1.88902080059052</t>
   </si>
   <si>
     <t xml:space="preserve">1.88002550601959</t>
@@ -3221,10 +3221,10 @@
     <t xml:space="preserve">1.81705820560455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78287589550018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76848340034485</t>
+    <t xml:space="preserve">1.78287577629089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76848328113556</t>
   </si>
   <si>
     <t xml:space="preserve">1.78467488288879</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">1.79546940326691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77388060092926</t>
+    <t xml:space="preserve">1.77388048171997</t>
   </si>
   <si>
     <t xml:space="preserve">1.80806279182434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83055126667023</t>
+    <t xml:space="preserve">1.83055114746094</t>
   </si>
   <si>
     <t xml:space="preserve">1.81256055831909</t>
@@ -3260,7 +3260,7 @@
     <t xml:space="preserve">1.77567958831787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85303938388824</t>
+    <t xml:space="preserve">1.85303950309753</t>
   </si>
   <si>
     <t xml:space="preserve">1.84404408931732</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">1.99696493148804</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98347175121307</t>
+    <t xml:space="preserve">1.98347187042236</t>
   </si>
   <si>
     <t xml:space="preserve">1.98796951770782</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99246716499329</t>
+    <t xml:space="preserve">1.99246728420258</t>
   </si>
   <si>
     <t xml:space="preserve">2.01045799255371</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">2.00596022605896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02844882011414</t>
+    <t xml:space="preserve">2.02844858169556</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897434234619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04194140434265</t>
+    <t xml:space="preserve">2.04194164276123</t>
   </si>
   <si>
     <t xml:space="preserve">2.12289953231812</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">2.11390423774719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10490870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14089035987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.221848487854</t>
+    <t xml:space="preserve">2.10490894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14089059829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22184824943542</t>
   </si>
   <si>
     <t xml:space="preserve">2.21285319328308</t>
@@ -69815,7 +69815,7 @@
     </row>
     <row r="2524">
       <c r="A2524" s="1" t="n">
-        <v>45993.691099537</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2524" t="n">
         <v>35198</v>
@@ -69836,6 +69836,32 @@
         <v>1288</v>
       </c>
       <c r="H2524" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="1" t="n">
+        <v>45994.6911111111</v>
+      </c>
+      <c r="B2525" t="n">
+        <v>85435</v>
+      </c>
+      <c r="C2525" t="n">
+        <v>3.31500005722046</v>
+      </c>
+      <c r="D2525" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E2525" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2525" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H2525" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ASC.MI.xlsx
+++ b/data/ASC.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27862000465393</t>
+    <t xml:space="preserve">1.27861988544464</t>
   </si>
   <si>
     <t xml:space="preserve">ASC.MI</t>
@@ -50,52 +50,52 @@
     <t xml:space="preserve">1.2682341337204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26938819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25554049015045</t>
+    <t xml:space="preserve">1.26938796043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25554025173187</t>
   </si>
   <si>
     <t xml:space="preserve">1.24861633777618</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27515828609467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24977040290833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2324606180191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19437885284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.19784080982208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.15975916385651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.18283891677856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25784802436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25438630580902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24746239185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27285003662109</t>
+    <t xml:space="preserve">1.27515804767609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24977016448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23246049880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19437873363495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.19784069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.15975904464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.18283879756927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25784814357758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25438618659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24746227264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27285027503967</t>
   </si>
   <si>
     <t xml:space="preserve">1.27746593952179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26361799240112</t>
+    <t xml:space="preserve">1.2636182308197</t>
   </si>
   <si>
     <t xml:space="preserve">1.20591855049133</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">1.19207084178925</t>
   </si>
   <si>
-    <t xml:space="preserve">1.2082267999649</t>
+    <t xml:space="preserve">1.20822668075562</t>
   </si>
   <si>
     <t xml:space="preserve">1.23130643367767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.22899854183197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23476839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.23707628250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2901599407196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28669786453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28900587558746</t>
+    <t xml:space="preserve">1.22899842262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23476850986481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23707640171051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29015982151031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28669798374176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28900611400604</t>
   </si>
   <si>
     <t xml:space="preserve">1.28208196163177</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">1.28438997268677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.27169585227966</t>
+    <t xml:space="preserve">1.27169609069824</t>
   </si>
   <si>
     <t xml:space="preserve">1.28323602676392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30054581165314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30862367153168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31093180179596</t>
+    <t xml:space="preserve">1.30054593086243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30862355232239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31093168258667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32477951049805</t>
@@ -161,52 +161,52 @@
     <t xml:space="preserve">1.32247149944305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31208562850952</t>
+    <t xml:space="preserve">1.31208574771881</t>
   </si>
   <si>
     <t xml:space="preserve">1.30746984481812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32593369483948</t>
+    <t xml:space="preserve">1.32593357563019</t>
   </si>
   <si>
     <t xml:space="preserve">1.30516171455383</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32016360759735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32362544536591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32708764076233</t>
+    <t xml:space="preserve">1.32016372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3236255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32708752155304</t>
   </si>
   <si>
     <t xml:space="preserve">1.31323957443237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32824146747589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35132122039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34439742565155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34670531749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3501672744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478341579437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36170721054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34208929538727</t>
+    <t xml:space="preserve">1.32824170589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35132145881653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34439730644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34670519828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35016739368439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478329658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36170732975006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34208941459656</t>
   </si>
   <si>
     <t xml:space="preserve">1.34324359893799</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">1.34555149078369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36516916751862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37324714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38017106056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37786304950714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36747705936432</t>
+    <t xml:space="preserve">1.36516904830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37324738502502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38017094135284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37786316871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3674772977829</t>
   </si>
   <si>
     <t xml:space="preserve">1.36286115646362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39497971534729</t>
+    <t xml:space="preserve">1.39497983455658</t>
   </si>
   <si>
     <t xml:space="preserve">1.39251506328583</t>
@@ -242,67 +242,67 @@
     <t xml:space="preserve">1.39621210098267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41099989414215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42702007293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42332291603088</t>
+    <t xml:space="preserve">1.41099977493286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42701995372772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42332303524017</t>
   </si>
   <si>
     <t xml:space="preserve">1.43687844276428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44427251815796</t>
+    <t xml:space="preserve">1.44427239894867</t>
   </si>
   <si>
     <t xml:space="preserve">1.44550454616547</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45043408870697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45536315441132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4627571105957</t>
+    <t xml:space="preserve">1.45043385028839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45536303520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46275722980499</t>
   </si>
   <si>
     <t xml:space="preserve">1.4911003112793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48863554000854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50342333316803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51821112632751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54162549972534</t>
+    <t xml:space="preserve">1.48863542079926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50342357158661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51821136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54162526130676</t>
   </si>
   <si>
     <t xml:space="preserve">1.50465571880341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51574683189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49849390983582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5403927564621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60817015171051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61433160305023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59707939624786</t>
+    <t xml:space="preserve">1.51574659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49849426746368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54039287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60816991329193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61433172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59707927703857</t>
   </si>
   <si>
     <t xml:space="preserve">1.52437269687653</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">1.50958502292633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55641293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60077631473541</t>
+    <t xml:space="preserve">1.55641305446625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60077619552612</t>
   </si>
   <si>
     <t xml:space="preserve">1.5465544462204</t>
@@ -323,181 +323,181 @@
     <t xml:space="preserve">1.52190828323364</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56257450580597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59584677219391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66362452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6500688791275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5946147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64883649349213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65992748737335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66115975379944</t>
+    <t xml:space="preserve">1.56257438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59584701061249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66362428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65006899833679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59461486339569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64883637428284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65992724895477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66115963459015</t>
   </si>
   <si>
     <t xml:space="preserve">1.71661376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72154307365417</t>
+    <t xml:space="preserve">1.72154295444489</t>
   </si>
   <si>
     <t xml:space="preserve">1.72400772571564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68950307369232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68827056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72523975372314</t>
+    <t xml:space="preserve">1.6895033121109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68827068805695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72523963451385</t>
   </si>
   <si>
     <t xml:space="preserve">1.73756301403046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70429062843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70059359073639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7067551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71784603595734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75851273536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79301702976227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75604784488678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78439104557037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77206802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74988615512848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74865388870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74618947505951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76837086677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7745326757431</t>
+    <t xml:space="preserve">1.70429050922394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70059370994568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70675528049469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71784579753876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79301726818085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7560476064682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77206766605377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74988603591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74865424633026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74618935585022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7683709859848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77453219890594</t>
   </si>
   <si>
     <t xml:space="preserve">1.76220917701721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77699732780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76344180107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6574627161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66855323314667</t>
+    <t xml:space="preserve">1.77699720859528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76344156265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65746283531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66855335235596</t>
   </si>
   <si>
     <t xml:space="preserve">1.74249243736267</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69443202018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61186707019806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63158416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60447299480438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63035178184509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61679625511169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64267480373383</t>
+    <t xml:space="preserve">1.69443213939667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61186695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63158404827118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60447335243225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6303516626358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61679649353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64267456531525</t>
   </si>
   <si>
     <t xml:space="preserve">1.65376591682434</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62049329280853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63281619548798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61309945583344</t>
+    <t xml:space="preserve">1.62049341201782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63281667232513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61309957504272</t>
   </si>
   <si>
     <t xml:space="preserve">1.6155641078949</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61802864074707</t>
+    <t xml:space="preserve">1.61802852153778</t>
   </si>
   <si>
     <t xml:space="preserve">1.64021039009094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64760410785675</t>
+    <t xml:space="preserve">1.64760422706604</t>
   </si>
   <si>
     <t xml:space="preserve">1.65130126476288</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6562305688858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61926090717316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64513981342316</t>
+    <t xml:space="preserve">1.65623033046722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61926102638245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64513957500458</t>
   </si>
   <si>
     <t xml:space="preserve">1.64144265651703</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63404870033264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59091782569885</t>
+    <t xml:space="preserve">1.63404893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59091758728027</t>
   </si>
   <si>
     <t xml:space="preserve">1.53546369075775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49356472492218</t>
+    <t xml:space="preserve">1.49356496334076</t>
   </si>
   <si>
     <t xml:space="preserve">1.49479734897614</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">1.49972653388977</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48247385025024</t>
+    <t xml:space="preserve">1.48247396945953</t>
   </si>
   <si>
     <t xml:space="preserve">1.55887758731842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5884530544281</t>
+    <t xml:space="preserve">1.58845317363739</t>
   </si>
   <si>
     <t xml:space="preserve">1.56503903865814</t>
@@ -524,46 +524,46 @@
     <t xml:space="preserve">1.49726188182831</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51451408863068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54532206058502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57120072841644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58598840236664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58105933666229</t>
+    <t xml:space="preserve">1.51451420783997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54532194137573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57120060920715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58598852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.581059217453</t>
   </si>
   <si>
     <t xml:space="preserve">1.60200846195221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59338223934174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5872209072113</t>
+    <t xml:space="preserve">1.59338212013245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58722054958344</t>
   </si>
   <si>
     <t xml:space="preserve">1.6365133523941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66485643386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65499818325043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67594730854034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67225086688995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67841219902039</t>
+    <t xml:space="preserve">1.66485667228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65499806404114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67594754695892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67225062847137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6784120798111</t>
   </si>
   <si>
     <t xml:space="preserve">1.69073522090912</t>
@@ -572,94 +572,94 @@
     <t xml:space="preserve">1.66978585720062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67717981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68703830242157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70552265644073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71538138389587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71291661262512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68457353115082</t>
+    <t xml:space="preserve">1.67717969417572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68703806400299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70552289485931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71538126468658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7129168510437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68457341194153</t>
   </si>
   <si>
     <t xml:space="preserve">1.76467430591583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75727999210358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74125981330872</t>
+    <t xml:space="preserve">1.75728011131287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74126017093658</t>
   </si>
   <si>
     <t xml:space="preserve">1.73016941547394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77330017089844</t>
+    <t xml:space="preserve">1.77330005168915</t>
   </si>
   <si>
     <t xml:space="preserve">1.77946186065674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74742150306702</t>
+    <t xml:space="preserve">1.74742197990417</t>
   </si>
   <si>
     <t xml:space="preserve">1.78069412708282</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79178512096405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76590633392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81766331195831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81150221824646</t>
+    <t xml:space="preserve">1.79178476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76590657234192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81766366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81150186061859</t>
   </si>
   <si>
     <t xml:space="preserve">1.83614838123322</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86695623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88297641277313</t>
+    <t xml:space="preserve">1.86695611476898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88297629356384</t>
   </si>
   <si>
     <t xml:space="preserve">1.89899635314941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90762221813202</t>
+    <t xml:space="preserve">1.9076224565506</t>
   </si>
   <si>
     <t xml:space="preserve">1.90392553806305</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94459187984467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9298038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98279345035553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00867247581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02838945388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04687428474426</t>
+    <t xml:space="preserve">1.94459164142609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92980408668518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9827938079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00867223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02838897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0468738079071</t>
   </si>
   <si>
     <t xml:space="preserve">2.01483392715454</t>
@@ -671,52 +671,52 @@
     <t xml:space="preserve">2.05796456336975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05303549766541</t>
+    <t xml:space="preserve">2.05303573608398</t>
   </si>
   <si>
     <t xml:space="preserve">2.06905555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.107257604599</t>
+    <t xml:space="preserve">2.10725712776184</t>
   </si>
   <si>
     <t xml:space="preserve">2.09493446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09986352920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13806509971619</t>
+    <t xml:space="preserve">2.0998637676239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13806533813477</t>
   </si>
   <si>
     <t xml:space="preserve">2.14669132232666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16024684906006</t>
+    <t xml:space="preserve">2.16024708747864</t>
   </si>
   <si>
     <t xml:space="preserve">2.16887307167053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1725697517395</t>
+    <t xml:space="preserve">2.17257022857666</t>
   </si>
   <si>
     <t xml:space="preserve">2.15655016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18119645118713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17380261421204</t>
+    <t xml:space="preserve">2.18119621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17380237579346</t>
   </si>
   <si>
     <t xml:space="preserve">2.17010569572449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15531730651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16640830039978</t>
+    <t xml:space="preserve">2.15531778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16640877723694</t>
   </si>
   <si>
     <t xml:space="preserve">2.21446895599365</t>
@@ -725,28 +725,28 @@
     <t xml:space="preserve">2.18366074562073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17996382713318</t>
+    <t xml:space="preserve">2.1799635887146</t>
   </si>
   <si>
     <t xml:space="preserve">2.21816563606262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20953917503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21323657035828</t>
+    <t xml:space="preserve">2.20953965187073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21323680877686</t>
   </si>
   <si>
     <t xml:space="preserve">2.23172116279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27978134155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28717541694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33030652999878</t>
+    <t xml:space="preserve">2.27978181838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28717517852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3303062915802</t>
   </si>
   <si>
     <t xml:space="preserve">2.35877180099487</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">2.34583306312561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33289432525635</t>
+    <t xml:space="preserve">2.33289408683777</t>
   </si>
   <si>
     <t xml:space="preserve">2.31477975845337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25526070594788</t>
+    <t xml:space="preserve">2.2552604675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.25137853622437</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">2.30313467979431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31866145133972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3367760181427</t>
+    <t xml:space="preserve">2.31866121292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33677577972412</t>
   </si>
   <si>
     <t xml:space="preserve">2.35100865364075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36782956123352</t>
+    <t xml:space="preserve">2.36782932281494</t>
   </si>
   <si>
     <t xml:space="preserve">2.35489058494568</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">2.36135983467102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36653566360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34065723419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32901215553284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34842085838318</t>
+    <t xml:space="preserve">2.36653542518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34065747261047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32901239395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34842109680176</t>
   </si>
   <si>
     <t xml:space="preserve">2.34971475601196</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.34324526786804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40535235404968</t>
+    <t xml:space="preserve">2.4053521156311</t>
   </si>
   <si>
     <t xml:space="preserve">2.32642483711243</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.31219148635864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29537129402161</t>
+    <t xml:space="preserve">2.29537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">2.29666519165039</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">2.25396656990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24490904808044</t>
+    <t xml:space="preserve">2.24490928649902</t>
   </si>
   <si>
     <t xml:space="preserve">2.26949310302734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26043605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25784802436829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26172995567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26690554618835</t>
+    <t xml:space="preserve">2.26043581962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25784850120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2617301940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26690530776978</t>
   </si>
   <si>
     <t xml:space="preserve">2.24361538887024</t>
@@ -869,40 +869,40 @@
     <t xml:space="preserve">2.19703507423401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21903157234192</t>
+    <t xml:space="preserve">2.21903133392334</t>
   </si>
   <si>
     <t xml:space="preserve">2.23197054862976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24102711677551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32254266738892</t>
+    <t xml:space="preserve">2.24102759361267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3225429058075</t>
   </si>
   <si>
     <t xml:space="preserve">2.31736755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31348609924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29407715797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27725672721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27855086326599</t>
+    <t xml:space="preserve">2.32771849632263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31348586082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29407739639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27725648880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27855062484741</t>
   </si>
   <si>
     <t xml:space="preserve">2.26431775093079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28890204429626</t>
+    <t xml:space="preserve">2.28890156745911</t>
   </si>
   <si>
     <t xml:space="preserve">2.24879097938538</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">2.29278326034546</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37041687965393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33548188209534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35747790336609</t>
+    <t xml:space="preserve">2.37041711807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33548212051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35747838020325</t>
   </si>
   <si>
     <t xml:space="preserve">2.28502011299133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27337503433228</t>
+    <t xml:space="preserve">2.28631377220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2733747959137</t>
   </si>
   <si>
     <t xml:space="preserve">2.26819944381714</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">2.33160042762756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30960392951965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33418798446655</t>
+    <t xml:space="preserve">2.30960416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33418822288513</t>
   </si>
   <si>
     <t xml:space="preserve">2.3057222366333</t>
@@ -953,28 +953,28 @@
     <t xml:space="preserve">2.40664625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41699743270874</t>
+    <t xml:space="preserve">2.41699767112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.46745920181274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4467568397522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44546341896057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47651648521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38723754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39241337776184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34195160865784</t>
+    <t xml:space="preserve">2.44675707817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44546294212341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47651672363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3872377872467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39241313934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34195137023926</t>
   </si>
   <si>
     <t xml:space="preserve">2.36524152755737</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.40794014930725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39370727539062</t>
+    <t xml:space="preserve">2.3937075138092</t>
   </si>
   <si>
     <t xml:space="preserve">2.37688660621643</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">2.3626537322998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38465046882629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.316073179245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36459445953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38076829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37429904937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37753367424011</t>
+    <t xml:space="preserve">2.38464999198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31607365608215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36459469795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3807680606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37429928779602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37753343582153</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930828094482</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">2.07346820831299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03788590431213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0896418094635</t>
+    <t xml:space="preserve">2.03788614273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08964157104492</t>
   </si>
   <si>
     <t xml:space="preserve">2.07993745803833</t>
@@ -1040,19 +1040,19 @@
     <t xml:space="preserve">2.12198901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06699872016907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0508246421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02818179130554</t>
+    <t xml:space="preserve">2.06699848175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05082511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02818131446838</t>
   </si>
   <si>
     <t xml:space="preserve">2.01847743988037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97966027259827</t>
+    <t xml:space="preserve">1.97966051101685</t>
   </si>
   <si>
     <